--- a/dados/precos_todos.xlsx
+++ b/dados/precos_todos.xlsx
@@ -14406,7 +14406,7 @@
         <v>1.01</v>
       </c>
       <c r="D524" s="7" t="n">
-        <v>0.909</v>
+        <v>0.82</v>
       </c>
       <c r="F524" s="1" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>1.98</v>
       </c>
       <c r="D525" s="7" t="n">
-        <v>1.782</v>
+        <v>1.61</v>
       </c>
       <c r="F525" s="1" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>1.23</v>
       </c>
       <c r="D526" s="7" t="n">
-        <v>1.107</v>
+        <v>1</v>
       </c>
       <c r="F526" s="1" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>2.4</v>
       </c>
       <c r="D527" s="7" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="F527" s="1" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>1.25</v>
       </c>
       <c r="D528" s="7" t="n">
-        <v>1.125</v>
+        <v>1.01</v>
       </c>
       <c r="F528" s="1" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>2.48</v>
       </c>
       <c r="D529" s="7" t="n">
-        <v>2.232</v>
+        <v>2.02</v>
       </c>
       <c r="F529" s="1" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>6.4</v>
       </c>
       <c r="D530" s="7" t="n">
-        <v>5.760000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="F530" s="1" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>6.4</v>
       </c>
       <c r="D531" s="7" t="n">
-        <v>5.760000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="F531" s="1" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>12.64</v>
       </c>
       <c r="D532" s="7" t="n">
-        <v>11.376</v>
+        <v>10.27</v>
       </c>
       <c r="F532" s="1" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>16.8</v>
       </c>
       <c r="D533" s="7" t="n">
-        <v>15.12</v>
+        <v>13.65</v>
       </c>
       <c r="F533" s="1" t="inlineStr">
         <is>

--- a/dados/precos_todos.xlsx
+++ b/dados/precos_todos.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a9e64bef5804d793/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_206AD2F0114A429FE8312C154A75067A3351903A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C40BC8F-90FB-4648-B26F-AB1B9423CE42}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDF59E69-D44A-4E1B-8B80-300AB6E495CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13730" yWindow="0" windowWidth="15160" windowHeight="17370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$G$748</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$B$1:$B$748</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -2346,7 +2346,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2354,36 +2354,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2400,10 +2383,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2710,31 +2689,31 @@
     <col min="2" max="2" width="46.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" style="1" customWidth="1"/>
-    <col min="7" max="8" width="11.36328125" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" style="1" customWidth="1"/>
+    <col min="7" max="8" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2757,7 +2736,7 @@
       <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2780,7 +2759,7 @@
       <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2803,7 +2782,7 @@
       <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2826,7 +2805,7 @@
       <c r="F5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2849,7 +2828,7 @@
       <c r="F6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2872,7 +2851,7 @@
       <c r="F7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2895,7 +2874,7 @@
       <c r="F8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2918,7 +2897,7 @@
       <c r="F9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2941,7 +2920,7 @@
       <c r="F10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2964,7 +2943,7 @@
       <c r="F11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2987,7 +2966,7 @@
       <c r="F12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3010,7 +2989,7 @@
       <c r="F13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3033,7 +3012,7 @@
       <c r="F14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3056,7 +3035,7 @@
       <c r="F15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3079,7 +3058,7 @@
       <c r="F16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3102,7 +3081,7 @@
       <c r="F17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3125,7 +3104,7 @@
       <c r="F18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3148,7 +3127,7 @@
       <c r="F19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3171,7 +3150,7 @@
       <c r="F20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3194,7 +3173,7 @@
       <c r="F21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3217,7 +3196,7 @@
       <c r="F22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3240,7 +3219,7 @@
       <c r="F23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3263,7 +3242,7 @@
       <c r="F24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3286,7 +3265,7 @@
       <c r="F25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3309,7 +3288,7 @@
       <c r="F26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3332,7 +3311,7 @@
       <c r="F27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3355,7 +3334,7 @@
       <c r="F28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3378,7 +3357,7 @@
       <c r="F29" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3401,7 +3380,7 @@
       <c r="F30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3424,7 +3403,7 @@
       <c r="F31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3447,7 +3426,7 @@
       <c r="F32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3470,7 +3449,7 @@
       <c r="F33" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3493,7 +3472,7 @@
       <c r="F34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3516,7 +3495,7 @@
       <c r="F35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G35" s="6">
+      <c r="G35" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3539,7 +3518,7 @@
       <c r="F36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G36" s="6">
+      <c r="G36" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3562,7 +3541,7 @@
       <c r="F37" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G37" s="6">
+      <c r="G37" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3585,7 +3564,7 @@
       <c r="F38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G38" s="6">
+      <c r="G38" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3608,7 +3587,7 @@
       <c r="F39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G39" s="6">
+      <c r="G39" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3631,7 +3610,7 @@
       <c r="F40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G40" s="6">
+      <c r="G40" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3654,7 +3633,7 @@
       <c r="F41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G41" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3677,7 +3656,7 @@
       <c r="F42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G42" s="6">
+      <c r="G42" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3700,7 +3679,7 @@
       <c r="F43" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G43" s="6">
+      <c r="G43" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3723,7 +3702,7 @@
       <c r="F44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G44" s="6">
+      <c r="G44" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3746,7 +3725,7 @@
       <c r="F45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G45" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3769,7 +3748,7 @@
       <c r="F46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G46" s="6">
+      <c r="G46" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3792,7 +3771,7 @@
       <c r="F47" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G47" s="6">
+      <c r="G47" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3815,7 +3794,7 @@
       <c r="F48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G48" s="6">
+      <c r="G48" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3838,7 +3817,7 @@
       <c r="F49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G49" s="6">
+      <c r="G49" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3861,7 +3840,7 @@
       <c r="F50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G50" s="6">
+      <c r="G50" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3884,7 +3863,7 @@
       <c r="F51" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G51" s="6">
+      <c r="G51" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3907,7 +3886,7 @@
       <c r="F52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G52" s="6">
+      <c r="G52" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3930,7 +3909,7 @@
       <c r="F53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G53" s="6">
+      <c r="G53" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3953,7 +3932,7 @@
       <c r="F54" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G54" s="6">
+      <c r="G54" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3976,7 +3955,7 @@
       <c r="F55" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G55" s="6">
+      <c r="G55" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3999,7 +3978,7 @@
       <c r="F56" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G56" s="6">
+      <c r="G56" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4022,7 +4001,7 @@
       <c r="F57" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G57" s="6">
+      <c r="G57" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4045,7 +4024,7 @@
       <c r="F58" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G58" s="6">
+      <c r="G58" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4068,7 +4047,7 @@
       <c r="F59" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G59" s="6">
+      <c r="G59" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4091,7 +4070,7 @@
       <c r="F60" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G60" s="6">
+      <c r="G60" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4114,7 +4093,7 @@
       <c r="F61" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G61" s="6">
+      <c r="G61" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4137,7 +4116,7 @@
       <c r="F62" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G62" s="6">
+      <c r="G62" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4160,7 +4139,7 @@
       <c r="F63" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G63" s="6">
+      <c r="G63" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4183,7 +4162,7 @@
       <c r="F64" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G64" s="6">
+      <c r="G64" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4206,7 +4185,7 @@
       <c r="F65" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G65" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4229,7 +4208,7 @@
       <c r="F66" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G66" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4252,7 +4231,7 @@
       <c r="F67" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G67" s="6">
+      <c r="G67" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4275,7 +4254,7 @@
       <c r="F68" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G68" s="6">
+      <c r="G68" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4298,7 +4277,7 @@
       <c r="F69" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G69" s="6">
+      <c r="G69" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4321,7 +4300,7 @@
       <c r="F70" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G70" s="6">
+      <c r="G70" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4344,7 +4323,7 @@
       <c r="F71" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G71" s="6">
+      <c r="G71" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4367,7 +4346,7 @@
       <c r="F72" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G72" s="6">
+      <c r="G72" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4390,7 +4369,7 @@
       <c r="F73" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G73" s="6">
+      <c r="G73" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4413,7 +4392,7 @@
       <c r="F74" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G74" s="6">
+      <c r="G74" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4436,7 +4415,7 @@
       <c r="F75" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G75" s="6">
+      <c r="G75" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4459,7 +4438,7 @@
       <c r="F76" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G76" s="6">
+      <c r="G76" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4482,7 +4461,7 @@
       <c r="F77" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G77" s="6">
+      <c r="G77" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4505,7 +4484,7 @@
       <c r="F78" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G78" s="6">
+      <c r="G78" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4528,7 +4507,7 @@
       <c r="F79" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G79" s="6">
+      <c r="G79" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4551,7 +4530,7 @@
       <c r="F80" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G80" s="6">
+      <c r="G80" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4574,7 +4553,7 @@
       <c r="F81" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G81" s="6">
+      <c r="G81" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4597,7 +4576,7 @@
       <c r="F82" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G82" s="6">
+      <c r="G82" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4620,7 +4599,7 @@
       <c r="F83" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G83" s="6">
+      <c r="G83" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4643,7 +4622,7 @@
       <c r="F84" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G84" s="6">
+      <c r="G84" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4666,7 +4645,7 @@
       <c r="F85" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G85" s="6">
+      <c r="G85" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4689,7 +4668,7 @@
       <c r="F86" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G86" s="6">
+      <c r="G86" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4712,7 +4691,7 @@
       <c r="F87" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G87" s="6">
+      <c r="G87" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4735,7 +4714,7 @@
       <c r="F88" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G88" s="6">
+      <c r="G88" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4758,7 +4737,7 @@
       <c r="F89" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G89" s="6">
+      <c r="G89" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4781,7 +4760,7 @@
       <c r="F90" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G90" s="6">
+      <c r="G90" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4804,7 +4783,7 @@
       <c r="F91" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G91" s="6">
+      <c r="G91" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4827,7 +4806,7 @@
       <c r="F92" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G92" s="6">
+      <c r="G92" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4850,7 +4829,7 @@
       <c r="F93" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G93" s="6">
+      <c r="G93" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4873,7 +4852,7 @@
       <c r="F94" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G94" s="6">
+      <c r="G94" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4896,7 +4875,7 @@
       <c r="F95" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G95" s="6">
+      <c r="G95" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4919,7 +4898,7 @@
       <c r="F96" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G96" s="6">
+      <c r="G96" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4942,7 +4921,7 @@
       <c r="F97" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G97" s="6">
+      <c r="G97" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4965,7 +4944,7 @@
       <c r="F98" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G98" s="6">
+      <c r="G98" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4988,7 +4967,7 @@
       <c r="F99" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G99" s="6">
+      <c r="G99" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5011,7 +4990,7 @@
       <c r="F100" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G100" s="6">
+      <c r="G100" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5034,7 +5013,7 @@
       <c r="F101" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G101" s="6">
+      <c r="G101" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5057,7 +5036,7 @@
       <c r="F102" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G102" s="6">
+      <c r="G102" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5080,7 +5059,7 @@
       <c r="F103" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G103" s="6">
+      <c r="G103" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5103,7 +5082,7 @@
       <c r="F104" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G104" s="6">
+      <c r="G104" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5126,7 +5105,7 @@
       <c r="F105" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G105" s="6">
+      <c r="G105" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5149,7 +5128,7 @@
       <c r="F106" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G106" s="6">
+      <c r="G106" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5172,7 +5151,7 @@
       <c r="F107" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G107" s="6">
+      <c r="G107" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5195,7 +5174,7 @@
       <c r="F108" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G108" s="6">
+      <c r="G108" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5218,7 +5197,7 @@
       <c r="F109" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G109" s="6">
+      <c r="G109" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5241,7 +5220,7 @@
       <c r="F110" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G110" s="6">
+      <c r="G110" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5264,7 +5243,7 @@
       <c r="F111" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G111" s="6">
+      <c r="G111" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5287,7 +5266,7 @@
       <c r="F112" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G112" s="6">
+      <c r="G112" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5310,7 +5289,7 @@
       <c r="F113" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G113" s="6">
+      <c r="G113" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5333,7 +5312,7 @@
       <c r="F114" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G114" s="6">
+      <c r="G114" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5356,7 +5335,7 @@
       <c r="F115" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G115" s="6">
+      <c r="G115" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5379,7 +5358,7 @@
       <c r="F116" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G116" s="6">
+      <c r="G116" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5402,7 +5381,7 @@
       <c r="F117" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G117" s="6">
+      <c r="G117" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5425,7 +5404,7 @@
       <c r="F118" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G118" s="6">
+      <c r="G118" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5448,7 +5427,7 @@
       <c r="F119" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G119" s="6">
+      <c r="G119" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5471,7 +5450,7 @@
       <c r="F120" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G120" s="6">
+      <c r="G120" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5494,7 +5473,7 @@
       <c r="F121" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G121" s="6">
+      <c r="G121" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5517,7 +5496,7 @@
       <c r="F122" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G122" s="6">
+      <c r="G122" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5540,7 +5519,7 @@
       <c r="F123" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G123" s="6">
+      <c r="G123" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5563,7 +5542,7 @@
       <c r="F124" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G124" s="6">
+      <c r="G124" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5586,7 +5565,7 @@
       <c r="F125" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G125" s="6">
+      <c r="G125" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5609,7 +5588,7 @@
       <c r="F126" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G126" s="6">
+      <c r="G126" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5632,7 +5611,7 @@
       <c r="F127" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G127" s="6">
+      <c r="G127" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5655,7 +5634,7 @@
       <c r="F128" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G128" s="6">
+      <c r="G128" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5678,7 +5657,7 @@
       <c r="F129" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G129" s="6">
+      <c r="G129" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5701,7 +5680,7 @@
       <c r="F130" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G130" s="6">
+      <c r="G130" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5724,7 +5703,7 @@
       <c r="F131" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G131" s="6">
+      <c r="G131" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5747,7 +5726,7 @@
       <c r="F132" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G132" s="6">
+      <c r="G132" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5770,7 +5749,7 @@
       <c r="F133" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G133" s="6">
+      <c r="G133" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5793,7 +5772,7 @@
       <c r="F134" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G134" s="6">
+      <c r="G134" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5816,7 +5795,7 @@
       <c r="F135" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G135" s="6">
+      <c r="G135" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5839,7 +5818,7 @@
       <c r="F136" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G136" s="6">
+      <c r="G136" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5862,7 +5841,7 @@
       <c r="F137" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G137" s="6">
+      <c r="G137" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5885,7 +5864,7 @@
       <c r="F138" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G138" s="6">
+      <c r="G138" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5908,7 +5887,7 @@
       <c r="F139" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G139" s="6">
+      <c r="G139" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5931,7 +5910,7 @@
       <c r="F140" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G140" s="6">
+      <c r="G140" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5954,7 +5933,7 @@
       <c r="F141" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G141" s="6">
+      <c r="G141" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5977,7 +5956,7 @@
       <c r="F142" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G142" s="6">
+      <c r="G142" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6000,7 +5979,7 @@
       <c r="F143" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G143" s="6">
+      <c r="G143" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6023,7 +6002,7 @@
       <c r="F144" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G144" s="6">
+      <c r="G144" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6046,7 +6025,7 @@
       <c r="F145" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G145" s="6">
+      <c r="G145" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6060,7 +6039,7 @@
       <c r="C146" s="2">
         <v>8.6330737500000012</v>
       </c>
-      <c r="D146">
+      <c r="D146" s="2">
         <v>6.9064590000000017</v>
       </c>
       <c r="E146">
@@ -6069,7 +6048,7 @@
       <c r="F146" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G146" s="6">
+      <c r="G146" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6083,7 +6062,7 @@
       <c r="C147" s="2">
         <v>13.964763749999999</v>
       </c>
-      <c r="D147">
+      <c r="D147" s="2">
         <v>11.171811</v>
       </c>
       <c r="E147">
@@ -6092,7 +6071,7 @@
       <c r="F147" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G147" s="6">
+      <c r="G147" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6115,7 +6094,7 @@
       <c r="F148" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G148" s="6">
+      <c r="G148" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6138,7 +6117,7 @@
       <c r="F149" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G149" s="6">
+      <c r="G149" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6161,7 +6140,7 @@
       <c r="F150" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G150" s="6">
+      <c r="G150" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6184,7 +6163,7 @@
       <c r="F151" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G151" s="6">
+      <c r="G151" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6207,7 +6186,7 @@
       <c r="F152" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G152" s="6">
+      <c r="G152" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6230,7 +6209,7 @@
       <c r="F153" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G153" s="6">
+      <c r="G153" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6253,7 +6232,7 @@
       <c r="F154" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G154" s="6">
+      <c r="G154" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6276,7 +6255,7 @@
       <c r="F155" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G155" s="6">
+      <c r="G155" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6299,7 +6278,7 @@
       <c r="F156" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G156" s="6">
+      <c r="G156" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6322,7 +6301,7 @@
       <c r="F157" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G157" s="6">
+      <c r="G157" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6345,7 +6324,7 @@
       <c r="F158" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G158" s="6">
+      <c r="G158" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6368,7 +6347,7 @@
       <c r="F159" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G159" s="6">
+      <c r="G159" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6391,7 +6370,7 @@
       <c r="F160" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G160" s="6">
+      <c r="G160" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6414,7 +6393,7 @@
       <c r="F161" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G161" s="6">
+      <c r="G161" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -6425,7 +6404,7 @@
       <c r="B162" t="s">
         <v>167</v>
       </c>
-      <c r="C162" s="3">
+      <c r="C162" s="2">
         <v>1.4588935488000001</v>
       </c>
       <c r="D162" s="2">
@@ -6437,7 +6416,7 @@
       <c r="F162" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G162" s="5">
+      <c r="G162" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6448,7 +6427,7 @@
       <c r="B163" t="s">
         <v>169</v>
       </c>
-      <c r="C163" s="3">
+      <c r="C163" s="2">
         <v>1.4888873136</v>
       </c>
       <c r="D163" s="2">
@@ -6460,7 +6439,7 @@
       <c r="F163" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G163" s="5">
+      <c r="G163" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6471,7 +6450,7 @@
       <c r="B164" t="s">
         <v>170</v>
       </c>
-      <c r="C164" s="3">
+      <c r="C164" s="2">
         <v>1.5125666015999999</v>
       </c>
       <c r="D164" s="2">
@@ -6483,7 +6462,7 @@
       <c r="F164" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G164" s="5">
+      <c r="G164" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6494,7 +6473,7 @@
       <c r="B165" t="s">
         <v>171</v>
       </c>
-      <c r="C165" s="3">
+      <c r="C165" s="2">
         <v>1.5346672703999999</v>
       </c>
       <c r="D165" s="2">
@@ -6506,7 +6485,7 @@
       <c r="F165" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G165" s="5">
+      <c r="G165" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6517,7 +6496,7 @@
       <c r="B166" t="s">
         <v>172</v>
       </c>
-      <c r="C166" s="3">
+      <c r="C166" s="2">
         <v>1.5599251776</v>
       </c>
       <c r="D166" s="2">
@@ -6529,7 +6508,7 @@
       <c r="F166" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G166" s="5">
+      <c r="G166" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6540,7 +6519,7 @@
       <c r="B167" t="s">
         <v>173</v>
       </c>
-      <c r="C167" s="3">
+      <c r="C167" s="2">
         <v>1.6483278528</v>
       </c>
       <c r="D167" s="2">
@@ -6552,7 +6531,7 @@
       <c r="F167" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G167" s="5">
+      <c r="G167" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6563,7 +6542,7 @@
       <c r="B168" t="s">
         <v>174</v>
       </c>
-      <c r="C168" s="3">
+      <c r="C168" s="2">
         <v>1.6941078096</v>
       </c>
       <c r="D168" s="2">
@@ -6575,7 +6554,7 @@
       <c r="F168" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G168" s="5">
+      <c r="G168" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6586,7 +6565,7 @@
       <c r="B169" t="s">
         <v>175</v>
       </c>
-      <c r="C169" s="3">
+      <c r="C169" s="2">
         <v>1.7540953392</v>
       </c>
       <c r="D169" s="2">
@@ -6598,7 +6577,7 @@
       <c r="F169" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G169" s="5">
+      <c r="G169" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6609,7 +6588,7 @@
       <c r="B170" t="s">
         <v>176</v>
       </c>
-      <c r="C170" s="3">
+      <c r="C170" s="2">
         <v>1.8030325344</v>
       </c>
       <c r="D170" s="2">
@@ -6621,7 +6600,7 @@
       <c r="F170" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G170" s="5">
+      <c r="G170" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6632,7 +6611,7 @@
       <c r="B171" t="s">
         <v>177</v>
       </c>
-      <c r="C171" s="3">
+      <c r="C171" s="2">
         <v>1.8724917792</v>
       </c>
       <c r="D171" s="2">
@@ -6644,7 +6623,7 @@
       <c r="F171" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G171" s="5">
+      <c r="G171" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6655,7 +6634,7 @@
       <c r="B172" t="s">
         <v>178</v>
       </c>
-      <c r="C172" s="3">
+      <c r="C172" s="2">
         <v>1.6187833152</v>
       </c>
       <c r="D172" s="2">
@@ -6667,7 +6646,7 @@
       <c r="F172" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G172" s="5">
+      <c r="G172" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6678,7 +6657,7 @@
       <c r="B173" t="s">
         <v>179</v>
       </c>
-      <c r="C173" s="3">
+      <c r="C173" s="2">
         <v>1.6673008944000001</v>
       </c>
       <c r="D173" s="2">
@@ -6690,7 +6669,7 @@
       <c r="F173" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G173" s="5">
+      <c r="G173" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6701,7 +6680,7 @@
       <c r="B174" t="s">
         <v>180</v>
       </c>
-      <c r="C174" s="3">
+      <c r="C174" s="2">
         <v>1.7056042464000001</v>
       </c>
       <c r="D174" s="2">
@@ -6713,7 +6692,7 @@
       <c r="F174" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G174" s="5">
+      <c r="G174" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6724,7 +6703,7 @@
       <c r="B175" t="s">
         <v>181</v>
       </c>
-      <c r="C175" s="3">
+      <c r="C175" s="2">
         <v>1.7413540416</v>
       </c>
       <c r="D175" s="2">
@@ -6736,7 +6715,7 @@
       <c r="F175" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G175" s="5">
+      <c r="G175" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6747,7 +6726,7 @@
       <c r="B176" t="s">
         <v>182</v>
       </c>
-      <c r="C176" s="3">
+      <c r="C176" s="2">
         <v>1.7822109504000001</v>
       </c>
       <c r="D176" s="2">
@@ -6759,7 +6738,7 @@
       <c r="F176" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G176" s="5">
+      <c r="G176" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6770,7 +6749,7 @@
       <c r="B177" t="s">
         <v>183</v>
       </c>
-      <c r="C177" s="3">
+      <c r="C177" s="2">
         <v>1.9252101312000001</v>
       </c>
       <c r="D177" s="2">
@@ -6782,7 +6761,7 @@
       <c r="F177" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G177" s="5">
+      <c r="G177" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6793,7 +6772,7 @@
       <c r="B178" t="s">
         <v>184</v>
       </c>
-      <c r="C178" s="3">
+      <c r="C178" s="2">
         <v>1.9992632784</v>
       </c>
       <c r="D178" s="2">
@@ -6805,7 +6784,7 @@
       <c r="F178" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G178" s="5">
+      <c r="G178" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6816,7 +6795,7 @@
       <c r="B179" t="s">
         <v>185</v>
       </c>
-      <c r="C179" s="3">
+      <c r="C179" s="2">
         <v>2.0962984368000002</v>
       </c>
       <c r="D179" s="2">
@@ -6828,7 +6807,7 @@
       <c r="F179" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G179" s="5">
+      <c r="G179" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6839,7 +6818,7 @@
       <c r="B180" t="s">
         <v>186</v>
       </c>
-      <c r="C180" s="3">
+      <c r="C180" s="2">
         <v>2.1754586975999999</v>
       </c>
       <c r="D180" s="2">
@@ -6851,7 +6830,7 @@
       <c r="F180" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G180" s="5">
+      <c r="G180" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6862,7 +6841,7 @@
       <c r="B181" t="s">
         <v>187</v>
       </c>
-      <c r="C181" s="3">
+      <c r="C181" s="2">
         <v>2.2878151968</v>
       </c>
       <c r="D181" s="2">
@@ -6874,7 +6853,7 @@
       <c r="F181" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G181" s="5">
+      <c r="G181" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6885,7 +6864,7 @@
       <c r="B182" t="s">
         <v>188</v>
       </c>
-      <c r="C182" s="3">
+      <c r="C182" s="2">
         <v>2.0685158399999999</v>
       </c>
       <c r="D182" s="2">
@@ -6897,7 +6876,7 @@
       <c r="F182" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G182" s="5">
+      <c r="G182" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6908,7 +6887,7 @@
       <c r="B183" t="s">
         <v>189</v>
       </c>
-      <c r="C183" s="3">
+      <c r="C183" s="2">
         <v>2.28183552</v>
       </c>
       <c r="D183" s="2">
@@ -6920,7 +6899,7 @@
       <c r="F183" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G183" s="5">
+      <c r="G183" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6931,7 +6910,7 @@
       <c r="B184" t="s">
         <v>190</v>
       </c>
-      <c r="C184" s="3">
+      <c r="C184" s="2">
         <v>2.3923046399999999</v>
       </c>
       <c r="D184" s="2">
@@ -6943,7 +6922,7 @@
       <c r="F184" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G184" s="5">
+      <c r="G184" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6954,7 +6933,7 @@
       <c r="B185" t="s">
         <v>191</v>
       </c>
-      <c r="C185" s="3">
+      <c r="C185" s="2">
         <v>2.53705728</v>
       </c>
       <c r="D185" s="2">
@@ -6966,7 +6945,7 @@
       <c r="F185" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G185" s="5">
+      <c r="G185" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6977,7 +6956,7 @@
       <c r="B186" t="s">
         <v>192</v>
       </c>
-      <c r="C186" s="3">
+      <c r="C186" s="2">
         <v>2.6551449599999999</v>
       </c>
       <c r="D186" s="2">
@@ -6989,7 +6968,7 @@
       <c r="F186" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G186" s="5">
+      <c r="G186" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7000,7 +6979,7 @@
       <c r="B187" t="s">
         <v>193</v>
       </c>
-      <c r="C187" s="3">
+      <c r="C187" s="2">
         <v>2.8227532800000001</v>
       </c>
       <c r="D187" s="2">
@@ -7012,7 +6991,7 @@
       <c r="F187" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G187" s="5">
+      <c r="G187" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7023,7 +7002,7 @@
       <c r="B188" t="s">
         <v>194</v>
       </c>
-      <c r="C188" s="3">
+      <c r="C188" s="2">
         <v>3.18844416</v>
       </c>
       <c r="D188" s="2">
@@ -7035,7 +7014,7 @@
       <c r="F188" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G188" s="5">
+      <c r="G188" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7046,7 +7025,7 @@
       <c r="B189" t="s">
         <v>195</v>
       </c>
-      <c r="C189" s="3">
+      <c r="C189" s="2">
         <v>3.5541350399999989</v>
       </c>
       <c r="D189" s="2">
@@ -7058,7 +7037,7 @@
       <c r="F189" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G189" s="5">
+      <c r="G189" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7069,7 +7048,7 @@
       <c r="B190" t="s">
         <v>196</v>
       </c>
-      <c r="C190" s="3">
+      <c r="C190" s="2">
         <v>4.0379136000000004</v>
       </c>
       <c r="D190" s="2">
@@ -7081,7 +7060,7 @@
       <c r="F190" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G190" s="5">
+      <c r="G190" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7092,7 +7071,7 @@
       <c r="B191" t="s">
         <v>197</v>
       </c>
-      <c r="C191" s="3">
+      <c r="C191" s="2">
         <v>4.6550169599999993</v>
       </c>
       <c r="D191" s="2">
@@ -7104,7 +7083,7 @@
       <c r="F191" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G191" s="5">
+      <c r="G191" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7115,7 +7094,7 @@
       <c r="B192" t="s">
         <v>198</v>
       </c>
-      <c r="C192" s="3">
+      <c r="C192" s="2">
         <v>4.9864243199999994</v>
       </c>
       <c r="D192" s="2">
@@ -7127,7 +7106,7 @@
       <c r="F192" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G192" s="5">
+      <c r="G192" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7138,7 +7117,7 @@
       <c r="B193" t="s">
         <v>199</v>
       </c>
-      <c r="C193" s="3">
+      <c r="C193" s="2">
         <v>4.9353023231999993</v>
       </c>
       <c r="D193" s="2">
@@ -7150,7 +7129,7 @@
       <c r="F193" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G193" s="5">
+      <c r="G193" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7161,7 +7140,7 @@
       <c r="B194" t="s">
         <v>200</v>
       </c>
-      <c r="C194" s="3">
+      <c r="C194" s="2">
         <v>5.1329212223999994</v>
       </c>
       <c r="D194" s="2">
@@ -7173,7 +7152,7 @@
       <c r="F194" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G194" s="5">
+      <c r="G194" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7184,7 +7163,7 @@
       <c r="B195" t="s">
         <v>201</v>
       </c>
-      <c r="C195" s="3">
+      <c r="C195" s="2">
         <v>5.3918701247999987</v>
       </c>
       <c r="D195" s="2">
@@ -7196,7 +7175,7 @@
       <c r="F195" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G195" s="5">
+      <c r="G195" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7207,7 +7186,7 @@
       <c r="B196" t="s">
         <v>202</v>
       </c>
-      <c r="C196" s="3">
+      <c r="C196" s="2">
         <v>5.6031179135999993</v>
       </c>
       <c r="D196" s="2">
@@ -7219,7 +7198,7 @@
       <c r="F196" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G196" s="5">
+      <c r="G196" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7230,7 +7209,7 @@
       <c r="B197" t="s">
         <v>203</v>
       </c>
-      <c r="C197" s="3">
+      <c r="C197" s="2">
         <v>5.9029534847999994</v>
       </c>
       <c r="D197" s="2">
@@ -7242,7 +7221,7 @@
       <c r="F197" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G197" s="5">
+      <c r="G197" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7253,7 +7232,7 @@
       <c r="B198" t="s">
         <v>204</v>
       </c>
-      <c r="C198" s="3">
+      <c r="C198" s="2">
         <v>6.5571401855999998</v>
       </c>
       <c r="D198" s="2">
@@ -7265,7 +7244,7 @@
       <c r="F198" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G198" s="5">
+      <c r="G198" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7276,7 +7255,7 @@
       <c r="B199" t="s">
         <v>205</v>
       </c>
-      <c r="C199" s="3">
+      <c r="C199" s="2">
         <v>7.2113268863999993</v>
       </c>
       <c r="D199" s="2">
@@ -7288,7 +7267,7 @@
       <c r="F199" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G199" s="5">
+      <c r="G199" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7299,7 +7278,7 @@
       <c r="B200" t="s">
         <v>206</v>
       </c>
-      <c r="C200" s="3">
+      <c r="C200" s="2">
         <v>8.0767613759999985</v>
       </c>
       <c r="D200" s="2">
@@ -7311,7 +7290,7 @@
       <c r="F200" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G200" s="5">
+      <c r="G200" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7322,7 +7301,7 @@
       <c r="B201" t="s">
         <v>207</v>
       </c>
-      <c r="C201" s="3">
+      <c r="C201" s="2">
         <v>9.1807014335999995</v>
       </c>
       <c r="D201" s="2">
@@ -7334,7 +7313,7 @@
       <c r="F201" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G201" s="5">
+      <c r="G201" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7345,7 +7324,7 @@
       <c r="B202" t="s">
         <v>208</v>
       </c>
-      <c r="C202" s="3">
+      <c r="C202" s="2">
         <v>9.7735581311999979</v>
       </c>
       <c r="D202" s="2">
@@ -7357,7 +7336,7 @@
       <c r="F202" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G202" s="5">
+      <c r="G202" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7368,7 +7347,7 @@
       <c r="B203" t="s">
         <v>209</v>
       </c>
-      <c r="C203" s="3">
+      <c r="C203" s="2">
         <v>12.500803917823999</v>
       </c>
       <c r="D203" s="2">
@@ -7380,7 +7359,7 @@
       <c r="F203" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G203" s="5">
+      <c r="G203" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7391,7 +7370,7 @@
       <c r="B204" t="s">
         <v>210</v>
       </c>
-      <c r="C204" s="3">
+      <c r="C204" s="2">
         <v>14.042231260159999</v>
       </c>
       <c r="D204" s="2">
@@ -7403,7 +7382,7 @@
       <c r="F204" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G204" s="5">
+      <c r="G204" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7414,7 +7393,7 @@
       <c r="B205" t="s">
         <v>211</v>
       </c>
-      <c r="C205" s="3">
+      <c r="C205" s="2">
         <v>16.008461413376001</v>
       </c>
       <c r="D205" s="2">
@@ -7426,7 +7405,7 @@
       <c r="F205" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G205" s="5">
+      <c r="G205" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7437,7 +7416,7 @@
       <c r="B206" t="s">
         <v>212</v>
       </c>
-      <c r="C206" s="3">
+      <c r="C206" s="2">
         <v>17.064399828991998</v>
       </c>
       <c r="D206" s="2">
@@ -7449,7 +7428,7 @@
       <c r="F206" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G206" s="5">
+      <c r="G206" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7472,7 +7451,7 @@
       <c r="F207" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G207" s="5">
+      <c r="G207" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7495,7 +7474,7 @@
       <c r="F208" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G208" s="5">
+      <c r="G208" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7518,7 +7497,7 @@
       <c r="F209" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G209" s="5">
+      <c r="G209" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7541,7 +7520,7 @@
       <c r="F210" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G210" s="5">
+      <c r="G210" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7564,7 +7543,7 @@
       <c r="F211" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G211" s="5">
+      <c r="G211" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7587,7 +7566,7 @@
       <c r="F212" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G212" s="5">
+      <c r="G212" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7610,7 +7589,7 @@
       <c r="F213" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G213" s="5">
+      <c r="G213" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7633,7 +7612,7 @@
       <c r="F214" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G214" s="5">
+      <c r="G214" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7656,7 +7635,7 @@
       <c r="F215" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G215" s="5">
+      <c r="G215" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7679,7 +7658,7 @@
       <c r="F216" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G216" s="5">
+      <c r="G216" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7702,7 +7681,7 @@
       <c r="F217" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G217" s="5">
+      <c r="G217" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7725,7 +7704,7 @@
       <c r="F218" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G218" s="5">
+      <c r="G218" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7748,7 +7727,7 @@
       <c r="F219" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G219" s="5">
+      <c r="G219" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7771,7 +7750,7 @@
       <c r="F220" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G220" s="5">
+      <c r="G220" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7794,7 +7773,7 @@
       <c r="F221" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G221" s="5">
+      <c r="G221" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7817,7 +7796,7 @@
       <c r="F222" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G222" s="5">
+      <c r="G222" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7840,7 +7819,7 @@
       <c r="F223" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G223" s="5">
+      <c r="G223" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7863,7 +7842,7 @@
       <c r="F224" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G224" s="5">
+      <c r="G224" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7886,7 +7865,7 @@
       <c r="F225" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G225" s="5">
+      <c r="G225" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7909,7 +7888,7 @@
       <c r="F226" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G226" s="5">
+      <c r="G226" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7932,7 +7911,7 @@
       <c r="F227" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G227" s="5">
+      <c r="G227" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7955,7 +7934,7 @@
       <c r="F228" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G228" s="5">
+      <c r="G228" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7978,7 +7957,7 @@
       <c r="F229" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G229" s="5">
+      <c r="G229" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8001,7 +7980,7 @@
       <c r="F230" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G230" s="5">
+      <c r="G230" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8024,7 +8003,7 @@
       <c r="F231" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G231" s="5">
+      <c r="G231" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8047,7 +8026,7 @@
       <c r="F232" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G232" s="5">
+      <c r="G232" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8070,7 +8049,7 @@
       <c r="F233" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G233" s="5">
+      <c r="G233" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8093,7 +8072,7 @@
       <c r="F234" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G234" s="5">
+      <c r="G234" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8116,7 +8095,7 @@
       <c r="F235" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G235" s="5">
+      <c r="G235" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8139,7 +8118,7 @@
       <c r="F236" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G236" s="5">
+      <c r="G236" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8162,7 +8141,7 @@
       <c r="F237" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G237" s="5">
+      <c r="G237" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8185,7 +8164,7 @@
       <c r="F238" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G238" s="5">
+      <c r="G238" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8208,7 +8187,7 @@
       <c r="F239" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G239" s="5">
+      <c r="G239" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8231,7 +8210,7 @@
       <c r="F240" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G240" s="5">
+      <c r="G240" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8254,7 +8233,7 @@
       <c r="F241" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G241" s="5">
+      <c r="G241" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8277,7 +8256,7 @@
       <c r="F242" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G242" s="5">
+      <c r="G242" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8300,7 +8279,7 @@
       <c r="F243" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G243" s="5">
+      <c r="G243" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8323,7 +8302,7 @@
       <c r="F244" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G244" s="5">
+      <c r="G244" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8346,7 +8325,7 @@
       <c r="F245" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G245" s="5">
+      <c r="G245" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8369,7 +8348,7 @@
       <c r="F246" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G246" s="5">
+      <c r="G246" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8392,7 +8371,7 @@
       <c r="F247" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G247" s="5">
+      <c r="G247" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8415,7 +8394,7 @@
       <c r="F248" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G248" s="5">
+      <c r="G248" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8438,7 +8417,7 @@
       <c r="F249" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G249" s="5">
+      <c r="G249" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8461,7 +8440,7 @@
       <c r="F250" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G250" s="5">
+      <c r="G250" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8484,7 +8463,7 @@
       <c r="F251" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G251" s="5">
+      <c r="G251" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8507,7 +8486,7 @@
       <c r="F252" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G252" s="5">
+      <c r="G252" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8530,7 +8509,7 @@
       <c r="F253" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G253" s="5">
+      <c r="G253" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8553,7 +8532,7 @@
       <c r="F254" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G254" s="5">
+      <c r="G254" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8576,7 +8555,7 @@
       <c r="F255" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G255" s="5">
+      <c r="G255" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8599,7 +8578,7 @@
       <c r="F256" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G256" s="5">
+      <c r="G256" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8622,7 +8601,7 @@
       <c r="F257" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G257" s="5">
+      <c r="G257" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8645,7 +8624,7 @@
       <c r="F258" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G258" s="5">
+      <c r="G258" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8668,7 +8647,7 @@
       <c r="F259" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G259" s="5">
+      <c r="G259" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8691,7 +8670,7 @@
       <c r="F260" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G260" s="5">
+      <c r="G260" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8714,7 +8693,7 @@
       <c r="F261" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G261" s="5">
+      <c r="G261" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8737,7 +8716,7 @@
       <c r="F262" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G262" s="5">
+      <c r="G262" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8760,7 +8739,7 @@
       <c r="F263" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G263" s="5">
+      <c r="G263" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8783,7 +8762,7 @@
       <c r="F264" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G264" s="5">
+      <c r="G264" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8806,7 +8785,7 @@
       <c r="F265" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G265" s="5">
+      <c r="G265" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8829,7 +8808,7 @@
       <c r="F266" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G266" s="5">
+      <c r="G266" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8852,7 +8831,7 @@
       <c r="F267" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G267" s="5">
+      <c r="G267" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8875,7 +8854,7 @@
       <c r="F268" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G268" s="5">
+      <c r="G268" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8898,7 +8877,7 @@
       <c r="F269" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G269" s="5">
+      <c r="G269" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8921,7 +8900,7 @@
       <c r="F270" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G270" s="5">
+      <c r="G270" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8944,7 +8923,7 @@
       <c r="F271" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G271" s="5">
+      <c r="G271" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8967,7 +8946,7 @@
       <c r="F272" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G272" s="5">
+      <c r="G272" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8990,7 +8969,7 @@
       <c r="F273" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G273" s="5">
+      <c r="G273" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9013,7 +8992,7 @@
       <c r="F274" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G274" s="5">
+      <c r="G274" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9036,7 +9015,7 @@
       <c r="F275" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G275" s="5">
+      <c r="G275" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9059,7 +9038,7 @@
       <c r="F276" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G276" s="5">
+      <c r="G276" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9082,7 +9061,7 @@
       <c r="F277" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G277" s="5">
+      <c r="G277" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9105,7 +9084,7 @@
       <c r="F278" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G278" s="5">
+      <c r="G278" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9128,7 +9107,7 @@
       <c r="F279" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G279" s="5">
+      <c r="G279" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9151,7 +9130,7 @@
       <c r="F280" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G280" s="5">
+      <c r="G280" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9174,7 +9153,7 @@
       <c r="F281" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G281" s="5">
+      <c r="G281" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9197,7 +9176,7 @@
       <c r="F282" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G282" s="5">
+      <c r="G282" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9220,7 +9199,7 @@
       <c r="F283" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G283" s="5">
+      <c r="G283" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9243,7 +9222,7 @@
       <c r="F284" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G284" s="5">
+      <c r="G284" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9266,7 +9245,7 @@
       <c r="F285" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G285" s="5">
+      <c r="G285" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9289,7 +9268,7 @@
       <c r="F286" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G286" s="5">
+      <c r="G286" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9312,7 +9291,7 @@
       <c r="F287" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G287" s="5">
+      <c r="G287" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9335,7 +9314,7 @@
       <c r="F288" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G288" s="5">
+      <c r="G288" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9358,7 +9337,7 @@
       <c r="F289" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G289" s="5">
+      <c r="G289" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9381,7 +9360,7 @@
       <c r="F290" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G290" s="5">
+      <c r="G290" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9404,7 +9383,7 @@
       <c r="F291" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G291" s="5">
+      <c r="G291" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9427,7 +9406,7 @@
       <c r="F292" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G292" s="5">
+      <c r="G292" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9450,7 +9429,7 @@
       <c r="F293" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G293" s="5">
+      <c r="G293" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9473,7 +9452,7 @@
       <c r="F294" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G294" s="5">
+      <c r="G294" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9496,7 +9475,7 @@
       <c r="F295" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G295" s="5">
+      <c r="G295" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9519,7 +9498,7 @@
       <c r="F296" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G296" s="5">
+      <c r="G296" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9542,7 +9521,7 @@
       <c r="F297" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G297" s="5">
+      <c r="G297" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9565,7 +9544,7 @@
       <c r="F298" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G298" s="5">
+      <c r="G298" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9588,7 +9567,7 @@
       <c r="F299" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G299" s="5">
+      <c r="G299" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9611,7 +9590,7 @@
       <c r="F300" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G300" s="5">
+      <c r="G300" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9634,7 +9613,7 @@
       <c r="F301" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G301" s="5">
+      <c r="G301" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9657,7 +9636,7 @@
       <c r="F302" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G302" s="5">
+      <c r="G302" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9680,7 +9659,7 @@
       <c r="F303" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G303" s="5">
+      <c r="G303" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9703,7 +9682,7 @@
       <c r="F304" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G304" s="5">
+      <c r="G304" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9726,7 +9705,7 @@
       <c r="F305" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G305" s="5">
+      <c r="G305" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9749,7 +9728,7 @@
       <c r="F306" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G306" s="5">
+      <c r="G306" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9772,7 +9751,7 @@
       <c r="F307" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G307" s="5">
+      <c r="G307" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9795,7 +9774,7 @@
       <c r="F308" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G308" s="5">
+      <c r="G308" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9818,7 +9797,7 @@
       <c r="F309" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G309" s="5">
+      <c r="G309" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9841,7 +9820,7 @@
       <c r="F310" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G310" s="5">
+      <c r="G310" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9864,7 +9843,7 @@
       <c r="F311" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G311" s="5">
+      <c r="G311" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9887,7 +9866,7 @@
       <c r="F312" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G312" s="5">
+      <c r="G312" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9910,7 +9889,7 @@
       <c r="F313" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G313" s="5">
+      <c r="G313" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9933,7 +9912,7 @@
       <c r="F314" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G314" s="5">
+      <c r="G314" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9956,7 +9935,7 @@
       <c r="F315" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G315" s="5">
+      <c r="G315" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9979,7 +9958,7 @@
       <c r="F316" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G316" s="5">
+      <c r="G316" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10002,7 +9981,7 @@
       <c r="F317" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G317" s="5">
+      <c r="G317" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10025,7 +10004,7 @@
       <c r="F318" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G318" s="5">
+      <c r="G318" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10048,7 +10027,7 @@
       <c r="F319" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G319" s="5">
+      <c r="G319" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10071,7 +10050,7 @@
       <c r="F320" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G320" s="5">
+      <c r="G320" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10094,7 +10073,7 @@
       <c r="F321" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G321" s="5">
+      <c r="G321" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10117,7 +10096,7 @@
       <c r="F322" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G322" s="5">
+      <c r="G322" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10140,7 +10119,7 @@
       <c r="F323" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G323" s="5">
+      <c r="G323" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10163,7 +10142,7 @@
       <c r="F324" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G324" s="5">
+      <c r="G324" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10186,7 +10165,7 @@
       <c r="F325" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G325" s="5">
+      <c r="G325" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10209,7 +10188,7 @@
       <c r="F326" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G326" s="5">
+      <c r="G326" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10232,7 +10211,7 @@
       <c r="F327" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G327" s="5">
+      <c r="G327" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10255,7 +10234,7 @@
       <c r="F328" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G328" s="5">
+      <c r="G328" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10278,7 +10257,7 @@
       <c r="F329" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G329" s="5">
+      <c r="G329" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10301,7 +10280,7 @@
       <c r="F330" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G330" s="5">
+      <c r="G330" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10324,7 +10303,7 @@
       <c r="F331" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G331" s="5">
+      <c r="G331" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10347,7 +10326,7 @@
       <c r="F332" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G332" s="5">
+      <c r="G332" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10370,7 +10349,7 @@
       <c r="F333" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G333" s="5">
+      <c r="G333" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10393,7 +10372,7 @@
       <c r="F334" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G334" s="5">
+      <c r="G334" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10416,7 +10395,7 @@
       <c r="F335" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G335" s="5">
+      <c r="G335" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10439,7 +10418,7 @@
       <c r="F336" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G336" s="5">
+      <c r="G336" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10462,7 +10441,7 @@
       <c r="F337" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G337" s="5">
+      <c r="G337" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10485,7 +10464,7 @@
       <c r="F338" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G338" s="5">
+      <c r="G338" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10508,7 +10487,7 @@
       <c r="F339" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G339" s="5">
+      <c r="G339" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10531,7 +10510,7 @@
       <c r="F340" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G340" s="5">
+      <c r="G340" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10554,7 +10533,7 @@
       <c r="F341" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G341" s="5">
+      <c r="G341" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10577,7 +10556,7 @@
       <c r="F342" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G342" s="5">
+      <c r="G342" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10600,7 +10579,7 @@
       <c r="F343" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G343" s="5">
+      <c r="G343" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10623,7 +10602,7 @@
       <c r="F344" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G344" s="5">
+      <c r="G344" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10646,7 +10625,7 @@
       <c r="F345" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G345" s="5">
+      <c r="G345" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10669,7 +10648,7 @@
       <c r="F346" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G346" s="5">
+      <c r="G346" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10692,7 +10671,7 @@
       <c r="F347" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G347" s="5">
+      <c r="G347" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10715,7 +10694,7 @@
       <c r="F348" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G348" s="5">
+      <c r="G348" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10738,7 +10717,7 @@
       <c r="F349" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G349" s="5">
+      <c r="G349" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10761,7 +10740,7 @@
       <c r="F350" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G350" s="5">
+      <c r="G350" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10784,7 +10763,7 @@
       <c r="F351" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G351" s="5">
+      <c r="G351" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10807,7 +10786,7 @@
       <c r="F352" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G352" s="5">
+      <c r="G352" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10830,7 +10809,7 @@
       <c r="F353" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G353" s="5">
+      <c r="G353" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10853,7 +10832,7 @@
       <c r="F354" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G354" s="5">
+      <c r="G354" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10876,7 +10855,7 @@
       <c r="F355" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G355" s="5">
+      <c r="G355" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10899,7 +10878,7 @@
       <c r="F356" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G356" s="5">
+      <c r="G356" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10922,7 +10901,7 @@
       <c r="F357" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G357" s="5">
+      <c r="G357" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10945,7 +10924,7 @@
       <c r="F358" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G358" s="5">
+      <c r="G358" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10968,7 +10947,7 @@
       <c r="F359" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G359" s="5">
+      <c r="G359" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10991,7 +10970,7 @@
       <c r="F360" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G360" s="5">
+      <c r="G360" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11014,7 +10993,7 @@
       <c r="F361" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G361" s="5">
+      <c r="G361" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11037,7 +11016,7 @@
       <c r="F362" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G362" s="5">
+      <c r="G362" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11060,7 +11039,7 @@
       <c r="F363" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G363" s="5">
+      <c r="G363" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11083,7 +11062,7 @@
       <c r="F364" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G364" s="5">
+      <c r="G364" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11106,7 +11085,7 @@
       <c r="F365" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G365" s="5">
+      <c r="G365" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11129,7 +11108,7 @@
       <c r="F366" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G366" s="5">
+      <c r="G366" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11152,7 +11131,7 @@
       <c r="F367" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G367" s="5">
+      <c r="G367" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11175,7 +11154,7 @@
       <c r="F368" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G368" s="5">
+      <c r="G368" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11198,7 +11177,7 @@
       <c r="F369" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G369" s="5">
+      <c r="G369" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11221,7 +11200,7 @@
       <c r="F370" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G370" s="5">
+      <c r="G370" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11244,7 +11223,7 @@
       <c r="F371" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G371" s="5">
+      <c r="G371" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11267,7 +11246,7 @@
       <c r="F372" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G372" s="5">
+      <c r="G372" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11290,7 +11269,7 @@
       <c r="F373" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G373" s="5">
+      <c r="G373" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11313,7 +11292,7 @@
       <c r="F374" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G374" s="5">
+      <c r="G374" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11336,7 +11315,7 @@
       <c r="F375" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G375" s="5">
+      <c r="G375" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11359,7 +11338,7 @@
       <c r="F376" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G376" s="5">
+      <c r="G376" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11382,7 +11361,7 @@
       <c r="F377" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G377" s="5">
+      <c r="G377" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11405,7 +11384,7 @@
       <c r="F378" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G378" s="5">
+      <c r="G378" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11428,7 +11407,7 @@
       <c r="F379" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G379" s="5">
+      <c r="G379" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11451,7 +11430,7 @@
       <c r="F380" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G380" s="5">
+      <c r="G380" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11474,7 +11453,7 @@
       <c r="F381" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G381" s="5">
+      <c r="G381" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11497,7 +11476,7 @@
       <c r="F382" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G382" s="5">
+      <c r="G382" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11520,7 +11499,7 @@
       <c r="F383" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G383" s="5">
+      <c r="G383" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11543,7 +11522,7 @@
       <c r="F384" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G384" s="5">
+      <c r="G384" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11566,7 +11545,7 @@
       <c r="F385" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G385" s="5">
+      <c r="G385" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11589,7 +11568,7 @@
       <c r="F386" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G386" s="5">
+      <c r="G386" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11612,7 +11591,7 @@
       <c r="F387" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G387" s="5">
+      <c r="G387" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11635,7 +11614,7 @@
       <c r="F388" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G388" s="5">
+      <c r="G388" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11658,7 +11637,7 @@
       <c r="F389" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G389" s="5">
+      <c r="G389" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11681,7 +11660,7 @@
       <c r="F390" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G390" s="5">
+      <c r="G390" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11704,7 +11683,7 @@
       <c r="F391" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G391" s="5">
+      <c r="G391" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11727,7 +11706,7 @@
       <c r="F392" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G392" s="5">
+      <c r="G392" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11750,7 +11729,7 @@
       <c r="F393" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G393" s="5">
+      <c r="G393" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11773,7 +11752,7 @@
       <c r="F394" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G394" s="5">
+      <c r="G394" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11796,7 +11775,7 @@
       <c r="F395" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G395" s="5">
+      <c r="G395" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11819,7 +11798,7 @@
       <c r="F396" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G396" s="5">
+      <c r="G396" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11842,7 +11821,7 @@
       <c r="F397" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G397" s="5">
+      <c r="G397" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11865,7 +11844,7 @@
       <c r="F398" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G398" s="5">
+      <c r="G398" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11888,7 +11867,7 @@
       <c r="F399" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G399" s="5">
+      <c r="G399" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11911,7 +11890,7 @@
       <c r="F400" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G400" s="5">
+      <c r="G400" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11934,7 +11913,7 @@
       <c r="F401" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G401" s="5">
+      <c r="G401" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11957,7 +11936,7 @@
       <c r="F402" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G402" s="5">
+      <c r="G402" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11980,7 +11959,7 @@
       <c r="F403" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G403" s="5">
+      <c r="G403" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12003,7 +11982,7 @@
       <c r="F404" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G404" s="5">
+      <c r="G404" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12026,7 +12005,7 @@
       <c r="F405" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G405" s="5">
+      <c r="G405" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12049,7 +12028,7 @@
       <c r="F406" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G406" s="5">
+      <c r="G406" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12072,7 +12051,7 @@
       <c r="F407" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G407" s="5">
+      <c r="G407" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12095,7 +12074,7 @@
       <c r="F408" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G408" s="5">
+      <c r="G408" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12118,7 +12097,7 @@
       <c r="F409" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G409" s="5">
+      <c r="G409" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12141,7 +12120,7 @@
       <c r="F410" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G410" s="5">
+      <c r="G410" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12164,7 +12143,7 @@
       <c r="F411" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G411" s="5">
+      <c r="G411" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12187,7 +12166,7 @@
       <c r="F412" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G412" s="5">
+      <c r="G412" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12210,7 +12189,7 @@
       <c r="F413" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G413" s="5">
+      <c r="G413" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12233,7 +12212,7 @@
       <c r="F414" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G414" s="5">
+      <c r="G414" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12256,7 +12235,7 @@
       <c r="F415" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G415" s="5">
+      <c r="G415" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12279,7 +12258,7 @@
       <c r="F416" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G416" s="5">
+      <c r="G416" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12302,7 +12281,7 @@
       <c r="F417" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G417" s="5">
+      <c r="G417" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12325,7 +12304,7 @@
       <c r="F418" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G418" s="5">
+      <c r="G418" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12348,7 +12327,7 @@
       <c r="F419" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G419" s="5">
+      <c r="G419" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12371,7 +12350,7 @@
       <c r="F420" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G420" s="5">
+      <c r="G420" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12394,7 +12373,7 @@
       <c r="F421" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G421" s="5">
+      <c r="G421" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12417,7 +12396,7 @@
       <c r="F422" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G422" s="5">
+      <c r="G422" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12440,7 +12419,7 @@
       <c r="F423" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G423" s="5">
+      <c r="G423" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12463,7 +12442,7 @@
       <c r="F424" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G424" s="5">
+      <c r="G424" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12486,7 +12465,7 @@
       <c r="F425" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G425" s="5">
+      <c r="G425" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12509,7 +12488,7 @@
       <c r="F426" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G426" s="5">
+      <c r="G426" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12532,7 +12511,7 @@
       <c r="F427" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G427" s="5">
+      <c r="G427" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12555,7 +12534,7 @@
       <c r="F428" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G428" s="5">
+      <c r="G428" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12578,7 +12557,7 @@
       <c r="F429" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G429" s="5">
+      <c r="G429" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12601,7 +12580,7 @@
       <c r="F430" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G430" s="5">
+      <c r="G430" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12624,7 +12603,7 @@
       <c r="F431" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G431" s="5">
+      <c r="G431" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12647,7 +12626,7 @@
       <c r="F432" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G432" s="5">
+      <c r="G432" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12670,7 +12649,7 @@
       <c r="F433" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G433" s="5">
+      <c r="G433" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12693,7 +12672,7 @@
       <c r="F434" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G434" s="5">
+      <c r="G434" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12716,7 +12695,7 @@
       <c r="F435" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G435" s="5">
+      <c r="G435" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12739,7 +12718,7 @@
       <c r="F436" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G436" s="5">
+      <c r="G436" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12762,7 +12741,7 @@
       <c r="F437" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G437" s="5">
+      <c r="G437" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12785,7 +12764,7 @@
       <c r="F438" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G438" s="5">
+      <c r="G438" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12808,7 +12787,7 @@
       <c r="F439" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G439" s="5">
+      <c r="G439" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12831,7 +12810,7 @@
       <c r="F440" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G440" s="5">
+      <c r="G440" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12854,7 +12833,7 @@
       <c r="F441" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G441" s="5">
+      <c r="G441" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12877,7 +12856,7 @@
       <c r="F442" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G442" s="5">
+      <c r="G442" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12900,7 +12879,7 @@
       <c r="F443" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G443" s="5">
+      <c r="G443" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12923,7 +12902,7 @@
       <c r="F444" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G444" s="5">
+      <c r="G444" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12946,7 +12925,7 @@
       <c r="F445" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G445" s="5">
+      <c r="G445" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12969,7 +12948,7 @@
       <c r="F446" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G446" s="5">
+      <c r="G446" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12992,7 +12971,7 @@
       <c r="F447" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G447" s="5">
+      <c r="G447" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13015,7 +12994,7 @@
       <c r="F448" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G448" s="5">
+      <c r="G448" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13038,7 +13017,7 @@
       <c r="F449" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G449" s="5">
+      <c r="G449" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13061,7 +13040,7 @@
       <c r="F450" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G450" s="5">
+      <c r="G450" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13084,7 +13063,7 @@
       <c r="F451" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G451" s="5">
+      <c r="G451" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13107,7 +13086,7 @@
       <c r="F452" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G452" s="5">
+      <c r="G452" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13130,7 +13109,7 @@
       <c r="F453" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G453" s="5">
+      <c r="G453" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13153,7 +13132,7 @@
       <c r="F454" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G454" s="5">
+      <c r="G454" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13176,7 +13155,7 @@
       <c r="F455" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G455" s="5">
+      <c r="G455" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13199,7 +13178,7 @@
       <c r="F456" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G456" s="5">
+      <c r="G456" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13222,7 +13201,7 @@
       <c r="F457" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G457" s="5">
+      <c r="G457" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13245,7 +13224,7 @@
       <c r="F458" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G458" s="5">
+      <c r="G458" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13268,7 +13247,7 @@
       <c r="F459" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G459" s="5">
+      <c r="G459" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13291,7 +13270,7 @@
       <c r="F460" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G460" s="5">
+      <c r="G460" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13314,7 +13293,7 @@
       <c r="F461" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G461" s="5">
+      <c r="G461" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13337,7 +13316,7 @@
       <c r="F462" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G462" s="5">
+      <c r="G462" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13360,7 +13339,7 @@
       <c r="F463" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G463" s="5">
+      <c r="G463" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13383,7 +13362,7 @@
       <c r="F464" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G464" s="5">
+      <c r="G464" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13406,7 +13385,7 @@
       <c r="F465" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G465" s="5">
+      <c r="G465" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13429,7 +13408,7 @@
       <c r="F466" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G466" s="5">
+      <c r="G466" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13452,7 +13431,7 @@
       <c r="F467" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G467" s="5">
+      <c r="G467" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13475,7 +13454,7 @@
       <c r="F468" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G468" s="5">
+      <c r="G468" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13498,7 +13477,7 @@
       <c r="F469" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G469" s="5">
+      <c r="G469" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13521,7 +13500,7 @@
       <c r="F470" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G470" s="5">
+      <c r="G470" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13544,7 +13523,7 @@
       <c r="F471" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G471" s="5">
+      <c r="G471" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13567,7 +13546,7 @@
       <c r="F472" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G472" s="5">
+      <c r="G472" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13590,7 +13569,7 @@
       <c r="F473" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G473" s="5">
+      <c r="G473" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13613,7 +13592,7 @@
       <c r="F474" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G474" s="5">
+      <c r="G474" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13636,7 +13615,7 @@
       <c r="F475" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G475" s="5">
+      <c r="G475" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13659,7 +13638,7 @@
       <c r="F476" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G476" s="5">
+      <c r="G476" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13682,7 +13661,7 @@
       <c r="F477" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G477" s="6">
+      <c r="G477" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13702,7 +13681,7 @@
       <c r="F478" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G478" s="6">
+      <c r="G478" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13725,7 +13704,7 @@
       <c r="F479" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G479" s="6">
+      <c r="G479" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13745,7 +13724,7 @@
       <c r="F480" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G480" s="6">
+      <c r="G480" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13768,7 +13747,7 @@
       <c r="F481" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G481" s="6">
+      <c r="G481" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13788,7 +13767,7 @@
       <c r="F482" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G482" s="6">
+      <c r="G482" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13808,7 +13787,7 @@
       <c r="F483" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G483" s="6">
+      <c r="G483" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13828,7 +13807,7 @@
       <c r="F484" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G484" s="6">
+      <c r="G484" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13848,7 +13827,7 @@
       <c r="F485" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G485" s="6">
+      <c r="G485" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13868,7 +13847,7 @@
       <c r="F486" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G486" s="6">
+      <c r="G486" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13891,7 +13870,7 @@
       <c r="F487" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G487" s="6">
+      <c r="G487" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13911,7 +13890,7 @@
       <c r="F488" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G488" s="6">
+      <c r="G488" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13934,7 +13913,7 @@
       <c r="F489" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G489" s="6">
+      <c r="G489" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13954,7 +13933,7 @@
       <c r="F490" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G490" s="6">
+      <c r="G490" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13977,7 +13956,7 @@
       <c r="F491" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G491" s="6">
+      <c r="G491" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13997,7 +13976,7 @@
       <c r="F492" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G492" s="6">
+      <c r="G492" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14017,7 +13996,7 @@
       <c r="F493" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G493" s="6">
+      <c r="G493" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14037,7 +14016,7 @@
       <c r="F494" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G494" s="6">
+      <c r="G494" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14057,7 +14036,7 @@
       <c r="F495" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G495" s="6">
+      <c r="G495" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14077,7 +14056,7 @@
       <c r="F496" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G496" s="6">
+      <c r="G496" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14100,7 +14079,7 @@
       <c r="F497" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G497" s="6">
+      <c r="G497" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14120,7 +14099,7 @@
       <c r="F498" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G498" s="6">
+      <c r="G498" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14143,7 +14122,7 @@
       <c r="F499" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G499" s="6">
+      <c r="G499" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14163,7 +14142,7 @@
       <c r="F500" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G500" s="6">
+      <c r="G500" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14186,7 +14165,7 @@
       <c r="F501" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G501" s="6">
+      <c r="G501" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14206,7 +14185,7 @@
       <c r="F502" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G502" s="6">
+      <c r="G502" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14226,7 +14205,7 @@
       <c r="F503" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G503" s="6">
+      <c r="G503" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14246,7 +14225,7 @@
       <c r="F504" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G504" s="6">
+      <c r="G504" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14266,7 +14245,7 @@
       <c r="F505" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G505" s="6">
+      <c r="G505" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14286,7 +14265,7 @@
       <c r="F506" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G506" s="6">
+      <c r="G506" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14303,11 +14282,14 @@
       <c r="D507" s="2">
         <v>17.77</v>
       </c>
+      <c r="E507">
+        <v>10</v>
+      </c>
       <c r="F507" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G507" s="5">
-        <v>0.05</v>
+      <c r="G507" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="508" spans="1:7" x14ac:dyDescent="0.35">
@@ -14323,11 +14305,14 @@
       <c r="D508" s="2">
         <v>20.059999999999999</v>
       </c>
+      <c r="E508">
+        <v>5</v>
+      </c>
       <c r="F508" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G508" s="5">
-        <v>0.05</v>
+      <c r="G508" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="509" spans="1:7" x14ac:dyDescent="0.35">
@@ -14343,11 +14328,14 @@
       <c r="D509" s="2">
         <v>25.68</v>
       </c>
+      <c r="E509">
+        <v>5</v>
+      </c>
       <c r="F509" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G509" s="5">
-        <v>0.05</v>
+      <c r="G509" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="510" spans="1:7" x14ac:dyDescent="0.35">
@@ -14363,11 +14351,14 @@
       <c r="D510" s="2">
         <v>35.93</v>
       </c>
+      <c r="E510">
+        <v>11</v>
+      </c>
       <c r="F510" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G510" s="5">
-        <v>0.05</v>
+      <c r="G510" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="511" spans="1:7" x14ac:dyDescent="0.35">
@@ -14383,11 +14374,14 @@
       <c r="D511" s="2">
         <v>47.98</v>
       </c>
+      <c r="E511">
+        <v>2</v>
+      </c>
       <c r="F511" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G511" s="5">
-        <v>0.05</v>
+      <c r="G511" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="512" spans="1:7" x14ac:dyDescent="0.35">
@@ -14403,11 +14397,14 @@
       <c r="D512" s="2">
         <v>83.96</v>
       </c>
+      <c r="E512">
+        <v>5</v>
+      </c>
       <c r="F512" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G512" s="5">
-        <v>0.05</v>
+      <c r="G512" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="513" spans="1:7" x14ac:dyDescent="0.35">
@@ -14423,11 +14420,14 @@
       <c r="D513" s="2">
         <v>112.32</v>
       </c>
+      <c r="E513">
+        <v>1</v>
+      </c>
       <c r="F513" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G513" s="5">
-        <v>0.05</v>
+      <c r="G513" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="514" spans="1:7" x14ac:dyDescent="0.35">
@@ -14443,11 +14443,14 @@
       <c r="D514" s="2">
         <v>219.57</v>
       </c>
+      <c r="E514">
+        <v>0.5</v>
+      </c>
       <c r="F514" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G514" s="5">
-        <v>0.05</v>
+      <c r="G514" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="515" spans="1:7" x14ac:dyDescent="0.35">
@@ -14463,11 +14466,14 @@
       <c r="D515" s="2">
         <v>285.3</v>
       </c>
+      <c r="E515">
+        <v>0.5</v>
+      </c>
       <c r="F515" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G515" s="5">
-        <v>0.05</v>
+      <c r="G515" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="516" spans="1:7" x14ac:dyDescent="0.35">
@@ -14486,7 +14492,7 @@
       <c r="F516" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G516" s="6">
+      <c r="G516" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14498,15 +14504,18 @@
         <v>525</v>
       </c>
       <c r="C517" s="2">
-        <v>24.16</v>
+        <v>14.2</v>
       </c>
       <c r="D517" s="2">
-        <v>21.74</v>
+        <v>12.44</v>
+      </c>
+      <c r="E517">
+        <v>20</v>
       </c>
       <c r="F517" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G517" s="6">
+      <c r="G517" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14518,15 +14527,18 @@
         <v>526</v>
       </c>
       <c r="C518" s="2">
-        <v>24.8</v>
+        <v>32.283999999999999</v>
       </c>
       <c r="D518" s="2">
-        <v>22.32</v>
+        <v>28.335999999999999</v>
+      </c>
+      <c r="E518">
+        <v>10</v>
       </c>
       <c r="F518" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G518" s="6">
+      <c r="G518" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14538,15 +14550,18 @@
         <v>527</v>
       </c>
       <c r="C519" s="2">
-        <v>72</v>
+        <v>56.54</v>
       </c>
       <c r="D519" s="2">
-        <v>64.8</v>
+        <v>49.74</v>
+      </c>
+      <c r="E519">
+        <v>10</v>
       </c>
       <c r="F519" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G519" s="6">
+      <c r="G519" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14558,15 +14573,15 @@
         <v>528</v>
       </c>
       <c r="C520" s="2">
-        <v>110.4</v>
+        <v>112.38</v>
       </c>
       <c r="D520" s="2">
-        <v>99.36</v>
+        <v>98.33</v>
       </c>
       <c r="F520" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G520" s="6">
+      <c r="G520" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14578,15 +14593,15 @@
         <v>529</v>
       </c>
       <c r="C521" s="2">
-        <v>118.4</v>
+        <v>154.80000000000001</v>
       </c>
       <c r="D521" s="2">
-        <v>106.56</v>
+        <v>135.44999999999999</v>
       </c>
       <c r="F521" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G521" s="6">
+      <c r="G521" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14598,15 +14613,15 @@
         <v>530</v>
       </c>
       <c r="C522" s="2">
-        <v>163.19999999999999</v>
+        <v>175.97</v>
       </c>
       <c r="D522" s="2">
-        <v>146.88</v>
+        <v>153.97999999999999</v>
       </c>
       <c r="F522" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G522" s="6">
+      <c r="G522" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14618,15 +14633,15 @@
         <v>531</v>
       </c>
       <c r="C523" s="2">
-        <v>222.4</v>
+        <v>314.25</v>
       </c>
       <c r="D523" s="2">
-        <v>200.16</v>
+        <v>274.97000000000003</v>
       </c>
       <c r="F523" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G523" s="6">
+      <c r="G523" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14638,16 +14653,16 @@
         <v>532</v>
       </c>
       <c r="C524" s="2">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="D524" s="2">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="F524" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G524" s="5">
-        <v>0.05</v>
+      <c r="G524" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="525" spans="1:7" x14ac:dyDescent="0.35">
@@ -14658,16 +14673,16 @@
         <v>533</v>
       </c>
       <c r="C525" s="2">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="D525" s="2">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="F525" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G525" s="5">
-        <v>0.05</v>
+      <c r="G525" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="526" spans="1:7" x14ac:dyDescent="0.35">
@@ -14678,16 +14693,16 @@
         <v>534</v>
       </c>
       <c r="C526" s="2">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="D526" s="2">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F526" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G526" s="5">
-        <v>0.05</v>
+      <c r="G526" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="527" spans="1:7" x14ac:dyDescent="0.35">
@@ -14701,13 +14716,13 @@
         <v>2.4</v>
       </c>
       <c r="D527" s="2">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="F527" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G527" s="5">
-        <v>0.05</v>
+      <c r="G527" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="528" spans="1:7" x14ac:dyDescent="0.35">
@@ -14718,16 +14733,16 @@
         <v>536</v>
       </c>
       <c r="C528" s="2">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="D528" s="2">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="F528" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G528" s="5">
-        <v>0.05</v>
+      <c r="G528" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="529" spans="1:7" x14ac:dyDescent="0.35">
@@ -14741,13 +14756,13 @@
         <v>2.48</v>
       </c>
       <c r="D529" s="2">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="F529" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G529" s="5">
-        <v>0.05</v>
+      <c r="G529" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="530" spans="1:7" x14ac:dyDescent="0.35">
@@ -14758,16 +14773,16 @@
         <v>538</v>
       </c>
       <c r="C530" s="2">
-        <v>6.4</v>
+        <v>6.24</v>
       </c>
       <c r="D530" s="2">
-        <v>5.2</v>
+        <v>5.46</v>
       </c>
       <c r="F530" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G530" s="5">
-        <v>0.05</v>
+      <c r="G530" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="531" spans="1:7" x14ac:dyDescent="0.35">
@@ -14778,16 +14793,16 @@
         <v>539</v>
       </c>
       <c r="C531" s="2">
-        <v>6.4</v>
+        <v>6.24</v>
       </c>
       <c r="D531" s="2">
-        <v>5.2</v>
+        <v>5.46</v>
       </c>
       <c r="F531" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G531" s="5">
-        <v>0.05</v>
+      <c r="G531" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="532" spans="1:7" x14ac:dyDescent="0.35">
@@ -14806,8 +14821,8 @@
       <c r="F532" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G532" s="5">
-        <v>0.05</v>
+      <c r="G532" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="533" spans="1:7" x14ac:dyDescent="0.35">
@@ -14826,8 +14841,8 @@
       <c r="F533" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G533" s="5">
-        <v>0.05</v>
+      <c r="G533" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="534" spans="1:7" x14ac:dyDescent="0.35">
@@ -14844,13 +14859,13 @@
         <v>3.65</v>
       </c>
       <c r="E534">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F534" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G534" s="5">
-        <v>0.05</v>
+      <c r="G534" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="535" spans="1:7" x14ac:dyDescent="0.35">
@@ -14872,8 +14887,8 @@
       <c r="F535" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G535" s="5">
-        <v>0.05</v>
+      <c r="G535" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="536" spans="1:7" x14ac:dyDescent="0.35">
@@ -14895,8 +14910,8 @@
       <c r="F536" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G536" s="5">
-        <v>0.05</v>
+      <c r="G536" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="537" spans="1:7" x14ac:dyDescent="0.35">
@@ -14918,8 +14933,8 @@
       <c r="F537" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G537" s="5">
-        <v>0.05</v>
+      <c r="G537" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="538" spans="1:7" x14ac:dyDescent="0.35">
@@ -14941,8 +14956,8 @@
       <c r="F538" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G538" s="5">
-        <v>0.05</v>
+      <c r="G538" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="539" spans="1:7" x14ac:dyDescent="0.35">
@@ -14964,8 +14979,8 @@
       <c r="F539" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G539" s="5">
-        <v>0.05</v>
+      <c r="G539" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="540" spans="1:7" x14ac:dyDescent="0.35">
@@ -14987,8 +15002,8 @@
       <c r="F540" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G540" s="5">
-        <v>0.05</v>
+      <c r="G540" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="541" spans="1:7" x14ac:dyDescent="0.35">
@@ -15010,8 +15025,8 @@
       <c r="F541" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G541" s="5">
-        <v>0.05</v>
+      <c r="G541" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="542" spans="1:7" x14ac:dyDescent="0.35">
@@ -15033,8 +15048,8 @@
       <c r="F542" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G542" s="5">
-        <v>0.05</v>
+      <c r="G542" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="543" spans="1:7" x14ac:dyDescent="0.35">
@@ -15056,8 +15071,8 @@
       <c r="F543" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G543" s="5">
-        <v>0.05</v>
+      <c r="G543" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="544" spans="1:7" x14ac:dyDescent="0.35">
@@ -15079,8 +15094,8 @@
       <c r="F544" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G544" s="5">
-        <v>0.05</v>
+      <c r="G544" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="545" spans="1:7" x14ac:dyDescent="0.35">
@@ -15102,8 +15117,8 @@
       <c r="F545" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G545" s="5">
-        <v>0.05</v>
+      <c r="G545" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="546" spans="1:7" x14ac:dyDescent="0.35">
@@ -15122,8 +15137,8 @@
       <c r="F546" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G546" s="5">
-        <v>0.05</v>
+      <c r="G546" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="547" spans="1:7" x14ac:dyDescent="0.35">
@@ -15142,8 +15157,8 @@
       <c r="F547" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G547" s="5">
-        <v>0.05</v>
+      <c r="G547" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="548" spans="1:7" x14ac:dyDescent="0.35">
@@ -15162,8 +15177,8 @@
       <c r="F548" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G548" s="5">
-        <v>0.05</v>
+      <c r="G548" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="549" spans="1:7" x14ac:dyDescent="0.35">
@@ -15174,10 +15189,10 @@
         <v>557</v>
       </c>
       <c r="C549" s="2">
-        <v>2.94</v>
+        <v>3.5649999999999999</v>
       </c>
       <c r="D549" s="2">
-        <v>2.65</v>
+        <v>3.12</v>
       </c>
       <c r="E549">
         <v>10</v>
@@ -15185,7 +15200,7 @@
       <c r="F549" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G549" s="6">
+      <c r="G549" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15197,10 +15212,10 @@
         <v>559</v>
       </c>
       <c r="C550" s="2">
-        <v>4.13</v>
+        <v>5.22</v>
       </c>
       <c r="D550" s="2">
-        <v>3.72</v>
+        <v>4.57</v>
       </c>
       <c r="E550">
         <v>10</v>
@@ -15208,7 +15223,7 @@
       <c r="F550" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G550" s="6">
+      <c r="G550" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15220,10 +15235,10 @@
         <v>560</v>
       </c>
       <c r="C551" s="2">
-        <v>4.96</v>
+        <v>7.0380000000000003</v>
       </c>
       <c r="D551" s="2">
-        <v>4.46</v>
+        <v>6.16</v>
       </c>
       <c r="E551">
         <v>10</v>
@@ -15231,7 +15246,7 @@
       <c r="F551" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G551" s="6">
+      <c r="G551" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15243,10 +15258,10 @@
         <v>561</v>
       </c>
       <c r="C552" s="2">
-        <v>5.28</v>
+        <v>13.06</v>
       </c>
       <c r="D552" s="2">
-        <v>4.75</v>
+        <v>11.42</v>
       </c>
       <c r="E552">
         <v>5</v>
@@ -15254,7 +15269,7 @@
       <c r="F552" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G552" s="6">
+      <c r="G552" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15266,10 +15281,10 @@
         <v>562</v>
       </c>
       <c r="C553" s="2">
-        <v>16</v>
+        <v>26.6</v>
       </c>
       <c r="D553" s="2">
-        <v>14.4</v>
+        <v>23.28</v>
       </c>
       <c r="E553">
         <v>5</v>
@@ -15277,7 +15292,7 @@
       <c r="F553" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G553" s="6">
+      <c r="G553" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15289,10 +15304,10 @@
         <v>563</v>
       </c>
       <c r="C554" s="2">
-        <v>20</v>
+        <v>24.18</v>
       </c>
       <c r="D554" s="2">
-        <v>18</v>
+        <v>21.16</v>
       </c>
       <c r="E554">
         <v>2.5</v>
@@ -15300,7 +15315,7 @@
       <c r="F554" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G554" s="6">
+      <c r="G554" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15312,10 +15327,10 @@
         <v>564</v>
       </c>
       <c r="C555" s="2">
-        <v>23.36</v>
+        <v>40.03</v>
       </c>
       <c r="D555" s="2">
-        <v>21.02</v>
+        <v>35.020000000000003</v>
       </c>
       <c r="E555">
         <v>2</v>
@@ -15323,7 +15338,7 @@
       <c r="F555" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G555" s="6">
+      <c r="G555" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15335,10 +15350,10 @@
         <v>565</v>
       </c>
       <c r="C556" s="2">
-        <v>35.92</v>
+        <v>42.74</v>
       </c>
       <c r="D556" s="2">
-        <v>32.33</v>
+        <v>37.4</v>
       </c>
       <c r="E556">
         <v>1</v>
@@ -15346,7 +15361,7 @@
       <c r="F556" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G556" s="6">
+      <c r="G556" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15358,10 +15373,10 @@
         <v>566</v>
       </c>
       <c r="C557" s="2">
-        <v>61.25</v>
+        <v>71.48</v>
       </c>
       <c r="D557" s="2">
-        <v>55.13</v>
+        <v>62.54</v>
       </c>
       <c r="E557">
         <v>1</v>
@@ -15369,7 +15384,7 @@
       <c r="F557" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G557" s="6">
+      <c r="G557" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15381,10 +15396,10 @@
         <v>567</v>
       </c>
       <c r="C558" s="2">
-        <v>94.03</v>
+        <v>172.02</v>
       </c>
       <c r="D558" s="2">
-        <v>84.63</v>
+        <v>150.51</v>
       </c>
       <c r="E558">
         <v>0.5</v>
@@ -15392,7 +15407,7 @@
       <c r="F558" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G558" s="6">
+      <c r="G558" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15404,10 +15419,10 @@
         <v>568</v>
       </c>
       <c r="C559" s="2">
-        <v>123.15</v>
+        <v>166.87</v>
       </c>
       <c r="D559" s="2">
-        <v>110.84</v>
+        <v>146</v>
       </c>
       <c r="E559">
         <v>0.25</v>
@@ -15415,7 +15430,7 @@
       <c r="F559" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G559" s="6">
+      <c r="G559" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15427,15 +15442,15 @@
         <v>569</v>
       </c>
       <c r="C560" s="2">
-        <v>191.15</v>
+        <v>261.10000000000002</v>
       </c>
       <c r="D560" s="2">
-        <v>172.04</v>
+        <v>228.46</v>
       </c>
       <c r="F560" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G560" s="6">
+      <c r="G560" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15447,15 +15462,15 @@
         <v>570</v>
       </c>
       <c r="C561" s="2">
-        <v>305.86</v>
+        <v>455.35</v>
       </c>
       <c r="D561" s="2">
-        <v>275.27</v>
+        <v>398.43</v>
       </c>
       <c r="F561" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G561" s="6">
+      <c r="G561" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15467,15 +15482,15 @@
         <v>571</v>
       </c>
       <c r="C562" s="2">
-        <v>841.14</v>
+        <v>839.44</v>
       </c>
       <c r="D562" s="2">
-        <v>757.03</v>
+        <v>734.51</v>
       </c>
       <c r="F562" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G562" s="6">
+      <c r="G562" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15487,10 +15502,10 @@
         <v>572</v>
       </c>
       <c r="C563" s="2">
-        <v>3.49</v>
+        <v>6.07</v>
       </c>
       <c r="D563" s="2">
-        <v>3.14</v>
+        <v>5.31</v>
       </c>
       <c r="E563">
         <v>10</v>
@@ -15498,7 +15513,7 @@
       <c r="F563" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G563" s="6">
+      <c r="G563" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15510,10 +15525,10 @@
         <v>573</v>
       </c>
       <c r="C564" s="2">
-        <v>4.88</v>
+        <v>9.73</v>
       </c>
       <c r="D564" s="2">
-        <v>4.3899999999999997</v>
+        <v>8.51</v>
       </c>
       <c r="E564">
         <v>10</v>
@@ -15521,7 +15536,7 @@
       <c r="F564" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G564" s="6">
+      <c r="G564" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15533,10 +15548,10 @@
         <v>574</v>
       </c>
       <c r="C565" s="2">
-        <v>5.76</v>
+        <v>12.06</v>
       </c>
       <c r="D565" s="2">
-        <v>5.18</v>
+        <v>10.55</v>
       </c>
       <c r="E565">
         <v>10</v>
@@ -15544,7 +15559,7 @@
       <c r="F565" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G565" s="6">
+      <c r="G565" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15556,10 +15571,10 @@
         <v>575</v>
       </c>
       <c r="C566" s="2">
-        <v>9.34</v>
+        <v>18.03</v>
       </c>
       <c r="D566" s="2">
-        <v>8.41</v>
+        <v>15.78</v>
       </c>
       <c r="E566">
         <v>5</v>
@@ -15567,7 +15582,7 @@
       <c r="F566" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G566" s="6">
+      <c r="G566" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15579,10 +15594,10 @@
         <v>576</v>
       </c>
       <c r="C567" s="2">
-        <v>21.76</v>
+        <v>41.47</v>
       </c>
       <c r="D567" s="2">
-        <v>19.579999999999998</v>
+        <v>36.28</v>
       </c>
       <c r="E567">
         <v>5</v>
@@ -15590,7 +15605,7 @@
       <c r="F567" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G567" s="6">
+      <c r="G567" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15602,10 +15617,10 @@
         <v>577</v>
       </c>
       <c r="C568" s="2">
-        <v>37.5</v>
+        <v>64.7</v>
       </c>
       <c r="D568" s="2">
-        <v>33.75</v>
+        <v>56.61</v>
       </c>
       <c r="E568">
         <v>2.5</v>
@@ -15613,7 +15628,7 @@
       <c r="F568" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G568" s="6">
+      <c r="G568" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15625,10 +15640,10 @@
         <v>578</v>
       </c>
       <c r="C569" s="2">
-        <v>41.39</v>
+        <v>59.33</v>
       </c>
       <c r="D569" s="2">
-        <v>37.25</v>
+        <v>51.92</v>
       </c>
       <c r="E569">
         <v>2</v>
@@ -15636,7 +15651,7 @@
       <c r="F569" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G569" s="6">
+      <c r="G569" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15648,10 +15663,10 @@
         <v>579</v>
       </c>
       <c r="C570" s="2">
-        <v>51.07</v>
+        <v>75.91</v>
       </c>
       <c r="D570" s="2">
-        <v>45.96</v>
+        <v>66.430000000000007</v>
       </c>
       <c r="E570">
         <v>1</v>
@@ -15659,7 +15674,7 @@
       <c r="F570" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G570" s="6">
+      <c r="G570" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15671,10 +15686,10 @@
         <v>580</v>
       </c>
       <c r="C571" s="2">
-        <v>66.67</v>
+        <v>102.29</v>
       </c>
       <c r="D571" s="2">
-        <v>60</v>
+        <v>89.52</v>
       </c>
       <c r="E571">
         <v>1</v>
@@ -15682,7 +15697,7 @@
       <c r="F571" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G571" s="6">
+      <c r="G571" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15694,10 +15709,10 @@
         <v>581</v>
       </c>
       <c r="C572" s="2">
-        <v>85.73</v>
+        <v>159.88</v>
       </c>
       <c r="D572" s="2">
-        <v>77.16</v>
+        <v>139.88999999999999</v>
       </c>
       <c r="E572">
         <v>0.5</v>
@@ -15705,7 +15720,7 @@
       <c r="F572" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G572" s="6">
+      <c r="G572" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15717,10 +15732,10 @@
         <v>582</v>
       </c>
       <c r="C573" s="2">
-        <v>109.1</v>
+        <v>161.94999999999999</v>
       </c>
       <c r="D573" s="2">
-        <v>98.19</v>
+        <v>141.69999999999999</v>
       </c>
       <c r="E573">
         <v>0.25</v>
@@ -15728,7 +15743,7 @@
       <c r="F573" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G573" s="6">
+      <c r="G573" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15748,7 +15763,7 @@
       <c r="F574" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G574" s="6">
+      <c r="G574" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15760,15 +15775,15 @@
         <v>584</v>
       </c>
       <c r="C575" s="2">
-        <v>159.9</v>
+        <v>1225.31</v>
       </c>
       <c r="D575" s="2">
-        <v>143.91</v>
+        <v>1072.1500000000001</v>
       </c>
       <c r="F575" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G575" s="6">
+      <c r="G575" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15780,15 +15795,15 @@
         <v>585</v>
       </c>
       <c r="C576" s="2">
-        <v>205.6</v>
+        <v>1518.66</v>
       </c>
       <c r="D576" s="2">
-        <v>185.04</v>
+        <v>1328.83</v>
       </c>
       <c r="F576" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G576" s="6">
+      <c r="G576" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15800,10 +15815,10 @@
         <v>586</v>
       </c>
       <c r="C577" s="2">
-        <v>12.16</v>
+        <v>11.52</v>
       </c>
       <c r="D577" s="2">
-        <v>10.94</v>
+        <v>10.08</v>
       </c>
       <c r="E577">
         <v>250</v>
@@ -15811,7 +15826,7 @@
       <c r="F577" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G577" s="6">
+      <c r="G577" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15823,10 +15838,10 @@
         <v>587</v>
       </c>
       <c r="C578" s="2">
-        <v>13.04</v>
+        <v>12.16</v>
       </c>
       <c r="D578" s="2">
-        <v>11.74</v>
+        <v>10.64</v>
       </c>
       <c r="E578">
         <v>250</v>
@@ -15834,7 +15849,7 @@
       <c r="F578" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G578" s="6">
+      <c r="G578" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15846,10 +15861,10 @@
         <v>588</v>
       </c>
       <c r="C579" s="2">
-        <v>14.08</v>
+        <v>13.12</v>
       </c>
       <c r="D579" s="2">
-        <v>12.67</v>
+        <v>11.48</v>
       </c>
       <c r="E579">
         <v>50</v>
@@ -15857,7 +15872,7 @@
       <c r="F579" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G579" s="6">
+      <c r="G579" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15869,10 +15884,10 @@
         <v>589</v>
       </c>
       <c r="C580" s="2">
-        <v>20.64</v>
+        <v>20.48</v>
       </c>
       <c r="D580" s="2">
-        <v>18.579999999999998</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="E580">
         <v>50</v>
@@ -15880,7 +15895,7 @@
       <c r="F580" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G580" s="6">
+      <c r="G580" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15892,10 +15907,10 @@
         <v>590</v>
       </c>
       <c r="C581" s="2">
-        <v>23.68</v>
+        <v>23.84</v>
       </c>
       <c r="D581" s="2">
-        <v>21.31</v>
+        <v>20.86</v>
       </c>
       <c r="E581">
         <v>25</v>
@@ -15903,7 +15918,7 @@
       <c r="F581" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G581" s="6">
+      <c r="G581" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15915,10 +15930,10 @@
         <v>591</v>
       </c>
       <c r="C582" s="2">
-        <v>32.159999999999997</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="D582" s="2">
-        <v>28.94</v>
+        <v>28.7</v>
       </c>
       <c r="E582">
         <v>50</v>
@@ -15926,7 +15941,7 @@
       <c r="F582" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G582" s="6">
+      <c r="G582" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15938,10 +15953,10 @@
         <v>592</v>
       </c>
       <c r="C583" s="2">
-        <v>37.44</v>
+        <v>34.4</v>
       </c>
       <c r="D583" s="2">
-        <v>33.700000000000003</v>
+        <v>30.1</v>
       </c>
       <c r="E583">
         <v>25</v>
@@ -15949,7 +15964,7 @@
       <c r="F583" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G583" s="6">
+      <c r="G583" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15961,10 +15976,10 @@
         <v>593</v>
       </c>
       <c r="C584" s="2">
-        <v>12.16</v>
+        <v>11.52</v>
       </c>
       <c r="D584" s="2">
-        <v>10.94</v>
+        <v>10.08</v>
       </c>
       <c r="E584">
         <v>250</v>
@@ -15972,7 +15987,7 @@
       <c r="F584" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G584" s="6">
+      <c r="G584" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15984,10 +15999,10 @@
         <v>594</v>
       </c>
       <c r="C585" s="2">
-        <v>13.04</v>
+        <v>12.16</v>
       </c>
       <c r="D585" s="2">
-        <v>11.74</v>
+        <v>10.64</v>
       </c>
       <c r="E585">
         <v>250</v>
@@ -15995,7 +16010,7 @@
       <c r="F585" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G585" s="6">
+      <c r="G585" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16007,10 +16022,10 @@
         <v>595</v>
       </c>
       <c r="C586" s="2">
-        <v>14.08</v>
+        <v>13.12</v>
       </c>
       <c r="D586" s="2">
-        <v>12.67</v>
+        <v>11.4</v>
       </c>
       <c r="E586">
         <v>50</v>
@@ -16018,7 +16033,7 @@
       <c r="F586" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G586" s="6">
+      <c r="G586" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16030,10 +16045,10 @@
         <v>596</v>
       </c>
       <c r="C587" s="2">
-        <v>20.64</v>
+        <v>20.48</v>
       </c>
       <c r="D587" s="2">
-        <v>18.579999999999998</v>
+        <v>17.920000000000002</v>
       </c>
       <c r="E587">
         <v>50</v>
@@ -16041,7 +16056,7 @@
       <c r="F587" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G587" s="6">
+      <c r="G587" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16053,10 +16068,10 @@
         <v>597</v>
       </c>
       <c r="C588" s="2">
-        <v>23.68</v>
+        <v>23.84</v>
       </c>
       <c r="D588" s="2">
-        <v>21.31</v>
+        <v>20.86</v>
       </c>
       <c r="E588">
         <v>25</v>
@@ -16064,7 +16079,7 @@
       <c r="F588" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G588" s="6">
+      <c r="G588" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16076,10 +16091,10 @@
         <v>598</v>
       </c>
       <c r="C589" s="2">
-        <v>32.159999999999997</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="D589" s="2">
-        <v>28.94</v>
+        <v>28.7</v>
       </c>
       <c r="E589">
         <v>50</v>
@@ -16087,7 +16102,7 @@
       <c r="F589" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G589" s="6">
+      <c r="G589" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16099,10 +16114,10 @@
         <v>599</v>
       </c>
       <c r="C590" s="2">
-        <v>37.44</v>
+        <v>34.4</v>
       </c>
       <c r="D590" s="2">
-        <v>33.700000000000003</v>
+        <v>30.1</v>
       </c>
       <c r="E590">
         <v>25</v>
@@ -16110,7 +16125,7 @@
       <c r="F590" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G590" s="6">
+      <c r="G590" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16122,15 +16137,15 @@
         <v>600</v>
       </c>
       <c r="C591" s="2">
-        <v>0.84</v>
+        <v>1.28</v>
       </c>
       <c r="D591" s="2">
-        <v>0.76</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="F591" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="G591" s="6">
+      <c r="G591" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16142,15 +16157,15 @@
         <v>602</v>
       </c>
       <c r="C592" s="2">
-        <v>1.36</v>
+        <v>1.92</v>
       </c>
       <c r="D592" s="2">
-        <v>1.22</v>
+        <v>1.68</v>
       </c>
       <c r="F592" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="G592" s="6">
+      <c r="G592" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16162,15 +16177,15 @@
         <v>603</v>
       </c>
       <c r="C593" s="2">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="D593" s="2">
-        <v>1.49</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="F593" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="G593" s="6">
+      <c r="G593" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16182,10 +16197,10 @@
         <v>604</v>
       </c>
       <c r="C594" s="2">
-        <v>5.21</v>
+        <v>5.89</v>
       </c>
       <c r="D594" s="2">
-        <v>4.6900000000000004</v>
+        <v>5.15</v>
       </c>
       <c r="E594">
         <v>250</v>
@@ -16193,7 +16208,7 @@
       <c r="F594" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="G594" s="6">
+      <c r="G594" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16216,7 +16231,7 @@
       <c r="F595" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="G595" s="6">
+      <c r="G595" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16228,15 +16243,15 @@
         <v>606</v>
       </c>
       <c r="C596" s="2">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
       <c r="D596" s="2">
-        <v>0.43</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="F596" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="G596" s="6">
+      <c r="G596" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16248,15 +16263,15 @@
         <v>607</v>
       </c>
       <c r="C597" s="2">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="D597" s="2">
-        <v>0.72</v>
+        <v>0.86</v>
       </c>
       <c r="F597" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="G597" s="6">
+      <c r="G597" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16268,15 +16283,15 @@
         <v>608</v>
       </c>
       <c r="C598" s="2">
-        <v>0.75</v>
+        <v>1.27</v>
       </c>
       <c r="D598" s="2">
-        <v>0.68</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="F598" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="G598" s="6">
+      <c r="G598" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16288,15 +16303,15 @@
         <v>609</v>
       </c>
       <c r="C599" s="2">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="D599" s="2">
-        <v>2.59</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="F599" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="G599" s="6">
+      <c r="G599" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16308,15 +16323,15 @@
         <v>610</v>
       </c>
       <c r="C600" s="2">
-        <v>6.88</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="D600" s="2">
-        <v>6.19</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="F600" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="G600" s="6">
+      <c r="G600" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16328,16 +16343,16 @@
         <v>611</v>
       </c>
       <c r="C601" s="2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="D601" s="2">
-        <v>0.96</v>
+        <v>0.94</v>
       </c>
       <c r="F601" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G601" s="5">
-        <v>0.05</v>
+      <c r="G601" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="602" spans="1:7" x14ac:dyDescent="0.35">
@@ -16351,12 +16366,12 @@
         <v>1.44</v>
       </c>
       <c r="D602" s="2">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="F602" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G602" s="6">
+      <c r="G602" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16371,13 +16386,13 @@
         <v>1.44</v>
       </c>
       <c r="D603" s="2">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="F603" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G603" s="5">
-        <v>0.05</v>
+      <c r="G603" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="604" spans="1:7" x14ac:dyDescent="0.35">
@@ -16388,16 +16403,16 @@
         <v>614</v>
       </c>
       <c r="C604" s="2">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="D604" s="2">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="F604" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G604" s="5">
-        <v>0.05</v>
+      <c r="G604" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="605" spans="1:7" x14ac:dyDescent="0.35">
@@ -16411,13 +16426,13 @@
         <v>1.04</v>
       </c>
       <c r="D605" s="2">
-        <v>0.94</v>
+        <v>0.91</v>
       </c>
       <c r="F605" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G605" s="5">
-        <v>0.05</v>
+      <c r="G605" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="606" spans="1:7" x14ac:dyDescent="0.35">
@@ -16431,13 +16446,13 @@
         <v>1.04</v>
       </c>
       <c r="D606" s="2">
-        <v>0.94</v>
+        <v>0.91</v>
       </c>
       <c r="F606" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G606" s="5">
-        <v>0.05</v>
+      <c r="G606" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="607" spans="1:7" x14ac:dyDescent="0.35">
@@ -16448,16 +16463,16 @@
         <v>617</v>
       </c>
       <c r="C607" s="2">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="D607" s="2">
-        <v>0.7</v>
+        <v>0.69</v>
       </c>
       <c r="F607" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G607" s="5">
-        <v>0.05</v>
+      <c r="G607" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="608" spans="1:7" x14ac:dyDescent="0.35">
@@ -16471,13 +16486,13 @@
         <v>1.46</v>
       </c>
       <c r="D608" s="2">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="F608" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G608" s="5">
-        <v>0.05</v>
+      <c r="G608" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="609" spans="1:7" x14ac:dyDescent="0.35">
@@ -16491,12 +16506,12 @@
         <v>1.46</v>
       </c>
       <c r="D609" s="2">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="F609" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G609" s="6">
+      <c r="G609" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16508,10 +16523,10 @@
         <v>620</v>
       </c>
       <c r="C610" s="2">
-        <v>15.42</v>
+        <v>18.739999999999998</v>
       </c>
       <c r="D610" s="2">
-        <v>13.88</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="E610">
         <v>25</v>
@@ -16519,7 +16534,7 @@
       <c r="F610" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="G610" s="6">
+      <c r="G610" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16542,7 +16557,7 @@
       <c r="F611" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="G611" s="6">
+      <c r="G611" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16565,7 +16580,7 @@
       <c r="F612" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="G612" s="6">
+      <c r="G612" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16588,7 +16603,7 @@
       <c r="F613" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="G613" s="6">
+      <c r="G613" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16608,7 +16623,7 @@
       <c r="F614" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="G614" s="6">
+      <c r="G614" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16631,7 +16646,7 @@
       <c r="F615" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G615" s="6">
+      <c r="G615" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16654,7 +16669,7 @@
       <c r="F616" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="G616" s="6">
+      <c r="G616" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16677,7 +16692,7 @@
       <c r="F617" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="G617" s="6">
+      <c r="G617" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16697,7 +16712,7 @@
       <c r="F618" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="G618" s="6">
+      <c r="G618" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16709,10 +16724,10 @@
         <v>630</v>
       </c>
       <c r="C619" s="2">
-        <v>14.83</v>
+        <v>18.5</v>
       </c>
       <c r="D619" s="2">
-        <v>13.35</v>
+        <v>16.190000000000001</v>
       </c>
       <c r="E619">
         <v>250</v>
@@ -16720,7 +16735,7 @@
       <c r="F619" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G619" s="6">
+      <c r="G619" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16732,10 +16747,10 @@
         <v>631</v>
       </c>
       <c r="C620" s="2">
-        <v>19.52</v>
+        <v>20.74</v>
       </c>
       <c r="D620" s="2">
-        <v>17.57</v>
+        <v>18.149999999999999</v>
       </c>
       <c r="E620">
         <v>250</v>
@@ -16743,7 +16758,7 @@
       <c r="F620" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G620" s="6">
+      <c r="G620" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16755,15 +16770,15 @@
         <v>632</v>
       </c>
       <c r="C621" s="2">
-        <v>24.38</v>
+        <v>25.94</v>
       </c>
       <c r="D621" s="2">
-        <v>21.94</v>
+        <v>22.7</v>
       </c>
       <c r="F621" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G621" s="6">
+      <c r="G621" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16775,10 +16790,10 @@
         <v>633</v>
       </c>
       <c r="C622" s="2">
-        <v>24.38</v>
+        <v>25.96</v>
       </c>
       <c r="D622" s="2">
-        <v>21.94</v>
+        <v>22.68</v>
       </c>
       <c r="E622">
         <v>50</v>
@@ -16786,7 +16801,7 @@
       <c r="F622" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G622" s="6">
+      <c r="G622" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16798,10 +16813,10 @@
         <v>634</v>
       </c>
       <c r="C623" s="2">
-        <v>31.22</v>
+        <v>33.19</v>
       </c>
       <c r="D623" s="2">
-        <v>28.1</v>
+        <v>29.04</v>
       </c>
       <c r="E623">
         <v>50</v>
@@ -16809,7 +16824,7 @@
       <c r="F623" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G623" s="6">
+      <c r="G623" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16821,15 +16836,15 @@
         <v>635</v>
       </c>
       <c r="C624" s="2">
-        <v>39.020000000000003</v>
+        <v>41.49</v>
       </c>
       <c r="D624" s="2">
-        <v>35.119999999999997</v>
+        <v>36.31</v>
       </c>
       <c r="F624" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G624" s="6">
+      <c r="G624" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16841,15 +16856,15 @@
         <v>636</v>
       </c>
       <c r="C625" s="2">
-        <v>42.93</v>
+        <v>49.8</v>
       </c>
       <c r="D625" s="2">
-        <v>38.64</v>
+        <v>43.57</v>
       </c>
       <c r="F625" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G625" s="6">
+      <c r="G625" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16861,10 +16876,10 @@
         <v>637</v>
       </c>
       <c r="C626" s="2">
-        <v>36.1</v>
+        <v>38.39</v>
       </c>
       <c r="D626" s="2">
-        <v>32.49</v>
+        <v>33.58</v>
       </c>
       <c r="E626">
         <v>50</v>
@@ -16872,7 +16887,7 @@
       <c r="F626" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G626" s="6">
+      <c r="G626" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16884,10 +16899,10 @@
         <v>638</v>
       </c>
       <c r="C627" s="2">
-        <v>46.83</v>
+        <v>49.8</v>
       </c>
       <c r="D627" s="2">
-        <v>42.15</v>
+        <v>46.57</v>
       </c>
       <c r="E627">
         <v>50</v>
@@ -16895,7 +16910,7 @@
       <c r="F627" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G627" s="6">
+      <c r="G627" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16907,15 +16922,15 @@
         <v>639</v>
       </c>
       <c r="C628" s="2">
-        <v>57.57</v>
+        <v>61.2</v>
       </c>
       <c r="D628" s="2">
-        <v>51.81</v>
+        <v>53.55</v>
       </c>
       <c r="F628" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G628" s="6">
+      <c r="G628" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16927,15 +16942,15 @@
         <v>640</v>
       </c>
       <c r="C629" s="2">
-        <v>68.290000000000006</v>
+        <v>72.61</v>
       </c>
       <c r="D629" s="2">
-        <v>61.46</v>
+        <v>63.54</v>
       </c>
       <c r="F629" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G629" s="6">
+      <c r="G629" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16947,10 +16962,10 @@
         <v>641</v>
       </c>
       <c r="C630" s="2">
-        <v>147.13999999999999</v>
+        <v>156.41999999999999</v>
       </c>
       <c r="D630" s="2">
-        <v>132.43</v>
+        <v>136.87</v>
       </c>
       <c r="E630">
         <v>250</v>
@@ -16958,7 +16973,7 @@
       <c r="F630" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G630" s="6">
+      <c r="G630" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16970,10 +16985,10 @@
         <v>642</v>
       </c>
       <c r="C631" s="2">
-        <v>273.52</v>
+        <v>290.79000000000002</v>
       </c>
       <c r="D631" s="2">
-        <v>246.17</v>
+        <v>254.44</v>
       </c>
       <c r="E631">
         <v>5</v>
@@ -16981,7 +16996,7 @@
       <c r="F631" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G631" s="6">
+      <c r="G631" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -16993,10 +17008,10 @@
         <v>643</v>
       </c>
       <c r="C632" s="2">
-        <v>424.42</v>
+        <v>451.22</v>
       </c>
       <c r="D632" s="2">
-        <v>381.98</v>
+        <v>394.82</v>
       </c>
       <c r="E632">
         <v>5</v>
@@ -17004,7 +17019,7 @@
       <c r="F632" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G632" s="6">
+      <c r="G632" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -17016,15 +17031,15 @@
         <v>644</v>
       </c>
       <c r="C633" s="2">
-        <v>682.9</v>
+        <v>834.84</v>
       </c>
       <c r="D633" s="2">
-        <v>614.61</v>
+        <v>730.48</v>
       </c>
       <c r="F633" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G633" s="6">
+      <c r="G633" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -17036,16 +17051,19 @@
         <v>645</v>
       </c>
       <c r="C634" s="2">
-        <v>23.54</v>
+        <v>17.760000000000002</v>
       </c>
       <c r="D634" s="2">
-        <v>21.19</v>
+        <v>15.54</v>
+      </c>
+      <c r="E634">
+        <v>20</v>
       </c>
       <c r="F634" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G634" s="5">
-        <v>0.05</v>
+      <c r="G634" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="635" spans="1:7" x14ac:dyDescent="0.35">
@@ -17056,16 +17074,19 @@
         <v>646</v>
       </c>
       <c r="C635" s="2">
-        <v>23.02</v>
+        <v>22.8</v>
       </c>
       <c r="D635" s="2">
-        <v>20.72</v>
+        <v>19.95</v>
+      </c>
+      <c r="E635">
+        <v>10</v>
       </c>
       <c r="F635" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G635" s="5">
-        <v>0.05</v>
+      <c r="G635" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="636" spans="1:7" x14ac:dyDescent="0.35">
@@ -17076,16 +17097,19 @@
         <v>647</v>
       </c>
       <c r="C636" s="2">
-        <v>33.020000000000003</v>
+        <v>26.91</v>
       </c>
       <c r="D636" s="2">
-        <v>29.72</v>
+        <v>23.55</v>
+      </c>
+      <c r="E636">
+        <v>5</v>
       </c>
       <c r="F636" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G636" s="5">
-        <v>0.05</v>
+      <c r="G636" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="637" spans="1:7" x14ac:dyDescent="0.35">
@@ -17096,16 +17120,19 @@
         <v>648</v>
       </c>
       <c r="C637" s="2">
-        <v>48.02</v>
+        <v>38.93</v>
       </c>
       <c r="D637" s="2">
-        <v>43.22</v>
+        <v>34.06</v>
+      </c>
+      <c r="E637">
+        <v>5</v>
       </c>
       <c r="F637" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G637" s="5">
-        <v>0.05</v>
+      <c r="G637" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="638" spans="1:7" x14ac:dyDescent="0.35">
@@ -17116,16 +17143,19 @@
         <v>649</v>
       </c>
       <c r="C638" s="2">
-        <v>114.72</v>
+        <v>91.6</v>
       </c>
       <c r="D638" s="2">
-        <v>103.25</v>
+        <v>80.150000000000006</v>
+      </c>
+      <c r="E638">
+        <v>2</v>
       </c>
       <c r="F638" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G638" s="5">
-        <v>0.05</v>
+      <c r="G638" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="639" spans="1:7" x14ac:dyDescent="0.35">
@@ -17136,16 +17166,19 @@
         <v>650</v>
       </c>
       <c r="C639" s="2">
-        <v>114.72</v>
+        <v>91.6</v>
       </c>
       <c r="D639" s="2">
-        <v>103.25</v>
+        <v>80.150000000000006</v>
+      </c>
+      <c r="E639">
+        <v>2</v>
       </c>
       <c r="F639" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G639" s="5">
-        <v>0.05</v>
+      <c r="G639" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="640" spans="1:7" x14ac:dyDescent="0.35">
@@ -17156,16 +17189,19 @@
         <v>651</v>
       </c>
       <c r="C640" s="2">
-        <v>194.08</v>
+        <v>156.94999999999999</v>
       </c>
       <c r="D640" s="2">
-        <v>174.67</v>
+        <v>137.33000000000001</v>
+      </c>
+      <c r="E640">
+        <v>2</v>
       </c>
       <c r="F640" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G640" s="5">
-        <v>0.05</v>
+      <c r="G640" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="641" spans="1:7" x14ac:dyDescent="0.35">
@@ -17176,16 +17212,16 @@
         <v>652</v>
       </c>
       <c r="C641" s="2">
-        <v>215.25</v>
+        <v>186.05</v>
       </c>
       <c r="D641" s="2">
-        <v>193.73</v>
+        <v>162.79</v>
       </c>
       <c r="F641" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G641" s="5">
-        <v>0.05</v>
+      <c r="G641" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="642" spans="1:7" x14ac:dyDescent="0.35">
@@ -17196,16 +17232,16 @@
         <v>653</v>
       </c>
       <c r="C642" s="2">
-        <v>368.96</v>
+        <v>347.61</v>
       </c>
       <c r="D642" s="2">
-        <v>332.06</v>
+        <v>304.16000000000003</v>
       </c>
       <c r="F642" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G642" s="5">
-        <v>0.05</v>
+      <c r="G642" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="643" spans="1:7" x14ac:dyDescent="0.35">
@@ -17216,16 +17252,16 @@
         <v>654</v>
       </c>
       <c r="C643" s="2">
-        <v>598.88</v>
+        <v>588.88</v>
       </c>
       <c r="D643" s="2">
-        <v>538.99</v>
+        <v>489.02</v>
       </c>
       <c r="F643" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G643" s="5">
-        <v>0.05</v>
+      <c r="G643" s="4">
+        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="644" spans="1:7" x14ac:dyDescent="0.35">
@@ -17236,15 +17272,15 @@
         <v>655</v>
       </c>
       <c r="C644" s="2">
-        <v>8.16</v>
+        <v>7.2</v>
       </c>
       <c r="D644" s="2">
-        <v>7.34</v>
+        <v>6.3</v>
       </c>
       <c r="F644" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G644" s="6">
+      <c r="G644" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -17256,15 +17292,15 @@
         <v>656</v>
       </c>
       <c r="C645" s="2">
-        <v>11.68</v>
+        <v>10.63</v>
       </c>
       <c r="D645" s="2">
-        <v>10.51</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="F645" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G645" s="6">
+      <c r="G645" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -17276,15 +17312,15 @@
         <v>657</v>
       </c>
       <c r="C646" s="2">
-        <v>16</v>
+        <v>14.21</v>
       </c>
       <c r="D646" s="2">
-        <v>14.4</v>
+        <v>12.43</v>
       </c>
       <c r="F646" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G646" s="6">
+      <c r="G646" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -17296,15 +17332,15 @@
         <v>658</v>
       </c>
       <c r="C647" s="2">
-        <v>20.32</v>
+        <v>18.88</v>
       </c>
       <c r="D647" s="2">
-        <v>18.29</v>
+        <v>16.54</v>
       </c>
       <c r="F647" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G647" s="6">
+      <c r="G647" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -17316,15 +17352,15 @@
         <v>659</v>
       </c>
       <c r="C648" s="2">
-        <v>29.28</v>
+        <v>45.62</v>
       </c>
       <c r="D648" s="2">
-        <v>26.35</v>
+        <v>39.92</v>
       </c>
       <c r="F648" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G648" s="6">
+      <c r="G648" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -17336,15 +17372,15 @@
         <v>660</v>
       </c>
       <c r="C649" s="2">
-        <v>79.040000000000006</v>
+        <v>71.38</v>
       </c>
       <c r="D649" s="2">
-        <v>71.14</v>
+        <v>62.46</v>
       </c>
       <c r="F649" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G649" s="6">
+      <c r="G649" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -17356,15 +17392,15 @@
         <v>661</v>
       </c>
       <c r="C650" s="2">
-        <v>124.32</v>
+        <v>116.16</v>
       </c>
       <c r="D650" s="2">
-        <v>111.89</v>
+        <v>101.59</v>
       </c>
       <c r="F650" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G650" s="6">
+      <c r="G650" s="4">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -17376,15 +17412,15 @@
         <v>662</v>
       </c>
       <c r="C651" s="2">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="D651" s="2">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="F651" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G651" s="5">
+      <c r="G651" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17396,15 +17432,15 @@
         <v>663</v>
       </c>
       <c r="C652" s="2">
-        <v>0.57999999999999996</v>
+        <v>0.48</v>
       </c>
       <c r="D652" s="2">
-        <v>0.52</v>
+        <v>0.42</v>
       </c>
       <c r="F652" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G652" s="5">
+      <c r="G652" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17416,15 +17452,15 @@
         <v>664</v>
       </c>
       <c r="C653" s="2">
-        <v>0.63</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="D653" s="2">
-        <v>0.56999999999999995</v>
+        <v>0.51</v>
       </c>
       <c r="F653" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G653" s="5">
+      <c r="G653" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17436,15 +17472,15 @@
         <v>665</v>
       </c>
       <c r="C654" s="2">
-        <v>1.06</v>
+        <v>0.95</v>
       </c>
       <c r="D654" s="2">
-        <v>0.95</v>
+        <v>0.83</v>
       </c>
       <c r="F654" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G654" s="5">
+      <c r="G654" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17456,15 +17492,15 @@
         <v>666</v>
       </c>
       <c r="C655" s="2">
-        <v>1.1599999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="D655" s="2">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
       <c r="F655" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G655" s="5">
+      <c r="G655" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17476,15 +17512,15 @@
         <v>667</v>
       </c>
       <c r="C656" s="2">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="D656" s="2">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="F656" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G656" s="5">
+      <c r="G656" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17496,15 +17532,15 @@
         <v>668</v>
       </c>
       <c r="C657" s="2">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="D657" s="2">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="F657" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G657" s="5">
+      <c r="G657" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17516,15 +17552,15 @@
         <v>669</v>
       </c>
       <c r="C658" s="2">
-        <v>2.52</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="D658" s="2">
-        <v>2.27</v>
+        <v>1.98</v>
       </c>
       <c r="F658" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G658" s="5">
+      <c r="G658" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17536,15 +17572,15 @@
         <v>670</v>
       </c>
       <c r="C659" s="2">
-        <v>3.13</v>
+        <v>2.85</v>
       </c>
       <c r="D659" s="2">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="F659" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G659" s="5">
+      <c r="G659" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17556,15 +17592,15 @@
         <v>671</v>
       </c>
       <c r="C660" s="2">
-        <v>3.61</v>
+        <v>3.22</v>
       </c>
       <c r="D660" s="2">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="F660" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G660" s="5">
+      <c r="G660" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17576,15 +17612,15 @@
         <v>672</v>
       </c>
       <c r="C661" s="2">
-        <v>0.54</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="D661" s="2">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="F661" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G661" s="5">
+      <c r="G661" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17596,15 +17632,15 @@
         <v>673</v>
       </c>
       <c r="C662" s="2">
-        <v>0.59</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="D662" s="2">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="F662" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G662" s="5">
+      <c r="G662" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17619,12 +17655,12 @@
         <v>0.64</v>
       </c>
       <c r="D663" s="2">
-        <v>0.57999999999999996</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F663" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G663" s="5">
+      <c r="G663" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17636,15 +17672,15 @@
         <v>675</v>
       </c>
       <c r="C664" s="2">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="D664" s="2">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="F664" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G664" s="5">
+      <c r="G664" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17659,12 +17695,12 @@
         <v>1.0900000000000001</v>
       </c>
       <c r="D665" s="2">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="F665" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G665" s="5">
+      <c r="G665" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17676,15 +17712,15 @@
         <v>677</v>
       </c>
       <c r="C666" s="2">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="D666" s="2">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="F666" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G666" s="5">
+      <c r="G666" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17696,15 +17732,15 @@
         <v>678</v>
       </c>
       <c r="C667" s="2">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="D667" s="2">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="F667" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G667" s="5">
+      <c r="G667" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17716,15 +17752,15 @@
         <v>679</v>
       </c>
       <c r="C668" s="2">
-        <v>2.64</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="D668" s="2">
-        <v>2.38</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="F668" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G668" s="5">
+      <c r="G668" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17736,15 +17772,15 @@
         <v>680</v>
       </c>
       <c r="C669" s="2">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="D669" s="2">
-        <v>2.4500000000000002</v>
+        <v>2.62</v>
       </c>
       <c r="F669" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G669" s="5">
+      <c r="G669" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17756,15 +17792,15 @@
         <v>681</v>
       </c>
       <c r="C670" s="2">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="D670" s="2">
-        <v>2.59</v>
+        <v>2.87</v>
       </c>
       <c r="F670" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G670" s="5">
+      <c r="G670" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17776,15 +17812,15 @@
         <v>682</v>
       </c>
       <c r="C671" s="2">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="D671" s="2">
-        <v>0.49</v>
+        <v>0.62</v>
       </c>
       <c r="F671" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G671" s="5">
+      <c r="G671" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17796,15 +17832,15 @@
         <v>683</v>
       </c>
       <c r="C672" s="2">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="D672" s="2">
-        <v>0.57999999999999996</v>
+        <v>0.65</v>
       </c>
       <c r="F672" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G672" s="5">
+      <c r="G672" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17816,15 +17852,15 @@
         <v>684</v>
       </c>
       <c r="C673" s="2">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="D673" s="2">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="F673" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G673" s="5">
+      <c r="G673" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17839,12 +17875,12 @@
         <v>1.06</v>
       </c>
       <c r="D674" s="2">
-        <v>0.95</v>
+        <v>0.84</v>
       </c>
       <c r="F674" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G674" s="5">
+      <c r="G674" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17859,12 +17895,12 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="D675" s="2">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="F675" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G675" s="5">
+      <c r="G675" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17876,15 +17912,15 @@
         <v>687</v>
       </c>
       <c r="C676" s="2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="D676" s="2">
-        <v>1.18</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F676" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G676" s="5">
+      <c r="G676" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17899,12 +17935,12 @@
         <v>1.52</v>
       </c>
       <c r="D677" s="2">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="F677" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G677" s="5">
+      <c r="G677" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17916,15 +17952,15 @@
         <v>689</v>
       </c>
       <c r="C678" s="2">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="D678" s="2">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="F678" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G678" s="5">
+      <c r="G678" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17939,12 +17975,12 @@
         <v>2.16</v>
       </c>
       <c r="D679" s="2">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="F679" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G679" s="5">
+      <c r="G679" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17956,15 +17992,15 @@
         <v>691</v>
       </c>
       <c r="C680" s="2">
-        <v>2.35</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="D680" s="2">
-        <v>2.12</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="F680" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G680" s="5">
+      <c r="G680" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17976,15 +18012,15 @@
         <v>692</v>
       </c>
       <c r="C681" s="2">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="D681" s="2">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="F681" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G681" s="5">
+      <c r="G681" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -17996,15 +18032,15 @@
         <v>693</v>
       </c>
       <c r="C682" s="2">
-        <v>4.8600000000000003</v>
+        <v>4.82</v>
       </c>
       <c r="D682" s="2">
-        <v>4.37</v>
+        <v>4.22</v>
       </c>
       <c r="F682" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G682" s="5">
+      <c r="G682" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18016,15 +18052,15 @@
         <v>694</v>
       </c>
       <c r="C683" s="2">
-        <v>8.4499999999999993</v>
+        <v>8.16</v>
       </c>
       <c r="D683" s="2">
-        <v>7.61</v>
+        <v>7.15</v>
       </c>
       <c r="F683" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G683" s="5">
+      <c r="G683" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18036,15 +18072,15 @@
         <v>695</v>
       </c>
       <c r="C684" s="2">
-        <v>13.76</v>
+        <v>13.6</v>
       </c>
       <c r="D684" s="2">
-        <v>12.38</v>
+        <v>11.9</v>
       </c>
       <c r="F684" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G684" s="5">
+      <c r="G684" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18056,15 +18092,15 @@
         <v>696</v>
       </c>
       <c r="C685" s="2">
-        <v>4.1399999999999997</v>
+        <v>5.52</v>
       </c>
       <c r="D685" s="2">
-        <v>3.73</v>
+        <v>4.83</v>
       </c>
       <c r="F685" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G685" s="5">
+      <c r="G685" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18076,15 +18112,15 @@
         <v>697</v>
       </c>
       <c r="C686" s="2">
-        <v>4.42</v>
+        <v>5.6</v>
       </c>
       <c r="D686" s="2">
-        <v>3.98</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F686" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G686" s="5">
+      <c r="G686" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18096,15 +18132,15 @@
         <v>698</v>
       </c>
       <c r="C687" s="2">
-        <v>4.7300000000000004</v>
+        <v>5.94</v>
       </c>
       <c r="D687" s="2">
-        <v>4.26</v>
+        <v>5.2</v>
       </c>
       <c r="F687" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G687" s="5">
+      <c r="G687" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18116,15 +18152,15 @@
         <v>699</v>
       </c>
       <c r="C688" s="2">
-        <v>5.19</v>
+        <v>6.26</v>
       </c>
       <c r="D688" s="2">
-        <v>4.67</v>
+        <v>5.48</v>
       </c>
       <c r="F688" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G688" s="5">
+      <c r="G688" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18136,15 +18172,15 @@
         <v>700</v>
       </c>
       <c r="C689" s="2">
-        <v>5.5</v>
+        <v>6.71</v>
       </c>
       <c r="D689" s="2">
-        <v>4.95</v>
+        <v>5.87</v>
       </c>
       <c r="F689" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G689" s="5">
+      <c r="G689" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18156,15 +18192,15 @@
         <v>701</v>
       </c>
       <c r="C690" s="2">
-        <v>8.19</v>
+        <v>7.36</v>
       </c>
       <c r="D690" s="2">
-        <v>7.37</v>
+        <v>6.44</v>
       </c>
       <c r="F690" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G690" s="5">
+      <c r="G690" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18176,15 +18212,15 @@
         <v>702</v>
       </c>
       <c r="C691" s="2">
-        <v>8.8699999999999992</v>
+        <v>7.72</v>
       </c>
       <c r="D691" s="2">
-        <v>7.98</v>
+        <v>6.75</v>
       </c>
       <c r="F691" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G691" s="5">
+      <c r="G691" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18196,15 +18232,15 @@
         <v>703</v>
       </c>
       <c r="C692" s="2">
-        <v>10.119999999999999</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="D692" s="2">
-        <v>9.11</v>
+        <v>7.7</v>
       </c>
       <c r="F692" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G692" s="5">
+      <c r="G692" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18216,15 +18252,15 @@
         <v>704</v>
       </c>
       <c r="C693" s="2">
-        <v>11.96</v>
+        <v>10.4</v>
       </c>
       <c r="D693" s="2">
-        <v>10.76</v>
+        <v>9.1</v>
       </c>
       <c r="F693" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G693" s="5">
+      <c r="G693" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18236,15 +18272,15 @@
         <v>705</v>
       </c>
       <c r="C694" s="2">
-        <v>13.1</v>
+        <v>11.4</v>
       </c>
       <c r="D694" s="2">
-        <v>11.79</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="F694" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G694" s="5">
+      <c r="G694" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18256,15 +18292,15 @@
         <v>706</v>
       </c>
       <c r="C695" s="2">
-        <v>14.7</v>
+        <v>12.76</v>
       </c>
       <c r="D695" s="2">
-        <v>13.23</v>
+        <v>11.16</v>
       </c>
       <c r="F695" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G695" s="5">
+      <c r="G695" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18276,15 +18312,15 @@
         <v>707</v>
       </c>
       <c r="C696" s="2">
-        <v>19.149999999999999</v>
+        <v>16.559999999999999</v>
       </c>
       <c r="D696" s="2">
-        <v>17.239999999999998</v>
+        <v>14.49</v>
       </c>
       <c r="F696" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G696" s="5">
+      <c r="G696" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18296,15 +18332,15 @@
         <v>708</v>
       </c>
       <c r="C697" s="2">
-        <v>37.61</v>
+        <v>32.479999999999997</v>
       </c>
       <c r="D697" s="2">
-        <v>33.85</v>
+        <v>30.45</v>
       </c>
       <c r="F697" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G697" s="5">
+      <c r="G697" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18316,15 +18352,15 @@
         <v>709</v>
       </c>
       <c r="C698" s="2">
-        <v>42.95</v>
+        <v>37.11</v>
       </c>
       <c r="D698" s="2">
-        <v>38.659999999999997</v>
+        <v>32.47</v>
       </c>
       <c r="F698" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G698" s="5">
+      <c r="G698" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18336,15 +18372,15 @@
         <v>710</v>
       </c>
       <c r="C699" s="2">
-        <v>47.64</v>
+        <v>41.24</v>
       </c>
       <c r="D699" s="2">
-        <v>42.88</v>
+        <v>36.08</v>
       </c>
       <c r="F699" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G699" s="5">
+      <c r="G699" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18364,7 +18400,7 @@
       <c r="F700" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G700" s="5">
+      <c r="G700" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18384,7 +18420,7 @@
       <c r="F701" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G701" s="5">
+      <c r="G701" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18404,7 +18440,7 @@
       <c r="F702" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G702" s="5">
+      <c r="G702" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18424,7 +18460,7 @@
       <c r="F703" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G703" s="5">
+      <c r="G703" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18444,7 +18480,7 @@
       <c r="F704" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G704" s="5">
+      <c r="G704" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18464,7 +18500,7 @@
       <c r="F705" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G705" s="5">
+      <c r="G705" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18484,7 +18520,7 @@
       <c r="F706" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G706" s="5">
+      <c r="G706" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18504,7 +18540,7 @@
       <c r="F707" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G707" s="5">
+      <c r="G707" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18524,7 +18560,7 @@
       <c r="F708" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G708" s="5">
+      <c r="G708" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18544,7 +18580,7 @@
       <c r="F709" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G709" s="5">
+      <c r="G709" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18564,7 +18600,7 @@
       <c r="F710" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G710" s="5">
+      <c r="G710" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18584,7 +18620,7 @@
       <c r="F711" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G711" s="5">
+      <c r="G711" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18604,7 +18640,7 @@
       <c r="F712" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G712" s="5">
+      <c r="G712" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18624,7 +18660,7 @@
       <c r="F713" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G713" s="5">
+      <c r="G713" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18644,7 +18680,7 @@
       <c r="F714" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G714" s="5">
+      <c r="G714" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18667,7 +18703,7 @@
       <c r="F715" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="G715" s="6">
+      <c r="G715" s="4">
         <v>0</v>
       </c>
     </row>
@@ -18690,7 +18726,7 @@
       <c r="F716" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="G716" s="6">
+      <c r="G716" s="4">
         <v>0</v>
       </c>
     </row>
@@ -18713,7 +18749,7 @@
       <c r="F717" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="G717" s="6">
+      <c r="G717" s="4">
         <v>0</v>
       </c>
     </row>
@@ -18736,7 +18772,7 @@
       <c r="F718" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="G718" s="6">
+      <c r="G718" s="4">
         <v>0</v>
       </c>
     </row>
@@ -18759,7 +18795,7 @@
       <c r="F719" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="G719" s="6">
+      <c r="G719" s="4">
         <v>0</v>
       </c>
     </row>
@@ -18782,7 +18818,7 @@
       <c r="F720" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="G720" s="6">
+      <c r="G720" s="4">
         <v>0</v>
       </c>
     </row>
@@ -18794,15 +18830,15 @@
         <v>734</v>
       </c>
       <c r="C721" s="2">
-        <v>0.6</v>
+        <v>0.69</v>
       </c>
       <c r="D721" s="2">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="F721" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G721" s="5">
+      <c r="G721" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18814,15 +18850,15 @@
         <v>735</v>
       </c>
       <c r="C722" s="2">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="D722" s="2">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="F722" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G722" s="5">
+      <c r="G722" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18834,15 +18870,15 @@
         <v>736</v>
       </c>
       <c r="C723" s="2">
-        <v>0.83</v>
+        <v>0.76</v>
       </c>
       <c r="D723" s="2">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="F723" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G723" s="5">
+      <c r="G723" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18854,15 +18890,15 @@
         <v>737</v>
       </c>
       <c r="C724" s="2">
-        <v>1.23</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="D724" s="2">
-        <v>1.1100000000000001</v>
+        <v>0.98</v>
       </c>
       <c r="F724" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G724" s="5">
+      <c r="G724" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18874,15 +18910,15 @@
         <v>738</v>
       </c>
       <c r="C725" s="2">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="D725" s="2">
-        <v>1.23</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F725" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G725" s="5">
+      <c r="G725" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18894,15 +18930,15 @@
         <v>739</v>
       </c>
       <c r="C726" s="2">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="D726" s="2">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="F726" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G726" s="5">
+      <c r="G726" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18914,15 +18950,15 @@
         <v>740</v>
       </c>
       <c r="C727" s="2">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="D727" s="2">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="F727" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G727" s="5">
+      <c r="G727" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18934,15 +18970,15 @@
         <v>741</v>
       </c>
       <c r="C728" s="2">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="D728" s="2">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="F728" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G728" s="5">
+      <c r="G728" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18954,15 +18990,15 @@
         <v>742</v>
       </c>
       <c r="C729" s="2">
-        <v>2.3199999999999998</v>
+        <v>2.15</v>
       </c>
       <c r="D729" s="2">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="F729" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G729" s="5">
+      <c r="G729" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18974,15 +19010,15 @@
         <v>743</v>
       </c>
       <c r="C730" s="2">
-        <v>2.5499999999999998</v>
+        <v>2.31</v>
       </c>
       <c r="D730" s="2">
-        <v>2.2999999999999998</v>
+        <v>2.02</v>
       </c>
       <c r="F730" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G730" s="5">
+      <c r="G730" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -18994,15 +19030,15 @@
         <v>744</v>
       </c>
       <c r="C731" s="2">
-        <v>4.91</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="D731" s="2">
-        <v>4.42</v>
+        <v>3.85</v>
       </c>
       <c r="F731" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G731" s="5">
+      <c r="G731" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19014,15 +19050,15 @@
         <v>745</v>
       </c>
       <c r="C732" s="2">
-        <v>6.09</v>
+        <v>5.52</v>
       </c>
       <c r="D732" s="2">
-        <v>5.48</v>
+        <v>4.83</v>
       </c>
       <c r="F732" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G732" s="5">
+      <c r="G732" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19034,15 +19070,15 @@
         <v>746</v>
       </c>
       <c r="C733" s="2">
-        <v>7.39</v>
+        <v>6.72</v>
       </c>
       <c r="D733" s="2">
-        <v>6.65</v>
+        <v>5.88</v>
       </c>
       <c r="F733" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G733" s="5">
+      <c r="G733" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19062,7 +19098,7 @@
       <c r="F734" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G734" s="5">
+      <c r="G734" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19082,7 +19118,7 @@
       <c r="F735" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G735" s="5">
+      <c r="G735" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19102,7 +19138,7 @@
       <c r="F736" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G736" s="5">
+      <c r="G736" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19122,7 +19158,7 @@
       <c r="F737" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G737" s="5">
+      <c r="G737" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19142,7 +19178,7 @@
       <c r="F738" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G738" s="5">
+      <c r="G738" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19162,7 +19198,7 @@
       <c r="F739" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G739" s="5">
+      <c r="G739" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19182,7 +19218,7 @@
       <c r="F740" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G740" s="5">
+      <c r="G740" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19202,7 +19238,7 @@
       <c r="F741" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G741" s="5">
+      <c r="G741" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19222,7 +19258,7 @@
       <c r="F742" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G742" s="5">
+      <c r="G742" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19242,7 +19278,7 @@
       <c r="F743" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G743" s="5">
+      <c r="G743" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19262,7 +19298,7 @@
       <c r="F744" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G744" s="5">
+      <c r="G744" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19282,7 +19318,7 @@
       <c r="F745" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G745" s="5">
+      <c r="G745" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19302,7 +19338,7 @@
       <c r="F746" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G746" s="5">
+      <c r="G746" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19322,7 +19358,7 @@
       <c r="F747" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G747" s="5">
+      <c r="G747" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -19342,12 +19378,12 @@
       <c r="F748" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G748" s="5">
+      <c r="G748" s="4">
         <v>0.05</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G748" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="B1:B748" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/dados/precos_todos.xlsx
+++ b/dados/precos_todos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a9e64bef5804d793/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDF59E69-D44A-4E1B-8B80-300AB6E495CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{CDF59E69-D44A-4E1B-8B80-300AB6E495CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B97B190-EDF0-4059-8492-095FADB9A1A4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="21600" windowHeight="12670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$B$1:$B$748</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2383,6 +2396,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14352,7 +14369,7 @@
         <v>35.93</v>
       </c>
       <c r="E510">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="F510" s="1" t="s">
         <v>514</v>
@@ -14375,7 +14392,7 @@
         <v>47.98</v>
       </c>
       <c r="E511">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F511" s="1" t="s">
         <v>514</v>
@@ -15755,10 +15772,10 @@
         <v>583</v>
       </c>
       <c r="C574" s="2">
-        <v>143.91999999999999</v>
+        <v>196</v>
       </c>
       <c r="D574" s="2">
-        <v>129.53</v>
+        <v>156.80000000000001</v>
       </c>
       <c r="F574" s="1" t="s">
         <v>524</v>
@@ -15775,10 +15792,10 @@
         <v>584</v>
       </c>
       <c r="C575" s="2">
-        <v>1225.31</v>
+        <v>274</v>
       </c>
       <c r="D575" s="2">
-        <v>1072.1500000000001</v>
+        <v>219.20000000000002</v>
       </c>
       <c r="F575" s="1" t="s">
         <v>524</v>
@@ -15795,10 +15812,10 @@
         <v>585</v>
       </c>
       <c r="C576" s="2">
-        <v>1518.66</v>
+        <v>303.77999999999997</v>
       </c>
       <c r="D576" s="2">
-        <v>1328.83</v>
+        <v>243.024</v>
       </c>
       <c r="F576" s="1" t="s">
         <v>524</v>

--- a/dados/precos_todos.xlsx
+++ b/dados/precos_todos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a9e64bef5804d793/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{CDF59E69-D44A-4E1B-8B80-300AB6E495CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B97B190-EDF0-4059-8492-095FADB9A1A4}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{CDF59E69-D44A-4E1B-8B80-300AB6E495CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF00B61D-4EC7-4D64-9375-ABFFA0039D4A}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="21600" windowHeight="12670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14310" yWindow="0" windowWidth="14580" windowHeight="17370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
@@ -15519,10 +15519,10 @@
         <v>572</v>
       </c>
       <c r="C563" s="2">
-        <v>6.07</v>
+        <v>6.39</v>
       </c>
       <c r="D563" s="2">
-        <v>5.31</v>
+        <v>5.59</v>
       </c>
       <c r="E563">
         <v>10</v>
@@ -15542,7 +15542,7 @@
         <v>573</v>
       </c>
       <c r="C564" s="2">
-        <v>9.73</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="D564" s="2">
         <v>8.51</v>
@@ -15565,10 +15565,10 @@
         <v>574</v>
       </c>
       <c r="C565" s="2">
-        <v>12.06</v>
+        <v>10.72</v>
       </c>
       <c r="D565" s="2">
-        <v>10.55</v>
+        <v>9.5</v>
       </c>
       <c r="E565">
         <v>10</v>
@@ -15588,10 +15588,10 @@
         <v>575</v>
       </c>
       <c r="C566" s="2">
-        <v>18.03</v>
+        <v>23.19</v>
       </c>
       <c r="D566" s="2">
-        <v>15.78</v>
+        <v>20.3</v>
       </c>
       <c r="E566">
         <v>5</v>
@@ -15611,10 +15611,10 @@
         <v>576</v>
       </c>
       <c r="C567" s="2">
-        <v>41.47</v>
+        <v>25.8</v>
       </c>
       <c r="D567" s="2">
-        <v>36.28</v>
+        <v>22.84</v>
       </c>
       <c r="E567">
         <v>5</v>
@@ -15634,10 +15634,10 @@
         <v>577</v>
       </c>
       <c r="C568" s="2">
-        <v>64.7</v>
+        <v>56.6</v>
       </c>
       <c r="D568" s="2">
-        <v>56.61</v>
+        <v>49.56</v>
       </c>
       <c r="E568">
         <v>2.5</v>
@@ -15657,10 +15657,10 @@
         <v>578</v>
       </c>
       <c r="C569" s="2">
-        <v>59.33</v>
+        <v>63.28</v>
       </c>
       <c r="D569" s="2">
-        <v>51.92</v>
+        <v>55.44</v>
       </c>
       <c r="E569">
         <v>2</v>
@@ -15680,10 +15680,10 @@
         <v>579</v>
       </c>
       <c r="C570" s="2">
-        <v>75.91</v>
+        <v>79.2</v>
       </c>
       <c r="D570" s="2">
-        <v>66.430000000000007</v>
+        <v>69.22</v>
       </c>
       <c r="E570">
         <v>1</v>
@@ -15703,10 +15703,10 @@
         <v>580</v>
       </c>
       <c r="C571" s="2">
-        <v>102.29</v>
+        <v>107.96</v>
       </c>
       <c r="D571" s="2">
-        <v>89.52</v>
+        <v>94.5</v>
       </c>
       <c r="E571">
         <v>1</v>
@@ -15726,10 +15726,10 @@
         <v>581</v>
       </c>
       <c r="C572" s="2">
-        <v>159.88</v>
+        <v>165.6</v>
       </c>
       <c r="D572" s="2">
-        <v>139.88999999999999</v>
+        <v>144.9</v>
       </c>
       <c r="E572">
         <v>0.5</v>
@@ -15749,10 +15749,10 @@
         <v>582</v>
       </c>
       <c r="C573" s="2">
-        <v>161.94999999999999</v>
+        <v>176.66</v>
       </c>
       <c r="D573" s="2">
-        <v>141.69999999999999</v>
+        <v>154.58000000000001</v>
       </c>
       <c r="E573">
         <v>0.25</v>
@@ -15772,10 +15772,10 @@
         <v>583</v>
       </c>
       <c r="C574" s="2">
-        <v>196</v>
+        <v>195.2</v>
       </c>
       <c r="D574" s="2">
-        <v>156.80000000000001</v>
+        <v>170.8</v>
       </c>
       <c r="F574" s="1" t="s">
         <v>524</v>
@@ -15792,10 +15792,10 @@
         <v>584</v>
       </c>
       <c r="C575" s="2">
-        <v>274</v>
+        <v>273.92</v>
       </c>
       <c r="D575" s="2">
-        <v>219.20000000000002</v>
+        <v>239.69</v>
       </c>
       <c r="F575" s="1" t="s">
         <v>524</v>
@@ -15812,10 +15812,10 @@
         <v>585</v>
       </c>
       <c r="C576" s="2">
-        <v>303.77999999999997</v>
+        <v>304</v>
       </c>
       <c r="D576" s="2">
-        <v>243.024</v>
+        <v>266</v>
       </c>
       <c r="F576" s="1" t="s">
         <v>524</v>

--- a/dados/precos_todos.xlsx
+++ b/dados/precos_todos.xlsx
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="C3" s="7" t="n">
-        <v>1.1839644</v>
+        <v>1.28</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>1.02610248</v>
+        <v>1.11</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
@@ -571,10 +571,10 @@
         </is>
       </c>
       <c r="C4" s="7" t="n">
-        <v>1.9151676</v>
+        <v>2.07</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>1.65981192</v>
+        <v>1.8</v>
       </c>
       <c r="E4" t="n">
         <v>50</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>2.85696</v>
+        <v>3.1</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2.476032</v>
+        <v>2.68</v>
       </c>
       <c r="E5" t="n">
         <v>50</v>
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>4.2001776</v>
+        <v>4.55</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.640153919999999</v>
+        <v>3.94</v>
       </c>
       <c r="E6" t="n">
         <v>25</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>5.110833599999999</v>
+        <v>5.54</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>4.429389119999999</v>
+        <v>4.8</v>
       </c>
       <c r="E7" t="n">
         <v>25</v>
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>5.110833599999999</v>
+        <v>5.54</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>4.429389119999999</v>
+        <v>4.8</v>
       </c>
       <c r="E8" t="n">
         <v>25</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>11.5499769</v>
+        <v>11.55</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>10.00997998</v>
+        <v>10.01</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>12.137223168</v>
+        <v>12.9</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>10.5189267456</v>
+        <v>11.18</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>17.20128</v>
+        <v>18.28</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>14.907776</v>
+        <v>15.84</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>23.808</v>
+        <v>25.3</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>20.6336</v>
+        <v>21.92</v>
       </c>
       <c r="E12" t="n">
         <v>5</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>31.48608</v>
+        <v>33.45</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>27.287936</v>
+        <v>28.99</v>
       </c>
       <c r="E13" t="n">
         <v>5</v>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>48.40836</v>
+        <v>48.41</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>41.95391200000001</v>
+        <v>41.95</v>
       </c>
       <c r="E14" t="n">
         <v>5</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>60.22401000000001</v>
+        <v>60.22</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>52.19414200000001</v>
+        <v>52.19</v>
       </c>
       <c r="E15" t="n">
         <v>3</v>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>87.72225</v>
+        <v>87.72</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>76.02594999999999</v>
+        <v>76.03</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="C17" s="7" t="n">
-        <v>1.1904</v>
+        <v>1.29</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1.0416</v>
+        <v>1.13</v>
       </c>
       <c r="E17" t="n">
         <v>100</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>2.201763839999999</v>
+        <v>2.39</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1.926543359999999</v>
+        <v>2.09</v>
       </c>
       <c r="E18" t="n">
         <v>50</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="C19" s="7" t="n">
-        <v>3.68738304</v>
+        <v>3.99</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>3.22646016</v>
+        <v>3.5</v>
       </c>
       <c r="E19" t="n">
         <v>25</v>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>5.451555839999999</v>
+        <v>5.91</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>4.770111359999999</v>
+        <v>5.17</v>
       </c>
       <c r="E20" t="n">
         <v>25</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>12.31997536</v>
+        <v>12.32</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>10.77997844</v>
+        <v>10.78</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>15.5761030656</v>
+        <v>15.58</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>13.6290901824</v>
+        <v>13.63</v>
       </c>
       <c r="E22" t="n">
         <v>10</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>24.748416</v>
+        <v>24.75</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>21.654864</v>
+        <v>21.65</v>
       </c>
       <c r="E23" t="n">
         <v>10</v>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>36.969856</v>
+        <v>36.97</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>32.34862399999999</v>
+        <v>32.35</v>
       </c>
       <c r="E24" t="n">
         <v>4</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>57.7654</v>
+        <v>57.77</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>50.544725</v>
+        <v>50.54</v>
       </c>
       <c r="E25" t="n">
         <v>4</v>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>84.19350016000001</v>
+        <v>84.19</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>73.66931264</v>
+        <v>73.67</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>1.5786192</v>
+        <v>1.68</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>1.36813664</v>
+        <v>1.45</v>
       </c>
       <c r="E28" t="n">
         <v>100</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>2.5535568</v>
+        <v>2.71</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2.21308256</v>
+        <v>2.35</v>
       </c>
       <c r="E29" t="n">
         <v>50</v>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>3.80928</v>
+        <v>4.05</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>3.301376</v>
+        <v>3.51</v>
       </c>
       <c r="E30" t="n">
         <v>50</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>5.600236799999999</v>
+        <v>5.95</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>4.85353856</v>
+        <v>5.16</v>
       </c>
       <c r="E31" t="n">
         <v>25</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>6.814444799999999</v>
+        <v>7.24</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>5.905852159999999</v>
+        <v>6.27</v>
       </c>
       <c r="E32" t="n">
         <v>25</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>6.814444799999999</v>
+        <v>7.24</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>5.905852159999999</v>
+        <v>6.27</v>
       </c>
       <c r="E33" t="n">
         <v>25</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>13.9499721</v>
+        <v>13.95</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>12.08997582</v>
+        <v>12.09</v>
       </c>
       <c r="E34" t="n">
         <v>10</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>15.17152896</v>
+        <v>15.93</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>13.148658432</v>
+        <v>13.81</v>
       </c>
       <c r="E35" t="n">
         <v>10</v>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>21.5016</v>
+        <v>22.58</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>18.63472</v>
+        <v>19.57</v>
       </c>
       <c r="E36" t="n">
         <v>10</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>29.76</v>
+        <v>31.25</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>25.792</v>
+        <v>27.08</v>
       </c>
       <c r="E37" t="n">
         <v>5</v>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>39.3576</v>
+        <v>41.33</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>34.10992</v>
+        <v>35.82</v>
       </c>
       <c r="E38" t="n">
         <v>5</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>58.46724</v>
+        <v>58.47</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>50.67160800000001</v>
+        <v>50.67</v>
       </c>
       <c r="E39" t="n">
         <v>5</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>72.73809</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>63.039678</v>
+        <v>63.04</v>
       </c>
       <c r="E40" t="n">
         <v>3</v>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>105.95025</v>
+        <v>105.95</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>91.82355</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>1.5872</v>
+        <v>1.69</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>1.3888</v>
+        <v>1.48</v>
       </c>
       <c r="E42" t="n">
         <v>100</v>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>2.93568512</v>
+        <v>3.12</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>2.568724479999999</v>
+        <v>2.73</v>
       </c>
       <c r="E43" t="n">
         <v>50</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>4.916510720000002</v>
+        <v>5.22</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>4.30194688</v>
+        <v>4.57</v>
       </c>
       <c r="E44" t="n">
         <v>25</v>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>7.268741119999999</v>
+        <v>7.72</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>6.360148479999999</v>
+        <v>6.76</v>
       </c>
       <c r="E45" t="n">
         <v>25</v>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="C46" s="7" t="n">
-        <v>14.87997024</v>
+        <v>14.88</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>13.01997396</v>
+        <v>13.02</v>
       </c>
       <c r="E46" t="n">
         <v>10</v>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>18.8126959104</v>
+        <v>18.81</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>16.4611089216</v>
+        <v>16.46</v>
       </c>
       <c r="E47" t="n">
         <v>10</v>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="C48" s="7" t="n">
-        <v>29.890944</v>
+        <v>29.89</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>26.154576</v>
+        <v>26.15</v>
       </c>
       <c r="E48" t="n">
         <v>10</v>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>44.651904</v>
+        <v>44.65</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>39.070416</v>
+        <v>39.07</v>
       </c>
       <c r="E49" t="n">
         <v>4</v>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>69.76860000000001</v>
+        <v>69.77</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>61.047525</v>
+        <v>61.05</v>
       </c>
       <c r="E50" t="n">
         <v>4</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>101.68825344</v>
+        <v>101.69</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>88.97722176000001</v>
+        <v>88.98</v>
       </c>
       <c r="E51" t="n">
         <v>2</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>3.5518932</v>
+        <v>3.85</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>3.07830744</v>
+        <v>3.33</v>
       </c>
       <c r="E52" t="n">
         <v>50</v>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>5.745502799999999</v>
+        <v>6.22</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>4.979435759999999</v>
+        <v>5.39</v>
       </c>
       <c r="E53" t="n">
         <v>25</v>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="C54" s="7" t="n">
-        <v>8.570879999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>7.428096</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="E54" t="n">
         <v>25</v>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>12.6005328</v>
+        <v>13.65</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>10.92046176</v>
+        <v>11.83</v>
       </c>
       <c r="E55" t="n">
         <v>10</v>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>15.3325008</v>
+        <v>16.61</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>13.28816736</v>
+        <v>14.4</v>
       </c>
       <c r="E56" t="n">
         <v>10</v>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="C57" s="7" t="n">
-        <v>15.3325008</v>
+        <v>16.61</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>13.28816736</v>
+        <v>14.4</v>
       </c>
       <c r="E57" t="n">
         <v>10</v>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>34.6499307</v>
+        <v>34.65</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>30.02993994</v>
+        <v>30.03</v>
       </c>
       <c r="E58" t="n">
         <v>10</v>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>36.411669504</v>
+        <v>38.69</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>31.5567802368</v>
+        <v>33.53</v>
       </c>
       <c r="E59" t="n">
         <v>5</v>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>51.60384000000001</v>
+        <v>54.83</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>44.723328</v>
+        <v>47.52</v>
       </c>
       <c r="E60" t="n">
         <v>5</v>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>71.42400000000001</v>
+        <v>75.89</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>61.9008</v>
+        <v>65.77</v>
       </c>
       <c r="E61" t="n">
         <v>3</v>
@@ -2137,10 +2137,10 @@
         </is>
       </c>
       <c r="C62" s="7" t="n">
-        <v>94.45824</v>
+        <v>100.36</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>81.86380800000001</v>
+        <v>86.98</v>
       </c>
       <c r="E62" t="n">
         <v>3</v>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>145.22508</v>
+        <v>145.23</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>125.861736</v>
+        <v>125.86</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="C64" s="7" t="n">
-        <v>180.67203</v>
+        <v>180.67</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>156.582426</v>
+        <v>156.58</v>
       </c>
       <c r="E64" t="n">
         <v>1</v>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>263.16675</v>
+        <v>263.17</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>228.07785</v>
+        <v>228.08</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="C66" s="7" t="n">
-        <v>3.5712</v>
+        <v>3.87</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>3.1248</v>
+        <v>3.39</v>
       </c>
       <c r="E66" t="n">
         <v>50</v>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>6.605291519999998</v>
+        <v>7.16</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>5.779630079999999</v>
+        <v>6.26</v>
       </c>
       <c r="E67" t="n">
         <v>25</v>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="C68" s="7" t="n">
-        <v>11.06214912</v>
+        <v>11.98</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>9.679380480000001</v>
+        <v>10.49</v>
       </c>
       <c r="E68" t="n">
         <v>25</v>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>16.35466752</v>
+        <v>17.72</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>14.31033408</v>
+        <v>15.5</v>
       </c>
       <c r="E69" t="n">
         <v>10</v>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="C70" s="7" t="n">
-        <v>36.95992608</v>
+        <v>36.96</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>32.33993532</v>
+        <v>32.34</v>
       </c>
       <c r="E70" t="n">
         <v>10</v>
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>46.72830919680001</v>
+        <v>46.73</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>40.8872705472</v>
+        <v>40.89</v>
       </c>
       <c r="E71" t="n">
         <v>10</v>
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="C72" s="7" t="n">
-        <v>74.245248</v>
+        <v>74.25</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>64.964592</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="E72" t="n">
         <v>5</v>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>110.909568</v>
+        <v>110.91</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>97.04587199999997</v>
+        <v>97.05</v>
       </c>
       <c r="E73" t="n">
         <v>3</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="C74" s="7" t="n">
-        <v>173.2962</v>
+        <v>173.3</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>151.634175</v>
+        <v>151.63</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>252.58050048</v>
+        <v>252.58</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>221.00793792</v>
+        <v>221.01</v>
       </c>
       <c r="E75" t="n">
         <v>1</v>
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="C76" s="7" t="n">
-        <v>4.735857600000001</v>
+        <v>5.03</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>4.104409920000001</v>
+        <v>4.36</v>
       </c>
       <c r="E76" t="n">
         <v>50</v>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="C77" s="7" t="n">
-        <v>7.660670399999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>6.639247679999999</v>
+        <v>7.05</v>
       </c>
       <c r="E77" t="n">
         <v>25</v>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="C78" s="7" t="n">
-        <v>11.42784</v>
+        <v>12.14</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>9.904128</v>
+        <v>10.52</v>
       </c>
       <c r="E78" t="n">
         <v>25</v>
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="C79" s="7" t="n">
-        <v>16.8007104</v>
+        <v>17.85</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>14.56061568</v>
+        <v>15.47</v>
       </c>
       <c r="E79" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="C80" s="7" t="n">
-        <v>20.4433344</v>
+        <v>21.72</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>17.71755648</v>
+        <v>18.82</v>
       </c>
       <c r="E80" t="n">
         <v>10</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="C81" s="7" t="n">
-        <v>20.4433344</v>
+        <v>21.72</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>17.71755648</v>
+        <v>18.82</v>
       </c>
       <c r="E81" t="n">
         <v>10</v>
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="C82" s="7" t="n">
-        <v>41.8499163</v>
+        <v>41.85</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>36.26992746000001</v>
+        <v>36.27</v>
       </c>
       <c r="E82" t="n">
         <v>10</v>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="C83" s="7" t="n">
-        <v>45.51458688</v>
+        <v>47.79</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>39.445975296</v>
+        <v>41.42</v>
       </c>
       <c r="E83" t="n">
         <v>5</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="C84" s="7" t="n">
-        <v>64.50479999999999</v>
+        <v>67.73</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>55.90415999999999</v>
+        <v>58.7</v>
       </c>
       <c r="E84" t="n">
         <v>5</v>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="C85" s="7" t="n">
-        <v>89.28</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>77.376</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="E85" t="n">
         <v>3</v>
@@ -2785,10 +2785,10 @@
         </is>
       </c>
       <c r="C86" s="7" t="n">
-        <v>118.0728</v>
+        <v>123.98</v>
       </c>
       <c r="D86" s="7" t="n">
-        <v>102.32976</v>
+        <v>107.45</v>
       </c>
       <c r="E86" t="n">
         <v>3</v>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="C87" s="7" t="n">
-        <v>175.40172</v>
+        <v>175.4</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>152.014824</v>
+        <v>152.01</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="C88" s="7" t="n">
-        <v>218.21427</v>
+        <v>218.21</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>189.119034</v>
+        <v>189.12</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="C89" s="7" t="n">
-        <v>317.85075</v>
+        <v>317.85</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>275.47065</v>
+        <v>275.47</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="C90" s="7" t="n">
-        <v>4.7616</v>
+        <v>5.06</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>4.166399999999999</v>
+        <v>4.43</v>
       </c>
       <c r="E90" t="n">
         <v>50</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="C91" s="7" t="n">
-        <v>8.80705536</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>7.706173439999998</v>
+        <v>8.19</v>
       </c>
       <c r="E91" t="n">
         <v>25</v>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="C92" s="7" t="n">
-        <v>14.74953216</v>
+        <v>15.67</v>
       </c>
       <c r="D92" s="7" t="n">
-        <v>12.90584064</v>
+        <v>13.71</v>
       </c>
       <c r="E92" t="n">
         <v>25</v>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="C93" s="7" t="n">
-        <v>21.80622336</v>
+        <v>23.17</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>19.08044543999999</v>
+        <v>20.27</v>
       </c>
       <c r="E93" t="n">
         <v>10</v>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="C94" s="7" t="n">
-        <v>44.63991072</v>
+        <v>44.64</v>
       </c>
       <c r="D94" s="7" t="n">
-        <v>39.05992188</v>
+        <v>39.06</v>
       </c>
       <c r="E94" t="n">
         <v>10</v>
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="C95" s="7" t="n">
-        <v>56.43808773120001</v>
+        <v>56.44</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>49.3833267648</v>
+        <v>49.38</v>
       </c>
       <c r="E95" t="n">
         <v>10</v>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="C96" s="7" t="n">
-        <v>89.67283200000001</v>
+        <v>89.67</v>
       </c>
       <c r="D96" s="7" t="n">
-        <v>78.463728</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="E96" t="n">
         <v>5</v>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="C97" s="7" t="n">
-        <v>133.955712</v>
+        <v>133.96</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>117.211248</v>
+        <v>117.21</v>
       </c>
       <c r="E97" t="n">
         <v>3</v>
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="C98" s="7" t="n">
-        <v>209.3058</v>
+        <v>209.31</v>
       </c>
       <c r="D98" s="7" t="n">
-        <v>183.142575</v>
+        <v>183.14</v>
       </c>
       <c r="E98" t="n">
         <v>1</v>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="C99" s="7" t="n">
-        <v>305.0647603200001</v>
+        <v>305.06</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>266.93166528</v>
+        <v>266.93</v>
       </c>
       <c r="E99" t="n">
         <v>1</v>
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="C100" s="7" t="n">
-        <v>2.84151456</v>
+        <v>2.96</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>2.52579072</v>
+        <v>2.63</v>
       </c>
       <c r="E100" t="n">
         <v>50</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="C101" s="7" t="n">
-        <v>4.596402239999999</v>
+        <v>4.79</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>4.08569088</v>
+        <v>4.26</v>
       </c>
       <c r="E101" t="n">
         <v>25</v>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="C102" s="7" t="n">
-        <v>6.856704</v>
+        <v>7.14</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>6.094848</v>
+        <v>6.35</v>
       </c>
       <c r="E102" t="n">
         <v>50</v>
@@ -3244,10 +3244,10 @@
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>10.08042624</v>
+        <v>10.5</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>8.960378879999999</v>
+        <v>9.33</v>
       </c>
       <c r="E103" t="n">
         <v>25</v>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="C104" s="7" t="n">
-        <v>12.26600064</v>
+        <v>12.78</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>10.90311168</v>
+        <v>11.36</v>
       </c>
       <c r="E104" t="n">
         <v>25</v>
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="C105" s="7" t="n">
-        <v>12.26600064</v>
+        <v>12.78</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>10.90311168</v>
+        <v>11.36</v>
       </c>
       <c r="E105" t="n">
         <v>25</v>
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="C106" s="7" t="n">
-        <v>22.499955</v>
+        <v>22.5</v>
       </c>
       <c r="D106" s="7" t="n">
-        <v>19.99996</v>
+        <v>20</v>
       </c>
       <c r="E106" t="n">
         <v>10</v>
@@ -3352,10 +3352,10 @@
         </is>
       </c>
       <c r="C107" s="7" t="n">
-        <v>28.4466168</v>
+        <v>28.45</v>
       </c>
       <c r="D107" s="7" t="n">
-        <v>25.2858816</v>
+        <v>25.29</v>
       </c>
       <c r="E107" t="n">
         <v>10</v>
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="C108" s="7" t="n">
-        <v>40.31549999999999</v>
+        <v>40.32</v>
       </c>
       <c r="D108" s="7" t="n">
-        <v>35.836</v>
+        <v>35.84</v>
       </c>
       <c r="E108" t="n">
         <v>10</v>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="C110" s="7" t="n">
-        <v>73.79549999999999</v>
+        <v>73.8</v>
       </c>
       <c r="D110" s="7" t="n">
-        <v>65.59599999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E110" t="n">
         <v>5</v>
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="C111" s="7" t="n">
-        <v>94.30200000000001</v>
+        <v>94.3</v>
       </c>
       <c r="D111" s="7" t="n">
-        <v>83.82400000000001</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="E111" t="n">
         <v>5</v>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="C112" s="7" t="n">
-        <v>117.3195</v>
+        <v>117.32</v>
       </c>
       <c r="D112" s="7" t="n">
-        <v>104.284</v>
+        <v>104.28</v>
       </c>
       <c r="E112" t="n">
         <v>3</v>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="C113" s="7" t="n">
-        <v>170.8875</v>
+        <v>170.89</v>
       </c>
       <c r="D113" s="7" t="n">
         <v>151.9</v>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="C114" s="7" t="n">
-        <v>5.504409599999999</v>
+        <v>5.73</v>
       </c>
       <c r="D114" s="7" t="n">
-        <v>4.678748159999999</v>
+        <v>4.87</v>
       </c>
       <c r="E114" t="n">
         <v>50</v>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="C115" s="7" t="n">
-        <v>9.218457600000001</v>
+        <v>9.6</v>
       </c>
       <c r="D115" s="7" t="n">
-        <v>7.835688960000001</v>
+        <v>8.16</v>
       </c>
       <c r="E115" t="n">
         <v>25</v>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="C116" s="7" t="n">
-        <v>13.6288896</v>
+        <v>14.2</v>
       </c>
       <c r="D116" s="7" t="n">
-        <v>11.58455616</v>
+        <v>12.07</v>
       </c>
       <c r="E116" t="n">
         <v>25</v>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="C117" s="7" t="n">
-        <v>24.99995</v>
+        <v>25</v>
       </c>
       <c r="D117" s="7" t="n">
-        <v>21.2499575</v>
+        <v>21.25</v>
       </c>
       <c r="E117" t="n">
         <v>10</v>
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="C118" s="7" t="n">
-        <v>31.607352</v>
+        <v>31.61</v>
       </c>
       <c r="D118" s="7" t="n">
-        <v>26.8662492</v>
+        <v>26.87</v>
       </c>
       <c r="E118" t="n">
         <v>100</v>
@@ -3677,7 +3677,7 @@
         <v>50.22</v>
       </c>
       <c r="D119" s="7" t="n">
-        <v>42.687</v>
+        <v>42.69</v>
       </c>
       <c r="E119" t="n">
         <v>10</v>
@@ -3704,7 +3704,7 @@
         <v>75.02</v>
       </c>
       <c r="D120" s="7" t="n">
-        <v>63.767</v>
+        <v>63.77</v>
       </c>
       <c r="E120" t="n">
         <v>4</v>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="C121" s="7" t="n">
-        <v>117.21875</v>
+        <v>117.22</v>
       </c>
       <c r="D121" s="7" t="n">
-        <v>99.6359375</v>
+        <v>99.64</v>
       </c>
       <c r="E121" t="n">
         <v>4</v>
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="C122" s="7" t="n">
-        <v>170.8472</v>
+        <v>170.85</v>
       </c>
       <c r="D122" s="7" t="n">
-        <v>145.22012</v>
+        <v>145.22</v>
       </c>
       <c r="E122" t="n">
         <v>2</v>
@@ -3782,10 +3782,10 @@
         </is>
       </c>
       <c r="C123" s="7" t="n">
-        <v>13.346238699</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="D123" s="7" t="n">
-        <v>11.863323288</v>
+        <v>7.89</v>
       </c>
       <c r="E123" t="n">
         <v>50</v>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="C124" s="7" t="n">
-        <v>21.588726771</v>
+        <v>14.36</v>
       </c>
       <c r="D124" s="7" t="n">
-        <v>19.189979352</v>
+        <v>12.77</v>
       </c>
       <c r="E124" t="n">
         <v>25</v>
@@ -3836,10 +3836,10 @@
         </is>
       </c>
       <c r="C125" s="7" t="n">
-        <v>32.2050816</v>
+        <v>21.43</v>
       </c>
       <c r="D125" s="7" t="n">
-        <v>28.6267392</v>
+        <v>19.05</v>
       </c>
       <c r="E125" t="n">
         <v>20</v>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="C126" s="7" t="n">
-        <v>47.34650199599999</v>
+        <v>31.5</v>
       </c>
       <c r="D126" s="7" t="n">
-        <v>42.085779552</v>
+        <v>28</v>
       </c>
       <c r="E126" t="n">
         <v>10</v>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="C127" s="7" t="n">
-        <v>57.611871756</v>
+        <v>38.33</v>
       </c>
       <c r="D127" s="7" t="n">
-        <v>51.21055267199999</v>
+        <v>34.07</v>
       </c>
       <c r="E127" t="n">
         <v>10</v>
@@ -3917,10 +3917,10 @@
         </is>
       </c>
       <c r="C128" s="7" t="n">
-        <v>57.611871756</v>
+        <v>38.33</v>
       </c>
       <c r="D128" s="7" t="n">
-        <v>51.21055267199999</v>
+        <v>34.07</v>
       </c>
       <c r="E128" t="n">
         <v>10</v>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="C129" s="7" t="n">
-        <v>96.821806356</v>
+        <v>67.5</v>
       </c>
       <c r="D129" s="7" t="n">
-        <v>59.99988</v>
+        <v>60</v>
       </c>
       <c r="E129" t="n">
         <v>10</v>
@@ -3971,10 +3971,10 @@
         </is>
       </c>
       <c r="C130" s="7" t="n">
-        <v>122.41148141376</v>
+        <v>85.34</v>
       </c>
       <c r="D130" s="7" t="n">
-        <v>75.8576448</v>
+        <v>75.86</v>
       </c>
       <c r="E130" t="n">
         <v>5</v>
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="C131" s="7" t="n">
-        <v>173.4856596</v>
+        <v>120.95</v>
       </c>
       <c r="D131" s="7" t="n">
-        <v>107.508</v>
+        <v>107.51</v>
       </c>
       <c r="E131" t="n">
         <v>5</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="C132" s="7" t="n">
-        <v>240.11856</v>
+        <v>167.4</v>
       </c>
       <c r="D132" s="7" t="n">
         <v>148.8</v>
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="C133" s="7" t="n">
-        <v>317.5567956</v>
+        <v>221.39</v>
       </c>
       <c r="D133" s="7" t="n">
-        <v>196.788</v>
+        <v>196.79</v>
       </c>
       <c r="E133" t="n">
         <v>3</v>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="C134" s="7" t="n">
-        <v>405.8003664</v>
+        <v>282.91</v>
       </c>
       <c r="D134" s="7" t="n">
-        <v>251.472</v>
+        <v>251.47</v>
       </c>
       <c r="E134" t="n">
         <v>1</v>
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="C135" s="7" t="n">
-        <v>504.8492724</v>
+        <v>351.96</v>
       </c>
       <c r="D135" s="7" t="n">
-        <v>312.852</v>
+        <v>312.85</v>
       </c>
       <c r="E135" t="n">
         <v>1</v>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="C136" s="7" t="n">
-        <v>735.3630899999999</v>
+        <v>512.66</v>
       </c>
       <c r="D136" s="7" t="n">
         <v>455.7</v>
@@ -4160,10 +4160,10 @@
         </is>
       </c>
       <c r="C137" s="7" t="n">
-        <v>25.85352383999999</v>
+        <v>17.2</v>
       </c>
       <c r="D137" s="7" t="n">
-        <v>21.975495264</v>
+        <v>14.62</v>
       </c>
       <c r="E137" t="n">
         <v>25</v>
@@ -4187,10 +4187,10 @@
         </is>
       </c>
       <c r="C138" s="7" t="n">
-        <v>43.29794304000001</v>
+        <v>28.81</v>
       </c>
       <c r="D138" s="7" t="n">
-        <v>36.80325158400001</v>
+        <v>24.49</v>
       </c>
       <c r="E138" t="n">
         <v>25</v>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="C139" s="7" t="n">
-        <v>64.01319083999999</v>
+        <v>42.59</v>
       </c>
       <c r="D139" s="7" t="n">
-        <v>54.411212214</v>
+        <v>36.2</v>
       </c>
       <c r="E139" t="n">
         <v>10</v>
@@ -4241,10 +4241,10 @@
         </is>
       </c>
       <c r="C140" s="7" t="n">
-        <v>107.57978484</v>
+        <v>75</v>
       </c>
       <c r="D140" s="7" t="n">
-        <v>91.44281711399999</v>
+        <v>63.75</v>
       </c>
       <c r="E140" t="n">
         <v>10</v>
@@ -4268,10 +4268,10 @@
         </is>
       </c>
       <c r="C141" s="7" t="n">
-        <v>136.0127571264</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="D141" s="7" t="n">
-        <v>115.61084355744</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="E141" t="n">
         <v>25</v>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="C142" s="7" t="n">
-        <v>216.106704</v>
+        <v>150.66</v>
       </c>
       <c r="D142" s="7" t="n">
-        <v>183.6906984</v>
+        <v>128.06</v>
       </c>
       <c r="E142" t="n">
         <v>5</v>
@@ -4322,10 +4322,10 @@
         </is>
       </c>
       <c r="C143" s="7" t="n">
-        <v>322.826064</v>
+        <v>225.06</v>
       </c>
       <c r="D143" s="7" t="n">
-        <v>274.4021544</v>
+        <v>191.3</v>
       </c>
       <c r="E143" t="n">
         <v>3</v>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="C144" s="7" t="n">
-        <v>504.415725</v>
+        <v>351.66</v>
       </c>
       <c r="D144" s="7" t="n">
-        <v>428.7533662499999</v>
+        <v>298.91</v>
       </c>
       <c r="E144" t="n">
         <v>1</v>
@@ -4374,10 +4374,10 @@
         </is>
       </c>
       <c r="C145" s="7" t="n">
-        <v>735.1896710400001</v>
+        <v>512.54</v>
       </c>
       <c r="D145" s="7" t="n">
-        <v>624.911220384</v>
+        <v>435.66</v>
       </c>
       <c r="E145" t="n">
         <v>1</v>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="C146" s="7" t="n">
-        <v>8.633073750000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="D146" t="n">
-        <v>6.906459000000002</v>
+        <v>6.91</v>
       </c>
       <c r="E146" t="n">
         <v>10</v>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="C147" s="7" t="n">
-        <v>13.96476375</v>
+        <v>13.96</v>
       </c>
       <c r="D147" t="n">
-        <v>11.171811</v>
+        <v>11.17</v>
       </c>
       <c r="E147" t="n">
         <v>10</v>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="C148" s="7" t="n">
-        <v>20.832</v>
+        <v>20.83</v>
       </c>
       <c r="D148" s="7" t="n">
-        <v>16.6656</v>
+        <v>16.67</v>
       </c>
       <c r="E148" t="n">
         <v>5</v>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="C149" s="7" t="n">
-        <v>30.626295</v>
+        <v>30.63</v>
       </c>
       <c r="D149" s="7" t="n">
-        <v>24.501036</v>
+        <v>24.5</v>
       </c>
       <c r="E149" t="n">
         <v>25</v>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="C150" s="7" t="n">
-        <v>37.26649499999999</v>
+        <v>37.27</v>
       </c>
       <c r="D150" s="7" t="n">
-        <v>29.81319599999999</v>
+        <v>29.81</v>
       </c>
       <c r="E150" t="n">
         <v>5</v>
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="C151" s="7" t="n">
-        <v>37.26649499999999</v>
+        <v>37.27</v>
       </c>
       <c r="D151" s="7" t="n">
-        <v>29.81319599999999</v>
+        <v>29.81</v>
       </c>
       <c r="E151" t="n">
         <v>5</v>
@@ -4559,10 +4559,10 @@
         </is>
       </c>
       <c r="C152" s="7" t="n">
-        <v>52.499895</v>
+        <v>52.5</v>
       </c>
       <c r="D152" s="7" t="n">
-        <v>41.999916</v>
+        <v>42</v>
       </c>
       <c r="E152" t="n">
         <v>10</v>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="C153" s="7" t="n">
-        <v>66.37543919999999</v>
+        <v>66.38</v>
       </c>
       <c r="D153" s="7" t="n">
-        <v>53.10035135999999</v>
+        <v>53.1</v>
       </c>
       <c r="E153" t="n">
         <v>2</v>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="C154" s="7" t="n">
-        <v>25.89922125</v>
+        <v>25.9</v>
       </c>
       <c r="D154" s="7" t="n">
-        <v>20.71937700000001</v>
+        <v>20.72</v>
       </c>
       <c r="E154" t="n">
         <v>50</v>
@@ -4638,10 +4638,10 @@
         </is>
       </c>
       <c r="C155" s="7" t="n">
-        <v>41.89429124999999</v>
+        <v>41.89</v>
       </c>
       <c r="D155" s="7" t="n">
-        <v>33.51543299999999</v>
+        <v>33.52</v>
       </c>
       <c r="E155" t="n">
         <v>25</v>
@@ -4665,10 +4665,10 @@
         </is>
       </c>
       <c r="C156" s="7" t="n">
-        <v>62.496</v>
+        <v>62.5</v>
       </c>
       <c r="D156" s="7" t="n">
-        <v>49.99680000000001</v>
+        <v>50</v>
       </c>
       <c r="E156" t="n">
         <v>25</v>
@@ -4692,10 +4692,10 @@
         </is>
       </c>
       <c r="C157" s="7" t="n">
-        <v>91.878885</v>
+        <v>91.88</v>
       </c>
       <c r="D157" s="7" t="n">
-        <v>73.503108</v>
+        <v>73.5</v>
       </c>
       <c r="E157" t="n">
         <v>10</v>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="C158" s="7" t="n">
-        <v>111.799485</v>
+        <v>111.8</v>
       </c>
       <c r="D158" s="7" t="n">
-        <v>89.43958799999999</v>
+        <v>89.44</v>
       </c>
       <c r="E158" t="n">
         <v>10</v>
@@ -4744,10 +4744,10 @@
         </is>
       </c>
       <c r="C159" s="7" t="n">
-        <v>111.799485</v>
+        <v>111.8</v>
       </c>
       <c r="D159" s="7" t="n">
-        <v>89.43958799999999</v>
+        <v>89.44</v>
       </c>
       <c r="E159" t="n">
         <v>10</v>
@@ -4771,10 +4771,10 @@
         </is>
       </c>
       <c r="C160" s="7" t="n">
-        <v>157.499685</v>
+        <v>157.5</v>
       </c>
       <c r="D160" s="7" t="n">
-        <v>125.999748</v>
+        <v>126</v>
       </c>
       <c r="E160" t="n">
         <v>10</v>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="C161" s="7" t="n">
-        <v>199.1263176</v>
+        <v>199.13</v>
       </c>
       <c r="D161" s="7" t="n">
-        <v>159.30105408</v>
+        <v>159.3</v>
       </c>
       <c r="E161" t="n">
         <v>5</v>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="C162" s="8" t="n">
-        <v>1.4588935488</v>
+        <v>1.48</v>
       </c>
       <c r="D162" s="7" t="n">
         <v>1</v>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="C163" s="8" t="n">
-        <v>1.4888873136</v>
+        <v>1.51</v>
       </c>
       <c r="D163" s="7" t="n">
         <v>1</v>
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="C164" s="8" t="n">
-        <v>1.5125666016</v>
+        <v>1.54</v>
       </c>
       <c r="D164" s="7" t="n">
         <v>1</v>
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="C165" s="8" t="n">
-        <v>1.5346672704</v>
+        <v>1.56</v>
       </c>
       <c r="D165" s="7" t="n">
         <v>1</v>
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="C166" s="8" t="n">
-        <v>1.5599251776</v>
+        <v>1.59</v>
       </c>
       <c r="D166" s="7" t="n">
-        <v>1.24794014208</v>
+        <v>1.27</v>
       </c>
       <c r="E166" t="n">
         <v>250</v>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="C167" s="8" t="n">
-        <v>1.6483278528</v>
+        <v>1.69</v>
       </c>
       <c r="D167" s="7" t="n">
-        <v>1.31866228224</v>
+        <v>1.35</v>
       </c>
       <c r="E167" t="n">
         <v>500</v>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="C168" s="8" t="n">
-        <v>1.6941078096</v>
+        <v>1.74</v>
       </c>
       <c r="D168" s="7" t="n">
-        <v>1.35528624768</v>
+        <v>1.39</v>
       </c>
       <c r="E168" t="n">
         <v>250</v>
@@ -5012,10 +5012,10 @@
         </is>
       </c>
       <c r="C169" s="8" t="n">
-        <v>1.7540953392</v>
+        <v>1.8</v>
       </c>
       <c r="D169" s="7" t="n">
-        <v>1.40327627136</v>
+        <v>1.44</v>
       </c>
       <c r="E169" t="n">
         <v>250</v>
@@ -5039,10 +5039,10 @@
         </is>
       </c>
       <c r="C170" s="8" t="n">
-        <v>1.8030325344</v>
+        <v>1.85</v>
       </c>
       <c r="D170" s="7" t="n">
-        <v>1.44242602752</v>
+        <v>1.48</v>
       </c>
       <c r="E170" t="n">
         <v>200</v>
@@ -5066,10 +5066,10 @@
         </is>
       </c>
       <c r="C171" s="8" t="n">
-        <v>1.8724917792</v>
+        <v>1.93</v>
       </c>
       <c r="D171" s="7" t="n">
-        <v>1.49799342336</v>
+        <v>1.54</v>
       </c>
       <c r="E171" t="n">
         <v>500</v>
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="C172" s="8" t="n">
-        <v>1.6187833152</v>
+        <v>1.65</v>
       </c>
       <c r="D172" s="7" t="n">
-        <v>1.29502665216</v>
+        <v>1.32</v>
       </c>
       <c r="E172" t="n">
         <v>250</v>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="C173" s="8" t="n">
-        <v>1.6673008944</v>
+        <v>1.71</v>
       </c>
       <c r="D173" s="7" t="n">
-        <v>1.33384071552</v>
+        <v>1.36</v>
       </c>
       <c r="E173" t="n">
         <v>250</v>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="C174" s="8" t="n">
-        <v>1.7056042464</v>
+        <v>1.75</v>
       </c>
       <c r="D174" s="7" t="n">
-        <v>1.36448339712</v>
+        <v>1.4</v>
       </c>
       <c r="E174" t="n">
         <v>250</v>
@@ -5174,10 +5174,10 @@
         </is>
       </c>
       <c r="C175" s="8" t="n">
-        <v>1.7413540416</v>
+        <v>1.79</v>
       </c>
       <c r="D175" s="7" t="n">
-        <v>1.39308323328</v>
+        <v>1.43</v>
       </c>
       <c r="E175" t="n">
         <v>250</v>
@@ -5201,10 +5201,10 @@
         </is>
       </c>
       <c r="C176" s="8" t="n">
-        <v>1.7822109504</v>
+        <v>1.83</v>
       </c>
       <c r="D176" s="7" t="n">
-        <v>1.42576876032</v>
+        <v>1.46</v>
       </c>
       <c r="E176" t="n">
         <v>250</v>
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="C177" s="8" t="n">
-        <v>1.9252101312</v>
+        <v>1.99</v>
       </c>
       <c r="D177" s="7" t="n">
-        <v>1.54016810496</v>
+        <v>1.59</v>
       </c>
       <c r="E177" t="n">
         <v>250</v>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="C178" s="8" t="n">
-        <v>1.9992632784</v>
+        <v>2.07</v>
       </c>
       <c r="D178" s="7" t="n">
-        <v>1.59941062272</v>
+        <v>1.65</v>
       </c>
       <c r="E178" t="n">
         <v>200</v>
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="C179" s="8" t="n">
-        <v>2.0962984368</v>
+        <v>2.17</v>
       </c>
       <c r="D179" s="7" t="n">
-        <v>1.67703874944</v>
+        <v>1.74</v>
       </c>
       <c r="E179" t="n">
         <v>200</v>
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="C180" s="8" t="n">
-        <v>2.1754586976</v>
+        <v>2.26</v>
       </c>
       <c r="D180" s="7" t="n">
-        <v>1.74036695808</v>
+        <v>1.81</v>
       </c>
       <c r="E180" t="n">
         <v>200</v>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="C181" s="8" t="n">
-        <v>2.2878151968</v>
+        <v>2.38</v>
       </c>
       <c r="D181" s="7" t="n">
-        <v>1.83025215744</v>
+        <v>1.9</v>
       </c>
       <c r="E181" t="n">
         <v>250</v>
@@ -5363,10 +5363,10 @@
         </is>
       </c>
       <c r="C182" s="8" t="n">
-        <v>2.06851584</v>
+        <v>2.14</v>
       </c>
       <c r="D182" s="7" t="n">
-        <v>1.654812672</v>
+        <v>1.71</v>
       </c>
       <c r="E182" t="n">
         <v>250</v>
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="C183" s="8" t="n">
-        <v>2.28183552</v>
+        <v>2.37</v>
       </c>
       <c r="D183" s="7" t="n">
-        <v>1.825468416</v>
+        <v>1.9</v>
       </c>
       <c r="E183" t="n">
         <v>250</v>
@@ -5417,10 +5417,10 @@
         </is>
       </c>
       <c r="C184" s="8" t="n">
-        <v>2.39230464</v>
+        <v>2.49</v>
       </c>
       <c r="D184" s="7" t="n">
-        <v>1.913843712</v>
+        <v>1.99</v>
       </c>
       <c r="E184" t="n">
         <v>150</v>
@@ -5444,10 +5444,10 @@
         </is>
       </c>
       <c r="C185" s="8" t="n">
-        <v>2.53705728</v>
+        <v>2.65</v>
       </c>
       <c r="D185" s="7" t="n">
-        <v>2.029645824</v>
+        <v>2.12</v>
       </c>
       <c r="E185" t="n">
         <v>150</v>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="C186" s="8" t="n">
-        <v>2.65514496</v>
+        <v>2.78</v>
       </c>
       <c r="D186" s="7" t="n">
-        <v>2.124115968</v>
+        <v>2.22</v>
       </c>
       <c r="E186" t="n">
         <v>150</v>
@@ -5498,10 +5498,10 @@
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>2.82275328</v>
+        <v>2.96</v>
       </c>
       <c r="D187" s="7" t="n">
-        <v>2.258202624</v>
+        <v>2.37</v>
       </c>
       <c r="E187" t="n">
         <v>100</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="C188" s="8" t="n">
-        <v>3.18844416</v>
+        <v>3.35</v>
       </c>
       <c r="D188" s="7" t="n">
-        <v>2.550755328</v>
+        <v>2.68</v>
       </c>
       <c r="E188" t="n">
         <v>100</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="C189" s="8" t="n">
-        <v>3.554135039999999</v>
+        <v>3.75</v>
       </c>
       <c r="D189" s="7" t="n">
-        <v>2.843308031999999</v>
+        <v>3</v>
       </c>
       <c r="E189" t="n">
         <v>100</v>
@@ -5579,10 +5579,10 @@
         </is>
       </c>
       <c r="C190" s="8" t="n">
-        <v>4.0379136</v>
+        <v>4.27</v>
       </c>
       <c r="D190" s="7" t="n">
-        <v>3.23033088</v>
+        <v>3.42</v>
       </c>
       <c r="E190" t="n">
         <v>50</v>
@@ -5606,10 +5606,10 @@
         </is>
       </c>
       <c r="C191" s="8" t="n">
-        <v>4.655016959999999</v>
+        <v>4.94</v>
       </c>
       <c r="D191" s="7" t="n">
-        <v>3.724013568</v>
+        <v>3.95</v>
       </c>
       <c r="E191" t="n">
         <v>25</v>
@@ -5633,10 +5633,10 @@
         </is>
       </c>
       <c r="C192" s="8" t="n">
-        <v>4.986424319999999</v>
+        <v>5.3</v>
       </c>
       <c r="D192" s="7" t="n">
-        <v>3.989139456</v>
+        <v>4.24</v>
       </c>
       <c r="E192" t="n">
         <v>10</v>
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="C193" s="8" t="n">
-        <v>4.935302323199999</v>
+        <v>5.1</v>
       </c>
       <c r="D193" s="7" t="n">
-        <v>3.948241858559999</v>
+        <v>4.08</v>
       </c>
       <c r="E193" t="n">
         <v>500</v>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="C194" s="8" t="n">
-        <v>5.132921222399999</v>
+        <v>5.31</v>
       </c>
       <c r="D194" s="7" t="n">
-        <v>4.10633697792</v>
+        <v>4.25</v>
       </c>
       <c r="E194" t="n">
         <v>250</v>
@@ -5714,10 +5714,10 @@
         </is>
       </c>
       <c r="C195" s="8" t="n">
-        <v>5.391870124799999</v>
+        <v>5.59</v>
       </c>
       <c r="D195" s="7" t="n">
-        <v>4.313496099839999</v>
+        <v>4.47</v>
       </c>
       <c r="E195" t="n">
         <v>250</v>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="C196" s="8" t="n">
-        <v>5.603117913599999</v>
+        <v>5.82</v>
       </c>
       <c r="D196" s="7" t="n">
-        <v>4.48249433088</v>
+        <v>4.66</v>
       </c>
       <c r="E196" t="n">
         <v>100</v>
@@ -5768,10 +5768,10 @@
         </is>
       </c>
       <c r="C197" s="8" t="n">
-        <v>5.902953484799999</v>
+        <v>6.14</v>
       </c>
       <c r="D197" s="7" t="n">
-        <v>4.72236278784</v>
+        <v>4.92</v>
       </c>
       <c r="E197" t="n">
         <v>500</v>
@@ -5795,10 +5795,10 @@
         </is>
       </c>
       <c r="C198" s="8" t="n">
-        <v>6.5571401856</v>
+        <v>6.85</v>
       </c>
       <c r="D198" s="7" t="n">
-        <v>5.24571214848</v>
+        <v>5.48</v>
       </c>
       <c r="E198" t="n">
         <v>50</v>
@@ -5822,10 +5822,10 @@
         </is>
       </c>
       <c r="C199" s="8" t="n">
-        <v>7.211326886399999</v>
+        <v>7.56</v>
       </c>
       <c r="D199" s="7" t="n">
-        <v>5.76906150912</v>
+        <v>6.05</v>
       </c>
       <c r="E199" t="n">
         <v>50</v>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="C200" s="8" t="n">
-        <v>8.076761375999999</v>
+        <v>8.5</v>
       </c>
       <c r="D200" s="7" t="n">
-        <v>6.461409100799999</v>
+        <v>6.8</v>
       </c>
       <c r="E200" t="n">
         <v>25</v>
@@ -5876,10 +5876,10 @@
         </is>
       </c>
       <c r="C201" s="8" t="n">
-        <v>9.180701433599999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D201" s="7" t="n">
-        <v>7.34456114688</v>
+        <v>7.76</v>
       </c>
       <c r="E201" t="n">
         <v>25</v>
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="C202" s="8" t="n">
-        <v>9.773558131199998</v>
+        <v>10.34</v>
       </c>
       <c r="D202" s="7" t="n">
-        <v>7.818846504959999</v>
+        <v>8.27</v>
       </c>
       <c r="E202" t="n">
         <v>10</v>
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="C203" s="8" t="n">
-        <v>12.500803917824</v>
+        <v>13.13</v>
       </c>
       <c r="D203" s="7" t="n">
-        <v>10.0006431342592</v>
+        <v>10.5</v>
       </c>
       <c r="E203" t="n">
         <v>25</v>
@@ -5957,10 +5957,10 @@
         </is>
       </c>
       <c r="C204" s="8" t="n">
-        <v>14.04223126016</v>
+        <v>14.8</v>
       </c>
       <c r="D204" s="7" t="n">
-        <v>11.233785008128</v>
+        <v>11.84</v>
       </c>
       <c r="E204" t="n">
         <v>25</v>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="C205" s="8" t="n">
-        <v>16.008461413376</v>
+        <v>16.93</v>
       </c>
       <c r="D205" s="7" t="n">
-        <v>12.8067691307008</v>
+        <v>13.54</v>
       </c>
       <c r="E205" t="n">
         <v>15</v>
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="C206" s="8" t="n">
-        <v>17.064399828992</v>
+        <v>18.07</v>
       </c>
       <c r="D206" s="7" t="n">
-        <v>13.6515198631936</v>
+        <v>14.46</v>
       </c>
       <c r="E206" t="n">
         <v>15</v>
@@ -6038,7 +6038,7 @@
         </is>
       </c>
       <c r="C207" s="7" t="n">
-        <v>1.5451913984</v>
+        <v>1.57</v>
       </c>
       <c r="D207" s="7" t="n">
         <v>1</v>
@@ -6065,10 +6065,10 @@
         </is>
       </c>
       <c r="C208" s="7" t="n">
-        <v>1.5851830848</v>
+        <v>1.61</v>
       </c>
       <c r="D208" s="7" t="n">
-        <v>1.26814646784</v>
+        <v>1.29</v>
       </c>
       <c r="E208" t="n">
         <v>500</v>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="C209" s="7" t="n">
-        <v>1.6167554688</v>
+        <v>1.64</v>
       </c>
       <c r="D209" s="7" t="n">
-        <v>1.29340437504</v>
+        <v>1.31</v>
       </c>
       <c r="E209" t="n">
         <v>250</v>
@@ -6119,10 +6119,10 @@
         </is>
       </c>
       <c r="C210" s="7" t="n">
-        <v>1.6462230272</v>
+        <v>1.67</v>
       </c>
       <c r="D210" s="7" t="n">
-        <v>1.31697842176</v>
+        <v>1.34</v>
       </c>
       <c r="E210" t="n">
         <v>250</v>
@@ -6146,10 +6146,10 @@
         </is>
       </c>
       <c r="C211" s="7" t="n">
-        <v>1.6799002368</v>
+        <v>1.71</v>
       </c>
       <c r="D211" s="7" t="n">
-        <v>1.34392018944</v>
+        <v>1.37</v>
       </c>
       <c r="E211" t="n">
         <v>250</v>
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="C212" s="7" t="n">
-        <v>1.7977704704</v>
+        <v>1.84</v>
       </c>
       <c r="D212" s="7" t="n">
-        <v>1.43821637632</v>
+        <v>1.47</v>
       </c>
       <c r="E212" t="n">
         <v>250</v>
@@ -6200,10 +6200,10 @@
         </is>
       </c>
       <c r="C213" s="7" t="n">
-        <v>1.8588104128</v>
+        <v>1.9</v>
       </c>
       <c r="D213" s="7" t="n">
-        <v>1.48704833024</v>
+        <v>1.52</v>
       </c>
       <c r="E213" t="n">
         <v>250</v>
@@ -6227,10 +6227,10 @@
         </is>
       </c>
       <c r="C214" s="7" t="n">
-        <v>1.9387937856</v>
+        <v>1.98</v>
       </c>
       <c r="D214" s="7" t="n">
-        <v>1.55103502848</v>
+        <v>1.59</v>
       </c>
       <c r="E214" t="n">
         <v>250</v>
@@ -6254,10 +6254,10 @@
         </is>
       </c>
       <c r="C215" s="7" t="n">
-        <v>2.0040433792</v>
+        <v>2.05</v>
       </c>
       <c r="D215" s="7" t="n">
-        <v>1.60323470336</v>
+        <v>1.64</v>
       </c>
       <c r="E215" t="n">
         <v>200</v>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="C216" s="7" t="n">
-        <v>2.0966557056</v>
+        <v>2.15</v>
       </c>
       <c r="D216" s="7" t="n">
-        <v>1.67732456448</v>
+        <v>1.72</v>
       </c>
       <c r="E216" t="n">
         <v>200</v>
@@ -6308,10 +6308,10 @@
         </is>
       </c>
       <c r="C217" s="7" t="n">
-        <v>1.7583777536</v>
+        <v>1.79</v>
       </c>
       <c r="D217" s="7" t="n">
-        <v>1.40670220288</v>
+        <v>1.43</v>
       </c>
       <c r="E217" t="n">
         <v>250</v>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="C218" s="7" t="n">
-        <v>1.8230678592</v>
+        <v>1.86</v>
       </c>
       <c r="D218" s="7" t="n">
-        <v>1.45845428736</v>
+        <v>1.49</v>
       </c>
       <c r="E218" t="n">
         <v>250</v>
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="C219" s="7" t="n">
-        <v>1.8741389952</v>
+        <v>1.92</v>
       </c>
       <c r="D219" s="7" t="n">
-        <v>1.49931119616</v>
+        <v>1.53</v>
       </c>
       <c r="E219" t="n">
         <v>250</v>
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="C220" s="7" t="n">
-        <v>1.9218053888</v>
+        <v>1.97</v>
       </c>
       <c r="D220" s="7" t="n">
-        <v>1.53744431104</v>
+        <v>1.57</v>
       </c>
       <c r="E220" t="n">
         <v>250</v>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="C221" s="7" t="n">
-        <v>1.9762812672</v>
+        <v>2.02</v>
       </c>
       <c r="D221" s="7" t="n">
-        <v>1.58102501376</v>
+        <v>1.62</v>
       </c>
       <c r="E221" t="n">
         <v>250</v>
@@ -6443,10 +6443,10 @@
         </is>
       </c>
       <c r="C222" s="7" t="n">
-        <v>2.1669468416</v>
+        <v>2.23</v>
       </c>
       <c r="D222" s="7" t="n">
-        <v>1.73355747328</v>
+        <v>1.78</v>
       </c>
       <c r="E222" t="n">
         <v>250</v>
@@ -6470,10 +6470,10 @@
         </is>
       </c>
       <c r="C223" s="7" t="n">
-        <v>2.2656843712</v>
+        <v>2.33</v>
       </c>
       <c r="D223" s="7" t="n">
-        <v>1.81254749696</v>
+        <v>1.87</v>
       </c>
       <c r="E223" t="n">
         <v>200</v>
@@ -6497,10 +6497,10 @@
         </is>
       </c>
       <c r="C224" s="7" t="n">
-        <v>2.3950645824</v>
+        <v>2.47</v>
       </c>
       <c r="D224" s="7" t="n">
-        <v>1.91605166592</v>
+        <v>1.98</v>
       </c>
       <c r="E224" t="n">
         <v>200</v>
@@ -6524,10 +6524,10 @@
         </is>
       </c>
       <c r="C225" s="7" t="n">
-        <v>2.5006115968</v>
+        <v>2.58</v>
       </c>
       <c r="D225" s="7" t="n">
-        <v>2.00048927744</v>
+        <v>2.07</v>
       </c>
       <c r="E225" t="n">
         <v>200</v>
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="C226" s="7" t="n">
-        <v>2.6504202624</v>
+        <v>2.74</v>
       </c>
       <c r="D226" s="7" t="n">
-        <v>2.12033620992</v>
+        <v>2.19</v>
       </c>
       <c r="E226" t="n">
         <v>100</v>
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="C227" s="7" t="n">
-        <v>2.35802112</v>
+        <v>2.43</v>
       </c>
       <c r="D227" s="7" t="n">
-        <v>1.886416896</v>
+        <v>1.94</v>
       </c>
       <c r="E227" t="n">
         <v>250</v>
@@ -6605,10 +6605,10 @@
         </is>
       </c>
       <c r="C228" s="7" t="n">
-        <v>2.64244736</v>
+        <v>2.73</v>
       </c>
       <c r="D228" s="7" t="n">
-        <v>2.113957888</v>
+        <v>2.19</v>
       </c>
       <c r="E228" t="n">
         <v>200</v>
@@ -6632,10 +6632,10 @@
         </is>
       </c>
       <c r="C229" s="7" t="n">
-        <v>2.78973952</v>
+        <v>2.89</v>
       </c>
       <c r="D229" s="7" t="n">
-        <v>2.231791616</v>
+        <v>2.31</v>
       </c>
       <c r="E229" t="n">
         <v>150</v>
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="C230" s="7" t="n">
-        <v>2.98274304</v>
+        <v>3.09</v>
       </c>
       <c r="D230" s="7" t="n">
-        <v>2.386194432</v>
+        <v>2.48</v>
       </c>
       <c r="E230" t="n">
         <v>150</v>
@@ -6686,10 +6686,10 @@
         </is>
       </c>
       <c r="C231" s="7" t="n">
-        <v>3.14019328</v>
+        <v>3.26</v>
       </c>
       <c r="D231" s="7" t="n">
-        <v>2.512154624</v>
+        <v>2.61</v>
       </c>
       <c r="E231" t="n">
         <v>150</v>
@@ -6713,10 +6713,10 @@
         </is>
       </c>
       <c r="C232" s="7" t="n">
-        <v>3.36367104</v>
+        <v>3.5</v>
       </c>
       <c r="D232" s="7" t="n">
-        <v>2.690936832</v>
+        <v>2.8</v>
       </c>
       <c r="E232" t="n">
         <v>100</v>
@@ -6740,10 +6740,10 @@
         </is>
       </c>
       <c r="C233" s="7" t="n">
-        <v>3.85125888</v>
+        <v>4.02</v>
       </c>
       <c r="D233" s="7" t="n">
-        <v>3.081007104000001</v>
+        <v>3.21</v>
       </c>
       <c r="E233" t="n">
         <v>100</v>
@@ -6767,10 +6767,10 @@
         </is>
       </c>
       <c r="C234" s="7" t="n">
-        <v>4.33884672</v>
+        <v>4.54</v>
       </c>
       <c r="D234" s="7" t="n">
-        <v>3.471077376</v>
+        <v>3.63</v>
       </c>
       <c r="E234" t="n">
         <v>100</v>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="C235" s="7" t="n">
-        <v>4.9838848</v>
+        <v>5.22</v>
       </c>
       <c r="D235" s="7" t="n">
-        <v>3.98710784</v>
+        <v>4.18</v>
       </c>
       <c r="E235" t="n">
         <v>50</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="C236" s="7" t="n">
-        <v>5.806689280000001</v>
+        <v>6.09</v>
       </c>
       <c r="D236" s="7" t="n">
-        <v>4.645351424</v>
+        <v>4.88</v>
       </c>
       <c r="E236" t="n">
         <v>25</v>
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="C237" s="7" t="n">
-        <v>6.24856576</v>
+        <v>6.56</v>
       </c>
       <c r="D237" s="7" t="n">
-        <v>4.998852608</v>
+        <v>5.25</v>
       </c>
       <c r="E237" t="n">
         <v>10</v>
@@ -6875,10 +6875,10 @@
         </is>
       </c>
       <c r="C238" s="7" t="n">
-        <v>5.5804030976</v>
+        <v>5.74</v>
       </c>
       <c r="D238" s="7" t="n">
-        <v>4.46432247808</v>
+        <v>4.59</v>
       </c>
       <c r="E238" t="n">
         <v>100</v>
@@ -6902,10 +6902,10 @@
         </is>
       </c>
       <c r="C239" s="7" t="n">
-        <v>5.843894963199999</v>
+        <v>6.02</v>
       </c>
       <c r="D239" s="7" t="n">
-        <v>4.675115970559999</v>
+        <v>4.82</v>
       </c>
       <c r="E239" t="n">
         <v>100</v>
@@ -6929,10 +6929,10 @@
         </is>
       </c>
       <c r="C240" s="7" t="n">
-        <v>6.189160166399999</v>
+        <v>6.39</v>
       </c>
       <c r="D240" s="7" t="n">
-        <v>4.95132813312</v>
+        <v>5.11</v>
       </c>
       <c r="E240" t="n">
         <v>100</v>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="C241" s="7" t="n">
-        <v>6.4708238848</v>
+        <v>6.69</v>
       </c>
       <c r="D241" s="7" t="n">
-        <v>5.17665910784</v>
+        <v>5.35</v>
       </c>
       <c r="E241" t="n">
         <v>100</v>
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="C242" s="7" t="n">
-        <v>6.870604646399999</v>
+        <v>7.11</v>
       </c>
       <c r="D242" s="7" t="n">
-        <v>5.496483717119999</v>
+        <v>5.69</v>
       </c>
       <c r="E242" t="n">
         <v>50</v>
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="C243" s="7" t="n">
-        <v>7.742853580799999</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="D243" s="7" t="n">
-        <v>6.19428286464</v>
+        <v>6.43</v>
       </c>
       <c r="E243" t="n">
         <v>50</v>
@@ -7037,10 +7037,10 @@
         </is>
       </c>
       <c r="C244" s="7" t="n">
-        <v>8.6151025152</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="D244" s="7" t="n">
-        <v>6.89208201216</v>
+        <v>7.17</v>
       </c>
       <c r="E244" t="n">
         <v>50</v>
@@ -7064,10 +7064,10 @@
         </is>
       </c>
       <c r="C245" s="7" t="n">
-        <v>9.769015167999999</v>
+        <v>10.19</v>
       </c>
       <c r="D245" s="7" t="n">
-        <v>7.815212134399999</v>
+        <v>8.15</v>
       </c>
       <c r="E245" t="n">
         <v>25</v>
@@ -7091,10 +7091,10 @@
         </is>
       </c>
       <c r="C246" s="7" t="n">
-        <v>11.2409352448</v>
+        <v>11.76</v>
       </c>
       <c r="D246" s="7" t="n">
-        <v>8.992748195839999</v>
+        <v>9.4</v>
       </c>
       <c r="E246" t="n">
         <v>25</v>
@@ -7118,10 +7118,10 @@
         </is>
       </c>
       <c r="C247" s="7" t="n">
-        <v>12.0314108416</v>
+        <v>12.6</v>
       </c>
       <c r="D247" s="7" t="n">
-        <v>9.625128673279999</v>
+        <v>10.08</v>
       </c>
       <c r="E247" t="n">
         <v>10</v>
@@ -7145,10 +7145,10 @@
         </is>
       </c>
       <c r="C248" s="7" t="n">
-        <v>15.001071890432</v>
+        <v>15.63</v>
       </c>
       <c r="D248" s="7" t="n">
-        <v>12.0008575123456</v>
+        <v>12.5</v>
       </c>
       <c r="E248" t="n">
         <v>25</v>
@@ -7172,10 +7172,10 @@
         </is>
       </c>
       <c r="C249" s="7" t="n">
-        <v>17.05630834688</v>
+        <v>17.81</v>
       </c>
       <c r="D249" s="7" t="n">
-        <v>13.645046677504</v>
+        <v>14.25</v>
       </c>
       <c r="E249" t="n">
         <v>25</v>
@@ -7199,10 +7199,10 @@
         </is>
       </c>
       <c r="C250" s="7" t="n">
-        <v>19.677948551168</v>
+        <v>20.6</v>
       </c>
       <c r="D250" s="7" t="n">
-        <v>15.7423588409344</v>
+        <v>16.48</v>
       </c>
       <c r="E250" t="n">
         <v>15</v>
@@ -7226,10 +7226,10 @@
         </is>
       </c>
       <c r="C251" s="7" t="n">
-        <v>21.085866438656</v>
+        <v>22.09</v>
       </c>
       <c r="D251" s="7" t="n">
-        <v>16.8686931509248</v>
+        <v>17.67</v>
       </c>
       <c r="E251" t="n">
         <v>15</v>
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="C252" s="7" t="n">
-        <v>3.0903827968</v>
+        <v>3.13</v>
       </c>
       <c r="D252" s="7" t="n">
-        <v>2.47230623744</v>
+        <v>2.51</v>
       </c>
       <c r="E252" t="n">
         <v>500</v>
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="C253" s="7" t="n">
-        <v>3.1703661696</v>
+        <v>3.22</v>
       </c>
       <c r="D253" s="7" t="n">
-        <v>2.53629293568</v>
+        <v>2.57</v>
       </c>
       <c r="E253" t="n">
         <v>500</v>
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="C254" s="7" t="n">
-        <v>3.2335109376</v>
+        <v>3.29</v>
       </c>
       <c r="D254" s="7" t="n">
-        <v>2.58680875008</v>
+        <v>2.63</v>
       </c>
       <c r="E254" t="n">
         <v>250</v>
@@ -7334,10 +7334,10 @@
         </is>
       </c>
       <c r="C255" s="7" t="n">
-        <v>3.2924460544</v>
+        <v>3.35</v>
       </c>
       <c r="D255" s="7" t="n">
-        <v>2.63395684352</v>
+        <v>2.68</v>
       </c>
       <c r="E255" t="n">
         <v>250</v>
@@ -7359,10 +7359,10 @@
         </is>
       </c>
       <c r="C256" s="7" t="n">
-        <v>3.3598004736</v>
+        <v>3.42</v>
       </c>
       <c r="D256" s="7" t="n">
-        <v>2.68784037888</v>
+        <v>2.74</v>
       </c>
       <c r="E256" t="n">
         <v>250</v>
@@ -7386,10 +7386,10 @@
         </is>
       </c>
       <c r="C257" s="7" t="n">
-        <v>3.5955409408</v>
+        <v>3.67</v>
       </c>
       <c r="D257" s="7" t="n">
-        <v>2.87643275264</v>
+        <v>2.94</v>
       </c>
       <c r="E257" t="n">
         <v>500</v>
@@ -7413,10 +7413,10 @@
         </is>
       </c>
       <c r="C258" s="7" t="n">
-        <v>3.7176208256</v>
+        <v>3.8</v>
       </c>
       <c r="D258" s="7" t="n">
-        <v>2.97409666048</v>
+        <v>3.04</v>
       </c>
       <c r="E258" t="n">
         <v>250</v>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="C259" s="7" t="n">
-        <v>3.8775875712</v>
+        <v>3.97</v>
       </c>
       <c r="D259" s="7" t="n">
-        <v>3.102070056960001</v>
+        <v>3.18</v>
       </c>
       <c r="E259" t="n">
         <v>250</v>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="C260" s="7" t="n">
-        <v>4.0080867584</v>
+        <v>4.11</v>
       </c>
       <c r="D260" s="7" t="n">
-        <v>3.20646940672</v>
+        <v>3.29</v>
       </c>
       <c r="E260" t="n">
         <v>200</v>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="C261" s="7" t="n">
-        <v>4.1933114112</v>
+        <v>4.31</v>
       </c>
       <c r="D261" s="7" t="n">
-        <v>3.35464912896</v>
+        <v>3.44</v>
       </c>
       <c r="E261" t="n">
         <v>500</v>
@@ -7517,10 +7517,10 @@
         </is>
       </c>
       <c r="C262" s="7" t="n">
-        <v>3.5167555072</v>
+        <v>3.59</v>
       </c>
       <c r="D262" s="7" t="n">
-        <v>2.81340440576</v>
+        <v>2.87</v>
       </c>
       <c r="E262" t="n">
         <v>250</v>
@@ -7544,10 +7544,10 @@
         </is>
       </c>
       <c r="C263" s="7" t="n">
-        <v>3.6461357184</v>
+        <v>3.72</v>
       </c>
       <c r="D263" s="7" t="n">
-        <v>2.91690857472</v>
+        <v>2.98</v>
       </c>
       <c r="E263" t="n">
         <v>250</v>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="C264" s="7" t="n">
-        <v>3.7482779904</v>
+        <v>3.83</v>
       </c>
       <c r="D264" s="7" t="n">
-        <v>2.99862239232</v>
+        <v>3.07</v>
       </c>
       <c r="E264" t="n">
         <v>250</v>
@@ -7598,10 +7598,10 @@
         </is>
       </c>
       <c r="C265" s="7" t="n">
-        <v>3.843610777599999</v>
+        <v>3.93</v>
       </c>
       <c r="D265" s="7" t="n">
-        <v>3.07488862208</v>
+        <v>3.15</v>
       </c>
       <c r="E265" t="n">
         <v>250</v>
@@ -7625,10 +7625,10 @@
         </is>
       </c>
       <c r="C266" s="7" t="n">
-        <v>3.9525625344</v>
+        <v>4.05</v>
       </c>
       <c r="D266" s="7" t="n">
-        <v>3.16205002752</v>
+        <v>3.24</v>
       </c>
       <c r="E266" t="n">
         <v>250</v>
@@ -7652,10 +7652,10 @@
         </is>
       </c>
       <c r="C267" s="7" t="n">
-        <v>4.333893683199999</v>
+        <v>4.45</v>
       </c>
       <c r="D267" s="7" t="n">
-        <v>3.46711494656</v>
+        <v>3.56</v>
       </c>
       <c r="E267" t="n">
         <v>250</v>
@@ -7679,10 +7679,10 @@
         </is>
       </c>
       <c r="C268" s="7" t="n">
-        <v>4.5313687424</v>
+        <v>4.66</v>
       </c>
       <c r="D268" s="7" t="n">
-        <v>3.62509499392</v>
+        <v>3.73</v>
       </c>
       <c r="E268" t="n">
         <v>200</v>
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="C269" s="7" t="n">
-        <v>4.7901291648</v>
+        <v>4.94</v>
       </c>
       <c r="D269" s="7" t="n">
-        <v>3.83210333184</v>
+        <v>3.95</v>
       </c>
       <c r="E269" t="n">
         <v>200</v>
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="C270" s="7" t="n">
-        <v>5.0012231936</v>
+        <v>5.16</v>
       </c>
       <c r="D270" s="7" t="n">
-        <v>4.00097855488</v>
+        <v>4.13</v>
       </c>
       <c r="E270" t="n">
         <v>200</v>
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="C271" s="7" t="n">
-        <v>5.3008405248</v>
+        <v>5.48</v>
       </c>
       <c r="D271" s="7" t="n">
-        <v>4.24067241984</v>
+        <v>4.39</v>
       </c>
       <c r="E271" t="n">
         <v>250</v>
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="C272" s="7" t="n">
-        <v>4.71604224</v>
+        <v>4.86</v>
       </c>
       <c r="D272" s="7" t="n">
-        <v>3.772833792</v>
+        <v>3.89</v>
       </c>
       <c r="E272" t="n">
         <v>250</v>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="C273" s="7" t="n">
-        <v>5.28489472</v>
+        <v>5.47</v>
       </c>
       <c r="D273" s="7" t="n">
-        <v>4.227915776000001</v>
+        <v>4.37</v>
       </c>
       <c r="E273" t="n">
         <v>250</v>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="C274" s="7" t="n">
-        <v>5.579479040000001</v>
+        <v>5.78</v>
       </c>
       <c r="D274" s="7" t="n">
-        <v>4.463583232</v>
+        <v>4.62</v>
       </c>
       <c r="E274" t="n">
         <v>150</v>
@@ -7868,10 +7868,10 @@
         </is>
       </c>
       <c r="C275" s="7" t="n">
-        <v>5.96548608</v>
+        <v>6.19</v>
       </c>
       <c r="D275" s="7" t="n">
-        <v>4.772388864</v>
+        <v>4.95</v>
       </c>
       <c r="E275" t="n">
         <v>150</v>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="C276" s="7" t="n">
-        <v>6.28038656</v>
+        <v>6.52</v>
       </c>
       <c r="D276" s="7" t="n">
-        <v>5.024309248000001</v>
+        <v>5.22</v>
       </c>
       <c r="E276" t="n">
         <v>150</v>
@@ -7920,10 +7920,10 @@
         </is>
       </c>
       <c r="C277" s="7" t="n">
-        <v>6.72734208</v>
+        <v>7</v>
       </c>
       <c r="D277" s="7" t="n">
-        <v>5.381873664</v>
+        <v>5.6</v>
       </c>
       <c r="E277" t="n">
         <v>100</v>
@@ -7947,10 +7947,10 @@
         </is>
       </c>
       <c r="C278" s="7" t="n">
-        <v>7.702517760000001</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="D278" s="7" t="n">
-        <v>6.162014208000001</v>
+        <v>6.43</v>
       </c>
       <c r="E278" t="n">
         <v>100</v>
@@ -7974,10 +7974,10 @@
         </is>
       </c>
       <c r="C279" s="7" t="n">
-        <v>8.677693440000001</v>
+        <v>9.07</v>
       </c>
       <c r="D279" s="7" t="n">
-        <v>6.942154752</v>
+        <v>7.26</v>
       </c>
       <c r="E279" t="n">
         <v>100</v>
@@ -8001,10 +8001,10 @@
         </is>
       </c>
       <c r="C280" s="7" t="n">
-        <v>9.9677696</v>
+        <v>10.44</v>
       </c>
       <c r="D280" s="7" t="n">
-        <v>7.97421568</v>
+        <v>8.35</v>
       </c>
       <c r="E280" t="n">
         <v>50</v>
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="C281" s="7" t="n">
-        <v>11.61337856</v>
+        <v>12.19</v>
       </c>
       <c r="D281" s="7" t="n">
-        <v>9.290702848</v>
+        <v>9.75</v>
       </c>
       <c r="E281" t="n">
         <v>25</v>
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="C282" s="7" t="n">
-        <v>12.49713152</v>
+        <v>13.13</v>
       </c>
       <c r="D282" s="7" t="n">
-        <v>9.997705216</v>
+        <v>10.5</v>
       </c>
       <c r="E282" t="n">
         <v>10</v>
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="C283" s="7" t="n">
-        <v>11.1608061952</v>
+        <v>11.48</v>
       </c>
       <c r="D283" s="7" t="n">
-        <v>8.928644956159999</v>
+        <v>9.19</v>
       </c>
       <c r="E283" t="n">
         <v>500</v>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="C284" s="7" t="n">
-        <v>11.6877899264</v>
+        <v>12.04</v>
       </c>
       <c r="D284" s="7" t="n">
-        <v>9.350231941119999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E284" t="n">
         <v>250</v>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="C285" s="7" t="n">
-        <v>12.3783203328</v>
+        <v>12.78</v>
       </c>
       <c r="D285" s="7" t="n">
-        <v>9.902656266239999</v>
+        <v>10.22</v>
       </c>
       <c r="E285" t="n">
         <v>250</v>
@@ -8161,10 +8161,10 @@
         </is>
       </c>
       <c r="C286" s="7" t="n">
-        <v>12.9416477696</v>
+        <v>13.38</v>
       </c>
       <c r="D286" s="7" t="n">
-        <v>10.35331821568</v>
+        <v>10.7</v>
       </c>
       <c r="E286" t="n">
         <v>200</v>
@@ -8186,10 +8186,10 @@
         </is>
       </c>
       <c r="C287" s="7" t="n">
-        <v>13.7412092928</v>
+        <v>14.23</v>
       </c>
       <c r="D287" s="7" t="n">
-        <v>10.99296743424</v>
+        <v>11.38</v>
       </c>
       <c r="E287" t="n">
         <v>500</v>
@@ -8213,10 +8213,10 @@
         </is>
       </c>
       <c r="C288" s="7" t="n">
-        <v>15.4857071616</v>
+        <v>16.08</v>
       </c>
       <c r="D288" s="7" t="n">
-        <v>12.38856572928</v>
+        <v>12.86</v>
       </c>
       <c r="E288" t="n">
         <v>50</v>
@@ -8240,10 +8240,10 @@
         </is>
       </c>
       <c r="C289" s="7" t="n">
-        <v>17.2302050304</v>
+        <v>17.93</v>
       </c>
       <c r="D289" s="7" t="n">
-        <v>13.78416402432</v>
+        <v>14.35</v>
       </c>
       <c r="E289" t="n">
         <v>50</v>
@@ -8267,10 +8267,10 @@
         </is>
       </c>
       <c r="C290" s="7" t="n">
-        <v>19.538030336</v>
+        <v>20.38</v>
       </c>
       <c r="D290" s="7" t="n">
-        <v>15.6304242688</v>
+        <v>16.31</v>
       </c>
       <c r="E290" t="n">
         <v>25</v>
@@ -8294,10 +8294,10 @@
         </is>
       </c>
       <c r="C291" s="7" t="n">
-        <v>22.4818704896</v>
+        <v>23.51</v>
       </c>
       <c r="D291" s="7" t="n">
-        <v>17.98549639168</v>
+        <v>18.81</v>
       </c>
       <c r="E291" t="n">
         <v>25</v>
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="C292" s="7" t="n">
-        <v>24.0628216832</v>
+        <v>25.19</v>
       </c>
       <c r="D292" s="7" t="n">
-        <v>19.25025734656</v>
+        <v>20.15</v>
       </c>
       <c r="E292" t="n">
         <v>10</v>
@@ -8348,10 +8348,10 @@
         </is>
       </c>
       <c r="C293" s="7" t="n">
-        <v>30.002143780864</v>
+        <v>31.25</v>
       </c>
       <c r="D293" s="7" t="n">
-        <v>24.0017150246912</v>
+        <v>25</v>
       </c>
       <c r="E293" t="n">
         <v>25</v>
@@ -8375,10 +8375,10 @@
         </is>
       </c>
       <c r="C294" s="7" t="n">
-        <v>34.11261669376</v>
+        <v>35.62</v>
       </c>
       <c r="D294" s="7" t="n">
-        <v>27.290093355008</v>
+        <v>28.5</v>
       </c>
       <c r="E294" t="n">
         <v>25</v>
@@ -8402,10 +8402,10 @@
         </is>
       </c>
       <c r="C295" s="7" t="n">
-        <v>39.355897102336</v>
+        <v>41.19</v>
       </c>
       <c r="D295" s="7" t="n">
-        <v>31.4847176818688</v>
+        <v>32.95</v>
       </c>
       <c r="E295" t="n">
         <v>15</v>
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="C296" s="7" t="n">
-        <v>42.171732877312</v>
+        <v>44.18</v>
       </c>
       <c r="D296" s="7" t="n">
-        <v>33.7373863018496</v>
+        <v>35.35</v>
       </c>
       <c r="E296" t="n">
         <v>15</v>
@@ -8454,10 +8454,10 @@
         </is>
       </c>
       <c r="C297" s="7" t="n">
-        <v>1.6905913984</v>
+        <v>1.71</v>
       </c>
       <c r="D297" s="7" t="n">
-        <v>1.1454</v>
+        <v>1.15</v>
       </c>
       <c r="E297" t="n">
         <v>500</v>
@@ -8481,10 +8481,10 @@
         </is>
       </c>
       <c r="C298" s="7" t="n">
-        <v>1.7305830848</v>
+        <v>1.75</v>
       </c>
       <c r="D298" s="7" t="n">
-        <v>1.41354646784</v>
+        <v>1.43</v>
       </c>
       <c r="E298" t="n">
         <v>500</v>
@@ -8508,10 +8508,10 @@
         </is>
       </c>
       <c r="C299" s="7" t="n">
-        <v>1.7621554688</v>
+        <v>1.79</v>
       </c>
       <c r="D299" s="7" t="n">
-        <v>1.43880437504</v>
+        <v>1.46</v>
       </c>
       <c r="E299" t="n">
         <v>250</v>
@@ -8535,10 +8535,10 @@
         </is>
       </c>
       <c r="C300" s="7" t="n">
-        <v>1.7916230272</v>
+        <v>1.82</v>
       </c>
       <c r="D300" s="7" t="n">
-        <v>1.46237842176</v>
+        <v>1.48</v>
       </c>
       <c r="E300" t="n">
         <v>250</v>
@@ -8562,10 +8562,10 @@
         </is>
       </c>
       <c r="C301" s="7" t="n">
-        <v>1.8253002368</v>
+        <v>1.86</v>
       </c>
       <c r="D301" s="7" t="n">
-        <v>1.48932018944</v>
+        <v>1.51</v>
       </c>
       <c r="E301" t="n">
         <v>250</v>
@@ -8589,10 +8589,10 @@
         </is>
       </c>
       <c r="C302" s="7" t="n">
-        <v>1.9431704704</v>
+        <v>1.98</v>
       </c>
       <c r="D302" s="7" t="n">
-        <v>1.58361637632</v>
+        <v>1.61</v>
       </c>
       <c r="E302" t="n">
         <v>250</v>
@@ -8616,10 +8616,10 @@
         </is>
       </c>
       <c r="C303" s="7" t="n">
-        <v>2.0042104128</v>
+        <v>2.05</v>
       </c>
       <c r="D303" s="7" t="n">
-        <v>1.63244833024</v>
+        <v>1.67</v>
       </c>
       <c r="E303" t="n">
         <v>250</v>
@@ -8643,10 +8643,10 @@
         </is>
       </c>
       <c r="C304" s="7" t="n">
-        <v>2.0841937856</v>
+        <v>2.13</v>
       </c>
       <c r="D304" s="7" t="n">
-        <v>1.69643502848</v>
+        <v>1.73</v>
       </c>
       <c r="E304" t="n">
         <v>250</v>
@@ -8670,10 +8670,10 @@
         </is>
       </c>
       <c r="C305" s="7" t="n">
-        <v>2.1494433792</v>
+        <v>2.2</v>
       </c>
       <c r="D305" s="7" t="n">
-        <v>1.74863470336</v>
+        <v>1.79</v>
       </c>
       <c r="E305" t="n">
         <v>200</v>
@@ -8697,10 +8697,10 @@
         </is>
       </c>
       <c r="C306" s="7" t="n">
-        <v>2.2420557056</v>
+        <v>2.3</v>
       </c>
       <c r="D306" s="7" t="n">
-        <v>1.82272456448</v>
+        <v>1.87</v>
       </c>
       <c r="E306" t="n">
         <v>200</v>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="C307" s="7" t="n">
-        <v>1.9683777536</v>
+        <v>2</v>
       </c>
       <c r="D307" s="7" t="n">
-        <v>1.61670220288</v>
+        <v>1.64</v>
       </c>
       <c r="E307" t="n">
         <v>250</v>
@@ -8751,10 +8751,10 @@
         </is>
       </c>
       <c r="C308" s="7" t="n">
-        <v>2.0330678592</v>
+        <v>2.07</v>
       </c>
       <c r="D308" s="7" t="n">
-        <v>1.66845428736</v>
+        <v>1.7</v>
       </c>
       <c r="E308" t="n">
         <v>250</v>
@@ -8778,10 +8778,10 @@
         </is>
       </c>
       <c r="C309" s="7" t="n">
-        <v>2.0841389952</v>
+        <v>2.13</v>
       </c>
       <c r="D309" s="7" t="n">
-        <v>1.70931119616</v>
+        <v>1.74</v>
       </c>
       <c r="E309" t="n">
         <v>250</v>
@@ -8805,10 +8805,10 @@
         </is>
       </c>
       <c r="C310" s="7" t="n">
-        <v>2.1318053888</v>
+        <v>2.18</v>
       </c>
       <c r="D310" s="7" t="n">
-        <v>1.74744431104</v>
+        <v>1.78</v>
       </c>
       <c r="E310" t="n">
         <v>250</v>
@@ -8832,10 +8832,10 @@
         </is>
       </c>
       <c r="C311" s="7" t="n">
-        <v>2.1862812672</v>
+        <v>2.23</v>
       </c>
       <c r="D311" s="7" t="n">
-        <v>1.79102501376</v>
+        <v>1.83</v>
       </c>
       <c r="E311" t="n">
         <v>250</v>
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="C312" s="7" t="n">
-        <v>2.3769468416</v>
+        <v>2.44</v>
       </c>
       <c r="D312" s="7" t="n">
-        <v>1.94355747328</v>
+        <v>1.99</v>
       </c>
       <c r="E312" t="n">
         <v>250</v>
@@ -8886,10 +8886,10 @@
         </is>
       </c>
       <c r="C313" s="7" t="n">
-        <v>2.4756843712</v>
+        <v>2.54</v>
       </c>
       <c r="D313" s="7" t="n">
-        <v>2.02254749696</v>
+        <v>2.08</v>
       </c>
       <c r="E313" t="n">
         <v>200</v>
@@ -8913,10 +8913,10 @@
         </is>
       </c>
       <c r="C314" s="7" t="n">
-        <v>2.6050645824</v>
+        <v>2.68</v>
       </c>
       <c r="D314" s="7" t="n">
-        <v>2.12605166592</v>
+        <v>2.19</v>
       </c>
       <c r="E314" t="n">
         <v>200</v>
@@ -8940,10 +8940,10 @@
         </is>
       </c>
       <c r="C315" s="7" t="n">
-        <v>2.7106115968</v>
+        <v>2.79</v>
       </c>
       <c r="D315" s="7" t="n">
-        <v>2.21048927744</v>
+        <v>2.28</v>
       </c>
       <c r="E315" t="n">
         <v>200</v>
@@ -8967,10 +8967,10 @@
         </is>
       </c>
       <c r="C316" s="7" t="n">
-        <v>2.8604202624</v>
+        <v>2.95</v>
       </c>
       <c r="D316" s="7" t="n">
-        <v>2.33033620992</v>
+        <v>2.4</v>
       </c>
       <c r="E316" t="n">
         <v>100</v>
@@ -8994,10 +8994,10 @@
         </is>
       </c>
       <c r="C317" s="7" t="n">
-        <v>2.64562112</v>
+        <v>2.72</v>
       </c>
       <c r="D317" s="7" t="n">
-        <v>2.174016896</v>
+        <v>2.23</v>
       </c>
       <c r="E317" t="n">
         <v>250</v>
@@ -9021,10 +9021,10 @@
         </is>
       </c>
       <c r="C318" s="7" t="n">
-        <v>2.93004736</v>
+        <v>3.02</v>
       </c>
       <c r="D318" s="7" t="n">
-        <v>2.401557888</v>
+        <v>2.47</v>
       </c>
       <c r="E318" t="n">
         <v>200</v>
@@ -9048,10 +9048,10 @@
         </is>
       </c>
       <c r="C319" s="7" t="n">
-        <v>3.07733952</v>
+        <v>3.18</v>
       </c>
       <c r="D319" s="7" t="n">
-        <v>2.519391616</v>
+        <v>2.6</v>
       </c>
       <c r="E319" t="n">
         <v>150</v>
@@ -9075,10 +9075,10 @@
         </is>
       </c>
       <c r="C320" s="7" t="n">
-        <v>3.27034304</v>
+        <v>3.38</v>
       </c>
       <c r="D320" s="7" t="n">
-        <v>2.673794432</v>
+        <v>2.76</v>
       </c>
       <c r="E320" t="n">
         <v>150</v>
@@ -9102,10 +9102,10 @@
         </is>
       </c>
       <c r="C321" s="7" t="n">
-        <v>3.42779328</v>
+        <v>3.55</v>
       </c>
       <c r="D321" s="7" t="n">
-        <v>2.799754624</v>
+        <v>2.9</v>
       </c>
       <c r="E321" t="n">
         <v>150</v>
@@ -9129,10 +9129,10 @@
         </is>
       </c>
       <c r="C322" s="7" t="n">
-        <v>3.65127104</v>
+        <v>3.79</v>
       </c>
       <c r="D322" s="7" t="n">
-        <v>2.978536832</v>
+        <v>3.09</v>
       </c>
       <c r="E322" t="n">
         <v>100</v>
@@ -9156,10 +9156,10 @@
         </is>
       </c>
       <c r="C323" s="7" t="n">
-        <v>4.138858880000001</v>
+        <v>4.3</v>
       </c>
       <c r="D323" s="7" t="n">
-        <v>3.368607104000001</v>
+        <v>3.5</v>
       </c>
       <c r="E323" t="n">
         <v>100</v>
@@ -9183,10 +9183,10 @@
         </is>
       </c>
       <c r="C324" s="7" t="n">
-        <v>4.626446720000001</v>
+        <v>4.82</v>
       </c>
       <c r="D324" s="7" t="n">
-        <v>3.758677376</v>
+        <v>3.92</v>
       </c>
       <c r="E324" t="n">
         <v>100</v>
@@ -9210,10 +9210,10 @@
         </is>
       </c>
       <c r="C325" s="7" t="n">
-        <v>5.271484800000001</v>
+        <v>5.51</v>
       </c>
       <c r="D325" s="7" t="n">
-        <v>4.27470784</v>
+        <v>4.46</v>
       </c>
       <c r="E325" t="n">
         <v>50</v>
@@ -9237,10 +9237,10 @@
         </is>
       </c>
       <c r="C326" s="7" t="n">
-        <v>6.094289280000001</v>
+        <v>6.38</v>
       </c>
       <c r="D326" s="7" t="n">
-        <v>4.932951424000001</v>
+        <v>5.16</v>
       </c>
       <c r="E326" t="n">
         <v>25</v>
@@ -9264,10 +9264,10 @@
         </is>
       </c>
       <c r="C327" s="7" t="n">
-        <v>6.53616576</v>
+        <v>6.85</v>
       </c>
       <c r="D327" s="7" t="n">
-        <v>5.286452608</v>
+        <v>5.54</v>
       </c>
       <c r="E327" t="n">
         <v>10</v>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="C328" s="7" t="n">
-        <v>6.392603097599999</v>
+        <v>6.55</v>
       </c>
       <c r="D328" s="7" t="n">
-        <v>5.27652247808</v>
+        <v>5.41</v>
       </c>
       <c r="E328" t="n">
         <v>100</v>
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="C329" s="7" t="n">
-        <v>6.656094963199999</v>
+        <v>6.83</v>
       </c>
       <c r="D329" s="7" t="n">
-        <v>5.487315970559999</v>
+        <v>5.63</v>
       </c>
       <c r="E329" t="n">
         <v>100</v>
@@ -9345,10 +9345,10 @@
         </is>
       </c>
       <c r="C330" s="7" t="n">
-        <v>7.001360166399999</v>
+        <v>7.2</v>
       </c>
       <c r="D330" s="7" t="n">
-        <v>5.763528133119999</v>
+        <v>5.92</v>
       </c>
       <c r="E330" t="n">
         <v>250</v>
@@ -9370,10 +9370,10 @@
         </is>
       </c>
       <c r="C331" s="7" t="n">
-        <v>7.2830238848</v>
+        <v>7.5</v>
       </c>
       <c r="D331" s="7" t="n">
-        <v>5.98885910784</v>
+        <v>6.16</v>
       </c>
       <c r="E331" t="n">
         <v>200</v>
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="C332" s="7" t="n">
-        <v>7.682804646399998</v>
+        <v>7.92</v>
       </c>
       <c r="D332" s="7" t="n">
-        <v>6.308683717119999</v>
+        <v>6.5</v>
       </c>
       <c r="E332" t="n">
         <v>50</v>
@@ -9424,10 +9424,10 @@
         </is>
       </c>
       <c r="C333" s="7" t="n">
-        <v>8.555053580799999</v>
+        <v>8.85</v>
       </c>
       <c r="D333" s="7" t="n">
-        <v>7.00648286464</v>
+        <v>7.24</v>
       </c>
       <c r="E333" t="n">
         <v>50</v>
@@ -9451,10 +9451,10 @@
         </is>
       </c>
       <c r="C334" s="7" t="n">
-        <v>9.427302515200001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="D334" s="7" t="n">
-        <v>7.70428201216</v>
+        <v>7.99</v>
       </c>
       <c r="E334" t="n">
         <v>50</v>
@@ -9478,10 +9478,10 @@
         </is>
       </c>
       <c r="C335" s="7" t="n">
-        <v>10.581215168</v>
+        <v>11</v>
       </c>
       <c r="D335" s="7" t="n">
-        <v>8.6274121344</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="E335" t="n">
         <v>25</v>
@@ -9505,10 +9505,10 @@
         </is>
       </c>
       <c r="C336" s="7" t="n">
-        <v>12.0531352448</v>
+        <v>12.57</v>
       </c>
       <c r="D336" s="7" t="n">
-        <v>9.80494819584</v>
+        <v>10.22</v>
       </c>
       <c r="E336" t="n">
         <v>25</v>
@@ -9532,10 +9532,10 @@
         </is>
       </c>
       <c r="C337" s="7" t="n">
-        <v>12.8436108416</v>
+        <v>13.41</v>
       </c>
       <c r="D337" s="7" t="n">
-        <v>10.43732867328</v>
+        <v>10.89</v>
       </c>
       <c r="E337" t="n">
         <v>10</v>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="C338" s="7" t="n">
-        <v>16.574471890432</v>
+        <v>17.2</v>
       </c>
       <c r="D338" s="7" t="n">
-        <v>13.5742575123456</v>
+        <v>14.07</v>
       </c>
       <c r="E338" t="n">
         <v>25</v>
@@ -9586,10 +9586,10 @@
         </is>
       </c>
       <c r="C339" s="7" t="n">
-        <v>18.62970834688</v>
+        <v>19.38</v>
       </c>
       <c r="D339" s="7" t="n">
-        <v>15.218446677504</v>
+        <v>15.82</v>
       </c>
       <c r="E339" t="n">
         <v>25</v>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="C340" s="7" t="n">
-        <v>21.251348551168</v>
+        <v>22.17</v>
       </c>
       <c r="D340" s="7" t="n">
-        <v>17.3157588409344</v>
+        <v>18.05</v>
       </c>
       <c r="E340" t="n">
         <v>15</v>
@@ -9640,10 +9640,10 @@
         </is>
       </c>
       <c r="C341" s="7" t="n">
-        <v>22.659266438656</v>
+        <v>23.66</v>
       </c>
       <c r="D341" s="7" t="n">
-        <v>18.4420931509248</v>
+        <v>19.25</v>
       </c>
       <c r="E341" t="n">
         <v>15</v>
@@ -9667,10 +9667,10 @@
         </is>
       </c>
       <c r="C342" s="7" t="n">
-        <v>3.3811827968</v>
+        <v>3.42</v>
       </c>
       <c r="D342" s="7" t="n">
-        <v>2.2908</v>
+        <v>2.29</v>
       </c>
       <c r="E342" t="n">
         <v>500</v>
@@ -9694,10 +9694,10 @@
         </is>
       </c>
       <c r="C343" s="7" t="n">
-        <v>3.4611661696</v>
+        <v>3.51</v>
       </c>
       <c r="D343" s="7" t="n">
-        <v>2.82709293568</v>
+        <v>2.87</v>
       </c>
       <c r="E343" t="n">
         <v>500</v>
@@ -9721,10 +9721,10 @@
         </is>
       </c>
       <c r="C344" s="7" t="n">
-        <v>3.5243109376</v>
+        <v>3.58</v>
       </c>
       <c r="D344" s="7" t="n">
-        <v>2.87760875008</v>
+        <v>2.92</v>
       </c>
       <c r="E344" t="n">
         <v>250</v>
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="C345" s="7" t="n">
-        <v>3.5832460544</v>
+        <v>3.64</v>
       </c>
       <c r="D345" s="7" t="n">
-        <v>2.92475684352</v>
+        <v>2.97</v>
       </c>
       <c r="E345" t="n">
         <v>250</v>
@@ -9773,10 +9773,10 @@
         </is>
       </c>
       <c r="C346" s="7" t="n">
-        <v>3.6506004736</v>
+        <v>3.71</v>
       </c>
       <c r="D346" s="7" t="n">
-        <v>2.97864037888</v>
+        <v>3.03</v>
       </c>
       <c r="E346" t="n">
         <v>250</v>
@@ -9800,10 +9800,10 @@
         </is>
       </c>
       <c r="C347" s="7" t="n">
-        <v>3.8863409408</v>
+        <v>3.96</v>
       </c>
       <c r="D347" s="7" t="n">
-        <v>3.16723275264</v>
+        <v>3.23</v>
       </c>
       <c r="E347" t="n">
         <v>500</v>
@@ -9827,10 +9827,10 @@
         </is>
       </c>
       <c r="C348" s="7" t="n">
-        <v>4.0084208256</v>
+        <v>4.09</v>
       </c>
       <c r="D348" s="7" t="n">
-        <v>3.26489666048</v>
+        <v>3.33</v>
       </c>
       <c r="E348" t="n">
         <v>250</v>
@@ -9854,10 +9854,10 @@
         </is>
       </c>
       <c r="C349" s="7" t="n">
-        <v>4.1683875712</v>
+        <v>4.26</v>
       </c>
       <c r="D349" s="7" t="n">
-        <v>3.392870056960001</v>
+        <v>3.47</v>
       </c>
       <c r="E349" t="n">
         <v>250</v>
@@ -9881,10 +9881,10 @@
         </is>
       </c>
       <c r="C350" s="7" t="n">
-        <v>4.2988867584</v>
+        <v>4.4</v>
       </c>
       <c r="D350" s="7" t="n">
-        <v>3.49726940672</v>
+        <v>3.58</v>
       </c>
       <c r="E350" t="n">
         <v>200</v>
@@ -9906,10 +9906,10 @@
         </is>
       </c>
       <c r="C351" s="7" t="n">
-        <v>4.4841114112</v>
+        <v>4.6</v>
       </c>
       <c r="D351" s="7" t="n">
-        <v>3.64544912896</v>
+        <v>3.74</v>
       </c>
       <c r="E351" t="n">
         <v>500</v>
@@ -9931,10 +9931,10 @@
         </is>
       </c>
       <c r="C352" s="7" t="n">
-        <v>3.9367555072</v>
+        <v>4.01</v>
       </c>
       <c r="D352" s="7" t="n">
-        <v>3.23340440576</v>
+        <v>3.29</v>
       </c>
       <c r="E352" t="n">
         <v>250</v>
@@ -9958,10 +9958,10 @@
         </is>
       </c>
       <c r="C353" s="7" t="n">
-        <v>4.0661357184</v>
+        <v>4.14</v>
       </c>
       <c r="D353" s="7" t="n">
-        <v>3.33690857472</v>
+        <v>3.4</v>
       </c>
       <c r="E353" t="n">
         <v>250</v>
@@ -9985,10 +9985,10 @@
         </is>
       </c>
       <c r="C354" s="7" t="n">
-        <v>4.1682779904</v>
+        <v>4.25</v>
       </c>
       <c r="D354" s="7" t="n">
-        <v>3.41862239232</v>
+        <v>3.49</v>
       </c>
       <c r="E354" t="n">
         <v>250</v>
@@ -10012,10 +10012,10 @@
         </is>
       </c>
       <c r="C355" s="7" t="n">
-        <v>4.263610777599999</v>
+        <v>4.35</v>
       </c>
       <c r="D355" s="7" t="n">
-        <v>3.49488862208</v>
+        <v>3.57</v>
       </c>
       <c r="E355" t="n">
         <v>250</v>
@@ -10039,10 +10039,10 @@
         </is>
       </c>
       <c r="C356" s="7" t="n">
-        <v>4.3725625344</v>
+        <v>4.47</v>
       </c>
       <c r="D356" s="7" t="n">
-        <v>3.58205002752</v>
+        <v>3.66</v>
       </c>
       <c r="E356" t="n">
         <v>250</v>
@@ -10066,10 +10066,10 @@
         </is>
       </c>
       <c r="C357" s="7" t="n">
-        <v>4.753893683199999</v>
+        <v>4.87</v>
       </c>
       <c r="D357" s="7" t="n">
-        <v>3.88711494656</v>
+        <v>3.98</v>
       </c>
       <c r="E357" t="n">
         <v>250</v>
@@ -10093,10 +10093,10 @@
         </is>
       </c>
       <c r="C358" s="7" t="n">
-        <v>4.9513687424</v>
+        <v>5.08</v>
       </c>
       <c r="D358" s="7" t="n">
-        <v>4.04509499392</v>
+        <v>4.15</v>
       </c>
       <c r="E358" t="n">
         <v>200</v>
@@ -10120,10 +10120,10 @@
         </is>
       </c>
       <c r="C359" s="7" t="n">
-        <v>5.2101291648</v>
+        <v>5.36</v>
       </c>
       <c r="D359" s="7" t="n">
-        <v>4.25210333184</v>
+        <v>4.37</v>
       </c>
       <c r="E359" t="n">
         <v>200</v>
@@ -10147,10 +10147,10 @@
         </is>
       </c>
       <c r="C360" s="7" t="n">
-        <v>5.421223193599999</v>
+        <v>5.58</v>
       </c>
       <c r="D360" s="7" t="n">
-        <v>4.42097855488</v>
+        <v>4.55</v>
       </c>
       <c r="E360" t="n">
         <v>200</v>
@@ -10174,10 +10174,10 @@
         </is>
       </c>
       <c r="C361" s="7" t="n">
-        <v>5.7208405248</v>
+        <v>5.9</v>
       </c>
       <c r="D361" s="7" t="n">
-        <v>4.66067241984</v>
+        <v>4.81</v>
       </c>
       <c r="E361" t="n">
         <v>250</v>
@@ -10201,10 +10201,10 @@
         </is>
       </c>
       <c r="C362" s="7" t="n">
-        <v>5.29124224</v>
+        <v>5.44</v>
       </c>
       <c r="D362" s="7" t="n">
-        <v>4.348033792</v>
+        <v>4.46</v>
       </c>
       <c r="E362" t="n">
         <v>250</v>
@@ -10228,10 +10228,10 @@
         </is>
       </c>
       <c r="C363" s="7" t="n">
-        <v>5.86009472</v>
+        <v>6.04</v>
       </c>
       <c r="D363" s="7" t="n">
-        <v>4.803115776</v>
+        <v>4.95</v>
       </c>
       <c r="E363" t="n">
         <v>250</v>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="C364" s="7" t="n">
-        <v>6.15467904</v>
+        <v>6.35</v>
       </c>
       <c r="D364" s="7" t="n">
-        <v>5.038783232</v>
+        <v>5.2</v>
       </c>
       <c r="E364" t="n">
         <v>150</v>
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="C365" s="7" t="n">
-        <v>6.54068608</v>
+        <v>6.76</v>
       </c>
       <c r="D365" s="7" t="n">
-        <v>5.347588864</v>
+        <v>5.53</v>
       </c>
       <c r="E365" t="n">
         <v>150</v>
@@ -10309,10 +10309,10 @@
         </is>
       </c>
       <c r="C366" s="7" t="n">
-        <v>6.85558656</v>
+        <v>7.1</v>
       </c>
       <c r="D366" s="7" t="n">
-        <v>5.599509248</v>
+        <v>5.79</v>
       </c>
       <c r="E366" t="n">
         <v>150</v>
@@ -10334,10 +10334,10 @@
         </is>
       </c>
       <c r="C367" s="7" t="n">
-        <v>7.302542079999999</v>
+        <v>7.57</v>
       </c>
       <c r="D367" s="7" t="n">
-        <v>5.957073664</v>
+        <v>6.17</v>
       </c>
       <c r="E367" t="n">
         <v>100</v>
@@ -10361,10 +10361,10 @@
         </is>
       </c>
       <c r="C368" s="7" t="n">
-        <v>8.277717760000002</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D368" s="7" t="n">
-        <v>6.737214208000001</v>
+        <v>7</v>
       </c>
       <c r="E368" t="n">
         <v>100</v>
@@ -10388,10 +10388,10 @@
         </is>
       </c>
       <c r="C369" s="7" t="n">
-        <v>9.252893440000001</v>
+        <v>9.65</v>
       </c>
       <c r="D369" s="7" t="n">
-        <v>7.517354752</v>
+        <v>7.83</v>
       </c>
       <c r="E369" t="n">
         <v>100</v>
@@ -10415,10 +10415,10 @@
         </is>
       </c>
       <c r="C370" s="7" t="n">
-        <v>10.5429696</v>
+        <v>11.02</v>
       </c>
       <c r="D370" s="7" t="n">
-        <v>8.549415680000001</v>
+        <v>8.93</v>
       </c>
       <c r="E370" t="n">
         <v>50</v>
@@ -10442,10 +10442,10 @@
         </is>
       </c>
       <c r="C371" s="7" t="n">
-        <v>12.18857856</v>
+        <v>12.76</v>
       </c>
       <c r="D371" s="7" t="n">
-        <v>9.865902848000001</v>
+        <v>10.33</v>
       </c>
       <c r="E371" t="n">
         <v>25</v>
@@ -10469,10 +10469,10 @@
         </is>
       </c>
       <c r="C372" s="7" t="n">
-        <v>13.07233152</v>
+        <v>13.7</v>
       </c>
       <c r="D372" s="7" t="n">
-        <v>10.572905216</v>
+        <v>11.08</v>
       </c>
       <c r="E372" t="n">
         <v>10</v>
@@ -10496,10 +10496,10 @@
         </is>
       </c>
       <c r="C373" s="7" t="n">
-        <v>12.7852061952</v>
+        <v>13.11</v>
       </c>
       <c r="D373" s="7" t="n">
-        <v>10.55304495616</v>
+        <v>10.81</v>
       </c>
       <c r="E373" t="n">
         <v>500</v>
@@ -10523,10 +10523,10 @@
         </is>
       </c>
       <c r="C374" s="7" t="n">
-        <v>13.3121899264</v>
+        <v>13.67</v>
       </c>
       <c r="D374" s="7" t="n">
-        <v>10.97463194112</v>
+        <v>11.26</v>
       </c>
       <c r="E374" t="n">
         <v>250</v>
@@ -10550,10 +10550,10 @@
         </is>
       </c>
       <c r="C375" s="7" t="n">
-        <v>14.0027203328</v>
+        <v>14.4</v>
       </c>
       <c r="D375" s="7" t="n">
-        <v>11.52705626624</v>
+        <v>11.85</v>
       </c>
       <c r="E375" t="n">
         <v>250</v>
@@ -10577,10 +10577,10 @@
         </is>
       </c>
       <c r="C376" s="7" t="n">
-        <v>14.5660477696</v>
+        <v>15</v>
       </c>
       <c r="D376" s="7" t="n">
-        <v>11.97771821568</v>
+        <v>12.32</v>
       </c>
       <c r="E376" t="n">
         <v>200</v>
@@ -10602,10 +10602,10 @@
         </is>
       </c>
       <c r="C377" s="7" t="n">
-        <v>15.3656092928</v>
+        <v>15.85</v>
       </c>
       <c r="D377" s="7" t="n">
-        <v>12.61736743424</v>
+        <v>13</v>
       </c>
       <c r="E377" t="n">
         <v>500</v>
@@ -10629,10 +10629,10 @@
         </is>
       </c>
       <c r="C378" s="7" t="n">
-        <v>17.1101071616</v>
+        <v>17.7</v>
       </c>
       <c r="D378" s="7" t="n">
-        <v>14.01296572928</v>
+        <v>14.49</v>
       </c>
       <c r="E378" t="n">
         <v>50</v>
@@ -10656,10 +10656,10 @@
         </is>
       </c>
       <c r="C379" s="7" t="n">
-        <v>18.8546050304</v>
+        <v>19.56</v>
       </c>
       <c r="D379" s="7" t="n">
-        <v>15.40856402432</v>
+        <v>15.97</v>
       </c>
       <c r="E379" t="n">
         <v>50</v>
@@ -10683,10 +10683,10 @@
         </is>
       </c>
       <c r="C380" s="7" t="n">
-        <v>21.162430336</v>
+        <v>22.01</v>
       </c>
       <c r="D380" s="7" t="n">
-        <v>17.2548242688</v>
+        <v>17.93</v>
       </c>
       <c r="E380" t="n">
         <v>25</v>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="C381" s="7" t="n">
-        <v>24.1062704896</v>
+        <v>25.14</v>
       </c>
       <c r="D381" s="7" t="n">
-        <v>19.60989639168</v>
+        <v>20.43</v>
       </c>
       <c r="E381" t="n">
         <v>25</v>
@@ -10737,10 +10737,10 @@
         </is>
       </c>
       <c r="C382" s="7" t="n">
-        <v>25.6872216832</v>
+        <v>26.82</v>
       </c>
       <c r="D382" s="7" t="n">
-        <v>20.87465734656</v>
+        <v>21.78</v>
       </c>
       <c r="E382" t="n">
         <v>10</v>
@@ -10764,10 +10764,10 @@
         </is>
       </c>
       <c r="C383" s="7" t="n">
-        <v>33.148943780864</v>
+        <v>34.4</v>
       </c>
       <c r="D383" s="7" t="n">
-        <v>27.1485150246912</v>
+        <v>28.15</v>
       </c>
       <c r="E383" t="n">
         <v>25</v>
@@ -10791,10 +10791,10 @@
         </is>
       </c>
       <c r="C384" s="7" t="n">
-        <v>37.25941669376</v>
+        <v>38.77</v>
       </c>
       <c r="D384" s="7" t="n">
-        <v>30.436893355008</v>
+        <v>31.64</v>
       </c>
       <c r="E384" t="n">
         <v>25</v>
@@ -10818,10 +10818,10 @@
         </is>
       </c>
       <c r="C385" s="7" t="n">
-        <v>42.502697102336</v>
+        <v>44.34</v>
       </c>
       <c r="D385" s="7" t="n">
-        <v>34.6315176818688</v>
+        <v>36.1</v>
       </c>
       <c r="E385" t="n">
         <v>15</v>
@@ -10845,10 +10845,10 @@
         </is>
       </c>
       <c r="C386" s="7" t="n">
-        <v>45.318532877312</v>
+        <v>47.33</v>
       </c>
       <c r="D386" s="7" t="n">
-        <v>36.8841863018496</v>
+        <v>38.49</v>
       </c>
       <c r="E386" t="n">
         <v>15</v>
@@ -10870,10 +10870,10 @@
         </is>
       </c>
       <c r="C387" s="7" t="n">
-        <v>2.778988914</v>
+        <v>2.78</v>
       </c>
       <c r="D387" s="7" t="n">
-        <v>2.2231911312</v>
+        <v>2.22</v>
       </c>
       <c r="E387" t="n">
         <v>500</v>
@@ -10897,10 +10897,10 @@
         </is>
       </c>
       <c r="C388" s="7" t="n">
-        <v>2.9758229955</v>
+        <v>2.98</v>
       </c>
       <c r="D388" s="7" t="n">
-        <v>2.3806583964</v>
+        <v>2.38</v>
       </c>
       <c r="E388" t="n">
         <v>500</v>
@@ -10924,10 +10924,10 @@
         </is>
       </c>
       <c r="C389" s="7" t="n">
-        <v>3.131218323000001</v>
+        <v>3.13</v>
       </c>
       <c r="D389" s="7" t="n">
-        <v>2.504974658400001</v>
+        <v>2.5</v>
       </c>
       <c r="E389" t="n">
         <v>250</v>
@@ -10951,10 +10951,10 @@
         </is>
       </c>
       <c r="C390" s="7" t="n">
-        <v>3.276253962</v>
+        <v>3.28</v>
       </c>
       <c r="D390" s="7" t="n">
-        <v>2.6210031696</v>
+        <v>2.62</v>
       </c>
       <c r="E390" t="n">
         <v>250</v>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="C391" s="7" t="n">
-        <v>3.442008978</v>
+        <v>3.44</v>
       </c>
       <c r="D391" s="7" t="n">
-        <v>2.753607182400001</v>
+        <v>2.75</v>
       </c>
       <c r="E391" t="n">
         <v>50</v>
@@ -11005,10 +11005,10 @@
         </is>
       </c>
       <c r="C392" s="7" t="n">
-        <v>4.022151534</v>
+        <v>4.02</v>
       </c>
       <c r="D392" s="7" t="n">
-        <v>3.2177212272</v>
+        <v>3.22</v>
       </c>
       <c r="E392" t="n">
         <v>500</v>
@@ -11032,10 +11032,10 @@
         </is>
       </c>
       <c r="C393" s="7" t="n">
-        <v>4.3225825005</v>
+        <v>4.32</v>
       </c>
       <c r="D393" s="7" t="n">
-        <v>3.458066000400001</v>
+        <v>3.46</v>
       </c>
       <c r="E393" t="n">
         <v>250</v>
@@ -11057,10 +11057,10 @@
         </is>
       </c>
       <c r="C394" s="7" t="n">
-        <v>4.716250663500001</v>
+        <v>4.72</v>
       </c>
       <c r="D394" s="7" t="n">
-        <v>3.773000530800001</v>
+        <v>3.77</v>
       </c>
       <c r="E394" t="n">
         <v>250</v>
@@ -11084,10 +11084,10 @@
         </is>
       </c>
       <c r="C395" s="7" t="n">
-        <v>5.037401007000001</v>
+        <v>5.04</v>
       </c>
       <c r="D395" s="7" t="n">
-        <v>4.029920805600002</v>
+        <v>4.03</v>
       </c>
       <c r="E395" t="n">
         <v>200</v>
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="C396" s="7" t="n">
-        <v>5.493227301000001</v>
+        <v>5.49</v>
       </c>
       <c r="D396" s="7" t="n">
-        <v>4.394581840800001</v>
+        <v>4.39</v>
       </c>
       <c r="E396" t="n">
         <v>500</v>
@@ -11134,10 +11134,10 @@
         </is>
       </c>
       <c r="C397" s="7" t="n">
-        <v>3.828265505999999</v>
+        <v>3.83</v>
       </c>
       <c r="D397" s="7" t="n">
-        <v>3.062612404799999</v>
+        <v>3.06</v>
       </c>
       <c r="E397" t="n">
         <v>250</v>
@@ -11161,10 +11161,10 @@
         </is>
       </c>
       <c r="C398" s="7" t="n">
-        <v>4.146662119499999</v>
+        <v>4.15</v>
       </c>
       <c r="D398" s="7" t="n">
-        <v>3.3173296956</v>
+        <v>3.32</v>
       </c>
       <c r="E398" t="n">
         <v>250</v>
@@ -11188,10 +11188,10 @@
         </is>
       </c>
       <c r="C399" s="7" t="n">
-        <v>4.398027867</v>
+        <v>4.4</v>
       </c>
       <c r="D399" s="7" t="n">
-        <v>3.5184222936</v>
+        <v>3.52</v>
       </c>
       <c r="E399" t="n">
         <v>250</v>
@@ -11215,10 +11215,10 @@
         </is>
       </c>
       <c r="C400" s="7" t="n">
-        <v>4.632635897999999</v>
+        <v>4.63</v>
       </c>
       <c r="D400" s="7" t="n">
-        <v>3.706108718399999</v>
+        <v>3.71</v>
       </c>
       <c r="E400" t="n">
         <v>250</v>
@@ -11242,10 +11242,10 @@
         </is>
       </c>
       <c r="C401" s="7" t="n">
-        <v>4.900759362</v>
+        <v>4.9</v>
       </c>
       <c r="D401" s="7" t="n">
-        <v>3.9206074896</v>
+        <v>3.92</v>
       </c>
       <c r="E401" t="n">
         <v>250</v>
@@ -11269,10 +11269,10 @@
         </is>
       </c>
       <c r="C402" s="7" t="n">
-        <v>5.839191485999999</v>
+        <v>5.84</v>
       </c>
       <c r="D402" s="7" t="n">
-        <v>4.6713531888</v>
+        <v>4.67</v>
       </c>
       <c r="E402" t="n">
         <v>250</v>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="C403" s="7" t="n">
-        <v>6.325165264499999</v>
+        <v>6.33</v>
       </c>
       <c r="D403" s="7" t="n">
-        <v>5.060132211599999</v>
+        <v>5.06</v>
       </c>
       <c r="E403" t="n">
         <v>200</v>
@@ -11323,10 +11323,10 @@
         </is>
       </c>
       <c r="C404" s="7" t="n">
-        <v>6.961958491499998</v>
+        <v>6.96</v>
       </c>
       <c r="D404" s="7" t="n">
-        <v>5.569566793199999</v>
+        <v>5.57</v>
       </c>
       <c r="E404" t="n">
         <v>200</v>
@@ -11350,10 +11350,10 @@
         </is>
       </c>
       <c r="C405" s="7" t="n">
-        <v>7.481447702999999</v>
+        <v>7.48</v>
       </c>
       <c r="D405" s="7" t="n">
-        <v>5.985158162399999</v>
+        <v>5.99</v>
       </c>
       <c r="E405" t="n">
         <v>200</v>
@@ -11377,10 +11377,10 @@
         </is>
       </c>
       <c r="C406" s="7" t="n">
-        <v>8.218787228999998</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="D406" s="7" t="n">
-        <v>6.575029783199999</v>
+        <v>6.58</v>
       </c>
       <c r="E406" t="n">
         <v>250</v>
@@ -11404,10 +11404,10 @@
         </is>
       </c>
       <c r="C407" s="7" t="n">
-        <v>6.779635200000001</v>
+        <v>6.78</v>
       </c>
       <c r="D407" s="7" t="n">
-        <v>5.423708160000001</v>
+        <v>5.42</v>
       </c>
       <c r="E407" t="n">
         <v>250</v>
@@ -11431,10 +11431,10 @@
         </is>
       </c>
       <c r="C408" s="7" t="n">
-        <v>8.179545599999999</v>
+        <v>8.18</v>
       </c>
       <c r="D408" s="7" t="n">
-        <v>6.54363648</v>
+        <v>6.54</v>
       </c>
       <c r="E408" t="n">
         <v>200</v>
@@ -11458,10 +11458,10 @@
         </is>
       </c>
       <c r="C409" s="7" t="n">
-        <v>8.904499199999998</v>
+        <v>8.9</v>
       </c>
       <c r="D409" s="7" t="n">
-        <v>7.123599359999999</v>
+        <v>7.12</v>
       </c>
       <c r="E409" t="n">
         <v>150</v>
@@ -11485,10 +11485,10 @@
         </is>
       </c>
       <c r="C410" s="7" t="n">
-        <v>9.854438399999998</v>
+        <v>9.85</v>
       </c>
       <c r="D410" s="7" t="n">
-        <v>7.883550719999999</v>
+        <v>7.88</v>
       </c>
       <c r="E410" t="n">
         <v>150</v>
@@ -11512,10 +11512,10 @@
         </is>
       </c>
       <c r="C411" s="7" t="n">
-        <v>10.6293888</v>
+        <v>10.63</v>
       </c>
       <c r="D411" s="7" t="n">
-        <v>8.503511040000001</v>
+        <v>8.5</v>
       </c>
       <c r="E411" t="n">
         <v>150</v>
@@ -11539,10 +11539,10 @@
         </is>
       </c>
       <c r="C412" s="7" t="n">
-        <v>11.7293184</v>
+        <v>11.73</v>
       </c>
       <c r="D412" s="7" t="n">
-        <v>9.38345472</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="E412" t="n">
         <v>100</v>
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="C413" s="7" t="n">
-        <v>14.1291648</v>
+        <v>14.13</v>
       </c>
       <c r="D413" s="7" t="n">
-        <v>11.30333184</v>
+        <v>11.3</v>
       </c>
       <c r="E413" t="n">
         <v>100</v>
@@ -11593,10 +11593,10 @@
         </is>
       </c>
       <c r="C414" s="7" t="n">
-        <v>16.5290112</v>
+        <v>16.53</v>
       </c>
       <c r="D414" s="7" t="n">
-        <v>13.22320896</v>
+        <v>13.22</v>
       </c>
       <c r="E414" t="n">
         <v>100</v>
@@ -11620,10 +11620,10 @@
         </is>
       </c>
       <c r="C415" s="7" t="n">
-        <v>19.703808</v>
+        <v>19.7</v>
       </c>
       <c r="D415" s="7" t="n">
-        <v>15.7630464</v>
+        <v>15.76</v>
       </c>
       <c r="E415" t="n">
         <v>50</v>
@@ -11647,10 +11647,10 @@
         </is>
       </c>
       <c r="C416" s="7" t="n">
-        <v>23.7535488</v>
+        <v>23.75</v>
       </c>
       <c r="D416" s="7" t="n">
-        <v>19.00283904</v>
+        <v>19</v>
       </c>
       <c r="E416" t="n">
         <v>25</v>
@@ -11674,10 +11674,10 @@
         </is>
       </c>
       <c r="C417" s="7" t="n">
-        <v>25.9284096</v>
+        <v>25.93</v>
       </c>
       <c r="D417" s="7" t="n">
-        <v>20.74272768</v>
+        <v>20.74</v>
       </c>
       <c r="E417" t="n">
         <v>10</v>
@@ -11699,10 +11699,10 @@
         </is>
       </c>
       <c r="C418" s="7" t="n">
-        <v>15.400421496</v>
+        <v>15.4</v>
       </c>
       <c r="D418" s="7" t="n">
-        <v>12.3203371968</v>
+        <v>12.32</v>
       </c>
       <c r="E418" t="n">
         <v>500</v>
@@ -11724,10 +11724,10 @@
         </is>
       </c>
       <c r="C419" s="7" t="n">
-        <v>16.697295522</v>
+        <v>16.7</v>
       </c>
       <c r="D419" s="7" t="n">
-        <v>13.3578364176</v>
+        <v>13.36</v>
       </c>
       <c r="E419" t="n">
         <v>250</v>
@@ -11749,10 +11749,10 @@
         </is>
       </c>
       <c r="C420" s="7" t="n">
-        <v>18.39664769399999</v>
+        <v>18.4</v>
       </c>
       <c r="D420" s="7" t="n">
-        <v>14.7173181552</v>
+        <v>14.72</v>
       </c>
       <c r="E420" t="n">
         <v>250</v>
@@ -11776,10 +11776,10 @@
         </is>
       </c>
       <c r="C421" s="7" t="n">
-        <v>19.782961308</v>
+        <v>19.78</v>
       </c>
       <c r="D421" s="7" t="n">
-        <v>15.8263690464</v>
+        <v>15.83</v>
       </c>
       <c r="E421" t="n">
         <v>200</v>
@@ -11801,10 +11801,10 @@
         </is>
       </c>
       <c r="C422" s="7" t="n">
-        <v>21.75063224399999</v>
+        <v>21.75</v>
       </c>
       <c r="D422" s="7" t="n">
-        <v>17.4005057952</v>
+        <v>17.4</v>
       </c>
       <c r="E422" t="n">
         <v>500</v>
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="C423" s="7" t="n">
-        <v>26.04373246799999</v>
+        <v>26.04</v>
       </c>
       <c r="D423" s="7" t="n">
-        <v>20.8349859744</v>
+        <v>20.83</v>
       </c>
       <c r="E423" t="n">
         <v>50</v>
@@ -11855,10 +11855,10 @@
         </is>
       </c>
       <c r="C424" s="7" t="n">
-        <v>30.336832692</v>
+        <v>30.34</v>
       </c>
       <c r="D424" s="7" t="n">
-        <v>24.2694661536</v>
+        <v>24.27</v>
       </c>
       <c r="E424" t="n">
         <v>50</v>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="C425" s="7" t="n">
-        <v>36.01624653</v>
+        <v>36.02</v>
       </c>
       <c r="D425" s="7" t="n">
-        <v>28.812997224</v>
+        <v>28.81</v>
       </c>
       <c r="E425" t="n">
         <v>25</v>
@@ -11909,10 +11909,10 @@
         </is>
       </c>
       <c r="C426" s="7" t="n">
-        <v>43.260853158</v>
+        <v>43.26</v>
       </c>
       <c r="D426" s="7" t="n">
-        <v>34.6086825264</v>
+        <v>34.61</v>
       </c>
       <c r="E426" t="n">
         <v>25</v>
@@ -11936,10 +11936,10 @@
         </is>
       </c>
       <c r="C427" s="7" t="n">
-        <v>47.151475236</v>
+        <v>47.15</v>
       </c>
       <c r="D427" s="7" t="n">
-        <v>37.7211801888</v>
+        <v>37.72</v>
       </c>
       <c r="E427" t="n">
         <v>10</v>
@@ -11961,10 +11961,10 @@
         </is>
       </c>
       <c r="C428" s="7" t="n">
-        <v>53.72402571072</v>
+        <v>53.72</v>
       </c>
       <c r="D428" s="7" t="n">
-        <v>42.979220568576</v>
+        <v>42.98</v>
       </c>
       <c r="E428" t="n">
         <v>25</v>
@@ -11988,10 +11988,10 @@
         </is>
       </c>
       <c r="C429" s="7" t="n">
-        <v>63.83964264480001</v>
+        <v>63.84</v>
       </c>
       <c r="D429" s="7" t="n">
-        <v>51.07171411584001</v>
+        <v>51.07</v>
       </c>
       <c r="E429" t="n">
         <v>25</v>
@@ -12015,10 +12015,10 @@
         </is>
       </c>
       <c r="C430" s="7" t="n">
-        <v>76.74302802528</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="D430" s="7" t="n">
-        <v>61.394422420224</v>
+        <v>61.39</v>
       </c>
       <c r="E430" t="n">
         <v>15</v>
@@ -12040,10 +12040,10 @@
         </is>
       </c>
       <c r="C431" s="7" t="n">
-        <v>83.67262387776002</v>
+        <v>83.67</v>
       </c>
       <c r="D431" s="7" t="n">
-        <v>66.93809910220801</v>
+        <v>66.94</v>
       </c>
       <c r="E431" t="n">
         <v>15</v>
@@ -12067,10 +12067,10 @@
         </is>
       </c>
       <c r="C432" s="7" t="n">
-        <v>3.342988914</v>
+        <v>3.34</v>
       </c>
       <c r="D432" s="7" t="n">
-        <v>2.7871911312</v>
+        <v>2.79</v>
       </c>
       <c r="E432" t="n">
         <v>500</v>
@@ -12094,10 +12094,10 @@
         </is>
       </c>
       <c r="C433" s="7" t="n">
-        <v>3.5398229955</v>
+        <v>3.54</v>
       </c>
       <c r="D433" s="7" t="n">
-        <v>2.9446583964</v>
+        <v>2.94</v>
       </c>
       <c r="E433" t="n">
         <v>500</v>
@@ -12121,10 +12121,10 @@
         </is>
       </c>
       <c r="C434" s="7" t="n">
-        <v>3.695218323000001</v>
+        <v>3.7</v>
       </c>
       <c r="D434" s="7" t="n">
-        <v>3.068974658400001</v>
+        <v>3.07</v>
       </c>
       <c r="E434" t="n">
         <v>250</v>
@@ -12148,10 +12148,10 @@
         </is>
       </c>
       <c r="C435" s="7" t="n">
-        <v>3.840253962</v>
+        <v>3.84</v>
       </c>
       <c r="D435" s="7" t="n">
-        <v>3.1850031696</v>
+        <v>3.19</v>
       </c>
       <c r="E435" t="n">
         <v>250</v>
@@ -12175,10 +12175,10 @@
         </is>
       </c>
       <c r="C436" s="7" t="n">
-        <v>4.006008978000001</v>
+        <v>4.01</v>
       </c>
       <c r="D436" s="7" t="n">
-        <v>3.317607182400001</v>
+        <v>3.32</v>
       </c>
       <c r="E436" t="n">
         <v>250</v>
@@ -12202,10 +12202,10 @@
         </is>
       </c>
       <c r="C437" s="7" t="n">
-        <v>4.586151534</v>
+        <v>4.59</v>
       </c>
       <c r="D437" s="7" t="n">
-        <v>3.7817212272</v>
+        <v>3.78</v>
       </c>
       <c r="E437" t="n">
         <v>500</v>
@@ -12229,10 +12229,10 @@
         </is>
       </c>
       <c r="C438" s="7" t="n">
-        <v>4.8865825005</v>
+        <v>4.89</v>
       </c>
       <c r="D438" s="7" t="n">
-        <v>4.022066000400001</v>
+        <v>4.02</v>
       </c>
       <c r="E438" t="n">
         <v>250</v>
@@ -12254,10 +12254,10 @@
         </is>
       </c>
       <c r="C439" s="7" t="n">
-        <v>5.280250663500001</v>
+        <v>5.28</v>
       </c>
       <c r="D439" s="7" t="n">
-        <v>4.337000530800001</v>
+        <v>4.34</v>
       </c>
       <c r="E439" t="n">
         <v>250</v>
@@ -12281,10 +12281,10 @@
         </is>
       </c>
       <c r="C440" s="7" t="n">
-        <v>5.601401007000002</v>
+        <v>5.6</v>
       </c>
       <c r="D440" s="7" t="n">
-        <v>4.593920805600002</v>
+        <v>4.59</v>
       </c>
       <c r="E440" t="n">
         <v>200</v>
@@ -12306,10 +12306,10 @@
         </is>
       </c>
       <c r="C441" s="7" t="n">
-        <v>6.057227301000001</v>
+        <v>6.06</v>
       </c>
       <c r="D441" s="7" t="n">
-        <v>4.958581840800001</v>
+        <v>4.96</v>
       </c>
       <c r="E441" t="n">
         <v>500</v>
@@ -12331,10 +12331,10 @@
         </is>
       </c>
       <c r="C442" s="7" t="n">
-        <v>4.624865505999999</v>
+        <v>4.62</v>
       </c>
       <c r="D442" s="7" t="n">
-        <v>3.859212404799999</v>
+        <v>3.86</v>
       </c>
       <c r="E442" t="n">
         <v>250</v>
@@ -12358,10 +12358,10 @@
         </is>
       </c>
       <c r="C443" s="7" t="n">
-        <v>4.943262119499999</v>
+        <v>4.94</v>
       </c>
       <c r="D443" s="7" t="n">
-        <v>4.1139296956</v>
+        <v>4.11</v>
       </c>
       <c r="E443" t="n">
         <v>250</v>
@@ -12385,10 +12385,10 @@
         </is>
       </c>
       <c r="C444" s="7" t="n">
-        <v>5.194627866999999</v>
+        <v>5.19</v>
       </c>
       <c r="D444" s="7" t="n">
-        <v>4.3150222936</v>
+        <v>4.32</v>
       </c>
       <c r="E444" t="n">
         <v>250</v>
@@ -12412,10 +12412,10 @@
         </is>
       </c>
       <c r="C445" s="7" t="n">
-        <v>5.429235897999999</v>
+        <v>5.43</v>
       </c>
       <c r="D445" s="7" t="n">
-        <v>4.502708718399999</v>
+        <v>4.5</v>
       </c>
       <c r="E445" t="n">
         <v>250</v>
@@ -12439,10 +12439,10 @@
         </is>
       </c>
       <c r="C446" s="7" t="n">
-        <v>5.697359361999999</v>
+        <v>5.7</v>
       </c>
       <c r="D446" s="7" t="n">
-        <v>4.7172074896</v>
+        <v>4.72</v>
       </c>
       <c r="E446" t="n">
         <v>250</v>
@@ -12466,10 +12466,10 @@
         </is>
       </c>
       <c r="C447" s="7" t="n">
-        <v>6.635791485999999</v>
+        <v>6.64</v>
       </c>
       <c r="D447" s="7" t="n">
-        <v>5.467953188799999</v>
+        <v>5.47</v>
       </c>
       <c r="E447" t="n">
         <v>250</v>
@@ -12493,10 +12493,10 @@
         </is>
       </c>
       <c r="C448" s="7" t="n">
-        <v>7.121765264499999</v>
+        <v>7.12</v>
       </c>
       <c r="D448" s="7" t="n">
-        <v>5.856732211599999</v>
+        <v>5.86</v>
       </c>
       <c r="E448" t="n">
         <v>200</v>
@@ -12520,10 +12520,10 @@
         </is>
       </c>
       <c r="C449" s="7" t="n">
-        <v>7.758558491499998</v>
+        <v>7.76</v>
       </c>
       <c r="D449" s="7" t="n">
-        <v>6.366166793199999</v>
+        <v>6.37</v>
       </c>
       <c r="E449" t="n">
         <v>200</v>
@@ -12547,10 +12547,10 @@
         </is>
       </c>
       <c r="C450" s="7" t="n">
-        <v>8.278047702999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D450" s="7" t="n">
-        <v>6.781758162399999</v>
+        <v>6.78</v>
       </c>
       <c r="E450" t="n">
         <v>200</v>
@@ -12574,10 +12574,10 @@
         </is>
       </c>
       <c r="C451" s="7" t="n">
-        <v>9.015387228999998</v>
+        <v>9.02</v>
       </c>
       <c r="D451" s="7" t="n">
-        <v>7.371629783199999</v>
+        <v>7.37</v>
       </c>
       <c r="E451" t="n">
         <v>250</v>
@@ -12601,10 +12601,10 @@
         </is>
       </c>
       <c r="C452" s="7" t="n">
-        <v>7.890035200000002</v>
+        <v>7.89</v>
       </c>
       <c r="D452" s="7" t="n">
-        <v>6.534108160000001</v>
+        <v>6.53</v>
       </c>
       <c r="E452" t="n">
         <v>250</v>
@@ -12628,10 +12628,10 @@
         </is>
       </c>
       <c r="C453" s="7" t="n">
-        <v>9.289945599999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="D453" s="7" t="n">
-        <v>7.65403648</v>
+        <v>7.65</v>
       </c>
       <c r="E453" t="n">
         <v>200</v>
@@ -12655,10 +12655,10 @@
         </is>
       </c>
       <c r="C454" s="7" t="n">
-        <v>10.0148992</v>
+        <v>10.01</v>
       </c>
       <c r="D454" s="7" t="n">
-        <v>8.233999359999999</v>
+        <v>8.23</v>
       </c>
       <c r="E454" t="n">
         <v>150</v>
@@ -12682,10 +12682,10 @@
         </is>
       </c>
       <c r="C455" s="7" t="n">
-        <v>10.9648384</v>
+        <v>10.96</v>
       </c>
       <c r="D455" s="7" t="n">
-        <v>8.993950719999999</v>
+        <v>8.99</v>
       </c>
       <c r="E455" t="n">
         <v>150</v>
@@ -12709,10 +12709,10 @@
         </is>
       </c>
       <c r="C456" s="7" t="n">
-        <v>11.7397888</v>
+        <v>11.74</v>
       </c>
       <c r="D456" s="7" t="n">
-        <v>9.613911040000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E456" t="n">
         <v>150</v>
@@ -12736,10 +12736,10 @@
         </is>
       </c>
       <c r="C457" s="7" t="n">
-        <v>12.8397184</v>
+        <v>12.84</v>
       </c>
       <c r="D457" s="7" t="n">
-        <v>10.49385472</v>
+        <v>10.49</v>
       </c>
       <c r="E457" t="n">
         <v>100</v>
@@ -12763,10 +12763,10 @@
         </is>
       </c>
       <c r="C458" s="7" t="n">
-        <v>15.2395648</v>
+        <v>15.24</v>
       </c>
       <c r="D458" s="7" t="n">
-        <v>12.41373184</v>
+        <v>12.41</v>
       </c>
       <c r="E458" t="n">
         <v>100</v>
@@ -12790,10 +12790,10 @@
         </is>
       </c>
       <c r="C459" s="7" t="n">
-        <v>17.63941119999999</v>
+        <v>17.64</v>
       </c>
       <c r="D459" s="7" t="n">
-        <v>14.33360896</v>
+        <v>14.33</v>
       </c>
       <c r="E459" t="n">
         <v>100</v>
@@ -12817,10 +12817,10 @@
         </is>
       </c>
       <c r="C460" s="7" t="n">
-        <v>20.814208</v>
+        <v>20.81</v>
       </c>
       <c r="D460" s="7" t="n">
-        <v>16.8734464</v>
+        <v>16.87</v>
       </c>
       <c r="E460" t="n">
         <v>50</v>
@@ -12844,10 +12844,10 @@
         </is>
       </c>
       <c r="C461" s="7" t="n">
-        <v>24.8639488</v>
+        <v>24.86</v>
       </c>
       <c r="D461" s="7" t="n">
-        <v>20.11323904</v>
+        <v>20.11</v>
       </c>
       <c r="E461" t="n">
         <v>25</v>
@@ -12871,10 +12871,10 @@
         </is>
       </c>
       <c r="C462" s="7" t="n">
-        <v>27.0388096</v>
+        <v>27.04</v>
       </c>
       <c r="D462" s="7" t="n">
-        <v>21.85312768</v>
+        <v>21.85</v>
       </c>
       <c r="E462" t="n">
         <v>10</v>
@@ -12896,10 +12896,10 @@
         </is>
       </c>
       <c r="C463" s="7" t="n">
-        <v>17.740421496</v>
+        <v>17.74</v>
       </c>
       <c r="D463" s="7" t="n">
-        <v>14.6603371968</v>
+        <v>14.66</v>
       </c>
       <c r="E463" t="n">
         <v>500</v>
@@ -12921,10 +12921,10 @@
         </is>
       </c>
       <c r="C464" s="7" t="n">
-        <v>19.037295522</v>
+        <v>19.04</v>
       </c>
       <c r="D464" s="7" t="n">
-        <v>15.6978364176</v>
+        <v>15.7</v>
       </c>
       <c r="E464" t="n">
         <v>250</v>
@@ -12946,10 +12946,10 @@
         </is>
       </c>
       <c r="C465" s="7" t="n">
-        <v>20.73664769399999</v>
+        <v>20.74</v>
       </c>
       <c r="D465" s="7" t="n">
-        <v>17.0573181552</v>
+        <v>17.06</v>
       </c>
       <c r="E465" t="n">
         <v>250</v>
@@ -12971,10 +12971,10 @@
         </is>
       </c>
       <c r="C466" s="7" t="n">
-        <v>22.122961308</v>
+        <v>22.12</v>
       </c>
       <c r="D466" s="7" t="n">
-        <v>18.1663690464</v>
+        <v>18.17</v>
       </c>
       <c r="E466" t="n">
         <v>200</v>
@@ -12996,10 +12996,10 @@
         </is>
       </c>
       <c r="C467" s="7" t="n">
-        <v>24.09063224399999</v>
+        <v>24.09</v>
       </c>
       <c r="D467" s="7" t="n">
-        <v>19.7405057952</v>
+        <v>19.74</v>
       </c>
       <c r="E467" t="n">
         <v>50</v>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="C468" s="7" t="n">
-        <v>28.38373246799999</v>
+        <v>28.38</v>
       </c>
       <c r="D468" s="7" t="n">
-        <v>23.1749859744</v>
+        <v>23.17</v>
       </c>
       <c r="E468" t="n">
         <v>50</v>
@@ -13050,10 +13050,10 @@
         </is>
       </c>
       <c r="C469" s="7" t="n">
-        <v>32.676832692</v>
+        <v>32.68</v>
       </c>
       <c r="D469" s="7" t="n">
-        <v>26.6094661536</v>
+        <v>26.61</v>
       </c>
       <c r="E469" t="n">
         <v>50</v>
@@ -13077,10 +13077,10 @@
         </is>
       </c>
       <c r="C470" s="7" t="n">
-        <v>38.35624652999999</v>
+        <v>38.36</v>
       </c>
       <c r="D470" s="7" t="n">
-        <v>31.152997224</v>
+        <v>31.15</v>
       </c>
       <c r="E470" t="n">
         <v>25</v>
@@ -13104,10 +13104,10 @@
         </is>
       </c>
       <c r="C471" s="7" t="n">
-        <v>45.60085315799999</v>
+        <v>45.6</v>
       </c>
       <c r="D471" s="7" t="n">
-        <v>36.94868252639999</v>
+        <v>36.95</v>
       </c>
       <c r="E471" t="n">
         <v>25</v>
@@ -13131,10 +13131,10 @@
         </is>
       </c>
       <c r="C472" s="7" t="n">
-        <v>49.491475236</v>
+        <v>49.49</v>
       </c>
       <c r="D472" s="7" t="n">
-        <v>40.06118018879999</v>
+        <v>40.06</v>
       </c>
       <c r="E472" t="n">
         <v>10</v>
@@ -13156,10 +13156,10 @@
         </is>
       </c>
       <c r="C473" s="7" t="n">
-        <v>58.50622571072</v>
+        <v>58.51</v>
       </c>
       <c r="D473" s="7" t="n">
-        <v>47.761420568576</v>
+        <v>47.76</v>
       </c>
       <c r="E473" t="n">
         <v>25</v>
@@ -13183,10 +13183,10 @@
         </is>
       </c>
       <c r="C474" s="7" t="n">
-        <v>68.62184264480001</v>
+        <v>68.62</v>
       </c>
       <c r="D474" s="7" t="n">
-        <v>55.85391411584001</v>
+        <v>55.85</v>
       </c>
       <c r="E474" t="n">
         <v>25</v>
@@ -13210,10 +13210,10 @@
         </is>
       </c>
       <c r="C475" s="7" t="n">
-        <v>81.52522802528</v>
+        <v>81.53</v>
       </c>
       <c r="D475" s="7" t="n">
-        <v>66.17662242022401</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="E475" t="n">
         <v>15</v>
@@ -13235,10 +13235,10 @@
         </is>
       </c>
       <c r="C476" s="7" t="n">
-        <v>88.45482387776002</v>
+        <v>88.45</v>
       </c>
       <c r="D476" s="7" t="n">
-        <v>71.72029910220802</v>
+        <v>71.72</v>
       </c>
       <c r="E476" t="n">
         <v>15</v>
@@ -13262,10 +13262,10 @@
         </is>
       </c>
       <c r="C477" s="7" t="n">
-        <v>1.35786192</v>
+        <v>1.37</v>
       </c>
       <c r="D477" s="7" t="n">
-        <v>1.086289536</v>
+        <v>1.1</v>
       </c>
       <c r="E477" t="n">
         <v>100</v>
@@ -13289,10 +13289,10 @@
         </is>
       </c>
       <c r="C478" s="7" t="n">
-        <v>1.43679288</v>
+        <v>1.46</v>
       </c>
       <c r="D478" s="7" t="n">
-        <v>1.149434304</v>
+        <v>1.17</v>
       </c>
       <c r="F478" s="1" t="inlineStr">
         <is>
@@ -13313,10 +13313,10 @@
         </is>
       </c>
       <c r="C479" s="7" t="n">
-        <v>1.45535568</v>
+        <v>1.48</v>
       </c>
       <c r="D479" s="7" t="n">
-        <v>1.164284544</v>
+        <v>1.18</v>
       </c>
       <c r="E479" t="n">
         <v>50</v>
@@ -13340,10 +13340,10 @@
         </is>
       </c>
       <c r="C480" s="7" t="n">
-        <v>1.58303352</v>
+        <v>1.61</v>
       </c>
       <c r="D480" s="7" t="n">
-        <v>1.266426816</v>
+        <v>1.29</v>
       </c>
       <c r="F480" s="1" t="inlineStr">
         <is>
@@ -13364,10 +13364,10 @@
         </is>
       </c>
       <c r="C481" s="7" t="n">
-        <v>1.580928</v>
+        <v>1.61</v>
       </c>
       <c r="D481" s="7" t="n">
-        <v>1.2647424</v>
+        <v>1.29</v>
       </c>
       <c r="E481" t="n">
         <v>50</v>
@@ -13391,10 +13391,10 @@
         </is>
       </c>
       <c r="C482" s="7" t="n">
-        <v>1.771392</v>
+        <v>1.82</v>
       </c>
       <c r="D482" s="7" t="n">
-        <v>1.4171136</v>
+        <v>1.46</v>
       </c>
       <c r="F482" s="1" t="inlineStr">
         <is>
@@ -13415,10 +13415,10 @@
         </is>
       </c>
       <c r="C483" s="7" t="n">
-        <v>4.26005328</v>
+        <v>4.37</v>
       </c>
       <c r="D483" s="7" t="n">
-        <v>3.408042624</v>
+        <v>3.49</v>
       </c>
       <c r="F483" s="1" t="inlineStr">
         <is>
@@ -13439,10 +13439,10 @@
         </is>
       </c>
       <c r="C484" s="7" t="n">
-        <v>4.54006512</v>
+        <v>4.67</v>
       </c>
       <c r="D484" s="7" t="n">
-        <v>3.632052096</v>
+        <v>3.73</v>
       </c>
       <c r="F484" s="1" t="inlineStr">
         <is>
@@ -13463,10 +13463,10 @@
         </is>
       </c>
       <c r="C485" s="7" t="n">
-        <v>4.53325008</v>
+        <v>4.66</v>
       </c>
       <c r="D485" s="7" t="n">
-        <v>3.626600064</v>
+        <v>3.73</v>
       </c>
       <c r="F485" s="1" t="inlineStr">
         <is>
@@ -13487,10 +13487,10 @@
         </is>
       </c>
       <c r="C486" s="7" t="n">
-        <v>4.87397232</v>
+        <v>5.03</v>
       </c>
       <c r="D486" s="7" t="n">
-        <v>3.899177856</v>
+        <v>4.02</v>
       </c>
       <c r="F486" s="1" t="inlineStr">
         <is>
@@ -13511,10 +13511,10 @@
         </is>
       </c>
       <c r="C487" s="7" t="n">
-        <v>1.41048256</v>
+        <v>1.42</v>
       </c>
       <c r="D487" s="7" t="n">
-        <v>1.128386048</v>
+        <v>1.14</v>
       </c>
       <c r="E487" t="n">
         <v>100</v>
@@ -13538,10 +13538,10 @@
         </is>
       </c>
       <c r="C488" s="7" t="n">
-        <v>1.51572384</v>
+        <v>1.54</v>
       </c>
       <c r="D488" s="7" t="n">
-        <v>1.212579072</v>
+        <v>1.23</v>
       </c>
       <c r="F488" s="1" t="inlineStr">
         <is>
@@ -13562,10 +13562,10 @@
         </is>
       </c>
       <c r="C489" s="7" t="n">
-        <v>1.54047424</v>
+        <v>1.56</v>
       </c>
       <c r="D489" s="7" t="n">
-        <v>1.232379392</v>
+        <v>1.25</v>
       </c>
       <c r="E489" t="n">
         <v>50</v>
@@ -13589,10 +13589,10 @@
         </is>
       </c>
       <c r="C490" s="7" t="n">
-        <v>1.71071136</v>
+        <v>1.74</v>
       </c>
       <c r="D490" s="7" t="n">
-        <v>1.368569088</v>
+        <v>1.39</v>
       </c>
       <c r="F490" s="1" t="inlineStr">
         <is>
@@ -13613,10 +13613,10 @@
         </is>
       </c>
       <c r="C491" s="7" t="n">
-        <v>1.707904</v>
+        <v>1.74</v>
       </c>
       <c r="D491" s="7" t="n">
-        <v>1.3663232</v>
+        <v>1.39</v>
       </c>
       <c r="E491" t="n">
         <v>50</v>
@@ -13640,10 +13640,10 @@
         </is>
       </c>
       <c r="C492" s="7" t="n">
-        <v>1.961856</v>
+        <v>2.01</v>
       </c>
       <c r="D492" s="7" t="n">
-        <v>1.5694848</v>
+        <v>1.61</v>
       </c>
       <c r="F492" s="1" t="inlineStr">
         <is>
@@ -13664,10 +13664,10 @@
         </is>
       </c>
       <c r="C493" s="7" t="n">
-        <v>4.68007104</v>
+        <v>4.79</v>
       </c>
       <c r="D493" s="7" t="n">
-        <v>3.744056832</v>
+        <v>3.83</v>
       </c>
       <c r="F493" s="1" t="inlineStr">
         <is>
@@ -13688,10 +13688,10 @@
         </is>
       </c>
       <c r="C494" s="7" t="n">
-        <v>5.05342016</v>
+        <v>5.18</v>
       </c>
       <c r="D494" s="7" t="n">
-        <v>4.042736128</v>
+        <v>4.15</v>
       </c>
       <c r="F494" s="1" t="inlineStr">
         <is>
@@ -13712,10 +13712,10 @@
         </is>
       </c>
       <c r="C495" s="7" t="n">
-        <v>5.04433344</v>
+        <v>5.17</v>
       </c>
       <c r="D495" s="7" t="n">
-        <v>4.035466752</v>
+        <v>4.14</v>
       </c>
       <c r="F495" s="1" t="inlineStr">
         <is>
@@ -13736,10 +13736,10 @@
         </is>
       </c>
       <c r="C496" s="7" t="n">
-        <v>5.49862976</v>
+        <v>5.65</v>
       </c>
       <c r="D496" s="7" t="n">
-        <v>4.398903808</v>
+        <v>4.52</v>
       </c>
       <c r="F496" s="1" t="inlineStr">
         <is>
@@ -13760,10 +13760,10 @@
         </is>
       </c>
       <c r="C497" s="7" t="n">
-        <v>2.82096512</v>
+        <v>2.85</v>
       </c>
       <c r="D497" s="7" t="n">
-        <v>2.256772096</v>
+        <v>2.28</v>
       </c>
       <c r="E497" t="n">
         <v>100</v>
@@ -13785,10 +13785,10 @@
         </is>
       </c>
       <c r="C498" s="7" t="n">
-        <v>3.03144768</v>
+        <v>3.07</v>
       </c>
       <c r="D498" s="7" t="n">
-        <v>2.425158144</v>
+        <v>2.46</v>
       </c>
       <c r="F498" s="1" t="inlineStr">
         <is>
@@ -13809,10 +13809,10 @@
         </is>
       </c>
       <c r="C499" s="7" t="n">
-        <v>3.08094848</v>
+        <v>3.12</v>
       </c>
       <c r="D499" s="7" t="n">
-        <v>2.464758784</v>
+        <v>2.5</v>
       </c>
       <c r="E499" t="n">
         <v>50</v>
@@ -13834,10 +13834,10 @@
         </is>
       </c>
       <c r="C500" s="7" t="n">
-        <v>3.42142272</v>
+        <v>3.49</v>
       </c>
       <c r="D500" s="7" t="n">
-        <v>2.737138176</v>
+        <v>2.79</v>
       </c>
       <c r="F500" s="1" t="e">
         <v>#N/A</v>
@@ -13856,10 +13856,10 @@
         </is>
       </c>
       <c r="C501" s="7" t="n">
-        <v>3.415808</v>
+        <v>3.48</v>
       </c>
       <c r="D501" s="7" t="n">
-        <v>2.7326464</v>
+        <v>2.78</v>
       </c>
       <c r="E501" t="n">
         <v>50</v>
@@ -13883,10 +13883,10 @@
         </is>
       </c>
       <c r="C502" s="7" t="n">
-        <v>3.923712</v>
+        <v>4.02</v>
       </c>
       <c r="D502" s="7" t="n">
-        <v>3.1389696</v>
+        <v>3.22</v>
       </c>
       <c r="F502" s="1" t="e">
         <v>#N/A</v>
@@ -13905,10 +13905,10 @@
         </is>
       </c>
       <c r="C503" s="7" t="n">
-        <v>9.360142079999999</v>
+        <v>9.57</v>
       </c>
       <c r="D503" s="7" t="n">
-        <v>7.488113664</v>
+        <v>7.66</v>
       </c>
       <c r="F503" s="1" t="e">
         <v>#N/A</v>
@@ -13927,10 +13927,10 @@
         </is>
       </c>
       <c r="C504" s="7" t="n">
-        <v>10.10684032</v>
+        <v>10.36</v>
       </c>
       <c r="D504" s="7" t="n">
-        <v>8.085472256000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="F504" s="1" t="e">
         <v>#N/A</v>
@@ -13949,10 +13949,10 @@
         </is>
       </c>
       <c r="C505" s="7" t="n">
-        <v>10.08866688</v>
+        <v>10.34</v>
       </c>
       <c r="D505" s="7" t="n">
-        <v>8.070933504000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="F505" s="1" t="inlineStr">
         <is>
@@ -13973,10 +13973,10 @@
         </is>
       </c>
       <c r="C506" s="7" t="n">
-        <v>10.99725952</v>
+        <v>11.31</v>
       </c>
       <c r="D506" s="7" t="n">
-        <v>8.797807616</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="F506" s="1" t="e">
         <v>#N/A</v>

--- a/dados/precos_todos.xlsx
+++ b/dados/precos_todos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a9e64bef5804d793/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_7341F0EF114A429FE8312C154A75067AC3578BDB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A7CB353-2095-4CC3-976D-A8F84860F3B5}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_7341F0EF114A429FE8312C154A75067AC3578BDB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA92A044-DE1E-4109-BF14-2A5E7F5E8077}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="14580" windowHeight="17370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
@@ -1866,7 +1866,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1874,32 +1874,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1920,6 +1904,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2232,22 +2220,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2270,7 +2258,7 @@
       <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2293,7 +2281,7 @@
       <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2316,7 +2304,7 @@
       <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2339,7 +2327,7 @@
       <c r="F5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2362,7 +2350,7 @@
       <c r="F6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2385,7 +2373,7 @@
       <c r="F7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2408,7 +2396,7 @@
       <c r="F8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2431,7 +2419,7 @@
       <c r="F9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2454,7 +2442,7 @@
       <c r="F10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2477,7 +2465,7 @@
       <c r="F11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2500,7 +2488,7 @@
       <c r="F12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2523,7 +2511,7 @@
       <c r="F13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2546,7 +2534,7 @@
       <c r="F14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2569,7 +2557,7 @@
       <c r="F15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2592,7 +2580,7 @@
       <c r="F16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2615,7 +2603,7 @@
       <c r="F17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2638,7 +2626,7 @@
       <c r="F18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2661,7 +2649,7 @@
       <c r="F19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2684,7 +2672,7 @@
       <c r="F20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2707,7 +2695,7 @@
       <c r="F21" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2730,7 +2718,7 @@
       <c r="F22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2753,7 +2741,7 @@
       <c r="F23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2776,7 +2764,7 @@
       <c r="F24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2799,7 +2787,7 @@
       <c r="F25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2822,7 +2810,7 @@
       <c r="F26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2845,7 +2833,7 @@
       <c r="F27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2868,7 +2856,7 @@
       <c r="F28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2891,7 +2879,7 @@
       <c r="F29" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2914,7 +2902,7 @@
       <c r="F30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G30" s="6">
+      <c r="G30" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2937,7 +2925,7 @@
       <c r="F31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2960,7 +2948,7 @@
       <c r="F32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -2983,7 +2971,7 @@
       <c r="F33" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3006,7 +2994,7 @@
       <c r="F34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G34" s="6">
+      <c r="G34" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3029,7 +3017,7 @@
       <c r="F35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G35" s="6">
+      <c r="G35" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3052,7 +3040,7 @@
       <c r="F36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G36" s="6">
+      <c r="G36" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3075,7 +3063,7 @@
       <c r="F37" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G37" s="6">
+      <c r="G37" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3098,7 +3086,7 @@
       <c r="F38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G38" s="6">
+      <c r="G38" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3121,7 +3109,7 @@
       <c r="F39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G39" s="6">
+      <c r="G39" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3144,7 +3132,7 @@
       <c r="F40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G40" s="6">
+      <c r="G40" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3167,7 +3155,7 @@
       <c r="F41" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G41" s="6">
+      <c r="G41" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3190,7 +3178,7 @@
       <c r="F42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G42" s="6">
+      <c r="G42" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3213,7 +3201,7 @@
       <c r="F43" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G43" s="6">
+      <c r="G43" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3236,7 +3224,7 @@
       <c r="F44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G44" s="6">
+      <c r="G44" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3259,7 +3247,7 @@
       <c r="F45" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G45" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3282,7 +3270,7 @@
       <c r="F46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G46" s="6">
+      <c r="G46" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3305,7 +3293,7 @@
       <c r="F47" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G47" s="6">
+      <c r="G47" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3328,7 +3316,7 @@
       <c r="F48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G48" s="6">
+      <c r="G48" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3351,7 +3339,7 @@
       <c r="F49" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G49" s="6">
+      <c r="G49" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3374,7 +3362,7 @@
       <c r="F50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G50" s="6">
+      <c r="G50" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3397,7 +3385,7 @@
       <c r="F51" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G51" s="6">
+      <c r="G51" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3420,7 +3408,7 @@
       <c r="F52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G52" s="6">
+      <c r="G52" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3443,7 +3431,7 @@
       <c r="F53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G53" s="6">
+      <c r="G53" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3466,7 +3454,7 @@
       <c r="F54" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G54" s="6">
+      <c r="G54" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3489,7 +3477,7 @@
       <c r="F55" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G55" s="6">
+      <c r="G55" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3512,7 +3500,7 @@
       <c r="F56" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G56" s="6">
+      <c r="G56" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3535,7 +3523,7 @@
       <c r="F57" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G57" s="6">
+      <c r="G57" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3558,7 +3546,7 @@
       <c r="F58" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G58" s="6">
+      <c r="G58" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3581,7 +3569,7 @@
       <c r="F59" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G59" s="6">
+      <c r="G59" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3604,7 +3592,7 @@
       <c r="F60" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G60" s="6">
+      <c r="G60" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3627,7 +3615,7 @@
       <c r="F61" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G61" s="6">
+      <c r="G61" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3650,7 +3638,7 @@
       <c r="F62" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G62" s="6">
+      <c r="G62" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3673,7 +3661,7 @@
       <c r="F63" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G63" s="6">
+      <c r="G63" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3696,7 +3684,7 @@
       <c r="F64" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G64" s="6">
+      <c r="G64" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3719,7 +3707,7 @@
       <c r="F65" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G65" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3742,7 +3730,7 @@
       <c r="F66" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G66" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3765,7 +3753,7 @@
       <c r="F67" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G67" s="6">
+      <c r="G67" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3788,7 +3776,7 @@
       <c r="F68" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G68" s="6">
+      <c r="G68" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3811,7 +3799,7 @@
       <c r="F69" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G69" s="6">
+      <c r="G69" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3834,7 +3822,7 @@
       <c r="F70" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G70" s="6">
+      <c r="G70" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3857,7 +3845,7 @@
       <c r="F71" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G71" s="6">
+      <c r="G71" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3880,7 +3868,7 @@
       <c r="F72" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G72" s="6">
+      <c r="G72" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3903,7 +3891,7 @@
       <c r="F73" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G73" s="6">
+      <c r="G73" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3926,7 +3914,7 @@
       <c r="F74" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G74" s="6">
+      <c r="G74" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3949,7 +3937,7 @@
       <c r="F75" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G75" s="6">
+      <c r="G75" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3972,7 +3960,7 @@
       <c r="F76" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G76" s="6">
+      <c r="G76" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -3995,7 +3983,7 @@
       <c r="F77" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G77" s="6">
+      <c r="G77" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4018,7 +4006,7 @@
       <c r="F78" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G78" s="6">
+      <c r="G78" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4041,7 +4029,7 @@
       <c r="F79" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G79" s="6">
+      <c r="G79" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4064,7 +4052,7 @@
       <c r="F80" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G80" s="6">
+      <c r="G80" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4087,7 +4075,7 @@
       <c r="F81" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G81" s="6">
+      <c r="G81" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4110,7 +4098,7 @@
       <c r="F82" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G82" s="6">
+      <c r="G82" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4133,7 +4121,7 @@
       <c r="F83" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G83" s="6">
+      <c r="G83" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4156,7 +4144,7 @@
       <c r="F84" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G84" s="6">
+      <c r="G84" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4179,7 +4167,7 @@
       <c r="F85" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G85" s="6">
+      <c r="G85" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4202,7 +4190,7 @@
       <c r="F86" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G86" s="6">
+      <c r="G86" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4225,7 +4213,7 @@
       <c r="F87" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G87" s="6">
+      <c r="G87" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4248,7 +4236,7 @@
       <c r="F88" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G88" s="6">
+      <c r="G88" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4271,7 +4259,7 @@
       <c r="F89" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G89" s="6">
+      <c r="G89" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4294,7 +4282,7 @@
       <c r="F90" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G90" s="6">
+      <c r="G90" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4317,7 +4305,7 @@
       <c r="F91" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G91" s="6">
+      <c r="G91" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4340,7 +4328,7 @@
       <c r="F92" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G92" s="6">
+      <c r="G92" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4363,7 +4351,7 @@
       <c r="F93" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G93" s="6">
+      <c r="G93" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4386,7 +4374,7 @@
       <c r="F94" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G94" s="6">
+      <c r="G94" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4409,7 +4397,7 @@
       <c r="F95" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G95" s="6">
+      <c r="G95" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4432,7 +4420,7 @@
       <c r="F96" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G96" s="6">
+      <c r="G96" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4455,7 +4443,7 @@
       <c r="F97" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G97" s="6">
+      <c r="G97" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4478,7 +4466,7 @@
       <c r="F98" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G98" s="6">
+      <c r="G98" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4501,7 +4489,7 @@
       <c r="F99" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G99" s="6">
+      <c r="G99" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4513,10 +4501,10 @@
         <v>105</v>
       </c>
       <c r="C100" s="2">
-        <v>2.96</v>
+        <v>3.0783074400000006</v>
       </c>
       <c r="D100" s="2">
-        <v>2.63</v>
+        <v>2.7362732800000007</v>
       </c>
       <c r="E100">
         <v>50</v>
@@ -4524,7 +4512,7 @@
       <c r="F100" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G100" s="6">
+      <c r="G100" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4536,10 +4524,10 @@
         <v>106</v>
       </c>
       <c r="C101" s="2">
-        <v>4.79</v>
+        <v>4.9794357599999985</v>
       </c>
       <c r="D101" s="2">
-        <v>4.26</v>
+        <v>4.4261651199999994</v>
       </c>
       <c r="E101">
         <v>25</v>
@@ -4547,7 +4535,7 @@
       <c r="F101" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G101" s="6">
+      <c r="G101" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4559,10 +4547,10 @@
         <v>107</v>
       </c>
       <c r="C102" s="2">
-        <v>7.14</v>
+        <v>7.428096</v>
       </c>
       <c r="D102" s="2">
-        <v>6.35</v>
+        <v>6.6027519999999997</v>
       </c>
       <c r="E102">
         <v>50</v>
@@ -4570,7 +4558,7 @@
       <c r="F102" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G102" s="6">
+      <c r="G102" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4582,10 +4570,10 @@
         <v>108</v>
       </c>
       <c r="C103" s="2">
-        <v>10.5</v>
+        <v>10.92046176</v>
       </c>
       <c r="D103" s="2">
-        <v>9.33</v>
+        <v>9.707077120000001</v>
       </c>
       <c r="E103">
         <v>25</v>
@@ -4593,7 +4581,7 @@
       <c r="F103" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G103" s="6">
+      <c r="G103" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4605,10 +4593,10 @@
         <v>109</v>
       </c>
       <c r="C104" s="2">
-        <v>12.78</v>
+        <v>13.288167359999999</v>
       </c>
       <c r="D104" s="2">
-        <v>11.36</v>
+        <v>11.811704319999999</v>
       </c>
       <c r="E104">
         <v>25</v>
@@ -4616,7 +4604,7 @@
       <c r="F104" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G104" s="6">
+      <c r="G104" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4628,10 +4616,10 @@
         <v>110</v>
       </c>
       <c r="C105" s="2">
-        <v>12.78</v>
+        <v>13.288167359999999</v>
       </c>
       <c r="D105" s="2">
-        <v>11.36</v>
+        <v>11.811704319999999</v>
       </c>
       <c r="E105">
         <v>25</v>
@@ -4639,7 +4627,7 @@
       <c r="F105" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G105" s="6">
+      <c r="G105" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4651,10 +4639,10 @@
         <v>111</v>
       </c>
       <c r="C106" s="2">
-        <v>22.5</v>
+        <v>23.21995356</v>
       </c>
       <c r="D106" s="2">
-        <v>20</v>
+        <v>20.639958719999999</v>
       </c>
       <c r="E106">
         <v>10</v>
@@ -4662,7 +4650,7 @@
       <c r="F106" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G106" s="6">
+      <c r="G106" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4674,10 +4662,10 @@
         <v>112</v>
       </c>
       <c r="C107" s="2">
-        <v>28.45</v>
+        <v>29.356908537599999</v>
       </c>
       <c r="D107" s="2">
-        <v>25.29</v>
+        <v>26.0950298112</v>
       </c>
       <c r="E107">
         <v>10</v>
@@ -4685,7 +4673,7 @@
       <c r="F107" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G107" s="6">
+      <c r="G107" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4697,10 +4685,10 @@
         <v>113</v>
       </c>
       <c r="C108" s="2">
-        <v>40.32</v>
+        <v>41.605595999999998</v>
       </c>
       <c r="D108" s="2">
-        <v>35.840000000000003</v>
+        <v>36.982751999999998</v>
       </c>
       <c r="E108">
         <v>10</v>
@@ -4708,7 +4696,7 @@
       <c r="F108" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G108" s="6">
+      <c r="G108" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4720,10 +4708,10 @@
         <v>114</v>
       </c>
       <c r="C109" s="2">
-        <v>55.8</v>
+        <v>57.585599999999999</v>
       </c>
       <c r="D109" s="2">
-        <v>49.6</v>
+        <v>51.187200000000004</v>
       </c>
       <c r="E109">
         <v>5</v>
@@ -4731,7 +4719,7 @@
       <c r="F109" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G109" s="6">
+      <c r="G109" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4743,10 +4731,10 @@
         <v>115</v>
       </c>
       <c r="C110" s="2">
-        <v>73.8</v>
+        <v>76.156955999999994</v>
       </c>
       <c r="D110" s="2">
-        <v>65.599999999999994</v>
+        <v>67.695071999999996</v>
       </c>
       <c r="E110">
         <v>5</v>
@@ -4754,7 +4742,7 @@
       <c r="F110" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G110" s="6">
+      <c r="G110" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4766,10 +4754,10 @@
         <v>116</v>
       </c>
       <c r="C111" s="2">
-        <v>94.3</v>
+        <v>97.319664000000017</v>
       </c>
       <c r="D111" s="2">
-        <v>83.82</v>
+        <v>86.506368000000009</v>
       </c>
       <c r="E111">
         <v>5</v>
@@ -4777,7 +4765,7 @@
       <c r="F111" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G111" s="6">
+      <c r="G111" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4789,10 +4777,10 @@
         <v>117</v>
       </c>
       <c r="C112" s="2">
-        <v>117.32</v>
+        <v>121.07372400000001</v>
       </c>
       <c r="D112" s="2">
-        <v>104.28</v>
+        <v>107.62108800000001</v>
       </c>
       <c r="E112">
         <v>3</v>
@@ -4800,7 +4788,7 @@
       <c r="F112" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G112" s="6">
+      <c r="G112" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4812,10 +4800,10 @@
         <v>118</v>
       </c>
       <c r="C113" s="2">
-        <v>170.89</v>
+        <v>176.35589999999999</v>
       </c>
       <c r="D113" s="2">
-        <v>151.9</v>
+        <v>156.76080000000002</v>
       </c>
       <c r="E113">
         <v>3</v>
@@ -4823,7 +4811,7 @@
       <c r="F113" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G113" s="6">
+      <c r="G113" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4835,10 +4823,10 @@
         <v>119</v>
       </c>
       <c r="C114" s="2">
-        <v>5.73</v>
+        <v>5.9631103999999988</v>
       </c>
       <c r="D114" s="2">
-        <v>4.87</v>
+        <v>5.0686438399999991</v>
       </c>
       <c r="E114">
         <v>50</v>
@@ -4846,7 +4834,7 @@
       <c r="F114" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G114" s="6">
+      <c r="G114" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4858,10 +4846,10 @@
         <v>120</v>
       </c>
       <c r="C115" s="2">
-        <v>9.6</v>
+        <v>9.9866624000000019</v>
       </c>
       <c r="D115" s="2">
-        <v>8.16</v>
+        <v>8.4886630400000023</v>
       </c>
       <c r="E115">
         <v>25</v>
@@ -4869,7 +4857,7 @@
       <c r="F115" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G115" s="6">
+      <c r="G115" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4881,10 +4869,10 @@
         <v>121</v>
       </c>
       <c r="C116" s="2">
-        <v>14.2</v>
+        <v>14.764630399999998</v>
       </c>
       <c r="D116" s="2">
-        <v>12.07</v>
+        <v>12.549935839999998</v>
       </c>
       <c r="E116">
         <v>25</v>
@@ -4892,7 +4880,7 @@
       <c r="F116" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G116" s="6">
+      <c r="G116" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4904,10 +4892,10 @@
         <v>122</v>
       </c>
       <c r="C117" s="2">
-        <v>25</v>
+        <v>25.799948399999998</v>
       </c>
       <c r="D117" s="2">
-        <v>21.25</v>
+        <v>21.929956139999998</v>
       </c>
       <c r="E117">
         <v>10</v>
@@ -4915,7 +4903,7 @@
       <c r="F117" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G117" s="6">
+      <c r="G117" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4927,10 +4915,10 @@
         <v>123</v>
       </c>
       <c r="C118" s="2">
-        <v>31.61</v>
+        <v>32.618787263999998</v>
       </c>
       <c r="D118" s="2">
-        <v>26.87</v>
+        <v>27.725969174399996</v>
       </c>
       <c r="E118">
         <v>100</v>
@@ -4938,7 +4926,7 @@
       <c r="F118" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G118" s="6">
+      <c r="G118" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4950,10 +4938,10 @@
         <v>124</v>
       </c>
       <c r="C119" s="2">
-        <v>50.22</v>
+        <v>51.827039999999997</v>
       </c>
       <c r="D119" s="2">
-        <v>42.69</v>
+        <v>44.052983999999995</v>
       </c>
       <c r="E119">
         <v>10</v>
@@ -4961,7 +4949,7 @@
       <c r="F119" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G119" s="6">
+      <c r="G119" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4973,10 +4961,10 @@
         <v>125</v>
       </c>
       <c r="C120" s="2">
-        <v>75.02</v>
+        <v>77.420640000000006</v>
       </c>
       <c r="D120" s="2">
-        <v>63.77</v>
+        <v>65.807544000000007</v>
       </c>
       <c r="E120">
         <v>4</v>
@@ -4984,7 +4972,7 @@
       <c r="F120" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G120" s="6">
+      <c r="G120" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -4996,10 +4984,10 @@
         <v>126</v>
       </c>
       <c r="C121" s="2">
-        <v>117.22</v>
+        <v>120.96974999999999</v>
       </c>
       <c r="D121" s="2">
-        <v>99.64</v>
+        <v>102.82428749999998</v>
       </c>
       <c r="E121">
         <v>4</v>
@@ -5007,7 +4995,7 @@
       <c r="F121" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G121" s="6">
+      <c r="G121" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5019,10 +5007,10 @@
         <v>127</v>
       </c>
       <c r="C122" s="2">
-        <v>170.85</v>
+        <v>176.31431040000004</v>
       </c>
       <c r="D122" s="2">
-        <v>145.22</v>
+        <v>149.86716384000002</v>
       </c>
       <c r="E122">
         <v>2</v>
@@ -5030,7 +5018,7 @@
       <c r="F122" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G122" s="6">
+      <c r="G122" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5042,10 +5030,10 @@
         <v>128</v>
       </c>
       <c r="C123" s="2">
-        <v>8.8800000000000008</v>
+        <v>18.825033960000003</v>
       </c>
       <c r="D123" s="2">
-        <v>7.89</v>
+        <v>16.733363520000005</v>
       </c>
       <c r="E123">
         <v>50</v>
@@ -5053,7 +5041,7 @@
       <c r="F123" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G123" s="6">
+      <c r="G123" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5065,10 +5053,10 @@
         <v>129</v>
       </c>
       <c r="C124" s="2">
-        <v>14.36</v>
+        <v>24.705662039999993</v>
       </c>
       <c r="D124" s="2">
-        <v>12.77</v>
+        <v>21.960588479999995</v>
       </c>
       <c r="E124">
         <v>25</v>
@@ -5076,7 +5064,7 @@
       <c r="F124" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G124" s="6">
+      <c r="G124" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5088,10 +5076,10 @@
         <v>130</v>
       </c>
       <c r="C125" s="2">
-        <v>21.43</v>
+        <v>29.998080000000002</v>
       </c>
       <c r="D125" s="2">
-        <v>19.05</v>
+        <v>26.664960000000001</v>
       </c>
       <c r="E125">
         <v>20</v>
@@ -5099,7 +5087,7 @@
       <c r="F125" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G125" s="6">
+      <c r="G125" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5111,10 +5099,10 @@
         <v>131</v>
       </c>
       <c r="C126" s="2">
-        <v>31.5</v>
+        <v>40.951731599999995</v>
       </c>
       <c r="D126" s="2">
-        <v>28</v>
+        <v>36.401539200000002</v>
       </c>
       <c r="E126">
         <v>10</v>
@@ -5122,7 +5110,7 @@
       <c r="F126" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G126" s="6">
+      <c r="G126" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5134,10 +5122,10 @@
         <v>132</v>
       </c>
       <c r="C127" s="2">
-        <v>38.33</v>
+        <v>49.830627599999985</v>
       </c>
       <c r="D127" s="2">
-        <v>34.07</v>
+        <v>44.29389119999999</v>
       </c>
       <c r="E127">
         <v>10</v>
@@ -5145,7 +5133,7 @@
       <c r="F127" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G127" s="6">
+      <c r="G127" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5157,10 +5145,10 @@
         <v>133</v>
       </c>
       <c r="C128" s="2">
-        <v>38.33</v>
+        <v>49.830627599999985</v>
       </c>
       <c r="D128" s="2">
-        <v>34.07</v>
+        <v>44.29389119999999</v>
       </c>
       <c r="E128">
         <v>10</v>
@@ -5168,7 +5156,7 @@
       <c r="F128" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G128" s="6">
+      <c r="G128" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5180,10 +5168,10 @@
         <v>134</v>
       </c>
       <c r="C129" s="2">
-        <v>67.5</v>
+        <v>70.199859599999996</v>
       </c>
       <c r="D129" s="2">
-        <v>60</v>
+        <v>62.399875200000004</v>
       </c>
       <c r="E129">
         <v>10</v>
@@ -5191,7 +5179,7 @@
       <c r="F129" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G129" s="6">
+      <c r="G129" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5203,10 +5191,10 @@
         <v>135</v>
       </c>
       <c r="C130" s="2">
-        <v>85.34</v>
+        <v>88.753444416000008</v>
       </c>
       <c r="D130" s="2">
-        <v>75.86</v>
+        <v>78.891950592000001</v>
       </c>
       <c r="E130">
         <v>5</v>
@@ -5214,7 +5202,7 @@
       <c r="F130" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G130" s="6">
+      <c r="G130" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5226,10 +5214,10 @@
         <v>136</v>
       </c>
       <c r="C131" s="2">
-        <v>120.95</v>
+        <v>125.78435999999999</v>
       </c>
       <c r="D131" s="2">
-        <v>107.51</v>
+        <v>111.80831999999998</v>
       </c>
       <c r="E131">
         <v>5</v>
@@ -5237,7 +5225,7 @@
       <c r="F131" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G131" s="6">
+      <c r="G131" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5249,10 +5237,10 @@
         <v>137</v>
       </c>
       <c r="C132" s="2">
-        <v>167.4</v>
+        <v>174.096</v>
       </c>
       <c r="D132" s="2">
-        <v>148.80000000000001</v>
+        <v>154.75200000000001</v>
       </c>
       <c r="E132">
         <v>3</v>
@@ -5260,7 +5248,7 @@
       <c r="F132" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G132" s="6">
+      <c r="G132" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5272,10 +5260,10 @@
         <v>138</v>
       </c>
       <c r="C133" s="2">
-        <v>221.39</v>
+        <v>230.24196000000001</v>
       </c>
       <c r="D133" s="2">
-        <v>196.79</v>
+        <v>204.65952000000001</v>
       </c>
       <c r="E133">
         <v>3</v>
@@ -5283,7 +5271,7 @@
       <c r="F133" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G133" s="6">
+      <c r="G133" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5295,10 +5283,10 @@
         <v>139</v>
       </c>
       <c r="C134" s="2">
-        <v>282.91000000000003</v>
+        <v>294.22224000000006</v>
       </c>
       <c r="D134" s="2">
-        <v>251.47</v>
+        <v>261.53088000000002</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -5306,7 +5294,7 @@
       <c r="F134" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G134" s="6">
+      <c r="G134" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5318,10 +5306,10 @@
         <v>140</v>
       </c>
       <c r="C135" s="2">
-        <v>351.96</v>
+        <v>366.03683999999998</v>
       </c>
       <c r="D135" s="2">
-        <v>312.85000000000002</v>
+        <v>325.36608000000001</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -5329,7 +5317,7 @@
       <c r="F135" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G135" s="6">
+      <c r="G135" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5341,10 +5329,10 @@
         <v>141</v>
       </c>
       <c r="C136" s="2">
-        <v>512.66</v>
+        <v>533.1690000000001</v>
       </c>
       <c r="D136" s="2">
-        <v>455.7</v>
+        <v>473.928</v>
       </c>
       <c r="E136">
         <v>1</v>
@@ -5352,7 +5340,7 @@
       <c r="F136" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G136" s="6">
+      <c r="G136" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5364,10 +5352,10 @@
         <v>142</v>
       </c>
       <c r="C137" s="2">
-        <v>17.2</v>
+        <v>20.125497599999996</v>
       </c>
       <c r="D137" s="2">
-        <v>14.62</v>
+        <v>17.889331199999997</v>
       </c>
       <c r="E137">
         <v>25</v>
@@ -5375,7 +5363,7 @@
       <c r="F137" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G137" s="6">
+      <c r="G137" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5387,10 +5375,10 @@
         <v>143</v>
       </c>
       <c r="C138" s="2">
-        <v>28.81</v>
+        <v>33.704985600000008</v>
       </c>
       <c r="D138" s="2">
-        <v>24.49</v>
+        <v>29.959987200000008</v>
       </c>
       <c r="E138">
         <v>25</v>
@@ -5398,7 +5386,7 @@
       <c r="F138" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G138" s="6">
+      <c r="G138" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5410,10 +5398,10 @@
         <v>144</v>
       </c>
       <c r="C139" s="2">
-        <v>42.59</v>
+        <v>49.830627599999985</v>
       </c>
       <c r="D139" s="2">
-        <v>36.200000000000003</v>
+        <v>44.29389119999999</v>
       </c>
       <c r="E139">
         <v>10</v>
@@ -5421,7 +5409,7 @@
       <c r="F139" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G139" s="6">
+      <c r="G139" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5433,10 +5421,10 @@
         <v>145</v>
       </c>
       <c r="C140" s="2">
-        <v>75</v>
+        <v>70.199859599999996</v>
       </c>
       <c r="D140" s="2">
-        <v>63.75</v>
+        <v>62.399875200000004</v>
       </c>
       <c r="E140">
         <v>10</v>
@@ -5444,7 +5432,7 @@
       <c r="F140" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G140" s="6">
+      <c r="G140" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5456,10 +5444,10 @@
         <v>146</v>
       </c>
       <c r="C141" s="2">
-        <v>94.82</v>
+        <v>88.753444416000008</v>
       </c>
       <c r="D141" s="2">
-        <v>80.599999999999994</v>
+        <v>78.891950592000001</v>
       </c>
       <c r="E141">
         <v>25</v>
@@ -5467,7 +5455,7 @@
       <c r="F141" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G141" s="6">
+      <c r="G141" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5479,10 +5467,10 @@
         <v>147</v>
       </c>
       <c r="C142" s="2">
-        <v>150.66</v>
+        <v>141.01776000000001</v>
       </c>
       <c r="D142" s="2">
-        <v>128.06</v>
+        <v>125.34912</v>
       </c>
       <c r="E142">
         <v>5</v>
@@ -5490,7 +5478,7 @@
       <c r="F142" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G142" s="6">
+      <c r="G142" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5502,10 +5490,10 @@
         <v>148</v>
       </c>
       <c r="C143" s="2">
-        <v>225.06</v>
+        <v>210.65615999999997</v>
       </c>
       <c r="D143" s="2">
-        <v>191.3</v>
+        <v>187.24992</v>
       </c>
       <c r="E143">
         <v>3</v>
@@ -5513,7 +5501,7 @@
       <c r="F143" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G143" s="6">
+      <c r="G143" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5525,10 +5513,10 @@
         <v>149</v>
       </c>
       <c r="C144" s="2">
-        <v>351.66</v>
+        <v>329.15025000000003</v>
       </c>
       <c r="D144" s="2">
-        <v>298.91000000000003</v>
+        <v>292.57800000000003</v>
       </c>
       <c r="E144">
         <v>1</v>
@@ -5536,7 +5524,7 @@
       <c r="F144" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G144" s="6">
+      <c r="G144" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5548,10 +5536,10 @@
         <v>150</v>
       </c>
       <c r="C145" s="2">
-        <v>512.54</v>
+        <v>479.7389376000001</v>
       </c>
       <c r="D145" s="2">
-        <v>435.66</v>
+        <v>426.43461120000006</v>
       </c>
       <c r="E145">
         <v>1</v>
@@ -5559,7 +5547,7 @@
       <c r="F145" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G145" s="6">
+      <c r="G145" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5573,7 +5561,7 @@
       <c r="C146" s="2">
         <v>8.6300000000000008</v>
       </c>
-      <c r="D146">
+      <c r="D146" s="2">
         <v>6.91</v>
       </c>
       <c r="E146">
@@ -5582,7 +5570,7 @@
       <c r="F146" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G146" s="6">
+      <c r="G146" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5596,7 +5584,7 @@
       <c r="C147" s="2">
         <v>13.96</v>
       </c>
-      <c r="D147">
+      <c r="D147" s="2">
         <v>11.17</v>
       </c>
       <c r="E147">
@@ -5605,7 +5593,7 @@
       <c r="F147" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G147" s="6">
+      <c r="G147" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5628,7 +5616,7 @@
       <c r="F148" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G148" s="6">
+      <c r="G148" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5651,7 +5639,7 @@
       <c r="F149" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G149" s="6">
+      <c r="G149" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5674,7 +5662,7 @@
       <c r="F150" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G150" s="6">
+      <c r="G150" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5697,7 +5685,7 @@
       <c r="F151" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G151" s="6">
+      <c r="G151" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5720,7 +5708,7 @@
       <c r="F152" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G152" s="6">
+      <c r="G152" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5743,7 +5731,7 @@
       <c r="F153" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G153" s="6">
+      <c r="G153" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5766,7 +5754,7 @@
       <c r="F154" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G154" s="6">
+      <c r="G154" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5789,7 +5777,7 @@
       <c r="F155" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G155" s="6">
+      <c r="G155" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5812,7 +5800,7 @@
       <c r="F156" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G156" s="6">
+      <c r="G156" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5835,7 +5823,7 @@
       <c r="F157" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G157" s="6">
+      <c r="G157" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5858,7 +5846,7 @@
       <c r="F158" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G158" s="6">
+      <c r="G158" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5881,7 +5869,7 @@
       <c r="F159" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G159" s="6">
+      <c r="G159" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5904,7 +5892,7 @@
       <c r="F160" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G160" s="6">
+      <c r="G160" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5927,7 +5915,7 @@
       <c r="F161" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G161" s="6">
+      <c r="G161" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -5938,7 +5926,7 @@
       <c r="B162" t="s">
         <v>167</v>
       </c>
-      <c r="C162" s="3">
+      <c r="C162" s="2">
         <v>1.48</v>
       </c>
       <c r="D162" s="2">
@@ -5950,7 +5938,7 @@
       <c r="F162" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G162" s="5">
+      <c r="G162" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -5961,7 +5949,7 @@
       <c r="B163" t="s">
         <v>169</v>
       </c>
-      <c r="C163" s="3">
+      <c r="C163" s="2">
         <v>1.51</v>
       </c>
       <c r="D163" s="2">
@@ -5973,7 +5961,7 @@
       <c r="F163" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G163" s="5">
+      <c r="G163" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -5984,7 +5972,7 @@
       <c r="B164" t="s">
         <v>170</v>
       </c>
-      <c r="C164" s="3">
+      <c r="C164" s="2">
         <v>1.54</v>
       </c>
       <c r="D164" s="2">
@@ -5996,7 +5984,7 @@
       <c r="F164" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G164" s="5">
+      <c r="G164" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6007,7 +5995,7 @@
       <c r="B165" t="s">
         <v>171</v>
       </c>
-      <c r="C165" s="3">
+      <c r="C165" s="2">
         <v>1.56</v>
       </c>
       <c r="D165" s="2">
@@ -6019,7 +6007,7 @@
       <c r="F165" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G165" s="5">
+      <c r="G165" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6030,7 +6018,7 @@
       <c r="B166" t="s">
         <v>172</v>
       </c>
-      <c r="C166" s="3">
+      <c r="C166" s="2">
         <v>1.59</v>
       </c>
       <c r="D166" s="2">
@@ -6042,7 +6030,7 @@
       <c r="F166" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G166" s="5">
+      <c r="G166" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6053,7 +6041,7 @@
       <c r="B167" t="s">
         <v>173</v>
       </c>
-      <c r="C167" s="3">
+      <c r="C167" s="2">
         <v>1.69</v>
       </c>
       <c r="D167" s="2">
@@ -6065,7 +6053,7 @@
       <c r="F167" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G167" s="5">
+      <c r="G167" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6076,7 +6064,7 @@
       <c r="B168" t="s">
         <v>174</v>
       </c>
-      <c r="C168" s="3">
+      <c r="C168" s="2">
         <v>1.74</v>
       </c>
       <c r="D168" s="2">
@@ -6088,7 +6076,7 @@
       <c r="F168" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G168" s="5">
+      <c r="G168" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6099,7 +6087,7 @@
       <c r="B169" t="s">
         <v>175</v>
       </c>
-      <c r="C169" s="3">
+      <c r="C169" s="2">
         <v>1.8</v>
       </c>
       <c r="D169" s="2">
@@ -6111,7 +6099,7 @@
       <c r="F169" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G169" s="5">
+      <c r="G169" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6122,7 +6110,7 @@
       <c r="B170" t="s">
         <v>176</v>
       </c>
-      <c r="C170" s="3">
+      <c r="C170" s="2">
         <v>1.85</v>
       </c>
       <c r="D170" s="2">
@@ -6134,7 +6122,7 @@
       <c r="F170" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G170" s="5">
+      <c r="G170" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6145,7 +6133,7 @@
       <c r="B171" t="s">
         <v>177</v>
       </c>
-      <c r="C171" s="3">
+      <c r="C171" s="2">
         <v>1.93</v>
       </c>
       <c r="D171" s="2">
@@ -6157,7 +6145,7 @@
       <c r="F171" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G171" s="5">
+      <c r="G171" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6168,7 +6156,7 @@
       <c r="B172" t="s">
         <v>178</v>
       </c>
-      <c r="C172" s="3">
+      <c r="C172" s="2">
         <v>1.65</v>
       </c>
       <c r="D172" s="2">
@@ -6180,7 +6168,7 @@
       <c r="F172" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G172" s="5">
+      <c r="G172" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6191,7 +6179,7 @@
       <c r="B173" t="s">
         <v>179</v>
       </c>
-      <c r="C173" s="3">
+      <c r="C173" s="2">
         <v>1.71</v>
       </c>
       <c r="D173" s="2">
@@ -6203,7 +6191,7 @@
       <c r="F173" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G173" s="5">
+      <c r="G173" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6214,7 +6202,7 @@
       <c r="B174" t="s">
         <v>180</v>
       </c>
-      <c r="C174" s="3">
+      <c r="C174" s="2">
         <v>1.75</v>
       </c>
       <c r="D174" s="2">
@@ -6226,7 +6214,7 @@
       <c r="F174" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G174" s="5">
+      <c r="G174" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6237,7 +6225,7 @@
       <c r="B175" t="s">
         <v>181</v>
       </c>
-      <c r="C175" s="3">
+      <c r="C175" s="2">
         <v>1.79</v>
       </c>
       <c r="D175" s="2">
@@ -6249,7 +6237,7 @@
       <c r="F175" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G175" s="5">
+      <c r="G175" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6260,7 +6248,7 @@
       <c r="B176" t="s">
         <v>182</v>
       </c>
-      <c r="C176" s="3">
+      <c r="C176" s="2">
         <v>1.83</v>
       </c>
       <c r="D176" s="2">
@@ -6272,7 +6260,7 @@
       <c r="F176" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G176" s="5">
+      <c r="G176" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6283,7 +6271,7 @@
       <c r="B177" t="s">
         <v>183</v>
       </c>
-      <c r="C177" s="3">
+      <c r="C177" s="2">
         <v>1.99</v>
       </c>
       <c r="D177" s="2">
@@ -6295,7 +6283,7 @@
       <c r="F177" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G177" s="5">
+      <c r="G177" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6306,7 +6294,7 @@
       <c r="B178" t="s">
         <v>184</v>
       </c>
-      <c r="C178" s="3">
+      <c r="C178" s="2">
         <v>2.0699999999999998</v>
       </c>
       <c r="D178" s="2">
@@ -6318,7 +6306,7 @@
       <c r="F178" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G178" s="5">
+      <c r="G178" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6329,7 +6317,7 @@
       <c r="B179" t="s">
         <v>185</v>
       </c>
-      <c r="C179" s="3">
+      <c r="C179" s="2">
         <v>2.17</v>
       </c>
       <c r="D179" s="2">
@@ -6341,7 +6329,7 @@
       <c r="F179" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G179" s="5">
+      <c r="G179" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6352,7 +6340,7 @@
       <c r="B180" t="s">
         <v>186</v>
       </c>
-      <c r="C180" s="3">
+      <c r="C180" s="2">
         <v>2.2599999999999998</v>
       </c>
       <c r="D180" s="2">
@@ -6364,7 +6352,7 @@
       <c r="F180" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G180" s="5">
+      <c r="G180" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6375,7 +6363,7 @@
       <c r="B181" t="s">
         <v>187</v>
       </c>
-      <c r="C181" s="3">
+      <c r="C181" s="2">
         <v>2.38</v>
       </c>
       <c r="D181" s="2">
@@ -6387,7 +6375,7 @@
       <c r="F181" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G181" s="5">
+      <c r="G181" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6398,7 +6386,7 @@
       <c r="B182" t="s">
         <v>188</v>
       </c>
-      <c r="C182" s="3">
+      <c r="C182" s="2">
         <v>2.14</v>
       </c>
       <c r="D182" s="2">
@@ -6410,7 +6398,7 @@
       <c r="F182" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G182" s="5">
+      <c r="G182" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6421,7 +6409,7 @@
       <c r="B183" t="s">
         <v>189</v>
       </c>
-      <c r="C183" s="3">
+      <c r="C183" s="2">
         <v>2.37</v>
       </c>
       <c r="D183" s="2">
@@ -6433,7 +6421,7 @@
       <c r="F183" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G183" s="5">
+      <c r="G183" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6444,7 +6432,7 @@
       <c r="B184" t="s">
         <v>190</v>
       </c>
-      <c r="C184" s="3">
+      <c r="C184" s="2">
         <v>2.4900000000000002</v>
       </c>
       <c r="D184" s="2">
@@ -6456,7 +6444,7 @@
       <c r="F184" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G184" s="5">
+      <c r="G184" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6467,7 +6455,7 @@
       <c r="B185" t="s">
         <v>191</v>
       </c>
-      <c r="C185" s="3">
+      <c r="C185" s="2">
         <v>2.65</v>
       </c>
       <c r="D185" s="2">
@@ -6479,7 +6467,7 @@
       <c r="F185" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G185" s="5">
+      <c r="G185" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6490,7 +6478,7 @@
       <c r="B186" t="s">
         <v>192</v>
       </c>
-      <c r="C186" s="3">
+      <c r="C186" s="2">
         <v>2.78</v>
       </c>
       <c r="D186" s="2">
@@ -6502,7 +6490,7 @@
       <c r="F186" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G186" s="5">
+      <c r="G186" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6513,7 +6501,7 @@
       <c r="B187" t="s">
         <v>193</v>
       </c>
-      <c r="C187" s="3">
+      <c r="C187" s="2">
         <v>2.96</v>
       </c>
       <c r="D187" s="2">
@@ -6525,7 +6513,7 @@
       <c r="F187" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G187" s="5">
+      <c r="G187" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6536,7 +6524,7 @@
       <c r="B188" t="s">
         <v>194</v>
       </c>
-      <c r="C188" s="3">
+      <c r="C188" s="2">
         <v>3.35</v>
       </c>
       <c r="D188" s="2">
@@ -6548,7 +6536,7 @@
       <c r="F188" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G188" s="5">
+      <c r="G188" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6559,7 +6547,7 @@
       <c r="B189" t="s">
         <v>195</v>
       </c>
-      <c r="C189" s="3">
+      <c r="C189" s="2">
         <v>3.75</v>
       </c>
       <c r="D189" s="2">
@@ -6571,7 +6559,7 @@
       <c r="F189" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G189" s="5">
+      <c r="G189" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6582,7 +6570,7 @@
       <c r="B190" t="s">
         <v>196</v>
       </c>
-      <c r="C190" s="3">
+      <c r="C190" s="2">
         <v>4.2699999999999996</v>
       </c>
       <c r="D190" s="2">
@@ -6594,7 +6582,7 @@
       <c r="F190" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G190" s="5">
+      <c r="G190" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6605,7 +6593,7 @@
       <c r="B191" t="s">
         <v>197</v>
       </c>
-      <c r="C191" s="3">
+      <c r="C191" s="2">
         <v>4.9400000000000004</v>
       </c>
       <c r="D191" s="2">
@@ -6617,7 +6605,7 @@
       <c r="F191" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G191" s="5">
+      <c r="G191" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6628,7 +6616,7 @@
       <c r="B192" t="s">
         <v>198</v>
       </c>
-      <c r="C192" s="3">
+      <c r="C192" s="2">
         <v>5.3</v>
       </c>
       <c r="D192" s="2">
@@ -6640,7 +6628,7 @@
       <c r="F192" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G192" s="5">
+      <c r="G192" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6651,7 +6639,7 @@
       <c r="B193" t="s">
         <v>199</v>
       </c>
-      <c r="C193" s="3">
+      <c r="C193" s="2">
         <v>5.0999999999999996</v>
       </c>
       <c r="D193" s="2">
@@ -6663,7 +6651,7 @@
       <c r="F193" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G193" s="5">
+      <c r="G193" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6674,7 +6662,7 @@
       <c r="B194" t="s">
         <v>200</v>
       </c>
-      <c r="C194" s="3">
+      <c r="C194" s="2">
         <v>5.31</v>
       </c>
       <c r="D194" s="2">
@@ -6686,7 +6674,7 @@
       <c r="F194" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G194" s="5">
+      <c r="G194" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6697,7 +6685,7 @@
       <c r="B195" t="s">
         <v>201</v>
       </c>
-      <c r="C195" s="3">
+      <c r="C195" s="2">
         <v>5.59</v>
       </c>
       <c r="D195" s="2">
@@ -6709,7 +6697,7 @@
       <c r="F195" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G195" s="5">
+      <c r="G195" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6720,7 +6708,7 @@
       <c r="B196" t="s">
         <v>202</v>
       </c>
-      <c r="C196" s="3">
+      <c r="C196" s="2">
         <v>5.82</v>
       </c>
       <c r="D196" s="2">
@@ -6732,7 +6720,7 @@
       <c r="F196" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G196" s="5">
+      <c r="G196" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6743,7 +6731,7 @@
       <c r="B197" t="s">
         <v>203</v>
       </c>
-      <c r="C197" s="3">
+      <c r="C197" s="2">
         <v>6.14</v>
       </c>
       <c r="D197" s="2">
@@ -6755,7 +6743,7 @@
       <c r="F197" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G197" s="5">
+      <c r="G197" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6766,7 +6754,7 @@
       <c r="B198" t="s">
         <v>204</v>
       </c>
-      <c r="C198" s="3">
+      <c r="C198" s="2">
         <v>6.85</v>
       </c>
       <c r="D198" s="2">
@@ -6778,7 +6766,7 @@
       <c r="F198" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G198" s="5">
+      <c r="G198" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6789,7 +6777,7 @@
       <c r="B199" t="s">
         <v>205</v>
       </c>
-      <c r="C199" s="3">
+      <c r="C199" s="2">
         <v>7.56</v>
       </c>
       <c r="D199" s="2">
@@ -6801,7 +6789,7 @@
       <c r="F199" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G199" s="5">
+      <c r="G199" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6812,7 +6800,7 @@
       <c r="B200" t="s">
         <v>206</v>
       </c>
-      <c r="C200" s="3">
+      <c r="C200" s="2">
         <v>8.5</v>
       </c>
       <c r="D200" s="2">
@@ -6824,7 +6812,7 @@
       <c r="F200" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G200" s="5">
+      <c r="G200" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6835,7 +6823,7 @@
       <c r="B201" t="s">
         <v>207</v>
       </c>
-      <c r="C201" s="3">
+      <c r="C201" s="2">
         <v>9.6999999999999993</v>
       </c>
       <c r="D201" s="2">
@@ -6847,7 +6835,7 @@
       <c r="F201" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G201" s="5">
+      <c r="G201" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6858,7 +6846,7 @@
       <c r="B202" t="s">
         <v>208</v>
       </c>
-      <c r="C202" s="3">
+      <c r="C202" s="2">
         <v>10.34</v>
       </c>
       <c r="D202" s="2">
@@ -6870,7 +6858,7 @@
       <c r="F202" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G202" s="5">
+      <c r="G202" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6881,7 +6869,7 @@
       <c r="B203" t="s">
         <v>209</v>
       </c>
-      <c r="C203" s="3">
+      <c r="C203" s="2">
         <v>13.13</v>
       </c>
       <c r="D203" s="2">
@@ -6893,7 +6881,7 @@
       <c r="F203" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G203" s="5">
+      <c r="G203" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6904,7 +6892,7 @@
       <c r="B204" t="s">
         <v>210</v>
       </c>
-      <c r="C204" s="3">
+      <c r="C204" s="2">
         <v>14.8</v>
       </c>
       <c r="D204" s="2">
@@ -6916,7 +6904,7 @@
       <c r="F204" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G204" s="5">
+      <c r="G204" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6927,7 +6915,7 @@
       <c r="B205" t="s">
         <v>211</v>
       </c>
-      <c r="C205" s="3">
+      <c r="C205" s="2">
         <v>16.93</v>
       </c>
       <c r="D205" s="2">
@@ -6939,7 +6927,7 @@
       <c r="F205" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G205" s="5">
+      <c r="G205" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6950,7 +6938,7 @@
       <c r="B206" t="s">
         <v>212</v>
       </c>
-      <c r="C206" s="3">
+      <c r="C206" s="2">
         <v>18.07</v>
       </c>
       <c r="D206" s="2">
@@ -6962,7 +6950,7 @@
       <c r="F206" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G206" s="5">
+      <c r="G206" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -6985,7 +6973,7 @@
       <c r="F207" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G207" s="5">
+      <c r="G207" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7008,7 +6996,7 @@
       <c r="F208" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G208" s="5">
+      <c r="G208" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7031,7 +7019,7 @@
       <c r="F209" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G209" s="5">
+      <c r="G209" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7054,7 +7042,7 @@
       <c r="F210" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G210" s="5">
+      <c r="G210" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7077,7 +7065,7 @@
       <c r="F211" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G211" s="5">
+      <c r="G211" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7100,7 +7088,7 @@
       <c r="F212" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G212" s="5">
+      <c r="G212" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7123,7 +7111,7 @@
       <c r="F213" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G213" s="5">
+      <c r="G213" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7146,7 +7134,7 @@
       <c r="F214" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G214" s="5">
+      <c r="G214" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7169,7 +7157,7 @@
       <c r="F215" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G215" s="5">
+      <c r="G215" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7192,7 +7180,7 @@
       <c r="F216" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G216" s="5">
+      <c r="G216" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7215,7 +7203,7 @@
       <c r="F217" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G217" s="5">
+      <c r="G217" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7238,7 +7226,7 @@
       <c r="F218" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G218" s="5">
+      <c r="G218" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7261,7 +7249,7 @@
       <c r="F219" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G219" s="5">
+      <c r="G219" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7284,7 +7272,7 @@
       <c r="F220" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G220" s="5">
+      <c r="G220" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7307,7 +7295,7 @@
       <c r="F221" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G221" s="5">
+      <c r="G221" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7330,7 +7318,7 @@
       <c r="F222" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G222" s="5">
+      <c r="G222" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7353,7 +7341,7 @@
       <c r="F223" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G223" s="5">
+      <c r="G223" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7376,7 +7364,7 @@
       <c r="F224" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G224" s="5">
+      <c r="G224" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7399,7 +7387,7 @@
       <c r="F225" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G225" s="5">
+      <c r="G225" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7422,7 +7410,7 @@
       <c r="F226" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G226" s="5">
+      <c r="G226" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7445,7 +7433,7 @@
       <c r="F227" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G227" s="5">
+      <c r="G227" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7468,7 +7456,7 @@
       <c r="F228" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G228" s="5">
+      <c r="G228" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7491,7 +7479,7 @@
       <c r="F229" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G229" s="5">
+      <c r="G229" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7514,7 +7502,7 @@
       <c r="F230" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G230" s="5">
+      <c r="G230" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7537,7 +7525,7 @@
       <c r="F231" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G231" s="5">
+      <c r="G231" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7560,7 +7548,7 @@
       <c r="F232" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G232" s="5">
+      <c r="G232" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7583,7 +7571,7 @@
       <c r="F233" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G233" s="5">
+      <c r="G233" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7606,7 +7594,7 @@
       <c r="F234" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G234" s="5">
+      <c r="G234" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7629,7 +7617,7 @@
       <c r="F235" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G235" s="5">
+      <c r="G235" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7652,7 +7640,7 @@
       <c r="F236" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G236" s="5">
+      <c r="G236" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7675,7 +7663,7 @@
       <c r="F237" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G237" s="5">
+      <c r="G237" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7698,7 +7686,7 @@
       <c r="F238" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G238" s="5">
+      <c r="G238" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7721,7 +7709,7 @@
       <c r="F239" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G239" s="5">
+      <c r="G239" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7744,7 +7732,7 @@
       <c r="F240" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G240" s="5">
+      <c r="G240" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7767,7 +7755,7 @@
       <c r="F241" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G241" s="5">
+      <c r="G241" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7790,7 +7778,7 @@
       <c r="F242" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G242" s="5">
+      <c r="G242" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7813,7 +7801,7 @@
       <c r="F243" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G243" s="5">
+      <c r="G243" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7836,7 +7824,7 @@
       <c r="F244" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G244" s="5">
+      <c r="G244" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7859,7 +7847,7 @@
       <c r="F245" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G245" s="5">
+      <c r="G245" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7882,7 +7870,7 @@
       <c r="F246" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G246" s="5">
+      <c r="G246" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7905,7 +7893,7 @@
       <c r="F247" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G247" s="5">
+      <c r="G247" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7928,7 +7916,7 @@
       <c r="F248" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G248" s="5">
+      <c r="G248" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7951,7 +7939,7 @@
       <c r="F249" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G249" s="5">
+      <c r="G249" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7974,7 +7962,7 @@
       <c r="F250" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G250" s="5">
+      <c r="G250" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -7997,7 +7985,7 @@
       <c r="F251" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G251" s="5">
+      <c r="G251" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8020,7 +8008,7 @@
       <c r="F252" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G252" s="5">
+      <c r="G252" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8043,7 +8031,7 @@
       <c r="F253" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G253" s="5">
+      <c r="G253" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8066,7 +8054,7 @@
       <c r="F254" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G254" s="5">
+      <c r="G254" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8089,7 +8077,7 @@
       <c r="F255" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G255" s="5">
+      <c r="G255" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8112,7 +8100,7 @@
       <c r="F256" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G256" s="5">
+      <c r="G256" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8135,7 +8123,7 @@
       <c r="F257" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G257" s="5">
+      <c r="G257" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8158,7 +8146,7 @@
       <c r="F258" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G258" s="5">
+      <c r="G258" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8181,7 +8169,7 @@
       <c r="F259" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G259" s="5">
+      <c r="G259" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8204,7 +8192,7 @@
       <c r="F260" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G260" s="5">
+      <c r="G260" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8227,7 +8215,7 @@
       <c r="F261" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G261" s="5">
+      <c r="G261" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8250,7 +8238,7 @@
       <c r="F262" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G262" s="5">
+      <c r="G262" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8273,7 +8261,7 @@
       <c r="F263" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G263" s="5">
+      <c r="G263" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8296,7 +8284,7 @@
       <c r="F264" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G264" s="5">
+      <c r="G264" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8319,7 +8307,7 @@
       <c r="F265" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G265" s="5">
+      <c r="G265" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8342,7 +8330,7 @@
       <c r="F266" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G266" s="5">
+      <c r="G266" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8365,7 +8353,7 @@
       <c r="F267" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G267" s="5">
+      <c r="G267" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8388,7 +8376,7 @@
       <c r="F268" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G268" s="5">
+      <c r="G268" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8411,7 +8399,7 @@
       <c r="F269" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G269" s="5">
+      <c r="G269" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8434,7 +8422,7 @@
       <c r="F270" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G270" s="5">
+      <c r="G270" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8457,7 +8445,7 @@
       <c r="F271" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G271" s="5">
+      <c r="G271" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8480,7 +8468,7 @@
       <c r="F272" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G272" s="5">
+      <c r="G272" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8503,7 +8491,7 @@
       <c r="F273" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G273" s="5">
+      <c r="G273" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8526,7 +8514,7 @@
       <c r="F274" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G274" s="5">
+      <c r="G274" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8549,7 +8537,7 @@
       <c r="F275" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G275" s="5">
+      <c r="G275" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8572,7 +8560,7 @@
       <c r="F276" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G276" s="5">
+      <c r="G276" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8595,7 +8583,7 @@
       <c r="F277" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G277" s="5">
+      <c r="G277" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8618,7 +8606,7 @@
       <c r="F278" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G278" s="5">
+      <c r="G278" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8641,7 +8629,7 @@
       <c r="F279" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G279" s="5">
+      <c r="G279" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8664,7 +8652,7 @@
       <c r="F280" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G280" s="5">
+      <c r="G280" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8687,7 +8675,7 @@
       <c r="F281" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G281" s="5">
+      <c r="G281" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8710,7 +8698,7 @@
       <c r="F282" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G282" s="5">
+      <c r="G282" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8733,7 +8721,7 @@
       <c r="F283" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G283" s="5">
+      <c r="G283" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8756,7 +8744,7 @@
       <c r="F284" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G284" s="5">
+      <c r="G284" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8779,7 +8767,7 @@
       <c r="F285" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G285" s="5">
+      <c r="G285" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8802,7 +8790,7 @@
       <c r="F286" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G286" s="5">
+      <c r="G286" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8825,7 +8813,7 @@
       <c r="F287" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G287" s="5">
+      <c r="G287" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8848,7 +8836,7 @@
       <c r="F288" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G288" s="5">
+      <c r="G288" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8871,7 +8859,7 @@
       <c r="F289" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G289" s="5">
+      <c r="G289" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8894,7 +8882,7 @@
       <c r="F290" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G290" s="5">
+      <c r="G290" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8917,7 +8905,7 @@
       <c r="F291" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G291" s="5">
+      <c r="G291" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8940,7 +8928,7 @@
       <c r="F292" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G292" s="5">
+      <c r="G292" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8963,7 +8951,7 @@
       <c r="F293" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G293" s="5">
+      <c r="G293" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -8986,7 +8974,7 @@
       <c r="F294" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G294" s="5">
+      <c r="G294" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9009,7 +8997,7 @@
       <c r="F295" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G295" s="5">
+      <c r="G295" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9032,7 +9020,7 @@
       <c r="F296" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G296" s="5">
+      <c r="G296" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9055,7 +9043,7 @@
       <c r="F297" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G297" s="5">
+      <c r="G297" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9078,7 +9066,7 @@
       <c r="F298" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G298" s="5">
+      <c r="G298" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9101,7 +9089,7 @@
       <c r="F299" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G299" s="5">
+      <c r="G299" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9124,7 +9112,7 @@
       <c r="F300" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G300" s="5">
+      <c r="G300" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9147,7 +9135,7 @@
       <c r="F301" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G301" s="5">
+      <c r="G301" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9170,7 +9158,7 @@
       <c r="F302" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G302" s="5">
+      <c r="G302" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9193,7 +9181,7 @@
       <c r="F303" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G303" s="5">
+      <c r="G303" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9216,7 +9204,7 @@
       <c r="F304" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G304" s="5">
+      <c r="G304" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9239,7 +9227,7 @@
       <c r="F305" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G305" s="5">
+      <c r="G305" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9262,7 +9250,7 @@
       <c r="F306" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G306" s="5">
+      <c r="G306" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9285,7 +9273,7 @@
       <c r="F307" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G307" s="5">
+      <c r="G307" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9308,7 +9296,7 @@
       <c r="F308" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G308" s="5">
+      <c r="G308" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9331,7 +9319,7 @@
       <c r="F309" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G309" s="5">
+      <c r="G309" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9354,7 +9342,7 @@
       <c r="F310" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G310" s="5">
+      <c r="G310" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9377,7 +9365,7 @@
       <c r="F311" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G311" s="5">
+      <c r="G311" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9400,7 +9388,7 @@
       <c r="F312" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G312" s="5">
+      <c r="G312" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9423,7 +9411,7 @@
       <c r="F313" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G313" s="5">
+      <c r="G313" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9446,7 +9434,7 @@
       <c r="F314" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G314" s="5">
+      <c r="G314" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9469,7 +9457,7 @@
       <c r="F315" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G315" s="5">
+      <c r="G315" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9492,7 +9480,7 @@
       <c r="F316" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G316" s="5">
+      <c r="G316" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9515,7 +9503,7 @@
       <c r="F317" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G317" s="5">
+      <c r="G317" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9538,7 +9526,7 @@
       <c r="F318" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G318" s="5">
+      <c r="G318" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9561,7 +9549,7 @@
       <c r="F319" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G319" s="5">
+      <c r="G319" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9584,7 +9572,7 @@
       <c r="F320" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G320" s="5">
+      <c r="G320" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9607,7 +9595,7 @@
       <c r="F321" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G321" s="5">
+      <c r="G321" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9630,7 +9618,7 @@
       <c r="F322" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G322" s="5">
+      <c r="G322" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9653,7 +9641,7 @@
       <c r="F323" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G323" s="5">
+      <c r="G323" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9676,7 +9664,7 @@
       <c r="F324" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G324" s="5">
+      <c r="G324" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9699,7 +9687,7 @@
       <c r="F325" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G325" s="5">
+      <c r="G325" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9722,7 +9710,7 @@
       <c r="F326" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G326" s="5">
+      <c r="G326" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9745,7 +9733,7 @@
       <c r="F327" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G327" s="5">
+      <c r="G327" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9768,7 +9756,7 @@
       <c r="F328" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G328" s="5">
+      <c r="G328" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9791,7 +9779,7 @@
       <c r="F329" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G329" s="5">
+      <c r="G329" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9814,7 +9802,7 @@
       <c r="F330" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G330" s="5">
+      <c r="G330" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9837,7 +9825,7 @@
       <c r="F331" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G331" s="5">
+      <c r="G331" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9860,7 +9848,7 @@
       <c r="F332" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G332" s="5">
+      <c r="G332" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9883,7 +9871,7 @@
       <c r="F333" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G333" s="5">
+      <c r="G333" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9906,7 +9894,7 @@
       <c r="F334" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G334" s="5">
+      <c r="G334" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9929,7 +9917,7 @@
       <c r="F335" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G335" s="5">
+      <c r="G335" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9952,7 +9940,7 @@
       <c r="F336" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G336" s="5">
+      <c r="G336" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9975,7 +9963,7 @@
       <c r="F337" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G337" s="5">
+      <c r="G337" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -9998,7 +9986,7 @@
       <c r="F338" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G338" s="5">
+      <c r="G338" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10021,7 +10009,7 @@
       <c r="F339" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G339" s="5">
+      <c r="G339" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10044,7 +10032,7 @@
       <c r="F340" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G340" s="5">
+      <c r="G340" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10067,7 +10055,7 @@
       <c r="F341" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G341" s="5">
+      <c r="G341" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10090,7 +10078,7 @@
       <c r="F342" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G342" s="5">
+      <c r="G342" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10113,7 +10101,7 @@
       <c r="F343" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G343" s="5">
+      <c r="G343" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10136,7 +10124,7 @@
       <c r="F344" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G344" s="5">
+      <c r="G344" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10159,7 +10147,7 @@
       <c r="F345" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G345" s="5">
+      <c r="G345" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10182,7 +10170,7 @@
       <c r="F346" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G346" s="5">
+      <c r="G346" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10205,7 +10193,7 @@
       <c r="F347" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G347" s="5">
+      <c r="G347" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10228,7 +10216,7 @@
       <c r="F348" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G348" s="5">
+      <c r="G348" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10251,7 +10239,7 @@
       <c r="F349" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G349" s="5">
+      <c r="G349" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10274,7 +10262,7 @@
       <c r="F350" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G350" s="5">
+      <c r="G350" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10297,7 +10285,7 @@
       <c r="F351" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G351" s="5">
+      <c r="G351" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10320,7 +10308,7 @@
       <c r="F352" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G352" s="5">
+      <c r="G352" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10343,7 +10331,7 @@
       <c r="F353" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G353" s="5">
+      <c r="G353" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10366,7 +10354,7 @@
       <c r="F354" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G354" s="5">
+      <c r="G354" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10389,7 +10377,7 @@
       <c r="F355" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G355" s="5">
+      <c r="G355" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10412,7 +10400,7 @@
       <c r="F356" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G356" s="5">
+      <c r="G356" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10435,7 +10423,7 @@
       <c r="F357" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G357" s="5">
+      <c r="G357" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10458,7 +10446,7 @@
       <c r="F358" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G358" s="5">
+      <c r="G358" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10481,7 +10469,7 @@
       <c r="F359" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G359" s="5">
+      <c r="G359" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10504,7 +10492,7 @@
       <c r="F360" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G360" s="5">
+      <c r="G360" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10527,7 +10515,7 @@
       <c r="F361" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G361" s="5">
+      <c r="G361" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10550,7 +10538,7 @@
       <c r="F362" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G362" s="5">
+      <c r="G362" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10573,7 +10561,7 @@
       <c r="F363" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G363" s="5">
+      <c r="G363" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10596,7 +10584,7 @@
       <c r="F364" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G364" s="5">
+      <c r="G364" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10619,7 +10607,7 @@
       <c r="F365" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G365" s="5">
+      <c r="G365" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10642,7 +10630,7 @@
       <c r="F366" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G366" s="5">
+      <c r="G366" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10665,7 +10653,7 @@
       <c r="F367" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G367" s="5">
+      <c r="G367" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10688,7 +10676,7 @@
       <c r="F368" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G368" s="5">
+      <c r="G368" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10711,7 +10699,7 @@
       <c r="F369" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G369" s="5">
+      <c r="G369" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10734,7 +10722,7 @@
       <c r="F370" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G370" s="5">
+      <c r="G370" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10757,7 +10745,7 @@
       <c r="F371" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G371" s="5">
+      <c r="G371" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10780,7 +10768,7 @@
       <c r="F372" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G372" s="5">
+      <c r="G372" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10803,7 +10791,7 @@
       <c r="F373" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G373" s="5">
+      <c r="G373" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10826,7 +10814,7 @@
       <c r="F374" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G374" s="5">
+      <c r="G374" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10849,7 +10837,7 @@
       <c r="F375" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G375" s="5">
+      <c r="G375" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10872,7 +10860,7 @@
       <c r="F376" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G376" s="5">
+      <c r="G376" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10895,7 +10883,7 @@
       <c r="F377" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G377" s="5">
+      <c r="G377" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10918,7 +10906,7 @@
       <c r="F378" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G378" s="5">
+      <c r="G378" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10941,7 +10929,7 @@
       <c r="F379" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G379" s="5">
+      <c r="G379" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10964,7 +10952,7 @@
       <c r="F380" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G380" s="5">
+      <c r="G380" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -10987,7 +10975,7 @@
       <c r="F381" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G381" s="5">
+      <c r="G381" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11010,7 +10998,7 @@
       <c r="F382" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G382" s="5">
+      <c r="G382" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11033,7 +11021,7 @@
       <c r="F383" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G383" s="5">
+      <c r="G383" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11056,7 +11044,7 @@
       <c r="F384" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G384" s="5">
+      <c r="G384" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11079,7 +11067,7 @@
       <c r="F385" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G385" s="5">
+      <c r="G385" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11102,7 +11090,7 @@
       <c r="F386" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G386" s="5">
+      <c r="G386" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11125,7 +11113,7 @@
       <c r="F387" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G387" s="5">
+      <c r="G387" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11148,7 +11136,7 @@
       <c r="F388" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G388" s="5">
+      <c r="G388" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11171,7 +11159,7 @@
       <c r="F389" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G389" s="5">
+      <c r="G389" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11194,7 +11182,7 @@
       <c r="F390" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G390" s="5">
+      <c r="G390" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11217,7 +11205,7 @@
       <c r="F391" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G391" s="5">
+      <c r="G391" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11240,7 +11228,7 @@
       <c r="F392" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G392" s="5">
+      <c r="G392" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11263,7 +11251,7 @@
       <c r="F393" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G393" s="5">
+      <c r="G393" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11286,7 +11274,7 @@
       <c r="F394" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G394" s="5">
+      <c r="G394" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11309,7 +11297,7 @@
       <c r="F395" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G395" s="5">
+      <c r="G395" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11332,7 +11320,7 @@
       <c r="F396" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G396" s="5">
+      <c r="G396" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11355,7 +11343,7 @@
       <c r="F397" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G397" s="5">
+      <c r="G397" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11378,7 +11366,7 @@
       <c r="F398" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G398" s="5">
+      <c r="G398" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11401,7 +11389,7 @@
       <c r="F399" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G399" s="5">
+      <c r="G399" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11424,7 +11412,7 @@
       <c r="F400" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G400" s="5">
+      <c r="G400" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11447,7 +11435,7 @@
       <c r="F401" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G401" s="5">
+      <c r="G401" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11470,7 +11458,7 @@
       <c r="F402" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G402" s="5">
+      <c r="G402" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11493,7 +11481,7 @@
       <c r="F403" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G403" s="5">
+      <c r="G403" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11516,7 +11504,7 @@
       <c r="F404" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G404" s="5">
+      <c r="G404" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11539,7 +11527,7 @@
       <c r="F405" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G405" s="5">
+      <c r="G405" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11562,7 +11550,7 @@
       <c r="F406" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G406" s="5">
+      <c r="G406" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11585,7 +11573,7 @@
       <c r="F407" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G407" s="5">
+      <c r="G407" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11608,7 +11596,7 @@
       <c r="F408" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G408" s="5">
+      <c r="G408" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11631,7 +11619,7 @@
       <c r="F409" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G409" s="5">
+      <c r="G409" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11654,7 +11642,7 @@
       <c r="F410" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G410" s="5">
+      <c r="G410" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11677,7 +11665,7 @@
       <c r="F411" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G411" s="5">
+      <c r="G411" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11700,7 +11688,7 @@
       <c r="F412" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G412" s="5">
+      <c r="G412" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11723,7 +11711,7 @@
       <c r="F413" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G413" s="5">
+      <c r="G413" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11746,7 +11734,7 @@
       <c r="F414" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G414" s="5">
+      <c r="G414" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11769,7 +11757,7 @@
       <c r="F415" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G415" s="5">
+      <c r="G415" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11792,7 +11780,7 @@
       <c r="F416" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G416" s="5">
+      <c r="G416" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11815,7 +11803,7 @@
       <c r="F417" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G417" s="5">
+      <c r="G417" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11838,7 +11826,7 @@
       <c r="F418" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G418" s="5">
+      <c r="G418" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11861,7 +11849,7 @@
       <c r="F419" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G419" s="5">
+      <c r="G419" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11884,7 +11872,7 @@
       <c r="F420" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G420" s="5">
+      <c r="G420" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11907,7 +11895,7 @@
       <c r="F421" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G421" s="5">
+      <c r="G421" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11930,7 +11918,7 @@
       <c r="F422" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G422" s="5">
+      <c r="G422" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11953,7 +11941,7 @@
       <c r="F423" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G423" s="5">
+      <c r="G423" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11976,7 +11964,7 @@
       <c r="F424" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G424" s="5">
+      <c r="G424" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -11999,7 +11987,7 @@
       <c r="F425" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G425" s="5">
+      <c r="G425" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12022,7 +12010,7 @@
       <c r="F426" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G426" s="5">
+      <c r="G426" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12045,7 +12033,7 @@
       <c r="F427" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G427" s="5">
+      <c r="G427" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12068,7 +12056,7 @@
       <c r="F428" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G428" s="5">
+      <c r="G428" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12091,7 +12079,7 @@
       <c r="F429" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G429" s="5">
+      <c r="G429" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12114,7 +12102,7 @@
       <c r="F430" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G430" s="5">
+      <c r="G430" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12137,7 +12125,7 @@
       <c r="F431" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G431" s="5">
+      <c r="G431" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12160,7 +12148,7 @@
       <c r="F432" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G432" s="5">
+      <c r="G432" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12183,7 +12171,7 @@
       <c r="F433" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G433" s="5">
+      <c r="G433" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12206,7 +12194,7 @@
       <c r="F434" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G434" s="5">
+      <c r="G434" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12229,7 +12217,7 @@
       <c r="F435" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G435" s="5">
+      <c r="G435" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12252,7 +12240,7 @@
       <c r="F436" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G436" s="5">
+      <c r="G436" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12275,7 +12263,7 @@
       <c r="F437" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G437" s="5">
+      <c r="G437" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12298,7 +12286,7 @@
       <c r="F438" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G438" s="5">
+      <c r="G438" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12321,7 +12309,7 @@
       <c r="F439" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G439" s="5">
+      <c r="G439" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12344,7 +12332,7 @@
       <c r="F440" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G440" s="5">
+      <c r="G440" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12367,7 +12355,7 @@
       <c r="F441" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G441" s="5">
+      <c r="G441" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12390,7 +12378,7 @@
       <c r="F442" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G442" s="5">
+      <c r="G442" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12413,7 +12401,7 @@
       <c r="F443" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G443" s="5">
+      <c r="G443" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12436,7 +12424,7 @@
       <c r="F444" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G444" s="5">
+      <c r="G444" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12459,7 +12447,7 @@
       <c r="F445" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G445" s="5">
+      <c r="G445" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12482,7 +12470,7 @@
       <c r="F446" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G446" s="5">
+      <c r="G446" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12505,7 +12493,7 @@
       <c r="F447" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G447" s="5">
+      <c r="G447" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12528,7 +12516,7 @@
       <c r="F448" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G448" s="5">
+      <c r="G448" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12551,7 +12539,7 @@
       <c r="F449" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G449" s="5">
+      <c r="G449" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12574,7 +12562,7 @@
       <c r="F450" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G450" s="5">
+      <c r="G450" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12597,7 +12585,7 @@
       <c r="F451" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G451" s="5">
+      <c r="G451" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12620,7 +12608,7 @@
       <c r="F452" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G452" s="5">
+      <c r="G452" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12643,7 +12631,7 @@
       <c r="F453" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G453" s="5">
+      <c r="G453" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12666,7 +12654,7 @@
       <c r="F454" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G454" s="5">
+      <c r="G454" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12689,7 +12677,7 @@
       <c r="F455" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G455" s="5">
+      <c r="G455" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12712,7 +12700,7 @@
       <c r="F456" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G456" s="5">
+      <c r="G456" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12735,7 +12723,7 @@
       <c r="F457" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G457" s="5">
+      <c r="G457" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12758,7 +12746,7 @@
       <c r="F458" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G458" s="5">
+      <c r="G458" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12781,7 +12769,7 @@
       <c r="F459" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G459" s="5">
+      <c r="G459" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12804,7 +12792,7 @@
       <c r="F460" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G460" s="5">
+      <c r="G460" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12827,7 +12815,7 @@
       <c r="F461" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G461" s="5">
+      <c r="G461" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12850,7 +12838,7 @@
       <c r="F462" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G462" s="5">
+      <c r="G462" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12873,7 +12861,7 @@
       <c r="F463" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G463" s="5">
+      <c r="G463" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12896,7 +12884,7 @@
       <c r="F464" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G464" s="5">
+      <c r="G464" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12919,7 +12907,7 @@
       <c r="F465" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G465" s="5">
+      <c r="G465" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12942,7 +12930,7 @@
       <c r="F466" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G466" s="5">
+      <c r="G466" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12965,7 +12953,7 @@
       <c r="F467" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G467" s="5">
+      <c r="G467" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -12988,7 +12976,7 @@
       <c r="F468" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G468" s="5">
+      <c r="G468" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13011,7 +12999,7 @@
       <c r="F469" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G469" s="5">
+      <c r="G469" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13034,7 +13022,7 @@
       <c r="F470" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G470" s="5">
+      <c r="G470" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13057,7 +13045,7 @@
       <c r="F471" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G471" s="5">
+      <c r="G471" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13080,7 +13068,7 @@
       <c r="F472" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G472" s="5">
+      <c r="G472" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13103,7 +13091,7 @@
       <c r="F473" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G473" s="5">
+      <c r="G473" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13126,7 +13114,7 @@
       <c r="F474" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G474" s="5">
+      <c r="G474" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13149,7 +13137,7 @@
       <c r="F475" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G475" s="5">
+      <c r="G475" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13172,7 +13160,7 @@
       <c r="F476" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="G476" s="5">
+      <c r="G476" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13195,7 +13183,7 @@
       <c r="F477" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G477" s="6">
+      <c r="G477" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13215,7 +13203,7 @@
       <c r="F478" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G478" s="6">
+      <c r="G478" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13238,7 +13226,7 @@
       <c r="F479" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G479" s="6">
+      <c r="G479" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13258,7 +13246,7 @@
       <c r="F480" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G480" s="6">
+      <c r="G480" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13281,7 +13269,7 @@
       <c r="F481" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G481" s="6">
+      <c r="G481" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13301,7 +13289,7 @@
       <c r="F482" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G482" s="6">
+      <c r="G482" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13321,7 +13309,7 @@
       <c r="F483" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G483" s="6">
+      <c r="G483" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13341,7 +13329,7 @@
       <c r="F484" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G484" s="6">
+      <c r="G484" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13361,7 +13349,7 @@
       <c r="F485" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G485" s="6">
+      <c r="G485" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13381,7 +13369,7 @@
       <c r="F486" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G486" s="6">
+      <c r="G486" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13404,7 +13392,7 @@
       <c r="F487" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G487" s="6">
+      <c r="G487" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13424,7 +13412,7 @@
       <c r="F488" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G488" s="6">
+      <c r="G488" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13447,7 +13435,7 @@
       <c r="F489" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G489" s="6">
+      <c r="G489" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13467,7 +13455,7 @@
       <c r="F490" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G490" s="6">
+      <c r="G490" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13490,7 +13478,7 @@
       <c r="F491" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G491" s="6">
+      <c r="G491" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13510,7 +13498,7 @@
       <c r="F492" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G492" s="6">
+      <c r="G492" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13530,7 +13518,7 @@
       <c r="F493" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G493" s="6">
+      <c r="G493" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13550,7 +13538,7 @@
       <c r="F494" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G494" s="6">
+      <c r="G494" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13570,7 +13558,7 @@
       <c r="F495" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G495" s="6">
+      <c r="G495" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13590,7 +13578,7 @@
       <c r="F496" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G496" s="6">
+      <c r="G496" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13613,7 +13601,7 @@
       <c r="F497" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G497" s="6">
+      <c r="G497" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13633,7 +13621,7 @@
       <c r="F498" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G498" s="6">
+      <c r="G498" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13656,7 +13644,7 @@
       <c r="F499" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G499" s="6">
+      <c r="G499" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13676,7 +13664,7 @@
       <c r="F500" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G500" s="6">
+      <c r="G500" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13699,7 +13687,7 @@
       <c r="F501" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G501" s="6">
+      <c r="G501" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13719,7 +13707,7 @@
       <c r="F502" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G502" s="6">
+      <c r="G502" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13739,7 +13727,7 @@
       <c r="F503" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G503" s="6">
+      <c r="G503" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13759,7 +13747,7 @@
       <c r="F504" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G504" s="6">
+      <c r="G504" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13779,7 +13767,7 @@
       <c r="F505" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G505" s="6">
+      <c r="G505" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13799,7 +13787,7 @@
       <c r="F506" s="1" t="e">
         <v>#N/A</v>
       </c>
-      <c r="G506" s="6">
+      <c r="G506" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -13819,7 +13807,7 @@
       <c r="F507" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G507" s="5">
+      <c r="G507" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13839,7 +13827,7 @@
       <c r="F508" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G508" s="5">
+      <c r="G508" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13859,7 +13847,7 @@
       <c r="F509" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G509" s="5">
+      <c r="G509" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13879,7 +13867,7 @@
       <c r="F510" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G510" s="5">
+      <c r="G510" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13899,7 +13887,7 @@
       <c r="F511" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G511" s="5">
+      <c r="G511" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13919,7 +13907,7 @@
       <c r="F512" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G512" s="5">
+      <c r="G512" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13939,7 +13927,7 @@
       <c r="F513" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G513" s="5">
+      <c r="G513" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13959,7 +13947,7 @@
       <c r="F514" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G514" s="5">
+      <c r="G514" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13979,7 +13967,7 @@
       <c r="F515" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G515" s="5">
+      <c r="G515" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -13999,7 +13987,7 @@
       <c r="F516" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G516" s="6">
+      <c r="G516" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14019,7 +14007,7 @@
       <c r="F517" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G517" s="6">
+      <c r="G517" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14039,7 +14027,7 @@
       <c r="F518" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G518" s="6">
+      <c r="G518" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14059,7 +14047,7 @@
       <c r="F519" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G519" s="6">
+      <c r="G519" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14079,7 +14067,7 @@
       <c r="F520" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G520" s="6">
+      <c r="G520" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14099,7 +14087,7 @@
       <c r="F521" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G521" s="6">
+      <c r="G521" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14119,7 +14107,7 @@
       <c r="F522" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G522" s="6">
+      <c r="G522" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14139,7 +14127,7 @@
       <c r="F523" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G523" s="6">
+      <c r="G523" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14159,7 +14147,7 @@
       <c r="F524" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G524" s="5">
+      <c r="G524" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14179,7 +14167,7 @@
       <c r="F525" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G525" s="5">
+      <c r="G525" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14199,7 +14187,7 @@
       <c r="F526" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G526" s="5">
+      <c r="G526" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14219,7 +14207,7 @@
       <c r="F527" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G527" s="5">
+      <c r="G527" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14239,7 +14227,7 @@
       <c r="F528" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G528" s="5">
+      <c r="G528" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14259,7 +14247,7 @@
       <c r="F529" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G529" s="5">
+      <c r="G529" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14279,7 +14267,7 @@
       <c r="F530" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G530" s="5">
+      <c r="G530" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14299,7 +14287,7 @@
       <c r="F531" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G531" s="5">
+      <c r="G531" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14319,7 +14307,7 @@
       <c r="F532" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G532" s="5">
+      <c r="G532" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14339,7 +14327,7 @@
       <c r="F533" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G533" s="5">
+      <c r="G533" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14362,7 +14350,7 @@
       <c r="F534" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G534" s="5">
+      <c r="G534" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14385,7 +14373,7 @@
       <c r="F535" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G535" s="5">
+      <c r="G535" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14408,7 +14396,7 @@
       <c r="F536" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G536" s="5">
+      <c r="G536" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14431,7 +14419,7 @@
       <c r="F537" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G537" s="5">
+      <c r="G537" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14454,7 +14442,7 @@
       <c r="F538" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G538" s="5">
+      <c r="G538" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14477,7 +14465,7 @@
       <c r="F539" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G539" s="5">
+      <c r="G539" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14500,7 +14488,7 @@
       <c r="F540" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G540" s="5">
+      <c r="G540" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14523,7 +14511,7 @@
       <c r="F541" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G541" s="5">
+      <c r="G541" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14546,7 +14534,7 @@
       <c r="F542" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G542" s="5">
+      <c r="G542" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14569,7 +14557,7 @@
       <c r="F543" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G543" s="5">
+      <c r="G543" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14592,7 +14580,7 @@
       <c r="F544" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G544" s="5">
+      <c r="G544" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14615,7 +14603,7 @@
       <c r="F545" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G545" s="5">
+      <c r="G545" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14635,7 +14623,7 @@
       <c r="F546" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G546" s="5">
+      <c r="G546" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14655,7 +14643,7 @@
       <c r="F547" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G547" s="5">
+      <c r="G547" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14675,7 +14663,7 @@
       <c r="F548" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G548" s="5">
+      <c r="G548" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -14698,7 +14686,7 @@
       <c r="F549" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G549" s="6">
+      <c r="G549" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14721,7 +14709,7 @@
       <c r="F550" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G550" s="6">
+      <c r="G550" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14744,7 +14732,7 @@
       <c r="F551" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G551" s="6">
+      <c r="G551" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14767,7 +14755,7 @@
       <c r="F552" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G552" s="6">
+      <c r="G552" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14790,7 +14778,7 @@
       <c r="F553" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G553" s="6">
+      <c r="G553" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14813,7 +14801,7 @@
       <c r="F554" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G554" s="6">
+      <c r="G554" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14836,7 +14824,7 @@
       <c r="F555" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G555" s="6">
+      <c r="G555" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14859,7 +14847,7 @@
       <c r="F556" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G556" s="6">
+      <c r="G556" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14882,7 +14870,7 @@
       <c r="F557" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G557" s="6">
+      <c r="G557" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14905,7 +14893,7 @@
       <c r="F558" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G558" s="6">
+      <c r="G558" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14928,7 +14916,7 @@
       <c r="F559" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G559" s="6">
+      <c r="G559" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14948,7 +14936,7 @@
       <c r="F560" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G560" s="6">
+      <c r="G560" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14968,7 +14956,7 @@
       <c r="F561" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G561" s="6">
+      <c r="G561" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -14988,7 +14976,7 @@
       <c r="F562" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G562" s="6">
+      <c r="G562" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15011,7 +14999,7 @@
       <c r="F563" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G563" s="6">
+      <c r="G563" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15034,7 +15022,7 @@
       <c r="F564" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G564" s="6">
+      <c r="G564" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15057,7 +15045,7 @@
       <c r="F565" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G565" s="6">
+      <c r="G565" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15080,7 +15068,7 @@
       <c r="F566" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G566" s="6">
+      <c r="G566" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15103,7 +15091,7 @@
       <c r="F567" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G567" s="6">
+      <c r="G567" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15126,7 +15114,7 @@
       <c r="F568" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G568" s="6">
+      <c r="G568" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15149,7 +15137,7 @@
       <c r="F569" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G569" s="6">
+      <c r="G569" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15172,7 +15160,7 @@
       <c r="F570" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G570" s="6">
+      <c r="G570" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15195,7 +15183,7 @@
       <c r="F571" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G571" s="6">
+      <c r="G571" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15218,7 +15206,7 @@
       <c r="F572" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G572" s="6">
+      <c r="G572" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15241,7 +15229,7 @@
       <c r="F573" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G573" s="6">
+      <c r="G573" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15261,7 +15249,7 @@
       <c r="F574" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G574" s="6">
+      <c r="G574" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15281,7 +15269,7 @@
       <c r="F575" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G575" s="6">
+      <c r="G575" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15301,7 +15289,7 @@
       <c r="F576" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G576" s="6">
+      <c r="G576" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15321,7 +15309,7 @@
       <c r="F577" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G577" s="5">
+      <c r="G577" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -15341,7 +15329,7 @@
       <c r="F578" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G578" s="5">
+      <c r="G578" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -15361,7 +15349,7 @@
       <c r="F579" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G579" s="5">
+      <c r="G579" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -15381,7 +15369,7 @@
       <c r="F580" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G580" s="5">
+      <c r="G580" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -15401,7 +15389,7 @@
       <c r="F581" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G581" s="5">
+      <c r="G581" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -15421,7 +15409,7 @@
       <c r="F582" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G582" s="5">
+      <c r="G582" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -15441,7 +15429,7 @@
       <c r="F583" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G583" s="5">
+      <c r="G583" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -15461,7 +15449,7 @@
       <c r="F584" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G584" s="5">
+      <c r="G584" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -15481,7 +15469,7 @@
       <c r="F585" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G585" s="5">
+      <c r="G585" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -15501,7 +15489,7 @@
       <c r="F586" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G586" s="5">
+      <c r="G586" s="4">
         <v>0.05</v>
       </c>
     </row>
@@ -15521,7 +15509,7 @@
       <c r="F587" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G587" s="6">
+      <c r="G587" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15541,7 +15529,7 @@
       <c r="F588" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G588" s="6">
+      <c r="G588" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15561,7 +15549,7 @@
       <c r="F589" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G589" s="6">
+      <c r="G589" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15581,7 +15569,7 @@
       <c r="F590" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G590" s="6">
+      <c r="G590" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15601,7 +15589,7 @@
       <c r="F591" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G591" s="6">
+      <c r="G591" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15621,7 +15609,7 @@
       <c r="F592" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G592" s="6">
+      <c r="G592" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
@@ -15641,7 +15629,7 @@
       <c r="F593" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="G593" s="6">
+      <c r="G593" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>

--- a/dados/precos_todos.xlsx
+++ b/dados/precos_todos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a9e64bef5804d793/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_7341F0EF114A429FE8312C154A75067AC3578BDB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA92A044-DE1E-4109-BF14-2A5E7F5E8077}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_7341F0EF114A429FE8312C154A75067AC3578BDB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98842439-9108-40DE-AB22-86500F6C1609}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="14580" windowHeight="17370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$G$593</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="604">
   <si>
     <t>ITEM</t>
   </si>
@@ -1832,6 +1845,10 @@
   </si>
   <si>
     <t>ARRUELA LISA INOX 3/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
   </si>
 </sst>
 </file>
@@ -1878,7 +1895,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1889,6 +1906,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2219,7 +2239,10 @@
     <col min="7" max="8" width="11.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>603</v>
+      </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>

--- a/dados/precos_todos.xlsx
+++ b/dados/precos_todos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a9e64bef5804d793/Área de Trabalho/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3249aeff9e842ea4/Área de Trabalho/Planilhas de compras/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="11_7341F0EF114A429FE8312C154A75067AC3578BDB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98842439-9108-40DE-AB22-86500F6C1609}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B2D2A0A-E1F1-4F9A-A9C0-2D5D4B705C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="14580" windowHeight="17370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1931,9 +1932,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1971,7 +1972,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2077,7 +2078,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2219,7 +2220,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2228,18 +2229,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G593"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.36328125" customWidth="1"/>
-    <col min="6" max="6" width="11.36328125" style="1" customWidth="1"/>
-    <col min="7" max="8" width="11.36328125" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="1" customWidth="1"/>
+    <col min="7" max="8" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>603</v>
       </c>
@@ -2262,7 +2263,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2706</v>
       </c>
@@ -2285,7 +2286,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>4645</v>
       </c>
@@ -2308,7 +2309,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>4644</v>
       </c>
@@ -2331,7 +2332,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4642</v>
       </c>
@@ -2354,7 +2355,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3082</v>
       </c>
@@ -2377,7 +2378,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5458</v>
       </c>
@@ -2400,7 +2401,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4643</v>
       </c>
@@ -2423,7 +2424,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>3143</v>
       </c>
@@ -2446,7 +2447,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2968</v>
       </c>
@@ -2469,7 +2470,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2712</v>
       </c>
@@ -2492,7 +2493,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3097</v>
       </c>
@@ -2515,7 +2516,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2385</v>
       </c>
@@ -2538,7 +2539,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2360</v>
       </c>
@@ -2561,7 +2562,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2321</v>
       </c>
@@ -2584,7 +2585,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2297</v>
       </c>
@@ -2607,7 +2608,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>3204</v>
       </c>
@@ -2630,7 +2631,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>3207</v>
       </c>
@@ -2653,7 +2654,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>3146</v>
       </c>
@@ -2676,7 +2677,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>3156</v>
       </c>
@@ -2699,7 +2700,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>3169</v>
       </c>
@@ -2722,7 +2723,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>3171</v>
       </c>
@@ -2745,7 +2746,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>3187</v>
       </c>
@@ -2768,7 +2769,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>3197</v>
       </c>
@@ -2791,7 +2792,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>4355</v>
       </c>
@@ -2814,7 +2815,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>6771</v>
       </c>
@@ -2837,7 +2838,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1657</v>
       </c>
@@ -2860,7 +2861,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>4650</v>
       </c>
@@ -2883,7 +2884,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>4648</v>
       </c>
@@ -2906,7 +2907,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>4646</v>
       </c>
@@ -2929,7 +2930,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>1987</v>
       </c>
@@ -2952,7 +2953,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>5485</v>
       </c>
@@ -2975,7 +2976,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>4647</v>
       </c>
@@ -2998,7 +2999,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2018</v>
       </c>
@@ -3021,7 +3022,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>1852</v>
       </c>
@@ -3044,7 +3045,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>1670</v>
       </c>
@@ -3067,7 +3068,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2001</v>
       </c>
@@ -3090,7 +3091,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1421</v>
       </c>
@@ -3113,7 +3114,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>1411</v>
       </c>
@@ -3136,7 +3137,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1400</v>
       </c>
@@ -3159,7 +3160,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1391</v>
       </c>
@@ -3182,7 +3183,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2058</v>
       </c>
@@ -3205,7 +3206,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2069</v>
       </c>
@@ -3228,7 +3229,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2024</v>
       </c>
@@ -3251,7 +3252,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2033</v>
       </c>
@@ -3274,7 +3275,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2039</v>
       </c>
@@ -3297,7 +3298,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2040</v>
       </c>
@@ -3320,7 +3321,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2048</v>
       </c>
@@ -3343,7 +3344,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2052</v>
       </c>
@@ -3366,7 +3367,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>4928</v>
       </c>
@@ -3389,7 +3390,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>6772</v>
       </c>
@@ -3412,7 +3413,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>4641</v>
       </c>
@@ -3435,7 +3436,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>4637</v>
       </c>
@@ -3458,7 +3459,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>4640</v>
       </c>
@@ -3481,7 +3482,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>3086</v>
       </c>
@@ -3504,7 +3505,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>5489</v>
       </c>
@@ -3527,7 +3528,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>5488</v>
       </c>
@@ -3550,7 +3551,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>3145</v>
       </c>
@@ -3573,7 +3574,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>3028</v>
       </c>
@@ -3596,7 +3597,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2744</v>
       </c>
@@ -3619,7 +3620,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>3124</v>
       </c>
@@ -3642,7 +3643,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2426</v>
       </c>
@@ -3665,7 +3666,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2375</v>
       </c>
@@ -3688,7 +3689,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2340</v>
       </c>
@@ -3711,7 +3712,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2308</v>
       </c>
@@ -3734,7 +3735,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>3206</v>
       </c>
@@ -3757,7 +3758,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>3209</v>
       </c>
@@ -3780,7 +3781,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>3149</v>
       </c>
@@ -3803,7 +3804,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>3162</v>
       </c>
@@ -3826,7 +3827,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>3170</v>
       </c>
@@ -3849,7 +3850,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>3177</v>
       </c>
@@ -3872,7 +3873,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>3190</v>
       </c>
@@ -3895,7 +3896,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>4353</v>
       </c>
@@ -3918,7 +3919,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>6705</v>
       </c>
@@ -3941,7 +3942,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>8570</v>
       </c>
@@ -3964,7 +3965,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>4636</v>
       </c>
@@ -3987,7 +3988,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>4634</v>
       </c>
@@ -4010,7 +4011,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>4635</v>
       </c>
@@ -4033,7 +4034,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>1992</v>
       </c>
@@ -4056,7 +4057,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>5486</v>
       </c>
@@ -4079,7 +4080,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>5487</v>
       </c>
@@ -4102,7 +4103,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2021</v>
       </c>
@@ -4125,7 +4126,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>1921</v>
       </c>
@@ -4148,7 +4149,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1697</v>
       </c>
@@ -4171,7 +4172,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>2014</v>
       </c>
@@ -4194,7 +4195,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1431</v>
       </c>
@@ -4217,7 +4218,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>1418</v>
       </c>
@@ -4240,7 +4241,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>1405</v>
       </c>
@@ -4263,7 +4264,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>1397</v>
       </c>
@@ -4286,7 +4287,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>4633</v>
       </c>
@@ -4309,7 +4310,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2084</v>
       </c>
@@ -4332,7 +4333,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>2031</v>
       </c>
@@ -4355,7 +4356,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>2034</v>
       </c>
@@ -4378,7 +4379,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>6002</v>
       </c>
@@ -4401,7 +4402,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>2045</v>
       </c>
@@ -4424,7 +4425,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>2050</v>
       </c>
@@ -4447,7 +4448,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2053</v>
       </c>
@@ -4470,7 +4471,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>8572</v>
       </c>
@@ -4493,7 +4494,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>8571</v>
       </c>
@@ -4516,7 +4517,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>8579</v>
       </c>
@@ -4539,7 +4540,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>8580</v>
       </c>
@@ -4562,7 +4563,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>8028</v>
       </c>
@@ -4585,7 +4586,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>8589</v>
       </c>
@@ -4608,7 +4609,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>8043</v>
       </c>
@@ -4631,7 +4632,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>8581</v>
       </c>
@@ -4654,7 +4655,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>8582</v>
       </c>
@@ -4677,7 +4678,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2128</v>
       </c>
@@ -4700,7 +4701,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2114</v>
       </c>
@@ -4723,7 +4724,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2148</v>
       </c>
@@ -4746,7 +4747,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2100</v>
       </c>
@@ -4769,7 +4770,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>8583</v>
       </c>
@@ -4792,7 +4793,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2097</v>
       </c>
@@ -4815,7 +4816,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2095</v>
       </c>
@@ -4838,7 +4839,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="e">
         <v>#N/A</v>
       </c>
@@ -4861,7 +4862,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2150</v>
       </c>
@@ -4884,7 +4885,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2153</v>
       </c>
@@ -4907,7 +4908,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>6035</v>
       </c>
@@ -4930,7 +4931,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2156</v>
       </c>
@@ -4953,7 +4954,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>2162</v>
       </c>
@@ -4976,7 +4977,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>11792</v>
       </c>
@@ -4999,7 +5000,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>11788</v>
       </c>
@@ -5022,7 +5023,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>8602</v>
       </c>
@@ -5045,7 +5046,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>6777</v>
       </c>
@@ -5068,7 +5069,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>7031</v>
       </c>
@@ -5091,7 +5092,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>6718</v>
       </c>
@@ -5114,7 +5115,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>8584</v>
       </c>
@@ -5137,7 +5138,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>7395</v>
       </c>
@@ -5160,7 +5161,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>7032</v>
       </c>
@@ -5183,7 +5184,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>8585</v>
       </c>
@@ -5206,7 +5207,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2139</v>
       </c>
@@ -5229,7 +5230,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2116</v>
       </c>
@@ -5252,7 +5253,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2149</v>
       </c>
@@ -5275,7 +5276,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2102</v>
       </c>
@@ -5298,7 +5299,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>8586</v>
       </c>
@@ -5321,7 +5322,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>8588</v>
       </c>
@@ -5344,7 +5345,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>8587</v>
       </c>
@@ -5367,7 +5368,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>2164</v>
       </c>
@@ -5390,7 +5391,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>2151</v>
       </c>
@@ -5413,7 +5414,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>2154</v>
       </c>
@@ -5436,7 +5437,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>10287</v>
       </c>
@@ -5459,7 +5460,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>2158</v>
       </c>
@@ -5482,7 +5483,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>6374</v>
       </c>
@@ -5505,7 +5506,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="e">
         <v>#N/A</v>
       </c>
@@ -5528,7 +5529,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>13065</v>
       </c>
@@ -5551,7 +5552,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="e">
         <v>#N/A</v>
       </c>
@@ -5574,7 +5575,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>2216</v>
       </c>
@@ -5597,7 +5598,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>2266</v>
       </c>
@@ -5620,7 +5621,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>2247</v>
       </c>
@@ -5643,7 +5644,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="e">
         <v>#N/A</v>
       </c>
@@ -5666,7 +5667,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>2168</v>
       </c>
@@ -5689,7 +5690,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2169</v>
       </c>
@@ -5712,7 +5713,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="e">
         <v>#N/A</v>
       </c>
@@ -5735,7 +5736,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2276</v>
       </c>
@@ -5758,7 +5759,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2226</v>
       </c>
@@ -5781,7 +5782,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>2269</v>
       </c>
@@ -5804,7 +5805,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>2256</v>
       </c>
@@ -5827,7 +5828,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="e">
         <v>#N/A</v>
       </c>
@@ -5850,7 +5851,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>2177</v>
       </c>
@@ -5873,7 +5874,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>2178</v>
       </c>
@@ -5896,7 +5897,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="e">
         <v>#N/A</v>
       </c>
@@ -5919,7 +5920,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2284</v>
       </c>
@@ -5942,7 +5943,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>4513</v>
       </c>
@@ -5965,7 +5966,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>4464</v>
       </c>
@@ -5988,7 +5989,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>4516</v>
       </c>
@@ -6011,7 +6012,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>4519</v>
       </c>
@@ -6034,7 +6035,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>4522</v>
       </c>
@@ -6057,7 +6058,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>4479</v>
       </c>
@@ -6080,7 +6081,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>4484</v>
       </c>
@@ -6103,7 +6104,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>4467</v>
       </c>
@@ -6126,7 +6127,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>4472</v>
       </c>
@@ -6149,7 +6150,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>4458</v>
       </c>
@@ -6172,7 +6173,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>4511</v>
       </c>
@@ -6195,7 +6196,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>4462</v>
       </c>
@@ -6218,7 +6219,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>4514</v>
       </c>
@@ -6241,7 +6242,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>4517</v>
       </c>
@@ -6264,7 +6265,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>4520</v>
       </c>
@@ -6287,7 +6288,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>4477</v>
       </c>
@@ -6310,7 +6311,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>4482</v>
       </c>
@@ -6333,7 +6334,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>4465</v>
       </c>
@@ -6356,7 +6357,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>4470</v>
       </c>
@@ -6379,7 +6380,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>4456</v>
       </c>
@@ -6402,7 +6403,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>4521</v>
       </c>
@@ -6425,7 +6426,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>4478</v>
       </c>
@@ -6448,7 +6449,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>4483</v>
       </c>
@@ -6471,7 +6472,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>4466</v>
       </c>
@@ -6494,7 +6495,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>4471</v>
       </c>
@@ -6517,7 +6518,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>4457</v>
       </c>
@@ -6540,7 +6541,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>4452</v>
       </c>
@@ -6563,7 +6564,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>4445</v>
       </c>
@@ -6586,7 +6587,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>4439</v>
       </c>
@@ -6609,7 +6610,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>4506</v>
       </c>
@@ -6632,7 +6633,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>4499</v>
       </c>
@@ -6655,7 +6656,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>4480</v>
       </c>
@@ -6678,7 +6679,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>4485</v>
       </c>
@@ -6701,7 +6702,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>4468</v>
       </c>
@@ -6724,7 +6725,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>4473</v>
       </c>
@@ -6747,7 +6748,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>4459</v>
       </c>
@@ -6770,7 +6771,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>4453</v>
       </c>
@@ -6793,7 +6794,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>4448</v>
       </c>
@@ -6816,7 +6817,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>4441</v>
       </c>
@@ -6839,7 +6840,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>4508</v>
       </c>
@@ -6862,7 +6863,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>4501</v>
       </c>
@@ -6885,7 +6886,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>4443</v>
       </c>
@@ -6908,7 +6909,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>4437</v>
       </c>
@@ -6931,7 +6932,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>4505</v>
       </c>
@@ -6954,7 +6955,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>4498</v>
       </c>
@@ -6977,7 +6978,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>647</v>
       </c>
@@ -7000,7 +7001,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>690</v>
       </c>
@@ -7023,7 +7024,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>644</v>
       </c>
@@ -7046,7 +7047,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>641</v>
       </c>
@@ -7069,7 +7070,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>638</v>
       </c>
@@ -7092,7 +7093,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>677</v>
       </c>
@@ -7115,7 +7116,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>673</v>
       </c>
@@ -7138,7 +7139,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>687</v>
       </c>
@@ -7161,7 +7162,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>684</v>
       </c>
@@ -7184,7 +7185,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>696</v>
       </c>
@@ -7207,7 +7208,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>649</v>
       </c>
@@ -7230,7 +7231,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>692</v>
       </c>
@@ -7253,7 +7254,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>646</v>
       </c>
@@ -7276,7 +7277,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>643</v>
       </c>
@@ -7299,7 +7300,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>640</v>
       </c>
@@ -7322,7 +7323,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>679</v>
       </c>
@@ -7345,7 +7346,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>4414</v>
       </c>
@@ -7368,7 +7369,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>689</v>
       </c>
@@ -7391,7 +7392,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>686</v>
       </c>
@@ -7414,7 +7415,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>698</v>
       </c>
@@ -7437,7 +7438,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>639</v>
       </c>
@@ -7460,7 +7461,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>678</v>
       </c>
@@ -7483,7 +7484,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>674</v>
       </c>
@@ -7506,7 +7507,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>688</v>
       </c>
@@ -7529,7 +7530,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>685</v>
       </c>
@@ -7552,7 +7553,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>697</v>
       </c>
@@ -7575,7 +7576,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>701</v>
       </c>
@@ -7598,7 +7599,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>708</v>
       </c>
@@ -7621,7 +7622,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>713</v>
       </c>
@@ -7644,7 +7645,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>654</v>
       </c>
@@ -7667,7 +7668,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>659</v>
       </c>
@@ -7690,7 +7691,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>675</v>
       </c>
@@ -7713,7 +7714,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>671</v>
       </c>
@@ -7736,7 +7737,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>6729</v>
       </c>
@@ -7759,7 +7760,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>682</v>
       </c>
@@ -7782,7 +7783,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>694</v>
       </c>
@@ -7805,7 +7806,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>699</v>
       </c>
@@ -7828,7 +7829,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>704</v>
       </c>
@@ -7851,7 +7852,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>710</v>
       </c>
@@ -7874,7 +7875,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>651</v>
       </c>
@@ -7897,7 +7898,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>656</v>
       </c>
@@ -7920,7 +7921,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>4416</v>
       </c>
@@ -7943,7 +7944,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>715</v>
       </c>
@@ -7966,7 +7967,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>655</v>
       </c>
@@ -7989,7 +7990,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>660</v>
       </c>
@@ -8012,7 +8013,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>10391</v>
       </c>
@@ -8035,7 +8036,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>6293</v>
       </c>
@@ -8058,7 +8059,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>720</v>
       </c>
@@ -8081,7 +8082,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="e">
         <v>#N/A</v>
       </c>
@@ -8104,7 +8105,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>716</v>
       </c>
@@ -8127,7 +8128,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>4655</v>
       </c>
@@ -8150,7 +8151,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>12463</v>
       </c>
@@ -8173,7 +8174,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>7582</v>
       </c>
@@ -8196,7 +8197,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="e">
         <v>#N/A</v>
       </c>
@@ -8219,7 +8220,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="e">
         <v>#N/A</v>
       </c>
@@ -8242,7 +8243,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>4418</v>
       </c>
@@ -8265,7 +8266,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>735</v>
       </c>
@@ -8288,7 +8289,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>721</v>
       </c>
@@ -8311,7 +8312,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>719</v>
       </c>
@@ -8334,7 +8335,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>718</v>
       </c>
@@ -8357,7 +8358,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>4431</v>
       </c>
@@ -8380,7 +8381,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>730</v>
       </c>
@@ -8403,7 +8404,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>10207</v>
       </c>
@@ -8426,7 +8427,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>6837</v>
       </c>
@@ -8449,7 +8450,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>737</v>
       </c>
@@ -8472,7 +8473,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>717</v>
       </c>
@@ -8495,7 +8496,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>731</v>
       </c>
@@ -8518,7 +8519,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>729</v>
       </c>
@@ -8541,7 +8542,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>734</v>
       </c>
@@ -8564,7 +8565,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="e">
         <v>#N/A</v>
       </c>
@@ -8587,7 +8588,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>736</v>
       </c>
@@ -8610,7 +8611,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>4417</v>
       </c>
@@ -8633,7 +8634,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>740</v>
       </c>
@@ -8656,7 +8657,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>4656</v>
       </c>
@@ -8679,7 +8680,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>6653</v>
       </c>
@@ -8702,7 +8703,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>726</v>
       </c>
@@ -8725,7 +8726,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>12336</v>
       </c>
@@ -8748,7 +8749,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="e">
         <v>#N/A</v>
       </c>
@@ -8771,7 +8772,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>732</v>
       </c>
@@ -8794,7 +8795,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="e">
         <v>#N/A</v>
       </c>
@@ -8817,7 +8818,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>5446</v>
       </c>
@@ -8840,7 +8841,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>9998</v>
       </c>
@@ -8863,7 +8864,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>738</v>
       </c>
@@ -8886,7 +8887,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>741</v>
       </c>
@@ -8909,7 +8910,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>722</v>
       </c>
@@ -8932,7 +8933,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>725</v>
       </c>
@@ -8955,7 +8956,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>4419</v>
       </c>
@@ -8978,7 +8979,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>743</v>
       </c>
@@ -9001,7 +9002,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>724</v>
       </c>
@@ -9024,7 +9025,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="e">
         <v>#N/A</v>
       </c>
@@ -9047,7 +9048,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>831</v>
       </c>
@@ -9070,7 +9071,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>874</v>
       </c>
@@ -9093,7 +9094,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>828</v>
       </c>
@@ -9116,7 +9117,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>825</v>
       </c>
@@ -9139,7 +9140,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>822</v>
       </c>
@@ -9162,7 +9163,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>861</v>
       </c>
@@ -9185,7 +9186,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>857</v>
       </c>
@@ -9208,7 +9209,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>871</v>
       </c>
@@ -9231,7 +9232,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>868</v>
       </c>
@@ -9254,7 +9255,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>880</v>
       </c>
@@ -9277,7 +9278,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>833</v>
       </c>
@@ -9300,7 +9301,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>876</v>
       </c>
@@ -9323,7 +9324,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>830</v>
       </c>
@@ -9346,7 +9347,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>827</v>
       </c>
@@ -9369,7 +9370,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>824</v>
       </c>
@@ -9392,7 +9393,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>863</v>
       </c>
@@ -9415,7 +9416,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>859</v>
       </c>
@@ -9438,7 +9439,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>873</v>
       </c>
@@ -9461,7 +9462,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>870</v>
       </c>
@@ -9484,7 +9485,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>882</v>
       </c>
@@ -9507,7 +9508,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>823</v>
       </c>
@@ -9530,7 +9531,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>862</v>
       </c>
@@ -9553,7 +9554,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>858</v>
       </c>
@@ -9576,7 +9577,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>872</v>
       </c>
@@ -9599,7 +9600,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>869</v>
       </c>
@@ -9622,7 +9623,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>881</v>
       </c>
@@ -9645,7 +9646,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>885</v>
       </c>
@@ -9668,7 +9669,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>892</v>
       </c>
@@ -9691,7 +9692,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>897</v>
       </c>
@@ -9714,7 +9715,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>838</v>
       </c>
@@ -9737,7 +9738,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>843</v>
       </c>
@@ -9760,7 +9761,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>3498</v>
       </c>
@@ -9783,7 +9784,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>3494</v>
       </c>
@@ -9806,7 +9807,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="e">
         <v>#N/A</v>
       </c>
@@ -9829,7 +9830,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>3500</v>
       </c>
@@ -9852,7 +9853,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>3503</v>
       </c>
@@ -9875,7 +9876,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>3506</v>
       </c>
@@ -9898,7 +9899,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>3510</v>
       </c>
@@ -9921,7 +9922,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>3512</v>
       </c>
@@ -9944,7 +9945,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>3487</v>
       </c>
@@ -9967,7 +9968,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>3488</v>
       </c>
@@ -9990,7 +9991,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>894</v>
       </c>
@@ -10013,7 +10014,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>899</v>
       </c>
@@ -10036,7 +10037,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>839</v>
       </c>
@@ -10059,7 +10060,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>844</v>
       </c>
@@ -10082,7 +10083,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>10392</v>
       </c>
@@ -10105,7 +10106,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>6294</v>
       </c>
@@ -10128,7 +10129,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>904</v>
       </c>
@@ -10151,7 +10152,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="e">
         <v>#N/A</v>
       </c>
@@ -10174,7 +10175,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>900</v>
       </c>
@@ -10197,7 +10198,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>4945</v>
       </c>
@@ -10220,7 +10221,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>12464</v>
       </c>
@@ -10243,7 +10244,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>7583</v>
       </c>
@@ -10266,7 +10267,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="e">
         <v>#N/A</v>
       </c>
@@ -10289,7 +10290,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="e">
         <v>#N/A</v>
       </c>
@@ -10312,7 +10313,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>906</v>
       </c>
@@ -10335,7 +10336,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>919</v>
       </c>
@@ -10358,7 +10359,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>905</v>
       </c>
@@ -10381,7 +10382,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>903</v>
       </c>
@@ -10404,7 +10405,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>902</v>
       </c>
@@ -10427,7 +10428,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>916</v>
       </c>
@@ -10450,7 +10451,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>914</v>
       </c>
@@ -10473,7 +10474,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>10206</v>
       </c>
@@ -10496,7 +10497,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>6836</v>
       </c>
@@ -10519,7 +10520,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>921</v>
       </c>
@@ -10542,7 +10543,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>901</v>
       </c>
@@ -10565,7 +10566,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>915</v>
       </c>
@@ -10588,7 +10589,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>913</v>
       </c>
@@ -10611,7 +10612,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>918</v>
       </c>
@@ -10634,7 +10635,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="e">
         <v>#N/A</v>
       </c>
@@ -10657,7 +10658,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>920</v>
       </c>
@@ -10680,7 +10681,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>922</v>
       </c>
@@ -10703,7 +10704,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>924</v>
       </c>
@@ -10726,7 +10727,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>5753</v>
       </c>
@@ -10749,7 +10750,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>7014</v>
       </c>
@@ -10772,7 +10773,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>910</v>
       </c>
@@ -10795,7 +10796,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>12335</v>
       </c>
@@ -10818,7 +10819,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>8987</v>
       </c>
@@ -10841,7 +10842,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>3525</v>
       </c>
@@ -10864,7 +10865,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="e">
         <v>#N/A</v>
       </c>
@@ -10887,7 +10888,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>8986</v>
       </c>
@@ -10910,7 +10911,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>9999</v>
       </c>
@@ -10933,7 +10934,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>3527</v>
       </c>
@@ -10956,7 +10957,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>3530</v>
       </c>
@@ -10979,7 +10980,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>3518</v>
       </c>
@@ -11002,7 +11003,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>3521</v>
       </c>
@@ -11025,7 +11026,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>925</v>
       </c>
@@ -11048,7 +11049,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>927</v>
       </c>
@@ -11071,7 +11072,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>908</v>
       </c>
@@ -11094,7 +11095,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="e">
         <v>#N/A</v>
       </c>
@@ -11117,7 +11118,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>755</v>
       </c>
@@ -11140,7 +11141,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>771</v>
       </c>
@@ -11163,7 +11164,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>751</v>
       </c>
@@ -11186,7 +11187,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>748</v>
       </c>
@@ -11209,7 +11210,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>744</v>
       </c>
@@ -11232,7 +11233,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>763</v>
       </c>
@@ -11255,7 +11256,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="e">
         <v>#N/A</v>
       </c>
@@ -11278,7 +11279,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>768</v>
       </c>
@@ -11301,7 +11302,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="e">
         <v>#N/A</v>
       </c>
@@ -11324,7 +11325,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="e">
         <v>#N/A</v>
       </c>
@@ -11347,7 +11348,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>756</v>
       </c>
@@ -11370,7 +11371,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>773</v>
       </c>
@@ -11393,7 +11394,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>753</v>
       </c>
@@ -11416,7 +11417,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>750</v>
       </c>
@@ -11439,7 +11440,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>746</v>
       </c>
@@ -11462,7 +11463,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>765</v>
       </c>
@@ -11485,7 +11486,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>762</v>
       </c>
@@ -11508,7 +11509,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>770</v>
       </c>
@@ -11531,7 +11532,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>12267</v>
       </c>
@@ -11554,7 +11555,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>4430</v>
       </c>
@@ -11577,7 +11578,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>745</v>
       </c>
@@ -11600,7 +11601,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>764</v>
       </c>
@@ -11623,7 +11624,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>761</v>
       </c>
@@ -11646,7 +11647,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>769</v>
       </c>
@@ -11669,7 +11670,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>767</v>
       </c>
@@ -11692,7 +11693,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>776</v>
       </c>
@@ -11715,7 +11716,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>4429</v>
       </c>
@@ -11738,7 +11739,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>781</v>
       </c>
@@ -11761,7 +11762,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>784</v>
       </c>
@@ -11784,7 +11785,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>8638</v>
       </c>
@@ -11807,7 +11808,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="e">
         <v>#N/A</v>
       </c>
@@ -11830,7 +11831,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="e">
         <v>#N/A</v>
       </c>
@@ -11853,7 +11854,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="e">
         <v>#N/A</v>
       </c>
@@ -11876,7 +11877,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>6730</v>
       </c>
@@ -11899,7 +11900,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="e">
         <v>#N/A</v>
       </c>
@@ -11922,7 +11923,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>774</v>
       </c>
@@ -11945,7 +11946,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>777</v>
       </c>
@@ -11968,7 +11969,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>779</v>
       </c>
@@ -11991,7 +11992,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>782</v>
       </c>
@@ -12014,7 +12015,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>12355</v>
       </c>
@@ -12037,7 +12038,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="e">
         <v>#N/A</v>
       </c>
@@ -12060,7 +12061,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>4421</v>
       </c>
@@ -12083,7 +12084,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>786</v>
       </c>
@@ -12106,7 +12107,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="e">
         <v>#N/A</v>
       </c>
@@ -12129,7 +12130,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>4420</v>
       </c>
@@ -12152,7 +12153,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>939</v>
       </c>
@@ -12175,7 +12176,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>955</v>
       </c>
@@ -12198,7 +12199,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>935</v>
       </c>
@@ -12221,7 +12222,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>932</v>
       </c>
@@ -12244,7 +12245,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>928</v>
       </c>
@@ -12267,7 +12268,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>947</v>
       </c>
@@ -12290,7 +12291,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="e">
         <v>#N/A</v>
       </c>
@@ -12313,7 +12314,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>952</v>
       </c>
@@ -12336,7 +12337,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="e">
         <v>#N/A</v>
       </c>
@@ -12359,7 +12360,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="e">
         <v>#N/A</v>
       </c>
@@ -12382,7 +12383,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>940</v>
       </c>
@@ -12405,7 +12406,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>957</v>
       </c>
@@ -12428,7 +12429,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>937</v>
       </c>
@@ -12451,7 +12452,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>934</v>
       </c>
@@ -12474,7 +12475,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>3555</v>
       </c>
@@ -12497,7 +12498,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>949</v>
       </c>
@@ -12520,7 +12521,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>946</v>
       </c>
@@ -12543,7 +12544,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>954</v>
       </c>
@@ -12566,7 +12567,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>12268</v>
       </c>
@@ -12589,7 +12590,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>961</v>
       </c>
@@ -12612,7 +12613,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>929</v>
       </c>
@@ -12635,7 +12636,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>948</v>
       </c>
@@ -12658,7 +12659,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>945</v>
       </c>
@@ -12681,7 +12682,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>953</v>
       </c>
@@ -12704,7 +12705,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>951</v>
       </c>
@@ -12727,7 +12728,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>960</v>
       </c>
@@ -12750,7 +12751,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>963</v>
       </c>
@@ -12773,7 +12774,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>965</v>
       </c>
@@ -12796,7 +12797,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>968</v>
       </c>
@@ -12819,7 +12820,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>8637</v>
       </c>
@@ -12842,7 +12843,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="e">
         <v>#N/A</v>
       </c>
@@ -12865,7 +12866,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" t="e">
         <v>#N/A</v>
       </c>
@@ -12888,7 +12889,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="e">
         <v>#N/A</v>
       </c>
@@ -12911,7 +12912,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" t="e">
         <v>#N/A</v>
       </c>
@@ -12934,7 +12935,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="e">
         <v>#N/A</v>
       </c>
@@ -12957,7 +12958,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>3543</v>
       </c>
@@ -12980,7 +12981,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>3546</v>
       </c>
@@ -13003,7 +13004,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>3548</v>
       </c>
@@ -13026,7 +13027,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>3551</v>
       </c>
@@ -13049,7 +13050,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>12356</v>
       </c>
@@ -13072,7 +13073,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" t="e">
         <v>#N/A</v>
       </c>
@@ -13095,7 +13096,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>966</v>
       </c>
@@ -13118,7 +13119,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>970</v>
       </c>
@@ -13141,7 +13142,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" t="e">
         <v>#N/A</v>
       </c>
@@ -13164,7 +13165,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>943</v>
       </c>
@@ -13187,7 +13188,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>4546</v>
       </c>
@@ -13210,7 +13211,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>4549</v>
       </c>
@@ -13230,7 +13231,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>4565</v>
       </c>
@@ -13253,7 +13254,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>4568</v>
       </c>
@@ -13273,7 +13274,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>4552</v>
       </c>
@@ -13296,7 +13297,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>4557</v>
       </c>
@@ -13316,7 +13317,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>4578</v>
       </c>
@@ -13336,7 +13337,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>4580</v>
       </c>
@@ -13356,7 +13357,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>4539</v>
       </c>
@@ -13376,7 +13377,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>4541</v>
       </c>
@@ -13396,7 +13397,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>996</v>
       </c>
@@ -13419,7 +13420,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>999</v>
       </c>
@@ -13439,7 +13440,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>1015</v>
       </c>
@@ -13462,7 +13463,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>1018</v>
       </c>
@@ -13482,7 +13483,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>1002</v>
       </c>
@@ -13505,7 +13506,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>1007</v>
       </c>
@@ -13525,7 +13526,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>1028</v>
       </c>
@@ -13545,7 +13546,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>1030</v>
       </c>
@@ -13565,7 +13566,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>989</v>
       </c>
@@ -13585,7 +13586,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>991</v>
       </c>
@@ -13605,7 +13606,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" t="e">
         <v>#N/A</v>
       </c>
@@ -13628,7 +13629,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>7652</v>
       </c>
@@ -13648,7 +13649,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" t="e">
         <v>#N/A</v>
       </c>
@@ -13671,7 +13672,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" t="e">
         <v>#N/A</v>
       </c>
@@ -13691,7 +13692,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>1034</v>
       </c>
@@ -13714,7 +13715,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" t="e">
         <v>#N/A</v>
       </c>
@@ -13734,7 +13735,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" t="e">
         <v>#N/A</v>
       </c>
@@ -13754,7 +13755,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" t="e">
         <v>#N/A</v>
       </c>
@@ -13774,7 +13775,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>1033</v>
       </c>
@@ -13794,7 +13795,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" t="e">
         <v>#N/A</v>
       </c>
@@ -13814,7 +13815,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>557</v>
       </c>
@@ -13834,7 +13835,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>560</v>
       </c>
@@ -13854,7 +13855,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>559</v>
       </c>
@@ -13874,7 +13875,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>555</v>
       </c>
@@ -13894,7 +13895,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>556</v>
       </c>
@@ -13914,7 +13915,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>562</v>
       </c>
@@ -13934,7 +13935,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>558</v>
       </c>
@@ -13954,7 +13955,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>563</v>
       </c>
@@ -13974,7 +13975,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>5025</v>
       </c>
@@ -13994,7 +13995,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>224</v>
       </c>
@@ -14014,7 +14015,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>4621</v>
       </c>
@@ -14034,7 +14035,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>226</v>
       </c>
@@ -14054,7 +14055,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>223</v>
       </c>
@@ -14074,7 +14075,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>227</v>
       </c>
@@ -14094,7 +14095,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>225</v>
       </c>
@@ -14114,7 +14115,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>228</v>
       </c>
@@ -14134,7 +14135,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>222</v>
       </c>
@@ -14154,7 +14155,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>582</v>
       </c>
@@ -14174,7 +14175,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>583</v>
       </c>
@@ -14194,7 +14195,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>590</v>
       </c>
@@ -14214,7 +14215,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>591</v>
       </c>
@@ -14234,7 +14235,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>587</v>
       </c>
@@ -14254,7 +14255,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>588</v>
       </c>
@@ -14274,7 +14275,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>579</v>
       </c>
@@ -14294,7 +14295,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>580</v>
       </c>
@@ -14314,7 +14315,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>592</v>
       </c>
@@ -14334,7 +14335,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>584</v>
       </c>
@@ -14354,7 +14355,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>546</v>
       </c>
@@ -14377,7 +14378,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>545</v>
       </c>
@@ -14400,7 +14401,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>549</v>
       </c>
@@ -14423,7 +14424,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>548</v>
       </c>
@@ -14446,7 +14447,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>551</v>
       </c>
@@ -14469,7 +14470,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>543</v>
       </c>
@@ -14492,7 +14493,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>544</v>
       </c>
@@ -14515,7 +14516,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>553</v>
       </c>
@@ -14538,7 +14539,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>550</v>
       </c>
@@ -14561,7 +14562,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>547</v>
       </c>
@@ -14584,7 +14585,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>552</v>
       </c>
@@ -14607,7 +14608,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>542</v>
       </c>
@@ -14630,7 +14631,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>541</v>
       </c>
@@ -14650,7 +14651,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>540</v>
       </c>
@@ -14670,7 +14671,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>539</v>
       </c>
@@ -14690,7 +14691,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>180</v>
       </c>
@@ -14698,10 +14699,10 @@
         <v>557</v>
       </c>
       <c r="C549" s="2">
-        <v>2.94</v>
+        <v>2.38</v>
       </c>
       <c r="D549" s="2">
-        <v>2.6459999999999999</v>
+        <v>2.09</v>
       </c>
       <c r="E549">
         <v>10</v>
@@ -14713,7 +14714,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>179</v>
       </c>
@@ -14721,10 +14722,10 @@
         <v>559</v>
       </c>
       <c r="C550" s="2">
-        <v>4.13</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="D550" s="2">
-        <v>3.7170000000000001</v>
+        <v>2.21</v>
       </c>
       <c r="E550">
         <v>10</v>
@@ -14736,7 +14737,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>183</v>
       </c>
@@ -14744,10 +14745,10 @@
         <v>560</v>
       </c>
       <c r="C551" s="2">
-        <v>4.96</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="D551" s="2">
-        <v>4.4640000000000004</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="E551">
         <v>10</v>
@@ -14759,7 +14760,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>182</v>
       </c>
@@ -14767,10 +14768,10 @@
         <v>561</v>
       </c>
       <c r="C552" s="2">
-        <v>5.28</v>
+        <v>6.24</v>
       </c>
       <c r="D552" s="2">
-        <v>4.7520000000000007</v>
+        <v>5.46</v>
       </c>
       <c r="E552">
         <v>5</v>
@@ -14782,7 +14783,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>185</v>
       </c>
@@ -14790,10 +14791,10 @@
         <v>562</v>
       </c>
       <c r="C553" s="2">
-        <v>16</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="D553" s="2">
-        <v>14.4</v>
+        <v>8.68</v>
       </c>
       <c r="E553">
         <v>5</v>
@@ -14805,7 +14806,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>178</v>
       </c>
@@ -14813,10 +14814,10 @@
         <v>563</v>
       </c>
       <c r="C554" s="2">
-        <v>20</v>
+        <v>14.24</v>
       </c>
       <c r="D554" s="2">
-        <v>18</v>
+        <v>12.46</v>
       </c>
       <c r="E554">
         <v>2.5</v>
@@ -14828,7 +14829,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>7391</v>
       </c>
@@ -14836,10 +14837,10 @@
         <v>564</v>
       </c>
       <c r="C555" s="2">
-        <v>23.36</v>
+        <v>19.36</v>
       </c>
       <c r="D555" s="2">
-        <v>21.024000000000001</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="E555">
         <v>2</v>
@@ -14851,7 +14852,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>184</v>
       </c>
@@ -14859,10 +14860,10 @@
         <v>565</v>
       </c>
       <c r="C556" s="2">
-        <v>35.92</v>
+        <v>21.6</v>
       </c>
       <c r="D556" s="2">
-        <v>32.328000000000003</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="E556">
         <v>1</v>
@@ -14874,7 +14875,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>181</v>
       </c>
@@ -14882,10 +14883,10 @@
         <v>566</v>
       </c>
       <c r="C557" s="2">
-        <v>61.25</v>
+        <v>29.6</v>
       </c>
       <c r="D557" s="2">
-        <v>55.125</v>
+        <v>25.9</v>
       </c>
       <c r="E557">
         <v>1</v>
@@ -14897,7 +14898,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>186</v>
       </c>
@@ -14905,10 +14906,10 @@
         <v>567</v>
       </c>
       <c r="C558" s="2">
-        <v>94.03</v>
+        <v>59.2</v>
       </c>
       <c r="D558" s="2">
-        <v>84.62700000000001</v>
+        <v>51.8</v>
       </c>
       <c r="E558">
         <v>0.5</v>
@@ -14920,7 +14921,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>3581</v>
       </c>
@@ -14928,10 +14929,10 @@
         <v>568</v>
       </c>
       <c r="C559" s="2">
-        <v>123.15</v>
+        <v>69.12</v>
       </c>
       <c r="D559" s="2">
-        <v>110.83499999999999</v>
+        <v>60.48</v>
       </c>
       <c r="E559">
         <v>0.25</v>
@@ -14943,7 +14944,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>7392</v>
       </c>
@@ -14951,10 +14952,10 @@
         <v>569</v>
       </c>
       <c r="C560" s="2">
-        <v>191.15</v>
+        <v>104</v>
       </c>
       <c r="D560" s="2">
-        <v>172.035</v>
+        <v>91</v>
       </c>
       <c r="F560" s="1" t="s">
         <v>558</v>
@@ -14963,7 +14964,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>7393</v>
       </c>
@@ -14971,10 +14972,10 @@
         <v>570</v>
       </c>
       <c r="C561" s="2">
-        <v>305.86</v>
+        <v>166.4</v>
       </c>
       <c r="D561" s="2">
-        <v>275.274</v>
+        <v>145.6</v>
       </c>
       <c r="F561" s="1" t="s">
         <v>558</v>
@@ -14983,7 +14984,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>7394</v>
       </c>
@@ -14991,10 +14992,10 @@
         <v>571</v>
       </c>
       <c r="C562" s="2">
-        <v>841.14</v>
+        <v>403.2</v>
       </c>
       <c r="D562" s="2">
-        <v>757.02599999999995</v>
+        <v>352.8</v>
       </c>
       <c r="F562" s="1" t="s">
         <v>558</v>
@@ -15003,7 +15004,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>214</v>
       </c>
@@ -15026,7 +15027,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>211</v>
       </c>
@@ -15049,7 +15050,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>217</v>
       </c>
@@ -15072,7 +15073,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>216</v>
       </c>
@@ -15095,7 +15096,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>219</v>
       </c>
@@ -15118,7 +15119,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>210</v>
       </c>
@@ -15141,7 +15142,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>221</v>
       </c>
@@ -15164,7 +15165,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>218</v>
       </c>
@@ -15187,7 +15188,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>215</v>
       </c>
@@ -15210,7 +15211,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>220</v>
       </c>
@@ -15233,7 +15234,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>209</v>
       </c>
@@ -15256,7 +15257,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>207</v>
       </c>
@@ -15276,7 +15277,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>206</v>
       </c>
@@ -15296,7 +15297,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>205</v>
       </c>
@@ -15316,7 +15317,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>567</v>
       </c>
@@ -15336,7 +15337,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>566</v>
       </c>
@@ -15356,7 +15357,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>570</v>
       </c>
@@ -15376,7 +15377,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>569</v>
       </c>
@@ -15396,7 +15397,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>565</v>
       </c>
@@ -15416,7 +15417,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>4585</v>
       </c>
@@ -15436,7 +15437,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>12351</v>
       </c>
@@ -15456,7 +15457,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>571</v>
       </c>
@@ -15476,7 +15477,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>568</v>
       </c>
@@ -15496,7 +15497,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>12352</v>
       </c>
@@ -15516,7 +15517,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>6863</v>
       </c>
@@ -15536,7 +15537,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>230</v>
       </c>
@@ -15556,7 +15557,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>232</v>
       </c>
@@ -15576,7 +15577,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>231</v>
       </c>
@@ -15596,7 +15597,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>229</v>
       </c>
@@ -15616,7 +15617,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>3588</v>
       </c>
@@ -15636,7 +15637,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>4982</v>
       </c>
